--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -835,7 +835,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="24"/>
   </cellStyleXfs>
-  <cellXfs count="312">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1650,6 +1650,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="12" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2785,9 +2803,7 @@
         <f>IF(G13=0,"-",H13/G13)</f>
         <v/>
       </c>
-      <c r="K13" s="304" t="n">
-        <v>90048</v>
-      </c>
+      <c r="K13" s="304" t="n"/>
       <c r="L13" s="306" t="inlineStr">
         <is>
           <t>120k Order, 89k Advance Production</t>
@@ -2973,22 +2989,23 @@
       </c>
       <c r="C16" s="300" t="inlineStr">
         <is>
-          <t>Habib Hanif Inc</t>
+          <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
       <c r="D16" s="301" t="inlineStr">
         <is>
-          <t>S-45</t>
+          <t>HELLO HAIR COLOR</t>
         </is>
       </c>
       <c r="E16" s="302" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F16" s="303" t="n">
-        <v>5389</v>
-      </c>
-      <c r="G16" s="303" t="n">
-        <v>0</v>
+        <v>6206</v>
+      </c>
+      <c r="G16" s="303">
+        <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F16,MRP!$D$3:$D$9,0)),0)</f>
+        <v/>
       </c>
       <c r="H16" s="304">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F16)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
@@ -3002,10 +3019,12 @@
         <f>IF(G16=0,"-",H16/G16)</f>
         <v/>
       </c>
-      <c r="K16" s="304" t="n">
-        <v>44352</v>
-      </c>
-      <c r="L16" s="306" t="n"/>
+      <c r="K16" s="304" t="n"/>
+      <c r="L16" s="306" t="inlineStr">
+        <is>
+          <t>Advance Production</t>
+        </is>
+      </c>
       <c r="M16" s="151" t="n"/>
       <c r="N16" s="151" t="n"/>
       <c r="O16" s="151" t="n"/>
@@ -3043,19 +3062,19 @@
       </c>
       <c r="C17" s="300" t="inlineStr">
         <is>
-          <t>Golden Pearl Cosmetics (PVT) LTD</t>
+          <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
       <c r="D17" s="301" t="inlineStr">
         <is>
-          <t>HELLO HAIR COLOR</t>
+          <t>VINCE NURTURAL</t>
         </is>
       </c>
       <c r="E17" s="302" t="n">
         <v>30</v>
       </c>
       <c r="F17" s="303" t="n">
-        <v>6206</v>
+        <v>5814</v>
       </c>
       <c r="G17" s="303">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F17,MRP!$D$3:$D$9,0)),0)</f>
@@ -3074,11 +3093,7 @@
         <v/>
       </c>
       <c r="K17" s="304" t="n"/>
-      <c r="L17" s="306" t="inlineStr">
-        <is>
-          <t>Advance Production</t>
-        </is>
-      </c>
+      <c r="L17" s="306" t="n"/>
       <c r="P17" s="151" t="n"/>
       <c r="Q17" s="151" t="n"/>
       <c r="R17" s="151" t="n"/>
@@ -3103,19 +3118,19 @@
       </c>
       <c r="C18" s="300" t="inlineStr">
         <is>
-          <t>Mablay Beauty PVT LTD.</t>
+          <t>Adore</t>
         </is>
       </c>
       <c r="D18" s="301" t="inlineStr">
         <is>
-          <t>VINCE NURTURAL</t>
+          <t>V- HC BROWN</t>
         </is>
       </c>
       <c r="E18" s="302" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F18" s="303" t="n">
-        <v>5814</v>
+        <v>6530</v>
       </c>
       <c r="G18" s="303">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F18,MRP!$D$3:$D$9,0)),0)</f>
@@ -3134,7 +3149,11 @@
         <v/>
       </c>
       <c r="K18" s="304" t="n"/>
-      <c r="L18" s="306" t="n"/>
+      <c r="L18" s="306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hold </t>
+        </is>
+      </c>
       <c r="P18" s="151" t="n"/>
       <c r="Q18" s="151" t="n"/>
       <c r="R18" s="151" t="n"/>
@@ -3162,49 +3181,33 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" s="254">
       <c r="A19" s="151" t="n"/>
-      <c r="B19" s="299" t="inlineStr">
-        <is>
-          <t>TUBE</t>
-        </is>
-      </c>
-      <c r="C19" s="300" t="inlineStr">
-        <is>
-          <t>Adore</t>
-        </is>
-      </c>
-      <c r="D19" s="301" t="inlineStr">
-        <is>
-          <t>V- HC BROWN</t>
-        </is>
-      </c>
-      <c r="E19" s="302" t="n">
-        <v>35</v>
-      </c>
-      <c r="F19" s="303" t="n">
-        <v>6530</v>
-      </c>
-      <c r="G19" s="303">
-        <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F19,MRP!$D$3:$D$9,0)),0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="304">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F19)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v/>
-      </c>
-      <c r="I19" s="303">
-        <f>G19-H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="305">
-        <f>IF(G19=0,"-",H19/G19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="304" t="n"/>
-      <c r="L19" s="306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hold </t>
-        </is>
-      </c>
+      <c r="B19" s="307" t="n"/>
+      <c r="C19" s="308" t="n"/>
+      <c r="D19" s="309" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E19" s="307" t="n"/>
+      <c r="F19" s="308" t="n"/>
+      <c r="G19" s="310">
+        <f>SUM(G11:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="310">
+        <f>SUM(H11:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="310">
+        <f>SUMIF(I11:I18,"&gt;"&amp;0)</f>
+        <v/>
+      </c>
+      <c r="J19" s="310" t="n"/>
+      <c r="K19" s="310">
+        <f>SUM(K11:K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="310" t="n"/>
       <c r="M19" s="151" t="n"/>
       <c r="N19" s="151" t="n"/>
       <c r="O19" s="151" t="n"/>
@@ -3235,33 +3238,46 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" s="254">
       <c r="A20" s="151" t="n"/>
-      <c r="B20" s="307" t="n"/>
-      <c r="C20" s="308" t="n"/>
-      <c r="D20" s="309" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E20" s="307" t="n"/>
-      <c r="F20" s="308" t="n"/>
-      <c r="G20" s="310">
-        <f>SUM(G11:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="310">
-        <f>SUM(H11:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="310">
-        <f>SUMIF(I11:I19,"&gt;"&amp;0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="310" t="n"/>
-      <c r="K20" s="310">
-        <f>SUM(K11:K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="310" t="n"/>
+      <c r="B20" s="299" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="C20" s="300" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D20" s="301" t="inlineStr">
+        <is>
+          <t>PET BOTTLE SMALL (120ML) YELLOW</t>
+        </is>
+      </c>
+      <c r="E20" s="302" t="inlineStr">
+        <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="F20" s="303" t="n">
+        <v>8005</v>
+      </c>
+      <c r="G20" s="303" t="n">
+        <v>19840</v>
+      </c>
+      <c r="H20" s="304">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F20)*Production_Log!$H$3:$H$8963)</f>
+        <v/>
+      </c>
+      <c r="I20" s="303">
+        <f>G20-H20</f>
+        <v/>
+      </c>
+      <c r="J20" s="305">
+        <f>IF(G20=0,"-",H20/G20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="304" t="n"/>
+      <c r="L20" s="306" t="n"/>
       <c r="M20" s="151" t="n"/>
       <c r="N20" s="151" t="n"/>
       <c r="O20" s="151" t="n"/>
@@ -3287,24 +3303,24 @@
       </c>
       <c r="C21" s="300" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
       <c r="D21" s="301" t="inlineStr">
         <is>
-          <t>PET BOTTLE SMALL (120ML) YELLOW</t>
+          <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
       <c r="E21" s="302" t="inlineStr">
         <is>
-          <t>120 ml</t>
+          <t>150 ml</t>
         </is>
       </c>
       <c r="F21" s="303" t="n">
-        <v>8005</v>
+        <v>8001</v>
       </c>
       <c r="G21" s="303" t="n">
-        <v>19840</v>
+        <v>249997</v>
       </c>
       <c r="H21" s="304">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F21)*Production_Log!$H$3:$H$8963)</f>
@@ -3345,24 +3361,24 @@
       </c>
       <c r="C22" s="300" t="inlineStr">
         <is>
-          <t>Alpha Labs PVT LTD</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D22" s="301" t="inlineStr">
         <is>
-          <t>TRANSPARENT BOTTLE 150ML</t>
+          <t>PET BOTTLE LARGE 200ML WHITE</t>
         </is>
       </c>
       <c r="E22" s="302" t="inlineStr">
         <is>
-          <t>150 ml</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="F22" s="303" t="n">
-        <v>8001</v>
+        <v>8007</v>
       </c>
       <c r="G22" s="303" t="n">
-        <v>249997</v>
+        <v>10000</v>
       </c>
       <c r="H22" s="304">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F22)*Production_Log!$H$3:$H$8963)</f>
@@ -3376,9 +3392,7 @@
         <f>IF(G22=0,"-",H22/G22)</f>
         <v/>
       </c>
-      <c r="K22" s="304" t="n">
-        <v>32200</v>
-      </c>
+      <c r="K22" s="304" t="n"/>
       <c r="L22" s="306" t="n"/>
       <c r="M22" s="151" t="n"/>
       <c r="N22" s="151" t="n"/>
@@ -3410,7 +3424,7 @@
       </c>
       <c r="D23" s="301" t="inlineStr">
         <is>
-          <t>PET BOTTLE LARGE 200ML WHITE</t>
+          <t>BT-200 ML YELLOW</t>
         </is>
       </c>
       <c r="E23" s="302" t="inlineStr">
@@ -3419,10 +3433,10 @@
         </is>
       </c>
       <c r="F23" s="303" t="n">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="G23" s="303" t="n">
-        <v>10000</v>
+        <v>42400</v>
       </c>
       <c r="H23" s="304">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F23)*Production_Log!$H$3:$H$8963)</f>
@@ -3468,7 +3482,7 @@
       </c>
       <c r="D24" s="301" t="inlineStr">
         <is>
-          <t>BT-200 ML YELLOW</t>
+          <t>BT-200ML MUSTARD OIL (TRANSPARENT)</t>
         </is>
       </c>
       <c r="E24" s="302" t="inlineStr">
@@ -3477,10 +3491,10 @@
         </is>
       </c>
       <c r="F24" s="303" t="n">
-        <v>8006</v>
+        <v>8014</v>
       </c>
       <c r="G24" s="303" t="n">
-        <v>42400</v>
+        <v>10000</v>
       </c>
       <c r="H24" s="304">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F24)*Production_Log!$H$3:$H$8963)</f>
@@ -3516,46 +3530,33 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="254">
       <c r="A25" s="151" t="n"/>
-      <c r="B25" s="299" t="inlineStr">
-        <is>
-          <t>PET</t>
-        </is>
-      </c>
-      <c r="C25" s="300" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D25" s="301" t="inlineStr">
-        <is>
-          <t>BT-200ML MUSTARD OIL (TRANSPARENT)</t>
-        </is>
-      </c>
-      <c r="E25" s="302" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="F25" s="303" t="n">
-        <v>8014</v>
-      </c>
-      <c r="G25" s="303" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H25" s="304">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F25)*Production_Log!$H$3:$H$8963)</f>
-        <v/>
-      </c>
-      <c r="I25" s="303">
-        <f>G25-H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="305">
-        <f>IF(G25=0,"-",H25/G25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="304" t="n"/>
-      <c r="L25" s="306" t="n"/>
+      <c r="B25" s="307" t="n"/>
+      <c r="C25" s="308" t="n"/>
+      <c r="D25" s="309" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E25" s="307" t="n"/>
+      <c r="F25" s="308" t="n"/>
+      <c r="G25" s="310">
+        <f>SUM(G20:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="310">
+        <f>SUM(H20:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="310">
+        <f>SUMIF(I20:I24,"&gt;"&amp;0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="310" t="n"/>
+      <c r="K25" s="310">
+        <f>SUM(K20:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="310" t="n"/>
       <c r="M25" s="151" t="n"/>
       <c r="N25" s="151" t="n"/>
       <c r="O25" s="151" t="n"/>
@@ -3576,33 +3577,44 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="254">
       <c r="A26" s="151" t="n"/>
-      <c r="B26" s="307" t="n"/>
-      <c r="C26" s="308" t="n"/>
-      <c r="D26" s="309" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E26" s="307" t="n"/>
-      <c r="F26" s="308" t="n"/>
-      <c r="G26" s="310">
-        <f>SUM(G21:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="310">
-        <f>SUM(H21:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="310">
-        <f>SUMIF(I21:I25,"&gt;"&amp;0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="310" t="n"/>
-      <c r="K26" s="310">
-        <f>SUM(K21:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="310" t="n"/>
+      <c r="B26" s="299" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="C26" s="300" t="inlineStr">
+        <is>
+          <t>Bahadur</t>
+        </is>
+      </c>
+      <c r="D26" s="301" t="inlineStr">
+        <is>
+          <t>BAHADUR TUBE 12.5MM</t>
+        </is>
+      </c>
+      <c r="E26" s="302" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F26" s="303" t="n">
+        <v>9004</v>
+      </c>
+      <c r="G26" s="303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="304">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F26)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
+        <v/>
+      </c>
+      <c r="I26" s="303">
+        <f>G26-H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="305">
+        <f>IF(G26=0,"-",H26/G26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="304" t="n"/>
+      <c r="L26" s="306" t="n"/>
       <c r="M26" s="151" t="n"/>
       <c r="N26" s="151" t="n"/>
       <c r="O26" s="151" t="n"/>
@@ -3630,19 +3642,19 @@
       </c>
       <c r="C27" s="300" t="inlineStr">
         <is>
-          <t>Bahadur</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D27" s="301" t="inlineStr">
         <is>
-          <t>BAHADUR TUBE 12.5MM</t>
+          <t>S-45 DIA 19MM</t>
         </is>
       </c>
       <c r="E27" s="302" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="F27" s="303" t="n">
-        <v>9004</v>
+        <v>6624</v>
       </c>
       <c r="G27" s="303" t="n">
         <v>0</v>
@@ -3693,14 +3705,14 @@
       </c>
       <c r="D28" s="301" t="inlineStr">
         <is>
-          <t>S-45 DIA 19MM</t>
+          <t>S-43 DIA 19MM</t>
         </is>
       </c>
       <c r="E28" s="302" t="n">
         <v>19</v>
       </c>
       <c r="F28" s="303" t="n">
-        <v>6624</v>
+        <v>6623</v>
       </c>
       <c r="G28" s="303" t="n">
         <v>0</v>
@@ -3744,19 +3756,19 @@
       </c>
       <c r="C29" s="300" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Brookes Pharma Private Limited</t>
         </is>
       </c>
       <c r="D29" s="301" t="inlineStr">
         <is>
-          <t>S-43 DIA 19MM</t>
+          <t>PHLOGIN GEL 20G</t>
         </is>
       </c>
       <c r="E29" s="302" t="n">
         <v>19</v>
       </c>
       <c r="F29" s="303" t="n">
-        <v>6623</v>
+        <v>6559</v>
       </c>
       <c r="G29" s="303" t="n">
         <v>0</v>
@@ -3805,14 +3817,14 @@
       </c>
       <c r="D30" s="301" t="inlineStr">
         <is>
-          <t>PHLOGIN GEL 20G</t>
+          <t>PYODINE GEL 20GM</t>
         </is>
       </c>
       <c r="E30" s="302" t="n">
         <v>19</v>
       </c>
       <c r="F30" s="303" t="n">
-        <v>6559</v>
+        <v>1085</v>
       </c>
       <c r="G30" s="303" t="n">
         <v>0</v>
@@ -3863,14 +3875,14 @@
       </c>
       <c r="D31" s="301" t="inlineStr">
         <is>
-          <t>PYODINE GEL 20GM</t>
+          <t>CONTRATUBEX GEL 20G</t>
         </is>
       </c>
       <c r="E31" s="302" t="n">
         <v>19</v>
       </c>
       <c r="F31" s="303" t="n">
-        <v>1085</v>
+        <v>6560</v>
       </c>
       <c r="G31" s="303" t="n">
         <v>0</v>
@@ -3916,19 +3928,19 @@
       </c>
       <c r="C32" s="300" t="inlineStr">
         <is>
-          <t>Brookes Pharma Private Limited</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D32" s="301" t="inlineStr">
         <is>
-          <t>CONTRATUBEX GEL 20G</t>
+          <t>S-43 DIA 20.5</t>
         </is>
       </c>
       <c r="E32" s="302" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="F32" s="303" t="n">
-        <v>6560</v>
+        <v>5699</v>
       </c>
       <c r="G32" s="303" t="n">
         <v>0</v>
@@ -3974,19 +3986,19 @@
       </c>
       <c r="C33" s="300" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
       <c r="D33" s="301" t="inlineStr">
         <is>
-          <t>S-43 DIA 20.5</t>
+          <t>VINCE HIS ONLY BEARD &amp; MUSTACHE COLOR CREAM</t>
         </is>
       </c>
       <c r="E33" s="302" t="n">
         <v>20.5</v>
       </c>
       <c r="F33" s="303" t="n">
-        <v>5699</v>
+        <v>6077</v>
       </c>
       <c r="G33" s="303" t="n">
         <v>0</v>
@@ -4030,19 +4042,19 @@
       </c>
       <c r="C34" s="300" t="inlineStr">
         <is>
-          <t>Mablay Beauty PVT LTD.</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D34" s="301" t="inlineStr">
         <is>
-          <t>VINCE HIS ONLY BEARD &amp; MUSTACHE COLOR CREAM</t>
+          <t>S-45 DIA 20.5</t>
         </is>
       </c>
       <c r="E34" s="302" t="n">
         <v>20.5</v>
       </c>
       <c r="F34" s="303" t="n">
-        <v>6077</v>
+        <v>5698</v>
       </c>
       <c r="G34" s="303" t="n">
         <v>0</v>
@@ -4091,14 +4103,14 @@
       </c>
       <c r="D35" s="301" t="inlineStr">
         <is>
-          <t>S-45 DIA 20.5</t>
+          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
       <c r="E35" s="302" t="n">
         <v>20.5</v>
       </c>
       <c r="F35" s="303" t="n">
-        <v>5698</v>
+        <v>5731</v>
       </c>
       <c r="G35" s="303" t="n">
         <v>0</v>
@@ -4147,14 +4159,14 @@
       </c>
       <c r="D36" s="301" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
+          <t>SAMSOL HAIR COLOR 43 DIA 20.5 MM</t>
         </is>
       </c>
       <c r="E36" s="302" t="n">
         <v>20.5</v>
       </c>
       <c r="F36" s="303" t="n">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="G36" s="303" t="n">
         <v>0</v>
@@ -4212,14 +4224,14 @@
       </c>
       <c r="D37" s="301" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 43 DIA 20.5 MM</t>
+          <t>SAMSOL HAIR COLOR 39 SMALL PURPLE</t>
         </is>
       </c>
       <c r="E37" s="302" t="n">
         <v>20.5</v>
       </c>
       <c r="F37" s="303" t="n">
-        <v>5732</v>
+        <v>6556</v>
       </c>
       <c r="G37" s="303" t="n">
         <v>0</v>
@@ -4270,14 +4282,14 @@
       </c>
       <c r="D38" s="301" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 39 SMALL PURPLE</t>
+          <t>SAMSOL HAIR COLOR 41 SMALL PURPLE</t>
         </is>
       </c>
       <c r="E38" s="302" t="n">
         <v>20.5</v>
       </c>
       <c r="F38" s="303" t="n">
-        <v>6556</v>
+        <v>6557</v>
       </c>
       <c r="G38" s="303" t="n">
         <v>0</v>
@@ -4323,19 +4335,19 @@
       </c>
       <c r="C39" s="300" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Habib Hanif Inc</t>
         </is>
       </c>
       <c r="D39" s="301" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 41 SMALL PURPLE</t>
+          <t>S-45</t>
         </is>
       </c>
       <c r="E39" s="302" t="n">
-        <v>20.5</v>
+        <v>25</v>
       </c>
       <c r="F39" s="303" t="n">
-        <v>6557</v>
+        <v>5389</v>
       </c>
       <c r="G39" s="303" t="n">
         <v>0</v>
@@ -32554,13 +32566,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="52" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="H7" s="53">
         <f>E7+F7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="52" t="n"/>
+      <c r="I7" s="52" t="n">
+        <v>75</v>
+      </c>
       <c r="J7" s="52">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
         <v/>
@@ -34001,10 +34015,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="52" t="n">
-        <v>38000</v>
+        <v>23000</v>
       </c>
       <c r="G44" s="52" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="H44" s="53">
         <f>E44+F44-G44</f>
@@ -34794,7 +34808,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H62" s="53">
         <f>E62+F62-G62</f>
@@ -34838,7 +34852,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="52" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H63" s="53">
         <f>E63+F63-G63</f>
@@ -34926,7 +34940,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="52" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H65" s="53">
         <f>E65+F65-G65</f>
@@ -35497,7 +35511,7 @@
         <v>4</v>
       </c>
       <c r="F78" s="52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="52" t="n">
         <v>0</v>
@@ -35667,10 +35681,10 @@
         <v>0</v>
       </c>
       <c r="F82" s="52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G82" s="52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82" s="53">
         <f>E82+F82-G82</f>
@@ -35702,13 +35716,13 @@
         </is>
       </c>
       <c r="E83" s="52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="52" t="n">
         <v>0</v>
-      </c>
-      <c r="G83" s="52" t="n">
-        <v>1</v>
       </c>
       <c r="H83" s="53">
         <f>E83+F83-G83</f>
@@ -36225,7 +36239,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="52" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H98" s="53">
         <f>E98+F98-G98</f>
@@ -36815,7 +36829,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="53">
         <f>E113+F113-G113</f>
@@ -42161,172 +42175,348 @@
       <c r="S42" s="276" t="n"/>
     </row>
     <row r="43" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A43" s="191" t="n"/>
-      <c r="B43" s="192" t="n"/>
-      <c r="C43" s="192" t="n"/>
-      <c r="D43" s="192" t="n"/>
-      <c r="E43" s="192" t="n"/>
-      <c r="F43" s="192" t="n"/>
-      <c r="G43" s="193" t="n"/>
-      <c r="H43" s="193" t="n"/>
-      <c r="I43" s="193" t="n"/>
-      <c r="J43" s="194" t="n"/>
-      <c r="K43" s="192" t="n"/>
-      <c r="L43" s="192" t="n"/>
-      <c r="M43" s="192" t="n"/>
-      <c r="N43" s="192" t="n"/>
-      <c r="O43" s="192" t="n"/>
-      <c r="P43" s="192" t="n"/>
-      <c r="Q43" s="192" t="n"/>
-      <c r="R43" s="192" t="n"/>
-      <c r="S43" s="192" t="n"/>
+      <c r="A43" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B43" s="276" t="inlineStr">
+        <is>
+          <t>Lacquer-02</t>
+        </is>
+      </c>
+      <c r="C43" s="276" t="inlineStr"/>
+      <c r="D43" s="276" t="inlineStr"/>
+      <c r="E43" s="276" t="inlineStr"/>
+      <c r="F43" s="276" t="n"/>
+      <c r="G43" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="278">
+        <f>IFERROR(I43/(H43+I43),"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="276" t="n"/>
+      <c r="L43" s="276" t="n"/>
+      <c r="M43" s="276" t="n"/>
+      <c r="N43" s="276" t="n"/>
+      <c r="O43" s="276" t="n"/>
+      <c r="P43" s="276" t="n"/>
+      <c r="Q43" s="276" t="n"/>
+      <c r="R43" s="276" t="n"/>
+      <c r="S43" s="276" t="n"/>
     </row>
     <row r="44" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A44" s="191" t="n"/>
-      <c r="B44" s="192" t="n"/>
-      <c r="C44" s="192" t="n"/>
-      <c r="D44" s="192" t="n"/>
-      <c r="E44" s="192" t="n"/>
-      <c r="F44" s="192" t="n"/>
-      <c r="G44" s="193" t="n"/>
-      <c r="H44" s="193" t="n"/>
-      <c r="I44" s="193" t="n"/>
-      <c r="J44" s="194" t="n"/>
-      <c r="K44" s="192" t="n"/>
-      <c r="L44" s="192" t="n"/>
-      <c r="M44" s="192" t="n"/>
-      <c r="N44" s="192" t="n"/>
-      <c r="O44" s="192" t="n"/>
-      <c r="P44" s="192" t="n"/>
-      <c r="Q44" s="192" t="n"/>
-      <c r="R44" s="192" t="n"/>
-      <c r="S44" s="192" t="n"/>
+      <c r="A44" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B44" s="276" t="inlineStr">
+        <is>
+          <t>Lacquer-04</t>
+        </is>
+      </c>
+      <c r="C44" s="276" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D44" s="276" t="inlineStr">
+        <is>
+          <t>TUBES COMMON RED</t>
+        </is>
+      </c>
+      <c r="E44" s="276" t="n">
+        <v>25</v>
+      </c>
+      <c r="F44" s="276" t="n">
+        <v>6470</v>
+      </c>
+      <c r="G44" s="277" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H44" s="277" t="n">
+        <v>20735</v>
+      </c>
+      <c r="I44" s="277" t="n">
+        <v>265</v>
+      </c>
+      <c r="J44" s="278">
+        <f>IFERROR(I44/(H44+I44),"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="276" t="n"/>
+      <c r="L44" s="276" t="n"/>
+      <c r="M44" s="276" t="n"/>
+      <c r="N44" s="276" t="n"/>
+      <c r="O44" s="276" t="n"/>
+      <c r="P44" s="276" t="n"/>
+      <c r="Q44" s="276" t="n"/>
+      <c r="R44" s="276" t="n"/>
+      <c r="S44" s="276" t="n"/>
     </row>
     <row r="45" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A45" s="191" t="n"/>
-      <c r="B45" s="192" t="n"/>
-      <c r="C45" s="192" t="n"/>
-      <c r="D45" s="192" t="n"/>
-      <c r="E45" s="192" t="n"/>
-      <c r="F45" s="192" t="n"/>
-      <c r="G45" s="193" t="n"/>
-      <c r="H45" s="193" t="n"/>
-      <c r="I45" s="193" t="n"/>
-      <c r="J45" s="194" t="n"/>
-      <c r="K45" s="192" t="n"/>
-      <c r="L45" s="192" t="n"/>
-      <c r="M45" s="192" t="n"/>
-      <c r="N45" s="192" t="n"/>
-      <c r="O45" s="192" t="n"/>
-      <c r="P45" s="192" t="n"/>
-      <c r="Q45" s="192" t="n"/>
-      <c r="R45" s="192" t="n"/>
-      <c r="S45" s="192" t="n"/>
+      <c r="A45" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B45" s="276" t="inlineStr">
+        <is>
+          <t>Latex-01</t>
+        </is>
+      </c>
+      <c r="C45" s="276" t="inlineStr"/>
+      <c r="D45" s="276" t="inlineStr"/>
+      <c r="E45" s="276" t="inlineStr"/>
+      <c r="F45" s="276" t="n"/>
+      <c r="G45" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="278">
+        <f>IFERROR(I45/(H45+I45),"")</f>
+        <v/>
+      </c>
+      <c r="K45" s="276" t="n"/>
+      <c r="L45" s="276" t="n"/>
+      <c r="M45" s="276" t="n"/>
+      <c r="N45" s="276" t="n"/>
+      <c r="O45" s="276" t="n"/>
+      <c r="P45" s="276" t="n"/>
+      <c r="Q45" s="276" t="n"/>
+      <c r="R45" s="276" t="n"/>
+      <c r="S45" s="276" t="n"/>
     </row>
     <row r="46" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A46" s="191" t="n"/>
-      <c r="B46" s="192" t="n"/>
-      <c r="C46" s="192" t="n"/>
-      <c r="D46" s="192" t="n"/>
-      <c r="E46" s="192" t="n"/>
-      <c r="F46" s="192" t="n"/>
-      <c r="G46" s="193" t="n"/>
-      <c r="H46" s="193" t="n"/>
-      <c r="I46" s="193" t="n"/>
-      <c r="J46" s="194" t="n"/>
-      <c r="K46" s="192" t="n"/>
-      <c r="L46" s="192" t="n"/>
-      <c r="M46" s="192" t="n"/>
-      <c r="N46" s="192" t="n"/>
-      <c r="O46" s="192" t="n"/>
-      <c r="P46" s="192" t="n"/>
-      <c r="Q46" s="192" t="n"/>
-      <c r="R46" s="192" t="n"/>
-      <c r="S46" s="192" t="n"/>
+      <c r="A46" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B46" s="276" t="inlineStr">
+        <is>
+          <t>PF Machine</t>
+        </is>
+      </c>
+      <c r="C46" s="276" t="inlineStr">
+        <is>
+          <t>Alpha Labs PVT LTD</t>
+        </is>
+      </c>
+      <c r="D46" s="276" t="inlineStr">
+        <is>
+          <t>TRANSPARENT BOTTLE 150ML</t>
+        </is>
+      </c>
+      <c r="E46" s="276" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="F46" s="276" t="n">
+        <v>8001</v>
+      </c>
+      <c r="G46" s="277" t="n">
+        <v>4080</v>
+      </c>
+      <c r="H46" s="277" t="n">
+        <v>3680</v>
+      </c>
+      <c r="I46" s="277" t="n">
+        <v>400</v>
+      </c>
+      <c r="J46" s="278">
+        <f>IFERROR(I46/(H46+I46),"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="276" t="n">
+        <v>150</v>
+      </c>
+      <c r="L46" s="276" t="n">
+        <v>210</v>
+      </c>
+      <c r="M46" s="276" t="n"/>
+      <c r="N46" s="276" t="n"/>
+      <c r="O46" s="276" t="n"/>
+      <c r="P46" s="276" t="n"/>
+      <c r="Q46" s="276" t="n"/>
+      <c r="R46" s="276" t="n"/>
+      <c r="S46" s="276" t="n"/>
     </row>
     <row r="47" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A47" s="191" t="n"/>
-      <c r="B47" s="192" t="n"/>
-      <c r="C47" s="192" t="n"/>
-      <c r="D47" s="192" t="n"/>
-      <c r="E47" s="192" t="n"/>
-      <c r="F47" s="192" t="n"/>
-      <c r="G47" s="193" t="n"/>
-      <c r="H47" s="193" t="n"/>
-      <c r="I47" s="193" t="n"/>
-      <c r="J47" s="194" t="n"/>
-      <c r="K47" s="192" t="n"/>
-      <c r="L47" s="192" t="n"/>
-      <c r="M47" s="192" t="n"/>
-      <c r="N47" s="192" t="n"/>
-      <c r="O47" s="192" t="n"/>
-      <c r="P47" s="192" t="n"/>
-      <c r="Q47" s="192" t="n"/>
-      <c r="R47" s="192" t="n"/>
-      <c r="S47" s="192" t="n"/>
+      <c r="A47" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B47" s="276" t="inlineStr">
+        <is>
+          <t>Press-04</t>
+        </is>
+      </c>
+      <c r="C47" s="276" t="inlineStr"/>
+      <c r="D47" s="276" t="inlineStr"/>
+      <c r="E47" s="276" t="inlineStr"/>
+      <c r="F47" s="276" t="n"/>
+      <c r="G47" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="278">
+        <f>IFERROR(I47/(H47+I47),"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="276" t="n"/>
+      <c r="L47" s="276" t="n"/>
+      <c r="M47" s="276" t="n"/>
+      <c r="N47" s="276" t="n"/>
+      <c r="O47" s="276" t="n"/>
+      <c r="P47" s="276" t="n"/>
+      <c r="Q47" s="276" t="n"/>
+      <c r="R47" s="276" t="n"/>
+      <c r="S47" s="276" t="n"/>
     </row>
     <row r="48" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A48" s="191" t="n"/>
-      <c r="B48" s="192" t="n"/>
-      <c r="C48" s="192" t="n"/>
-      <c r="D48" s="192" t="n"/>
-      <c r="E48" s="192" t="n"/>
-      <c r="F48" s="192" t="n"/>
-      <c r="G48" s="193" t="n"/>
-      <c r="H48" s="193" t="n"/>
-      <c r="I48" s="193" t="n"/>
-      <c r="J48" s="194" t="n"/>
-      <c r="K48" s="192" t="n"/>
-      <c r="L48" s="192" t="n"/>
-      <c r="M48" s="192" t="n"/>
-      <c r="N48" s="192" t="n"/>
-      <c r="O48" s="192" t="n"/>
-      <c r="P48" s="192" t="n"/>
-      <c r="Q48" s="192" t="n"/>
-      <c r="R48" s="192" t="n"/>
-      <c r="S48" s="192" t="n"/>
+      <c r="A48" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B48" s="276" t="inlineStr">
+        <is>
+          <t>Press-06</t>
+        </is>
+      </c>
+      <c r="C48" s="276" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="276" t="inlineStr">
+        <is>
+          <t>TUBES COMMON RED</t>
+        </is>
+      </c>
+      <c r="E48" s="276" t="n">
+        <v>25</v>
+      </c>
+      <c r="F48" s="276" t="n">
+        <v>6470</v>
+      </c>
+      <c r="G48" s="277" t="n">
+        <v>24000</v>
+      </c>
+      <c r="H48" s="277" t="n">
+        <v>23850</v>
+      </c>
+      <c r="I48" s="277" t="n">
+        <v>150</v>
+      </c>
+      <c r="J48" s="278">
+        <f>IFERROR(I48/(H48+I48),"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="276" t="n"/>
+      <c r="L48" s="276" t="n"/>
+      <c r="M48" s="276" t="n"/>
+      <c r="N48" s="276" t="n"/>
+      <c r="O48" s="276" t="n"/>
+      <c r="P48" s="276" t="n"/>
+      <c r="Q48" s="276" t="n"/>
+      <c r="R48" s="276" t="n"/>
+      <c r="S48" s="276" t="n"/>
     </row>
     <row r="49" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A49" s="191" t="n"/>
-      <c r="B49" s="192" t="n"/>
-      <c r="C49" s="192" t="n"/>
-      <c r="D49" s="192" t="n"/>
-      <c r="E49" s="192" t="n"/>
-      <c r="F49" s="192" t="n"/>
-      <c r="G49" s="193" t="n"/>
-      <c r="H49" s="193" t="n"/>
-      <c r="I49" s="193" t="n"/>
-      <c r="J49" s="194" t="n"/>
-      <c r="K49" s="192" t="n"/>
-      <c r="L49" s="192" t="n"/>
-      <c r="M49" s="192" t="n"/>
-      <c r="N49" s="192" t="n"/>
-      <c r="O49" s="192" t="n"/>
-      <c r="P49" s="192" t="n"/>
-      <c r="Q49" s="192" t="n"/>
-      <c r="R49" s="192" t="n"/>
-      <c r="S49" s="192" t="n"/>
+      <c r="A49" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B49" s="276" t="inlineStr">
+        <is>
+          <t>Printing-03</t>
+        </is>
+      </c>
+      <c r="C49" s="276" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D49" s="276" t="inlineStr">
+        <is>
+          <t>TUBES COMMON RED</t>
+        </is>
+      </c>
+      <c r="E49" s="276" t="n">
+        <v>25</v>
+      </c>
+      <c r="F49" s="276" t="n">
+        <v>6470</v>
+      </c>
+      <c r="G49" s="277" t="n">
+        <v>15816</v>
+      </c>
+      <c r="H49" s="277" t="n">
+        <v>15456</v>
+      </c>
+      <c r="I49" s="277" t="n">
+        <v>360</v>
+      </c>
+      <c r="J49" s="278">
+        <f>IFERROR(I49/(H49+I49),"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="276" t="n"/>
+      <c r="L49" s="276" t="n"/>
+      <c r="M49" s="276" t="n">
+        <v>120</v>
+      </c>
+      <c r="N49" s="276" t="n"/>
+      <c r="O49" s="276" t="n"/>
+      <c r="P49" s="276" t="n"/>
+      <c r="Q49" s="276" t="n"/>
+      <c r="R49" s="276" t="n"/>
+      <c r="S49" s="276" t="n"/>
     </row>
     <row r="50" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A50" s="191" t="n"/>
-      <c r="B50" s="192" t="n"/>
-      <c r="C50" s="192" t="n"/>
-      <c r="D50" s="192" t="n"/>
-      <c r="E50" s="192" t="n"/>
-      <c r="F50" s="192" t="n"/>
-      <c r="G50" s="193" t="n"/>
-      <c r="H50" s="193" t="n"/>
-      <c r="I50" s="193" t="n"/>
-      <c r="J50" s="194" t="n"/>
-      <c r="K50" s="192" t="n"/>
-      <c r="L50" s="192" t="n"/>
-      <c r="M50" s="192" t="n"/>
-      <c r="N50" s="192" t="n"/>
-      <c r="O50" s="192" t="n"/>
-      <c r="P50" s="192" t="n"/>
-      <c r="Q50" s="192" t="n"/>
-      <c r="R50" s="192" t="n"/>
-      <c r="S50" s="192" t="n"/>
+      <c r="A50" s="285" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B50" s="276" t="inlineStr">
+        <is>
+          <t>Printing-04</t>
+        </is>
+      </c>
+      <c r="C50" s="276" t="inlineStr"/>
+      <c r="D50" s="276" t="inlineStr"/>
+      <c r="E50" s="276" t="inlineStr"/>
+      <c r="F50" s="276" t="n"/>
+      <c r="G50" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="278">
+        <f>IFERROR(I50/(H50+I50),"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="276" t="n"/>
+      <c r="L50" s="276" t="n"/>
+      <c r="M50" s="276" t="n"/>
+      <c r="N50" s="276" t="n"/>
+      <c r="O50" s="276" t="n"/>
+      <c r="P50" s="276" t="n"/>
+      <c r="Q50" s="276" t="n"/>
+      <c r="R50" s="276" t="n"/>
+      <c r="S50" s="276" t="n"/>
     </row>
     <row r="51" hidden="1" ht="15" customHeight="1" s="254">
       <c r="A51" s="191" t="n"/>
@@ -49820,7 +50010,7 @@
     <row r="1" ht="30" customHeight="1" s="254">
       <c r="A1" s="280" t="inlineStr">
         <is>
-          <t>FG STOCK IN HAND — Last Updated: 08-Jun-2026</t>
+          <t>FG STOCK IN HAND — Last Updated: 09-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -49879,31 +50069,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="254">
-      <c r="A4" s="286" t="n">
+      <c r="A4" s="312" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="286" t="n">
+      <c r="B4" s="312" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="287" t="inlineStr">
+      <c r="C4" s="313" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="287" t="inlineStr">
+      <c r="D4" s="313" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="286" t="inlineStr">
+      <c r="E4" s="312" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="288" t="n">
-        <v>28060</v>
-      </c>
-      <c r="G4" s="286" t="inlineStr">
+      <c r="F4" s="314" t="n">
+        <v>31740</v>
+      </c>
+      <c r="G4" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -49919,31 +50109,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="254">
-      <c r="A5" s="286" t="n">
+      <c r="A5" s="312" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="286" t="n">
+      <c r="B5" s="312" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="287" t="inlineStr">
+      <c r="C5" s="313" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="287" t="inlineStr">
+      <c r="D5" s="313" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="286" t="inlineStr">
+      <c r="E5" s="312" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="288" t="n">
+      <c r="F5" s="314" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="286" t="inlineStr">
+      <c r="G5" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -49959,31 +50149,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="254">
-      <c r="A6" s="286" t="n">
+      <c r="A6" s="312" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="286" t="n">
+      <c r="B6" s="312" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="287" t="inlineStr">
+      <c r="C6" s="313" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="287" t="inlineStr">
+      <c r="D6" s="313" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="286" t="inlineStr">
+      <c r="E6" s="312" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="288" t="n">
+      <c r="F6" s="314" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="286" t="inlineStr">
+      <c r="G6" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -49999,31 +50189,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="254">
-      <c r="A7" s="286" t="n">
+      <c r="A7" s="312" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="286" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C7" s="287" t="inlineStr">
-        <is>
-          <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
-        </is>
-      </c>
-      <c r="D7" s="287" t="inlineStr">
-        <is>
-          <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
-        </is>
-      </c>
-      <c r="E7" s="286" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F7" s="288" t="n">
-        <v>9450</v>
-      </c>
-      <c r="G7" s="286" t="inlineStr">
+      <c r="B7" s="312" t="n">
+        <v>6470</v>
+      </c>
+      <c r="C7" s="313" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="313" t="inlineStr">
+        <is>
+          <t>TUBES COMMON RED</t>
+        </is>
+      </c>
+      <c r="E7" s="312" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="314" t="n">
+        <v>15456</v>
+      </c>
+      <c r="G7" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50039,31 +50229,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="254">
-      <c r="A8" s="286" t="n">
+      <c r="A8" s="312" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="286" t="n">
-        <v>6337</v>
-      </c>
-      <c r="C8" s="287" t="inlineStr">
-        <is>
-          <t>Al-Rehman Group</t>
-        </is>
-      </c>
-      <c r="D8" s="287" t="inlineStr">
-        <is>
-          <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
-        </is>
-      </c>
-      <c r="E8" s="286" t="inlineStr">
+      <c r="B8" s="312" t="n">
+        <v>4050</v>
+      </c>
+      <c r="C8" s="313" t="inlineStr">
+        <is>
+          <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
+        </is>
+      </c>
+      <c r="D8" s="313" t="inlineStr">
+        <is>
+          <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
+        </is>
+      </c>
+      <c r="E8" s="312" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="288" t="n">
-        <v>15680</v>
-      </c>
-      <c r="G8" s="286" t="inlineStr">
+      <c r="F8" s="314" t="n">
+        <v>9450</v>
+      </c>
+      <c r="G8" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50079,31 +50269,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="254">
-      <c r="A9" s="286" t="n">
+      <c r="A9" s="312" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="286" t="n">
-        <v>6416</v>
-      </c>
-      <c r="C9" s="287" t="inlineStr">
+      <c r="B9" s="312" t="n">
+        <v>6337</v>
+      </c>
+      <c r="C9" s="313" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="287" t="inlineStr">
-        <is>
-          <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
-        </is>
-      </c>
-      <c r="E9" s="286" t="inlineStr">
+      <c r="D9" s="313" t="inlineStr">
+        <is>
+          <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
+        </is>
+      </c>
+      <c r="E9" s="312" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="288" t="n">
-        <v>15435</v>
-      </c>
-      <c r="G9" s="286" t="inlineStr">
+      <c r="F9" s="314" t="n">
+        <v>15680</v>
+      </c>
+      <c r="G9" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50119,31 +50309,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="254">
-      <c r="A10" s="286" t="n">
+      <c r="A10" s="312" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="286" t="n">
-        <v>5782</v>
-      </c>
-      <c r="C10" s="287" t="inlineStr">
-        <is>
-          <t>Mega Grey</t>
-        </is>
-      </c>
-      <c r="D10" s="287" t="inlineStr">
-        <is>
-          <t>M.G</t>
-        </is>
-      </c>
-      <c r="E10" s="286" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F10" s="288" t="n">
-        <v>63648</v>
-      </c>
-      <c r="G10" s="286" t="inlineStr">
+      <c r="B10" s="312" t="n">
+        <v>6416</v>
+      </c>
+      <c r="C10" s="313" t="inlineStr">
+        <is>
+          <t>Al-Rehman Group</t>
+        </is>
+      </c>
+      <c r="D10" s="313" t="inlineStr">
+        <is>
+          <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
+        </is>
+      </c>
+      <c r="E10" s="312" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" s="314" t="n">
+        <v>15435</v>
+      </c>
+      <c r="G10" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50159,31 +50349,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="254">
-      <c r="A11" s="286" t="n">
+      <c r="A11" s="312" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="286" t="n">
-        <v>6531</v>
-      </c>
-      <c r="C11" s="287" t="inlineStr">
-        <is>
-          <t>Adore</t>
-        </is>
-      </c>
-      <c r="D11" s="287" t="inlineStr">
-        <is>
-          <t>V-HC BLACK</t>
-        </is>
-      </c>
-      <c r="E11" s="286" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F11" s="288" t="n">
-        <v>4380</v>
-      </c>
-      <c r="G11" s="286" t="inlineStr">
+      <c r="B11" s="312" t="n">
+        <v>5782</v>
+      </c>
+      <c r="C11" s="313" t="inlineStr">
+        <is>
+          <t>Mega Grey</t>
+        </is>
+      </c>
+      <c r="D11" s="313" t="inlineStr">
+        <is>
+          <t>M.G</t>
+        </is>
+      </c>
+      <c r="E11" s="312" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F11" s="314" t="n">
+        <v>63648</v>
+      </c>
+      <c r="G11" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50199,38 +50389,38 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="254">
-      <c r="A12" s="286" t="n">
+      <c r="A12" s="312" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="286" t="n">
-        <v>6206</v>
-      </c>
-      <c r="C12" s="287" t="inlineStr">
-        <is>
-          <t>Golden Pearl Cosmetics (PVT) LTD</t>
-        </is>
-      </c>
-      <c r="D12" s="287" t="inlineStr">
-        <is>
-          <t>HELLO HAIR COLOR</t>
-        </is>
-      </c>
-      <c r="E12" s="286" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F12" s="288" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G12" s="286" t="inlineStr">
+      <c r="B12" s="312" t="n">
+        <v>6531</v>
+      </c>
+      <c r="C12" s="313" t="inlineStr">
+        <is>
+          <t>Adore</t>
+        </is>
+      </c>
+      <c r="D12" s="313" t="inlineStr">
+        <is>
+          <t>V-HC BLACK</t>
+        </is>
+      </c>
+      <c r="E12" s="312" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F12" s="314" t="n">
+        <v>4380</v>
+      </c>
+      <c r="G12" s="312" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="H12" s="289" t="inlineStr">
         <is>
-          <t>No JOF</t>
+          <t>Ready for dispatch</t>
         </is>
       </c>
       <c r="I12" s="109">
@@ -50239,38 +50429,38 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="254">
-      <c r="A13" s="290" t="n">
+      <c r="A13" s="312" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="290" t="n">
-        <v>6515</v>
-      </c>
-      <c r="C13" s="291" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="291" t="inlineStr">
-        <is>
-          <t>H.H 100GM</t>
-        </is>
-      </c>
-      <c r="E13" s="290" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F13" s="292" t="n">
-        <v>38896</v>
-      </c>
-      <c r="G13" s="290" t="inlineStr">
-        <is>
-          <t>Not Ready</t>
-        </is>
-      </c>
-      <c r="H13" s="293" t="inlineStr">
-        <is>
-          <t>To be dispatch after packing</t>
+      <c r="B13" s="312" t="n">
+        <v>6206</v>
+      </c>
+      <c r="C13" s="313" t="inlineStr">
+        <is>
+          <t>Golden Pearl Cosmetics (PVT) LTD</t>
+        </is>
+      </c>
+      <c r="D13" s="313" t="inlineStr">
+        <is>
+          <t>HELLO HAIR COLOR</t>
+        </is>
+      </c>
+      <c r="E13" s="312" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="314" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G13" s="312" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H13" s="289" t="inlineStr">
+        <is>
+          <t>No JOF</t>
         </is>
       </c>
       <c r="I13" s="109">
@@ -50279,31 +50469,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="254">
-      <c r="A14" s="290" t="n">
+      <c r="A14" s="315" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="290" t="n">
-        <v>6530</v>
-      </c>
-      <c r="C14" s="291" t="inlineStr">
-        <is>
-          <t>Adore</t>
-        </is>
-      </c>
-      <c r="D14" s="291" t="inlineStr">
-        <is>
-          <t>V- HC BROWN</t>
-        </is>
-      </c>
-      <c r="E14" s="290" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F14" s="292" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G14" s="290" t="inlineStr">
+      <c r="B14" s="315" t="n">
+        <v>6515</v>
+      </c>
+      <c r="C14" s="316" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D14" s="316" t="inlineStr">
+        <is>
+          <t>H.H 100GM</t>
+        </is>
+      </c>
+      <c r="E14" s="315" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F14" s="317" t="n">
+        <v>38896</v>
+      </c>
+      <c r="G14" s="315" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50319,31 +50509,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="254">
-      <c r="A15" s="290" t="n">
+      <c r="A15" s="315" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="290" t="n">
-        <v>6206</v>
-      </c>
-      <c r="C15" s="291" t="inlineStr">
-        <is>
-          <t>Golden Pearl Cosmetics (PVT) LTD</t>
-        </is>
-      </c>
-      <c r="D15" s="291" t="inlineStr">
-        <is>
-          <t>HELLO HAIR COLOR</t>
-        </is>
-      </c>
-      <c r="E15" s="290" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F15" s="292" t="n">
-        <v>63674</v>
-      </c>
-      <c r="G15" s="290" t="inlineStr">
+      <c r="B15" s="315" t="n">
+        <v>6530</v>
+      </c>
+      <c r="C15" s="316" t="inlineStr">
+        <is>
+          <t>Adore</t>
+        </is>
+      </c>
+      <c r="D15" s="316" t="inlineStr">
+        <is>
+          <t>V- HC BROWN</t>
+        </is>
+      </c>
+      <c r="E15" s="315" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F15" s="317" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G15" s="315" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50359,38 +50549,38 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="254">
-      <c r="A16" s="290" t="n">
+      <c r="A16" s="315" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="290" t="n">
-        <v>5782</v>
-      </c>
-      <c r="C16" s="291" t="inlineStr">
-        <is>
-          <t>Mega Grey</t>
-        </is>
-      </c>
-      <c r="D16" s="291" t="inlineStr">
-        <is>
-          <t>M.G</t>
-        </is>
-      </c>
-      <c r="E16" s="290" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F16" s="292" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G16" s="290" t="inlineStr">
+      <c r="B16" s="315" t="n">
+        <v>6206</v>
+      </c>
+      <c r="C16" s="316" t="inlineStr">
+        <is>
+          <t>Golden Pearl Cosmetics (PVT) LTD</t>
+        </is>
+      </c>
+      <c r="D16" s="316" t="inlineStr">
+        <is>
+          <t>HELLO HAIR COLOR</t>
+        </is>
+      </c>
+      <c r="E16" s="315" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="317" t="n">
+        <v>23674</v>
+      </c>
+      <c r="G16" s="315" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
       </c>
       <c r="H16" s="293" t="inlineStr">
         <is>
-          <t>Cap Not Available</t>
+          <t>To be dispatch after packing</t>
         </is>
       </c>
       <c r="I16" s="110">
@@ -50399,31 +50589,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="254">
-      <c r="A17" s="290" t="n">
+      <c r="A17" s="315" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="290" t="n">
-        <v>6624</v>
-      </c>
-      <c r="C17" s="291" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D17" s="291" t="inlineStr">
-        <is>
-          <t>S-45 DIA 19MM</t>
-        </is>
-      </c>
-      <c r="E17" s="290" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F17" s="292" t="n">
-        <v>15288</v>
-      </c>
-      <c r="G17" s="290" t="inlineStr">
+      <c r="B17" s="315" t="n">
+        <v>5782</v>
+      </c>
+      <c r="C17" s="316" t="inlineStr">
+        <is>
+          <t>Mega Grey</t>
+        </is>
+      </c>
+      <c r="D17" s="316" t="inlineStr">
+        <is>
+          <t>M.G</t>
+        </is>
+      </c>
+      <c r="E17" s="315" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F17" s="317" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G17" s="315" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50439,31 +50629,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="254">
-      <c r="A18" s="290" t="n">
+      <c r="A18" s="315" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="290" t="n">
-        <v>5731</v>
-      </c>
-      <c r="C18" s="291" t="inlineStr">
+      <c r="B18" s="315" t="n">
+        <v>6624</v>
+      </c>
+      <c r="C18" s="316" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="291" t="inlineStr">
-        <is>
-          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
-        </is>
-      </c>
-      <c r="E18" s="290" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="F18" s="292" t="n">
-        <v>37030</v>
-      </c>
-      <c r="G18" s="290" t="inlineStr">
+      <c r="D18" s="316" t="inlineStr">
+        <is>
+          <t>S-45 DIA 19MM</t>
+        </is>
+      </c>
+      <c r="E18" s="315" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F18" s="317" t="n">
+        <v>15288</v>
+      </c>
+      <c r="G18" s="315" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50479,14 +50669,40 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="254">
-      <c r="A19" s="294" t="n"/>
-      <c r="B19" s="294" t="n"/>
-      <c r="C19" s="295" t="n"/>
-      <c r="D19" s="295" t="n"/>
-      <c r="E19" s="294" t="n"/>
-      <c r="F19" s="296" t="n"/>
-      <c r="G19" s="294" t="n"/>
-      <c r="H19" s="297" t="n"/>
+      <c r="A19" s="315" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="315" t="n">
+        <v>5731</v>
+      </c>
+      <c r="C19" s="316" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D19" s="316" t="inlineStr">
+        <is>
+          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
+        </is>
+      </c>
+      <c r="E19" s="315" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="F19" s="317" t="n">
+        <v>37030</v>
+      </c>
+      <c r="G19" s="315" t="inlineStr">
+        <is>
+          <t>Not Ready</t>
+        </is>
+      </c>
+      <c r="H19" s="293" t="inlineStr">
+        <is>
+          <t>Cap Not Available</t>
+        </is>
+      </c>
       <c r="I19" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B19)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tubex_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Product_Catalog'!$A$2:$S$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Production_Log'!$A$2:$S$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BOM Issues'!$A$52:$J$64</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001" forceFullCalc="1"/>
@@ -495,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -712,6 +711,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -756,28 +770,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -797,6 +789,12 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
     <border/>
     <border>
       <left style="thin">
@@ -812,28 +810,22 @@
         <color rgb="FFB0B0B0"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="10">
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="173" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="173" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="24"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="21"/>
   </cellStyleXfs>
   <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1371,47 +1363,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1425,6 +1376,47 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="12" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="13" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1449,20 +1441,20 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1528,54 +1520,91 @@
     <xf numFmtId="0" fontId="26" fillId="14" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="24" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="24" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="48" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="12" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1613,43 +1642,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="12" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2151,8 +2143,8 @@
     <col width="14.7109375" customWidth="1" style="242" min="13" max="13"/>
     <col width="13.28515625" customWidth="1" style="242" min="14" max="14"/>
     <col width="9.5703125" customWidth="1" style="242" min="15" max="15"/>
-    <col width="8.7109375" customWidth="1" style="242" min="16" max="43"/>
-    <col width="8.7109375" customWidth="1" style="242" min="44" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="242" min="16" max="44"/>
+    <col width="8.7109375" customWidth="1" style="242" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1" s="254">
@@ -2616,45 +2608,45 @@
     </row>
     <row r="11" ht="16.5" customFormat="1" customHeight="1" s="187">
       <c r="A11" s="186" t="n"/>
-      <c r="B11" s="299" t="inlineStr">
+      <c r="B11" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C11" s="300" t="inlineStr">
+      <c r="C11" s="282" t="inlineStr">
         <is>
           <t>Brookes Pharma Private Limited</t>
         </is>
       </c>
-      <c r="D11" s="301" t="inlineStr">
+      <c r="D11" s="283" t="inlineStr">
         <is>
           <t>ECZEMUS OINTMENT 0.03% 10G</t>
         </is>
       </c>
-      <c r="E11" s="302" t="n">
+      <c r="E11" s="284" t="n">
         <v>16</v>
       </c>
-      <c r="F11" s="303" t="n">
+      <c r="F11" s="285" t="n">
         <v>6561</v>
       </c>
-      <c r="G11" s="303">
+      <c r="G11" s="285">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F11,MRP!$D$3:$D$9,0)),0)</f>
         <v/>
       </c>
-      <c r="H11" s="304">
+      <c r="H11" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F11)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I11" s="303">
+      <c r="I11" s="285">
         <f>G11-H11</f>
         <v/>
       </c>
-      <c r="J11" s="305">
+      <c r="J11" s="287">
         <f>IF(G11=0,"-",H11/G11)</f>
         <v/>
       </c>
-      <c r="K11" s="304" t="n"/>
-      <c r="L11" s="306" t="inlineStr">
+      <c r="K11" s="286" t="n"/>
+      <c r="L11" s="288" t="inlineStr">
         <is>
           <t>Hold (Caps Not Approved)</t>
         </is>
@@ -2686,44 +2678,44 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" s="254">
       <c r="A12" s="151" t="n"/>
-      <c r="B12" s="299" t="inlineStr">
+      <c r="B12" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C12" s="300" t="inlineStr">
+      <c r="C12" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D12" s="301" t="inlineStr">
+      <c r="D12" s="283" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E12" s="302" t="n">
+      <c r="E12" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="303" t="n">
+      <c r="F12" s="285" t="n">
         <v>3726</v>
       </c>
-      <c r="G12" s="303" t="n">
+      <c r="G12" s="285" t="n">
         <v>48176</v>
       </c>
-      <c r="H12" s="304">
+      <c r="H12" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F12)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I12" s="303">
+      <c r="I12" s="285">
         <f>G12-H12</f>
         <v/>
       </c>
-      <c r="J12" s="305">
+      <c r="J12" s="287">
         <f>IF(G12=0,"-",H12/G12)</f>
         <v/>
       </c>
-      <c r="K12" s="304" t="n"/>
-      <c r="L12" s="306" t="inlineStr">
+      <c r="K12" s="286" t="n"/>
+      <c r="L12" s="288" t="inlineStr">
         <is>
           <t>70k Order, 44k Advance Production</t>
         </is>
@@ -2767,44 +2759,46 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" s="254">
       <c r="A13" s="151" t="n"/>
-      <c r="B13" s="299" t="inlineStr">
+      <c r="B13" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C13" s="300" t="inlineStr">
+      <c r="C13" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D13" s="301" t="inlineStr">
+      <c r="D13" s="283" t="inlineStr">
         <is>
           <t>S 43 25MM</t>
         </is>
       </c>
-      <c r="E13" s="302" t="n">
+      <c r="E13" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F13" s="303" t="n">
+      <c r="F13" s="285" t="n">
         <v>3447</v>
       </c>
-      <c r="G13" s="303" t="n">
+      <c r="G13" s="285" t="n">
         <v>31000</v>
       </c>
-      <c r="H13" s="304">
+      <c r="H13" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F13)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I13" s="303">
+      <c r="I13" s="285">
         <f>G13-H13</f>
         <v/>
       </c>
-      <c r="J13" s="305">
+      <c r="J13" s="287">
         <f>IF(G13=0,"-",H13/G13)</f>
         <v/>
       </c>
-      <c r="K13" s="304" t="n"/>
-      <c r="L13" s="306" t="inlineStr">
+      <c r="K13" s="286" t="n">
+        <v>90048</v>
+      </c>
+      <c r="L13" s="288" t="inlineStr">
         <is>
           <t>120k Order, 89k Advance Production</t>
         </is>
@@ -2848,44 +2842,44 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" s="254">
       <c r="A14" s="151" t="n"/>
-      <c r="B14" s="299" t="inlineStr">
+      <c r="B14" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C14" s="300" t="inlineStr">
+      <c r="C14" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="301" t="inlineStr">
+      <c r="D14" s="283" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E14" s="302" t="n">
+      <c r="E14" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F14" s="303" t="n">
+      <c r="F14" s="285" t="n">
         <v>6470</v>
       </c>
-      <c r="G14" s="303" t="n">
+      <c r="G14" s="285" t="n">
         <v>61776</v>
       </c>
-      <c r="H14" s="304">
+      <c r="H14" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F14)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I14" s="303">
+      <c r="I14" s="285">
         <f>G14-H14</f>
         <v/>
       </c>
-      <c r="J14" s="305">
+      <c r="J14" s="287">
         <f>IF(G14=0,"-",H14/G14)</f>
         <v/>
       </c>
-      <c r="K14" s="304" t="n"/>
-      <c r="L14" s="306" t="n"/>
+      <c r="K14" s="286" t="n"/>
+      <c r="L14" s="288" t="n"/>
       <c r="M14" s="170" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -2927,44 +2921,44 @@
     </row>
     <row r="15" ht="16.5" customHeight="1" s="254">
       <c r="A15" s="151" t="n"/>
-      <c r="B15" s="299" t="inlineStr">
+      <c r="B15" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C15" s="300" t="inlineStr">
+      <c r="C15" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D15" s="301" t="inlineStr">
+      <c r="D15" s="283" t="inlineStr">
         <is>
           <t>TUBE COMMON PURPLE</t>
         </is>
       </c>
-      <c r="E15" s="302" t="n">
+      <c r="E15" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="303" t="n">
+      <c r="F15" s="285" t="n">
         <v>6532</v>
       </c>
-      <c r="G15" s="303" t="n">
+      <c r="G15" s="285" t="n">
         <v>30000</v>
       </c>
-      <c r="H15" s="304">
+      <c r="H15" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F15)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I15" s="303">
+      <c r="I15" s="285">
         <f>G15-H15</f>
         <v/>
       </c>
-      <c r="J15" s="305">
+      <c r="J15" s="287">
         <f>IF(G15=0,"-",H15/G15)</f>
         <v/>
       </c>
-      <c r="K15" s="304" t="n"/>
-      <c r="L15" s="306" t="n"/>
+      <c r="K15" s="286" t="n"/>
+      <c r="L15" s="288" t="n"/>
       <c r="P15" s="151" t="n"/>
       <c r="Q15" s="151" t="n"/>
       <c r="R15" s="151" t="n"/>
@@ -2982,49 +2976,46 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" s="254">
       <c r="A16" s="151" t="n"/>
-      <c r="B16" s="299" t="inlineStr">
+      <c r="B16" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C16" s="300" t="inlineStr">
-        <is>
-          <t>Golden Pearl Cosmetics (PVT) LTD</t>
-        </is>
-      </c>
-      <c r="D16" s="301" t="inlineStr">
-        <is>
-          <t>HELLO HAIR COLOR</t>
-        </is>
-      </c>
-      <c r="E16" s="302" t="n">
-        <v>30</v>
-      </c>
-      <c r="F16" s="303" t="n">
-        <v>6206</v>
-      </c>
-      <c r="G16" s="303">
-        <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F16,MRP!$D$3:$D$9,0)),0)</f>
-        <v/>
-      </c>
-      <c r="H16" s="304">
+      <c r="C16" s="282" t="inlineStr">
+        <is>
+          <t>Habib Hanif Inc</t>
+        </is>
+      </c>
+      <c r="D16" s="283" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E16" s="284" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" s="285" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G16" s="285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F16)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I16" s="303">
+      <c r="I16" s="285">
         <f>G16-H16</f>
         <v/>
       </c>
-      <c r="J16" s="305">
+      <c r="J16" s="287">
         <f>IF(G16=0,"-",H16/G16)</f>
         <v/>
       </c>
-      <c r="K16" s="304" t="n"/>
-      <c r="L16" s="306" t="inlineStr">
-        <is>
-          <t>Advance Production</t>
-        </is>
-      </c>
+      <c r="K16" s="286" t="n">
+        <v>44352</v>
+      </c>
+      <c r="L16" s="288" t="n"/>
       <c r="M16" s="151" t="n"/>
       <c r="N16" s="151" t="n"/>
       <c r="O16" s="151" t="n"/>
@@ -3055,45 +3046,49 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" s="254">
       <c r="A17" s="151" t="n"/>
-      <c r="B17" s="299" t="inlineStr">
+      <c r="B17" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C17" s="300" t="inlineStr">
-        <is>
-          <t>Mablay Beauty PVT LTD.</t>
-        </is>
-      </c>
-      <c r="D17" s="301" t="inlineStr">
-        <is>
-          <t>VINCE NURTURAL</t>
-        </is>
-      </c>
-      <c r="E17" s="302" t="n">
+      <c r="C17" s="282" t="inlineStr">
+        <is>
+          <t>Golden Pearl Cosmetics (PVT) LTD</t>
+        </is>
+      </c>
+      <c r="D17" s="283" t="inlineStr">
+        <is>
+          <t>HELLO HAIR COLOR</t>
+        </is>
+      </c>
+      <c r="E17" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="303" t="n">
-        <v>5814</v>
-      </c>
-      <c r="G17" s="303">
+      <c r="F17" s="285" t="n">
+        <v>6206</v>
+      </c>
+      <c r="G17" s="285">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F17,MRP!$D$3:$D$9,0)),0)</f>
         <v/>
       </c>
-      <c r="H17" s="304">
+      <c r="H17" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F17)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I17" s="303">
+      <c r="I17" s="285">
         <f>G17-H17</f>
         <v/>
       </c>
-      <c r="J17" s="305">
+      <c r="J17" s="287">
         <f>IF(G17=0,"-",H17/G17)</f>
         <v/>
       </c>
-      <c r="K17" s="304" t="n"/>
-      <c r="L17" s="306" t="n"/>
+      <c r="K17" s="286" t="n"/>
+      <c r="L17" s="288" t="inlineStr">
+        <is>
+          <t>Advance Production</t>
+        </is>
+      </c>
       <c r="P17" s="151" t="n"/>
       <c r="Q17" s="151" t="n"/>
       <c r="R17" s="151" t="n"/>
@@ -3111,49 +3106,45 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" s="254">
       <c r="A18" s="151" t="n"/>
-      <c r="B18" s="299" t="inlineStr">
+      <c r="B18" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C18" s="300" t="inlineStr">
-        <is>
-          <t>Adore</t>
-        </is>
-      </c>
-      <c r="D18" s="301" t="inlineStr">
-        <is>
-          <t>V- HC BROWN</t>
-        </is>
-      </c>
-      <c r="E18" s="302" t="n">
-        <v>35</v>
-      </c>
-      <c r="F18" s="303" t="n">
-        <v>6530</v>
-      </c>
-      <c r="G18" s="303">
+      <c r="C18" s="282" t="inlineStr">
+        <is>
+          <t>Mablay Beauty PVT LTD.</t>
+        </is>
+      </c>
+      <c r="D18" s="283" t="inlineStr">
+        <is>
+          <t>VINCE NURTURAL</t>
+        </is>
+      </c>
+      <c r="E18" s="284" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="285" t="n">
+        <v>5814</v>
+      </c>
+      <c r="G18" s="285">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F18,MRP!$D$3:$D$9,0)),0)</f>
         <v/>
       </c>
-      <c r="H18" s="304">
+      <c r="H18" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F18)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I18" s="303">
+      <c r="I18" s="285">
         <f>G18-H18</f>
         <v/>
       </c>
-      <c r="J18" s="305">
+      <c r="J18" s="287">
         <f>IF(G18=0,"-",H18/G18)</f>
         <v/>
       </c>
-      <c r="K18" s="304" t="n"/>
-      <c r="L18" s="306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hold </t>
-        </is>
-      </c>
+      <c r="K18" s="286" t="n"/>
+      <c r="L18" s="288" t="n"/>
       <c r="P18" s="151" t="n"/>
       <c r="Q18" s="151" t="n"/>
       <c r="R18" s="151" t="n"/>
@@ -3181,33 +3172,49 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" s="254">
       <c r="A19" s="151" t="n"/>
-      <c r="B19" s="307" t="n"/>
-      <c r="C19" s="308" t="n"/>
-      <c r="D19" s="309" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E19" s="307" t="n"/>
-      <c r="F19" s="308" t="n"/>
-      <c r="G19" s="310">
-        <f>SUM(G11:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="310">
-        <f>SUM(H11:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="310">
-        <f>SUMIF(I11:I18,"&gt;"&amp;0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="310" t="n"/>
-      <c r="K19" s="310">
-        <f>SUM(K11:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="310" t="n"/>
+      <c r="B19" s="281" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="C19" s="282" t="inlineStr">
+        <is>
+          <t>Adore</t>
+        </is>
+      </c>
+      <c r="D19" s="283" t="inlineStr">
+        <is>
+          <t>V- HC BROWN</t>
+        </is>
+      </c>
+      <c r="E19" s="284" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="285" t="n">
+        <v>6530</v>
+      </c>
+      <c r="G19" s="285">
+        <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F19,MRP!$D$3:$D$9,0)),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="286">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F19)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
+        <v/>
+      </c>
+      <c r="I19" s="285">
+        <f>G19-H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="287">
+        <f>IF(G19=0,"-",H19/G19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="286" t="n"/>
+      <c r="L19" s="288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hold </t>
+        </is>
+      </c>
       <c r="M19" s="151" t="n"/>
       <c r="N19" s="151" t="n"/>
       <c r="O19" s="151" t="n"/>
@@ -3238,46 +3245,33 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" s="254">
       <c r="A20" s="151" t="n"/>
-      <c r="B20" s="299" t="inlineStr">
-        <is>
-          <t>PET</t>
-        </is>
-      </c>
-      <c r="C20" s="300" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="301" t="inlineStr">
-        <is>
-          <t>PET BOTTLE SMALL (120ML) YELLOW</t>
-        </is>
-      </c>
-      <c r="E20" s="302" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
-      <c r="F20" s="303" t="n">
-        <v>8005</v>
-      </c>
-      <c r="G20" s="303" t="n">
-        <v>19840</v>
-      </c>
-      <c r="H20" s="304">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F20)*Production_Log!$H$3:$H$8963)</f>
-        <v/>
-      </c>
-      <c r="I20" s="303">
-        <f>G20-H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="305">
-        <f>IF(G20=0,"-",H20/G20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="304" t="n"/>
-      <c r="L20" s="306" t="n"/>
+      <c r="B20" s="289" t="n"/>
+      <c r="C20" s="290" t="n"/>
+      <c r="D20" s="291" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E20" s="289" t="n"/>
+      <c r="F20" s="290" t="n"/>
+      <c r="G20" s="292">
+        <f>SUM(G11:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="292">
+        <f>SUM(H11:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="292">
+        <f>SUMIF(I11:I19,"&gt;"&amp;0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="292" t="n"/>
+      <c r="K20" s="292">
+        <f>SUM(K11:K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="292" t="n"/>
       <c r="M20" s="151" t="n"/>
       <c r="N20" s="151" t="n"/>
       <c r="O20" s="151" t="n"/>
@@ -3296,46 +3290,46 @@
     </row>
     <row r="21" ht="16.5" customHeight="1" s="254">
       <c r="A21" s="151" t="n"/>
-      <c r="B21" s="299" t="inlineStr">
+      <c r="B21" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C21" s="300" t="inlineStr">
-        <is>
-          <t>Alpha Labs PVT LTD</t>
-        </is>
-      </c>
-      <c r="D21" s="301" t="inlineStr">
-        <is>
-          <t>TRANSPARENT BOTTLE 150ML</t>
-        </is>
-      </c>
-      <c r="E21" s="302" t="inlineStr">
-        <is>
-          <t>150 ml</t>
-        </is>
-      </c>
-      <c r="F21" s="303" t="n">
-        <v>8001</v>
-      </c>
-      <c r="G21" s="303" t="n">
-        <v>249997</v>
-      </c>
-      <c r="H21" s="304">
+      <c r="C21" s="282" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="283" t="inlineStr">
+        <is>
+          <t>PET BOTTLE SMALL (120ML) YELLOW</t>
+        </is>
+      </c>
+      <c r="E21" s="284" t="inlineStr">
+        <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="F21" s="285" t="n">
+        <v>8005</v>
+      </c>
+      <c r="G21" s="285" t="n">
+        <v>19840</v>
+      </c>
+      <c r="H21" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F21)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I21" s="303">
+      <c r="I21" s="285">
         <f>G21-H21</f>
         <v/>
       </c>
-      <c r="J21" s="305">
+      <c r="J21" s="287">
         <f>IF(G21=0,"-",H21/G21)</f>
         <v/>
       </c>
-      <c r="K21" s="304" t="n"/>
-      <c r="L21" s="306" t="n"/>
+      <c r="K21" s="286" t="n"/>
+      <c r="L21" s="288" t="n"/>
       <c r="M21" s="151" t="n"/>
       <c r="N21" s="151" t="n"/>
       <c r="O21" s="151" t="n"/>
@@ -3354,46 +3348,48 @@
     </row>
     <row r="22" ht="16.5" customHeight="1" s="254">
       <c r="A22" s="151" t="n"/>
-      <c r="B22" s="299" t="inlineStr">
+      <c r="B22" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C22" s="300" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D22" s="301" t="inlineStr">
-        <is>
-          <t>PET BOTTLE LARGE 200ML WHITE</t>
-        </is>
-      </c>
-      <c r="E22" s="302" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="F22" s="303" t="n">
-        <v>8007</v>
-      </c>
-      <c r="G22" s="303" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H22" s="304">
+      <c r="C22" s="282" t="inlineStr">
+        <is>
+          <t>Alpha Labs PVT LTD</t>
+        </is>
+      </c>
+      <c r="D22" s="283" t="inlineStr">
+        <is>
+          <t>TRANSPARENT BOTTLE 150ML</t>
+        </is>
+      </c>
+      <c r="E22" s="284" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="F22" s="285" t="n">
+        <v>8001</v>
+      </c>
+      <c r="G22" s="285" t="n">
+        <v>249997</v>
+      </c>
+      <c r="H22" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F22)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I22" s="303">
+      <c r="I22" s="285">
         <f>G22-H22</f>
         <v/>
       </c>
-      <c r="J22" s="305">
+      <c r="J22" s="287">
         <f>IF(G22=0,"-",H22/G22)</f>
         <v/>
       </c>
-      <c r="K22" s="304" t="n"/>
-      <c r="L22" s="306" t="n"/>
+      <c r="K22" s="286" t="n">
+        <v>32200</v>
+      </c>
+      <c r="L22" s="288" t="n"/>
       <c r="M22" s="151" t="n"/>
       <c r="N22" s="151" t="n"/>
       <c r="O22" s="151" t="n"/>
@@ -3412,46 +3408,46 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" s="254">
       <c r="A23" s="151" t="n"/>
-      <c r="B23" s="299" t="inlineStr">
+      <c r="B23" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C23" s="300" t="inlineStr">
+      <c r="C23" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D23" s="301" t="inlineStr">
-        <is>
-          <t>BT-200 ML YELLOW</t>
-        </is>
-      </c>
-      <c r="E23" s="302" t="inlineStr">
+      <c r="D23" s="283" t="inlineStr">
+        <is>
+          <t>PET BOTTLE LARGE 200ML WHITE</t>
+        </is>
+      </c>
+      <c r="E23" s="284" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F23" s="303" t="n">
-        <v>8006</v>
-      </c>
-      <c r="G23" s="303" t="n">
-        <v>42400</v>
-      </c>
-      <c r="H23" s="304">
+      <c r="F23" s="285" t="n">
+        <v>8007</v>
+      </c>
+      <c r="G23" s="285" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H23" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F23)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I23" s="303">
+      <c r="I23" s="285">
         <f>G23-H23</f>
         <v/>
       </c>
-      <c r="J23" s="305">
+      <c r="J23" s="287">
         <f>IF(G23=0,"-",H23/G23)</f>
         <v/>
       </c>
-      <c r="K23" s="304" t="n"/>
-      <c r="L23" s="306" t="n"/>
+      <c r="K23" s="286" t="n"/>
+      <c r="L23" s="288" t="n"/>
       <c r="M23" s="151" t="n"/>
       <c r="N23" s="151" t="n"/>
       <c r="O23" s="151" t="n"/>
@@ -3470,46 +3466,46 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" s="254">
       <c r="A24" s="151" t="n"/>
-      <c r="B24" s="299" t="inlineStr">
+      <c r="B24" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C24" s="300" t="inlineStr">
+      <c r="C24" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D24" s="301" t="inlineStr">
-        <is>
-          <t>BT-200ML MUSTARD OIL (TRANSPARENT)</t>
-        </is>
-      </c>
-      <c r="E24" s="302" t="inlineStr">
+      <c r="D24" s="283" t="inlineStr">
+        <is>
+          <t>BT-200 ML YELLOW</t>
+        </is>
+      </c>
+      <c r="E24" s="284" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F24" s="303" t="n">
-        <v>8014</v>
-      </c>
-      <c r="G24" s="303" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H24" s="304">
+      <c r="F24" s="285" t="n">
+        <v>8006</v>
+      </c>
+      <c r="G24" s="285" t="n">
+        <v>42400</v>
+      </c>
+      <c r="H24" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F24)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I24" s="303">
+      <c r="I24" s="285">
         <f>G24-H24</f>
         <v/>
       </c>
-      <c r="J24" s="305">
+      <c r="J24" s="287">
         <f>IF(G24=0,"-",H24/G24)</f>
         <v/>
       </c>
-      <c r="K24" s="304" t="n"/>
-      <c r="L24" s="306" t="n"/>
+      <c r="K24" s="286" t="n"/>
+      <c r="L24" s="288" t="n"/>
       <c r="M24" s="151" t="n"/>
       <c r="N24" s="151" t="n"/>
       <c r="O24" s="151" t="n"/>
@@ -3530,33 +3526,46 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="254">
       <c r="A25" s="151" t="n"/>
-      <c r="B25" s="307" t="n"/>
-      <c r="C25" s="308" t="n"/>
-      <c r="D25" s="309" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E25" s="307" t="n"/>
-      <c r="F25" s="308" t="n"/>
-      <c r="G25" s="310">
-        <f>SUM(G20:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="310">
-        <f>SUM(H20:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="310">
-        <f>SUMIF(I20:I24,"&gt;"&amp;0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="310" t="n"/>
-      <c r="K25" s="310">
-        <f>SUM(K20:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="310" t="n"/>
+      <c r="B25" s="281" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="C25" s="282" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="283" t="inlineStr">
+        <is>
+          <t>BT-200ML MUSTARD OIL (TRANSPARENT)</t>
+        </is>
+      </c>
+      <c r="E25" s="284" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="F25" s="285" t="n">
+        <v>8014</v>
+      </c>
+      <c r="G25" s="285" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H25" s="286">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F25)*Production_Log!$H$3:$H$8963)</f>
+        <v/>
+      </c>
+      <c r="I25" s="285">
+        <f>G25-H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="287">
+        <f>IF(G25=0,"-",H25/G25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="286" t="n"/>
+      <c r="L25" s="288" t="n"/>
       <c r="M25" s="151" t="n"/>
       <c r="N25" s="151" t="n"/>
       <c r="O25" s="151" t="n"/>
@@ -3577,44 +3586,33 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="254">
       <c r="A26" s="151" t="n"/>
-      <c r="B26" s="299" t="inlineStr">
-        <is>
-          <t>TUBE</t>
-        </is>
-      </c>
-      <c r="C26" s="300" t="inlineStr">
-        <is>
-          <t>Bahadur</t>
-        </is>
-      </c>
-      <c r="D26" s="301" t="inlineStr">
-        <is>
-          <t>BAHADUR TUBE 12.5MM</t>
-        </is>
-      </c>
-      <c r="E26" s="302" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F26" s="303" t="n">
-        <v>9004</v>
-      </c>
-      <c r="G26" s="303" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="304">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F26)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v/>
-      </c>
-      <c r="I26" s="303">
-        <f>G26-H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="305">
-        <f>IF(G26=0,"-",H26/G26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="304" t="n"/>
-      <c r="L26" s="306" t="n"/>
+      <c r="B26" s="289" t="n"/>
+      <c r="C26" s="290" t="n"/>
+      <c r="D26" s="291" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E26" s="289" t="n"/>
+      <c r="F26" s="290" t="n"/>
+      <c r="G26" s="292">
+        <f>SUM(G21:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="292">
+        <f>SUM(H21:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="292">
+        <f>SUMIF(I21:I25,"&gt;"&amp;0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="292" t="n"/>
+      <c r="K26" s="292">
+        <f>SUM(K21:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="292" t="n"/>
       <c r="M26" s="151" t="n"/>
       <c r="N26" s="151" t="n"/>
       <c r="O26" s="151" t="n"/>
@@ -3635,44 +3633,44 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" s="254">
       <c r="A27" s="151" t="n"/>
-      <c r="B27" s="299" t="inlineStr">
+      <c r="B27" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C27" s="300" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D27" s="301" t="inlineStr">
-        <is>
-          <t>S-45 DIA 19MM</t>
-        </is>
-      </c>
-      <c r="E27" s="302" t="n">
-        <v>19</v>
-      </c>
-      <c r="F27" s="303" t="n">
-        <v>6624</v>
-      </c>
-      <c r="G27" s="303" t="n">
+      <c r="C27" s="282" t="inlineStr">
+        <is>
+          <t>Bahadur</t>
+        </is>
+      </c>
+      <c r="D27" s="283" t="inlineStr">
+        <is>
+          <t>BAHADUR TUBE 12.5MM</t>
+        </is>
+      </c>
+      <c r="E27" s="284" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F27" s="285" t="n">
+        <v>9004</v>
+      </c>
+      <c r="G27" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="304">
+      <c r="H27" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F27)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I27" s="303">
+      <c r="I27" s="285">
         <f>G27-H27</f>
         <v/>
       </c>
-      <c r="J27" s="305">
+      <c r="J27" s="287">
         <f>IF(G27=0,"-",H27/G27)</f>
         <v/>
       </c>
-      <c r="K27" s="304" t="n"/>
-      <c r="L27" s="306" t="n"/>
+      <c r="K27" s="286" t="n"/>
+      <c r="L27" s="288" t="n"/>
       <c r="M27" s="151" t="n"/>
       <c r="N27" s="151" t="n"/>
       <c r="O27" s="151" t="n"/>
@@ -3693,44 +3691,44 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" s="254">
       <c r="A28" s="151" t="n"/>
-      <c r="B28" s="299" t="inlineStr">
+      <c r="B28" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C28" s="300" t="inlineStr">
+      <c r="C28" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D28" s="301" t="inlineStr">
-        <is>
-          <t>S-43 DIA 19MM</t>
-        </is>
-      </c>
-      <c r="E28" s="302" t="n">
+      <c r="D28" s="283" t="inlineStr">
+        <is>
+          <t>S-45 DIA 19MM</t>
+        </is>
+      </c>
+      <c r="E28" s="284" t="n">
         <v>19</v>
       </c>
-      <c r="F28" s="303" t="n">
-        <v>6623</v>
-      </c>
-      <c r="G28" s="303" t="n">
+      <c r="F28" s="285" t="n">
+        <v>6624</v>
+      </c>
+      <c r="G28" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="304">
+      <c r="H28" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F28)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I28" s="303">
+      <c r="I28" s="285">
         <f>G28-H28</f>
         <v/>
       </c>
-      <c r="J28" s="305">
+      <c r="J28" s="287">
         <f>IF(G28=0,"-",H28/G28)</f>
         <v/>
       </c>
-      <c r="K28" s="304" t="n"/>
-      <c r="L28" s="306" t="n"/>
+      <c r="K28" s="286" t="n"/>
+      <c r="L28" s="288" t="n"/>
       <c r="M28" s="151" t="n"/>
       <c r="N28" s="151" t="n"/>
       <c r="O28" s="151" t="n"/>
@@ -3749,44 +3747,44 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" s="254">
       <c r="A29" s="151" t="n"/>
-      <c r="B29" s="299" t="inlineStr">
+      <c r="B29" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C29" s="300" t="inlineStr">
-        <is>
-          <t>Brookes Pharma Private Limited</t>
-        </is>
-      </c>
-      <c r="D29" s="301" t="inlineStr">
-        <is>
-          <t>PHLOGIN GEL 20G</t>
-        </is>
-      </c>
-      <c r="E29" s="302" t="n">
+      <c r="C29" s="282" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D29" s="283" t="inlineStr">
+        <is>
+          <t>S-43 DIA 19MM</t>
+        </is>
+      </c>
+      <c r="E29" s="284" t="n">
         <v>19</v>
       </c>
-      <c r="F29" s="303" t="n">
-        <v>6559</v>
-      </c>
-      <c r="G29" s="303" t="n">
+      <c r="F29" s="285" t="n">
+        <v>6623</v>
+      </c>
+      <c r="G29" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="304">
+      <c r="H29" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F29)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I29" s="303">
+      <c r="I29" s="285">
         <f>G29-H29</f>
         <v/>
       </c>
-      <c r="J29" s="305">
+      <c r="J29" s="287">
         <f>IF(G29=0,"-",H29/G29)</f>
         <v/>
       </c>
-      <c r="K29" s="304" t="n"/>
-      <c r="L29" s="306" t="n"/>
+      <c r="K29" s="286" t="n"/>
+      <c r="L29" s="288" t="n"/>
       <c r="M29" s="151" t="n"/>
       <c r="N29" s="151" t="n"/>
       <c r="O29" s="151" t="n"/>
@@ -3805,44 +3803,44 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" s="254">
       <c r="A30" s="151" t="n"/>
-      <c r="B30" s="299" t="inlineStr">
+      <c r="B30" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C30" s="300" t="inlineStr">
+      <c r="C30" s="282" t="inlineStr">
         <is>
           <t>Brookes Pharma Private Limited</t>
         </is>
       </c>
-      <c r="D30" s="301" t="inlineStr">
-        <is>
-          <t>PYODINE GEL 20GM</t>
-        </is>
-      </c>
-      <c r="E30" s="302" t="n">
+      <c r="D30" s="283" t="inlineStr">
+        <is>
+          <t>PHLOGIN GEL 20G</t>
+        </is>
+      </c>
+      <c r="E30" s="284" t="n">
         <v>19</v>
       </c>
-      <c r="F30" s="303" t="n">
-        <v>1085</v>
-      </c>
-      <c r="G30" s="303" t="n">
+      <c r="F30" s="285" t="n">
+        <v>6559</v>
+      </c>
+      <c r="G30" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="304">
+      <c r="H30" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F30)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I30" s="303">
+      <c r="I30" s="285">
         <f>G30-H30</f>
         <v/>
       </c>
-      <c r="J30" s="305">
+      <c r="J30" s="287">
         <f>IF(G30=0,"-",H30/G30)</f>
         <v/>
       </c>
-      <c r="K30" s="304" t="n"/>
-      <c r="L30" s="306" t="n"/>
+      <c r="K30" s="286" t="n"/>
+      <c r="L30" s="288" t="n"/>
       <c r="M30" s="151" t="n"/>
       <c r="N30" s="151" t="n"/>
       <c r="O30" s="151" t="n"/>
@@ -3863,44 +3861,44 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="254">
       <c r="A31" s="151" t="n"/>
-      <c r="B31" s="299" t="inlineStr">
+      <c r="B31" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C31" s="300" t="inlineStr">
+      <c r="C31" s="282" t="inlineStr">
         <is>
           <t>Brookes Pharma Private Limited</t>
         </is>
       </c>
-      <c r="D31" s="301" t="inlineStr">
-        <is>
-          <t>CONTRATUBEX GEL 20G</t>
-        </is>
-      </c>
-      <c r="E31" s="302" t="n">
+      <c r="D31" s="283" t="inlineStr">
+        <is>
+          <t>PYODINE GEL 20GM</t>
+        </is>
+      </c>
+      <c r="E31" s="284" t="n">
         <v>19</v>
       </c>
-      <c r="F31" s="303" t="n">
-        <v>6560</v>
-      </c>
-      <c r="G31" s="303" t="n">
+      <c r="F31" s="285" t="n">
+        <v>1085</v>
+      </c>
+      <c r="G31" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="304">
+      <c r="H31" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F31)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I31" s="303">
+      <c r="I31" s="285">
         <f>G31-H31</f>
         <v/>
       </c>
-      <c r="J31" s="305">
+      <c r="J31" s="287">
         <f>IF(G31=0,"-",H31/G31)</f>
         <v/>
       </c>
-      <c r="K31" s="304" t="n"/>
-      <c r="L31" s="306" t="n"/>
+      <c r="K31" s="286" t="n"/>
+      <c r="L31" s="288" t="n"/>
       <c r="M31" s="151" t="n"/>
       <c r="N31" s="151" t="n"/>
       <c r="O31" s="151" t="n"/>
@@ -3921,44 +3919,44 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" s="254">
       <c r="A32" s="151" t="n"/>
-      <c r="B32" s="299" t="inlineStr">
+      <c r="B32" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C32" s="300" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D32" s="301" t="inlineStr">
-        <is>
-          <t>S-43 DIA 20.5</t>
-        </is>
-      </c>
-      <c r="E32" s="302" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F32" s="303" t="n">
-        <v>5699</v>
-      </c>
-      <c r="G32" s="303" t="n">
+      <c r="C32" s="282" t="inlineStr">
+        <is>
+          <t>Brookes Pharma Private Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="283" t="inlineStr">
+        <is>
+          <t>CONTRATUBEX GEL 20G</t>
+        </is>
+      </c>
+      <c r="E32" s="284" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" s="285" t="n">
+        <v>6560</v>
+      </c>
+      <c r="G32" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="304">
+      <c r="H32" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F32)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I32" s="303">
+      <c r="I32" s="285">
         <f>G32-H32</f>
         <v/>
       </c>
-      <c r="J32" s="305">
+      <c r="J32" s="287">
         <f>IF(G32=0,"-",H32/G32)</f>
         <v/>
       </c>
-      <c r="K32" s="304" t="n"/>
-      <c r="L32" s="306" t="n"/>
+      <c r="K32" s="286" t="n"/>
+      <c r="L32" s="288" t="n"/>
       <c r="M32" s="151" t="n"/>
       <c r="N32" s="151" t="n"/>
       <c r="O32" s="151" t="n"/>
@@ -3979,44 +3977,44 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" s="254">
       <c r="A33" s="151" t="n"/>
-      <c r="B33" s="299" t="inlineStr">
+      <c r="B33" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C33" s="300" t="inlineStr">
-        <is>
-          <t>Mablay Beauty PVT LTD.</t>
-        </is>
-      </c>
-      <c r="D33" s="301" t="inlineStr">
-        <is>
-          <t>VINCE HIS ONLY BEARD &amp; MUSTACHE COLOR CREAM</t>
-        </is>
-      </c>
-      <c r="E33" s="302" t="n">
+      <c r="C33" s="282" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="283" t="inlineStr">
+        <is>
+          <t>S-43 DIA 20.5</t>
+        </is>
+      </c>
+      <c r="E33" s="284" t="n">
         <v>20.5</v>
       </c>
-      <c r="F33" s="303" t="n">
-        <v>6077</v>
-      </c>
-      <c r="G33" s="303" t="n">
+      <c r="F33" s="285" t="n">
+        <v>5699</v>
+      </c>
+      <c r="G33" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="304">
+      <c r="H33" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F33)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I33" s="303">
+      <c r="I33" s="285">
         <f>G33-H33</f>
         <v/>
       </c>
-      <c r="J33" s="305">
+      <c r="J33" s="287">
         <f>IF(G33=0,"-",H33/G33)</f>
         <v/>
       </c>
-      <c r="K33" s="304" t="n"/>
-      <c r="L33" s="306" t="n"/>
+      <c r="K33" s="286" t="n"/>
+      <c r="L33" s="288" t="n"/>
       <c r="M33" s="151" t="n"/>
       <c r="N33" s="151" t="n"/>
       <c r="O33" s="151" t="n"/>
@@ -4035,44 +4033,44 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" s="254">
       <c r="A34" s="151" t="n"/>
-      <c r="B34" s="299" t="inlineStr">
+      <c r="B34" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C34" s="300" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D34" s="301" t="inlineStr">
-        <is>
-          <t>S-45 DIA 20.5</t>
-        </is>
-      </c>
-      <c r="E34" s="302" t="n">
+      <c r="C34" s="282" t="inlineStr">
+        <is>
+          <t>Mablay Beauty PVT LTD.</t>
+        </is>
+      </c>
+      <c r="D34" s="283" t="inlineStr">
+        <is>
+          <t>VINCE HIS ONLY BEARD &amp; MUSTACHE COLOR CREAM</t>
+        </is>
+      </c>
+      <c r="E34" s="284" t="n">
         <v>20.5</v>
       </c>
-      <c r="F34" s="303" t="n">
-        <v>5698</v>
-      </c>
-      <c r="G34" s="303" t="n">
+      <c r="F34" s="285" t="n">
+        <v>6077</v>
+      </c>
+      <c r="G34" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="304">
+      <c r="H34" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F34)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I34" s="303">
+      <c r="I34" s="285">
         <f>G34-H34</f>
         <v/>
       </c>
-      <c r="J34" s="305">
+      <c r="J34" s="287">
         <f>IF(G34=0,"-",H34/G34)</f>
         <v/>
       </c>
-      <c r="K34" s="304" t="n"/>
-      <c r="L34" s="306" t="n"/>
+      <c r="K34" s="286" t="n"/>
+      <c r="L34" s="288" t="n"/>
       <c r="M34" s="151" t="n"/>
       <c r="N34" s="151" t="n"/>
       <c r="O34" s="151" t="n"/>
@@ -4091,44 +4089,44 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" s="254">
       <c r="A35" s="151" t="n"/>
-      <c r="B35" s="299" t="inlineStr">
+      <c r="B35" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C35" s="300" t="inlineStr">
+      <c r="C35" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D35" s="301" t="inlineStr">
-        <is>
-          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
-        </is>
-      </c>
-      <c r="E35" s="302" t="n">
+      <c r="D35" s="283" t="inlineStr">
+        <is>
+          <t>S-45 DIA 20.5</t>
+        </is>
+      </c>
+      <c r="E35" s="284" t="n">
         <v>20.5</v>
       </c>
-      <c r="F35" s="303" t="n">
-        <v>5731</v>
-      </c>
-      <c r="G35" s="303" t="n">
+      <c r="F35" s="285" t="n">
+        <v>5698</v>
+      </c>
+      <c r="G35" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="304">
+      <c r="H35" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F35)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I35" s="303">
+      <c r="I35" s="285">
         <f>G35-H35</f>
         <v/>
       </c>
-      <c r="J35" s="305">
+      <c r="J35" s="287">
         <f>IF(G35=0,"-",H35/G35)</f>
         <v/>
       </c>
-      <c r="K35" s="304" t="n"/>
-      <c r="L35" s="306" t="n"/>
+      <c r="K35" s="286" t="n"/>
+      <c r="L35" s="288" t="n"/>
       <c r="M35" s="151" t="n"/>
       <c r="N35" s="151" t="n"/>
       <c r="O35" s="151" t="n"/>
@@ -4147,44 +4145,44 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" s="254">
       <c r="A36" s="151" t="n"/>
-      <c r="B36" s="299" t="inlineStr">
+      <c r="B36" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C36" s="300" t="inlineStr">
+      <c r="C36" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D36" s="301" t="inlineStr">
-        <is>
-          <t>SAMSOL HAIR COLOR 43 DIA 20.5 MM</t>
-        </is>
-      </c>
-      <c r="E36" s="302" t="n">
+      <c r="D36" s="283" t="inlineStr">
+        <is>
+          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
+        </is>
+      </c>
+      <c r="E36" s="284" t="n">
         <v>20.5</v>
       </c>
-      <c r="F36" s="303" t="n">
-        <v>5732</v>
-      </c>
-      <c r="G36" s="303" t="n">
+      <c r="F36" s="285" t="n">
+        <v>5731</v>
+      </c>
+      <c r="G36" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="304">
+      <c r="H36" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F36)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I36" s="303">
+      <c r="I36" s="285">
         <f>G36-H36</f>
         <v/>
       </c>
-      <c r="J36" s="305">
+      <c r="J36" s="287">
         <f>IF(G36=0,"-",H36/G36)</f>
         <v/>
       </c>
-      <c r="K36" s="304" t="n"/>
-      <c r="L36" s="306" t="n"/>
+      <c r="K36" s="286" t="n"/>
+      <c r="L36" s="288" t="n"/>
       <c r="P36" s="151" t="n"/>
       <c r="Q36" s="151" t="n"/>
       <c r="R36" s="151" t="n"/>
@@ -4212,44 +4210,44 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="254">
       <c r="A37" s="151" t="n"/>
-      <c r="B37" s="299" t="inlineStr">
+      <c r="B37" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C37" s="300" t="inlineStr">
+      <c r="C37" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D37" s="301" t="inlineStr">
-        <is>
-          <t>SAMSOL HAIR COLOR 39 SMALL PURPLE</t>
-        </is>
-      </c>
-      <c r="E37" s="302" t="n">
+      <c r="D37" s="283" t="inlineStr">
+        <is>
+          <t>SAMSOL HAIR COLOR 43 DIA 20.5 MM</t>
+        </is>
+      </c>
+      <c r="E37" s="284" t="n">
         <v>20.5</v>
       </c>
-      <c r="F37" s="303" t="n">
-        <v>6556</v>
-      </c>
-      <c r="G37" s="303" t="n">
+      <c r="F37" s="285" t="n">
+        <v>5732</v>
+      </c>
+      <c r="G37" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="304">
+      <c r="H37" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F37)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I37" s="303">
+      <c r="I37" s="285">
         <f>G37-H37</f>
         <v/>
       </c>
-      <c r="J37" s="305">
+      <c r="J37" s="287">
         <f>IF(G37=0,"-",H37/G37)</f>
         <v/>
       </c>
-      <c r="K37" s="304" t="n"/>
-      <c r="L37" s="306" t="n"/>
+      <c r="K37" s="286" t="n"/>
+      <c r="L37" s="288" t="n"/>
       <c r="M37" s="151" t="n"/>
       <c r="N37" s="151" t="n"/>
       <c r="O37" s="151" t="n"/>
@@ -4270,44 +4268,44 @@
     </row>
     <row r="38" ht="16.5" customHeight="1" s="254">
       <c r="A38" s="151" t="n"/>
-      <c r="B38" s="299" t="inlineStr">
+      <c r="B38" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C38" s="300" t="inlineStr">
+      <c r="C38" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D38" s="301" t="inlineStr">
-        <is>
-          <t>SAMSOL HAIR COLOR 41 SMALL PURPLE</t>
-        </is>
-      </c>
-      <c r="E38" s="302" t="n">
+      <c r="D38" s="283" t="inlineStr">
+        <is>
+          <t>SAMSOL HAIR COLOR 39 SMALL PURPLE</t>
+        </is>
+      </c>
+      <c r="E38" s="284" t="n">
         <v>20.5</v>
       </c>
-      <c r="F38" s="303" t="n">
-        <v>6557</v>
-      </c>
-      <c r="G38" s="303" t="n">
+      <c r="F38" s="285" t="n">
+        <v>6556</v>
+      </c>
+      <c r="G38" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="304">
+      <c r="H38" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F38)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I38" s="303">
+      <c r="I38" s="285">
         <f>G38-H38</f>
         <v/>
       </c>
-      <c r="J38" s="305">
+      <c r="J38" s="287">
         <f>IF(G38=0,"-",H38/G38)</f>
         <v/>
       </c>
-      <c r="K38" s="304" t="n"/>
-      <c r="L38" s="306" t="n"/>
+      <c r="K38" s="286" t="n"/>
+      <c r="L38" s="288" t="n"/>
       <c r="M38" s="151" t="n"/>
       <c r="N38" s="151" t="n"/>
       <c r="O38" s="151" t="n"/>
@@ -4328,44 +4326,44 @@
     </row>
     <row r="39" ht="16.5" customHeight="1" s="254">
       <c r="A39" s="151" t="n"/>
-      <c r="B39" s="299" t="inlineStr">
+      <c r="B39" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C39" s="300" t="inlineStr">
-        <is>
-          <t>Habib Hanif Inc</t>
-        </is>
-      </c>
-      <c r="D39" s="301" t="inlineStr">
-        <is>
-          <t>S-45</t>
-        </is>
-      </c>
-      <c r="E39" s="302" t="n">
-        <v>25</v>
-      </c>
-      <c r="F39" s="303" t="n">
-        <v>5389</v>
-      </c>
-      <c r="G39" s="303" t="n">
+      <c r="C39" s="282" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="283" t="inlineStr">
+        <is>
+          <t>SAMSOL HAIR COLOR 41 SMALL PURPLE</t>
+        </is>
+      </c>
+      <c r="E39" s="284" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F39" s="285" t="n">
+        <v>6557</v>
+      </c>
+      <c r="G39" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="304">
+      <c r="H39" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F39)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I39" s="303">
+      <c r="I39" s="285">
         <f>G39-H39</f>
         <v/>
       </c>
-      <c r="J39" s="305">
+      <c r="J39" s="287">
         <f>IF(G39=0,"-",H39/G39)</f>
         <v/>
       </c>
-      <c r="K39" s="304" t="n"/>
-      <c r="L39" s="306" t="n"/>
+      <c r="K39" s="286" t="n"/>
+      <c r="L39" s="288" t="n"/>
       <c r="M39" s="151" t="n"/>
       <c r="N39" s="151" t="n"/>
       <c r="O39" s="151" t="n"/>
@@ -4386,44 +4384,44 @@
     </row>
     <row r="40" ht="16.5" customHeight="1" s="254">
       <c r="A40" s="151" t="n"/>
-      <c r="B40" s="299" t="inlineStr">
+      <c r="B40" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C40" s="300" t="inlineStr">
+      <c r="C40" s="282" t="inlineStr">
         <is>
           <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
-      <c r="D40" s="301" t="inlineStr">
+      <c r="D40" s="283" t="inlineStr">
         <is>
           <t>HIS ONLY HAIR COLOR CREAM 40GM</t>
         </is>
       </c>
-      <c r="E40" s="302" t="n">
+      <c r="E40" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F40" s="303" t="n">
+      <c r="F40" s="285" t="n">
         <v>6228</v>
       </c>
-      <c r="G40" s="303" t="n">
+      <c r="G40" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="304">
+      <c r="H40" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F40)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I40" s="303">
+      <c r="I40" s="285">
         <f>G40-H40</f>
         <v/>
       </c>
-      <c r="J40" s="305">
+      <c r="J40" s="287">
         <f>IF(G40=0,"-",H40/G40)</f>
         <v/>
       </c>
-      <c r="K40" s="304" t="n"/>
-      <c r="L40" s="306" t="n"/>
+      <c r="K40" s="286" t="n"/>
+      <c r="L40" s="288" t="n"/>
       <c r="M40" s="151" t="n"/>
       <c r="N40" s="151" t="n"/>
       <c r="O40" s="151" t="n"/>
@@ -4444,44 +4442,44 @@
     </row>
     <row r="41" ht="16.5" customHeight="1" s="254">
       <c r="A41" s="151" t="n"/>
-      <c r="B41" s="299" t="inlineStr">
+      <c r="B41" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C41" s="300" t="inlineStr">
+      <c r="C41" s="282" t="inlineStr">
         <is>
           <t>DTM</t>
         </is>
       </c>
-      <c r="D41" s="301" t="inlineStr">
+      <c r="D41" s="283" t="inlineStr">
         <is>
           <t>DTM DIA 25MM</t>
         </is>
       </c>
-      <c r="E41" s="302" t="n">
+      <c r="E41" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F41" s="303" t="n">
+      <c r="F41" s="285" t="n">
         <v>6338</v>
       </c>
-      <c r="G41" s="303" t="n">
+      <c r="G41" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="304">
+      <c r="H41" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F41)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I41" s="303">
+      <c r="I41" s="285">
         <f>G41-H41</f>
         <v/>
       </c>
-      <c r="J41" s="305">
+      <c r="J41" s="287">
         <f>IF(G41=0,"-",H41/G41)</f>
         <v/>
       </c>
-      <c r="K41" s="304" t="n"/>
-      <c r="L41" s="306" t="n"/>
+      <c r="K41" s="286" t="n"/>
+      <c r="L41" s="288" t="n"/>
       <c r="M41" s="151" t="n"/>
       <c r="N41" s="151" t="n"/>
       <c r="O41" s="151" t="n"/>
@@ -4502,44 +4500,44 @@
     </row>
     <row r="42" ht="16.5" customHeight="1" s="254">
       <c r="A42" s="151" t="n"/>
-      <c r="B42" s="299" t="inlineStr">
+      <c r="B42" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C42" s="300" t="inlineStr">
+      <c r="C42" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D42" s="301" t="inlineStr">
+      <c r="D42" s="283" t="inlineStr">
         <is>
           <t>TUBES MEN BLUE</t>
         </is>
       </c>
-      <c r="E42" s="302" t="n">
+      <c r="E42" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F42" s="303" t="n">
+      <c r="F42" s="285" t="n">
         <v>6506</v>
       </c>
-      <c r="G42" s="303" t="n">
+      <c r="G42" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="304">
+      <c r="H42" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F42)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I42" s="303">
+      <c r="I42" s="285">
         <f>G42-H42</f>
         <v/>
       </c>
-      <c r="J42" s="305">
+      <c r="J42" s="287">
         <f>IF(G42=0,"-",H42/G42)</f>
         <v/>
       </c>
-      <c r="K42" s="304" t="n"/>
-      <c r="L42" s="306" t="n"/>
+      <c r="K42" s="286" t="n"/>
+      <c r="L42" s="288" t="n"/>
       <c r="M42" s="151" t="n"/>
       <c r="N42" s="151" t="n"/>
       <c r="O42" s="151" t="n"/>
@@ -4560,44 +4558,44 @@
     </row>
     <row r="43" ht="16.5" customHeight="1" s="254">
       <c r="A43" s="151" t="n"/>
-      <c r="B43" s="299" t="inlineStr">
+      <c r="B43" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C43" s="300" t="inlineStr">
+      <c r="C43" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D43" s="301" t="inlineStr">
+      <c r="D43" s="283" t="inlineStr">
         <is>
           <t>SAMSOL RED 25MM</t>
         </is>
       </c>
-      <c r="E43" s="302" t="n">
+      <c r="E43" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F43" s="303" t="n">
+      <c r="F43" s="285" t="n">
         <v>9006</v>
       </c>
-      <c r="G43" s="303" t="n">
+      <c r="G43" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="304">
+      <c r="H43" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F43)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I43" s="303">
+      <c r="I43" s="285">
         <f>G43-H43</f>
         <v/>
       </c>
-      <c r="J43" s="305">
+      <c r="J43" s="287">
         <f>IF(G43=0,"-",H43/G43)</f>
         <v/>
       </c>
-      <c r="K43" s="304" t="n"/>
-      <c r="L43" s="306" t="n"/>
+      <c r="K43" s="286" t="n"/>
+      <c r="L43" s="288" t="n"/>
       <c r="M43" s="151" t="n"/>
       <c r="N43" s="151" t="n"/>
       <c r="O43" s="151" t="n"/>
@@ -4618,44 +4616,44 @@
     </row>
     <row r="44" ht="16.5" customHeight="1" s="254">
       <c r="A44" s="151" t="n"/>
-      <c r="B44" s="299" t="inlineStr">
+      <c r="B44" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C44" s="300" t="inlineStr">
+      <c r="C44" s="282" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (Pvt) Ltd</t>
         </is>
       </c>
-      <c r="D44" s="301" t="inlineStr">
+      <c r="D44" s="283" t="inlineStr">
         <is>
           <t>BELINI HAIR COLOR 50ML</t>
         </is>
       </c>
-      <c r="E44" s="302" t="n">
+      <c r="E44" s="284" t="n">
         <v>25</v>
       </c>
-      <c r="F44" s="303" t="n">
+      <c r="F44" s="285" t="n">
         <v>4227</v>
       </c>
-      <c r="G44" s="303" t="n">
+      <c r="G44" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="304">
+      <c r="H44" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F44)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I44" s="303">
+      <c r="I44" s="285">
         <f>G44-H44</f>
         <v/>
       </c>
-      <c r="J44" s="305">
+      <c r="J44" s="287">
         <f>IF(G44=0,"-",H44/G44)</f>
         <v/>
       </c>
-      <c r="K44" s="304" t="n"/>
-      <c r="L44" s="306" t="n"/>
+      <c r="K44" s="286" t="n"/>
+      <c r="L44" s="288" t="n"/>
       <c r="M44" s="151" t="n"/>
       <c r="N44" s="151" t="n"/>
       <c r="O44" s="151" t="n"/>
@@ -4676,44 +4674,44 @@
     </row>
     <row r="45" ht="16.5" customHeight="1" s="254">
       <c r="A45" s="151" t="n"/>
-      <c r="B45" s="299" t="inlineStr">
+      <c r="B45" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C45" s="300" t="inlineStr">
+      <c r="C45" s="282" t="inlineStr">
         <is>
           <t>Seatle (Private) Limited</t>
         </is>
       </c>
-      <c r="D45" s="301" t="inlineStr">
+      <c r="D45" s="283" t="inlineStr">
         <is>
           <t>DOWFEN GEL 50G</t>
         </is>
       </c>
-      <c r="E45" s="302" t="n">
+      <c r="E45" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F45" s="303" t="n">
+      <c r="F45" s="285" t="n">
         <v>6595</v>
       </c>
-      <c r="G45" s="303" t="n">
+      <c r="G45" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="304">
+      <c r="H45" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F45)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I45" s="303">
+      <c r="I45" s="285">
         <f>G45-H45</f>
         <v/>
       </c>
-      <c r="J45" s="305">
+      <c r="J45" s="287">
         <f>IF(G45=0,"-",H45/G45)</f>
         <v/>
       </c>
-      <c r="K45" s="304" t="n"/>
-      <c r="L45" s="306" t="n"/>
+      <c r="K45" s="286" t="n"/>
+      <c r="L45" s="288" t="n"/>
       <c r="M45" s="151" t="n"/>
       <c r="N45" s="151" t="n"/>
       <c r="O45" s="151" t="n"/>
@@ -4734,44 +4732,44 @@
     </row>
     <row r="46" ht="16.5" customHeight="1" s="254">
       <c r="A46" s="151" t="n"/>
-      <c r="B46" s="299" t="inlineStr">
+      <c r="B46" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C46" s="300" t="inlineStr">
+      <c r="C46" s="282" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D46" s="301" t="inlineStr">
+      <c r="D46" s="283" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E46" s="302" t="n">
+      <c r="E46" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F46" s="303" t="n">
+      <c r="F46" s="285" t="n">
         <v>6416</v>
       </c>
-      <c r="G46" s="303" t="n">
+      <c r="G46" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="304">
+      <c r="H46" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F46)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I46" s="303">
+      <c r="I46" s="285">
         <f>G46-H46</f>
         <v/>
       </c>
-      <c r="J46" s="305">
+      <c r="J46" s="287">
         <f>IF(G46=0,"-",H46/G46)</f>
         <v/>
       </c>
-      <c r="K46" s="304" t="n"/>
-      <c r="L46" s="306" t="n"/>
+      <c r="K46" s="286" t="n"/>
+      <c r="L46" s="288" t="n"/>
       <c r="M46" s="151" t="n"/>
       <c r="N46" s="151" t="n"/>
       <c r="O46" s="151" t="n"/>
@@ -4792,44 +4790,44 @@
     </row>
     <row r="47" ht="16.5" customHeight="1" s="254">
       <c r="A47" s="151" t="n"/>
-      <c r="B47" s="299" t="inlineStr">
+      <c r="B47" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C47" s="300" t="inlineStr">
+      <c r="C47" s="282" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D47" s="301" t="inlineStr">
+      <c r="D47" s="283" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E47" s="302" t="n">
+      <c r="E47" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F47" s="303" t="n">
+      <c r="F47" s="285" t="n">
         <v>6337</v>
       </c>
-      <c r="G47" s="303" t="n">
+      <c r="G47" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="304">
+      <c r="H47" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F47)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I47" s="303">
+      <c r="I47" s="285">
         <f>G47-H47</f>
         <v/>
       </c>
-      <c r="J47" s="305">
+      <c r="J47" s="287">
         <f>IF(G47=0,"-",H47/G47)</f>
         <v/>
       </c>
-      <c r="K47" s="304" t="n"/>
-      <c r="L47" s="306" t="n"/>
+      <c r="K47" s="286" t="n"/>
+      <c r="L47" s="288" t="n"/>
       <c r="M47" s="151" t="n"/>
       <c r="N47" s="151" t="n"/>
       <c r="O47" s="151" t="n"/>
@@ -4850,44 +4848,44 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" s="254">
       <c r="A48" s="151" t="n"/>
-      <c r="B48" s="299" t="inlineStr">
+      <c r="B48" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C48" s="300" t="inlineStr">
+      <c r="C48" s="282" t="inlineStr">
         <is>
           <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
-      <c r="D48" s="301" t="inlineStr">
+      <c r="D48" s="283" t="inlineStr">
         <is>
           <t>VINCE NURTURAL (Varnish)</t>
         </is>
       </c>
-      <c r="E48" s="302" t="n">
+      <c r="E48" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F48" s="303" t="n">
+      <c r="F48" s="285" t="n">
         <v>9002</v>
       </c>
-      <c r="G48" s="303" t="n">
+      <c r="G48" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="304">
+      <c r="H48" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F48)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I48" s="303">
+      <c r="I48" s="285">
         <f>G48-H48</f>
         <v/>
       </c>
-      <c r="J48" s="305">
+      <c r="J48" s="287">
         <f>IF(G48=0,"-",H48/G48)</f>
         <v/>
       </c>
-      <c r="K48" s="304" t="n"/>
-      <c r="L48" s="306" t="n"/>
+      <c r="K48" s="286" t="n"/>
+      <c r="L48" s="288" t="n"/>
       <c r="M48" s="151" t="n"/>
       <c r="N48" s="151" t="n"/>
       <c r="O48" s="151" t="n"/>
@@ -4908,44 +4906,44 @@
     </row>
     <row r="49" ht="16.5" customHeight="1" s="254">
       <c r="A49" s="151" t="n"/>
-      <c r="B49" s="299" t="inlineStr">
+      <c r="B49" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C49" s="300" t="inlineStr">
+      <c r="C49" s="282" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D49" s="301" t="inlineStr">
+      <c r="D49" s="283" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E49" s="302" t="n">
+      <c r="E49" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F49" s="303" t="n">
+      <c r="F49" s="285" t="n">
         <v>4050</v>
       </c>
-      <c r="G49" s="303" t="n">
+      <c r="G49" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="304">
+      <c r="H49" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F49)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I49" s="303">
+      <c r="I49" s="285">
         <f>G49-H49</f>
         <v/>
       </c>
-      <c r="J49" s="305">
+      <c r="J49" s="287">
         <f>IF(G49=0,"-",H49/G49)</f>
         <v/>
       </c>
-      <c r="K49" s="304" t="n"/>
-      <c r="L49" s="306" t="n"/>
+      <c r="K49" s="286" t="n"/>
+      <c r="L49" s="288" t="n"/>
       <c r="M49" s="151" t="n"/>
       <c r="N49" s="151" t="n"/>
       <c r="O49" s="151" t="n"/>
@@ -4966,44 +4964,44 @@
     </row>
     <row r="50" ht="16.5" customHeight="1" s="254">
       <c r="A50" s="151" t="n"/>
-      <c r="B50" s="299" t="inlineStr">
+      <c r="B50" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C50" s="300" t="inlineStr">
+      <c r="C50" s="282" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D50" s="301" t="inlineStr">
+      <c r="D50" s="283" t="inlineStr">
         <is>
           <t>HIBA S HAIR COLOR 60ML</t>
         </is>
       </c>
-      <c r="E50" s="302" t="n">
+      <c r="E50" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F50" s="303" t="n">
+      <c r="F50" s="285" t="n">
         <v>6312</v>
       </c>
-      <c r="G50" s="303" t="n">
+      <c r="G50" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="304">
+      <c r="H50" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F50)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I50" s="303">
+      <c r="I50" s="285">
         <f>G50-H50</f>
         <v/>
       </c>
-      <c r="J50" s="305">
+      <c r="J50" s="287">
         <f>IF(G50=0,"-",H50/G50)</f>
         <v/>
       </c>
-      <c r="K50" s="304" t="n"/>
-      <c r="L50" s="306" t="n"/>
+      <c r="K50" s="286" t="n"/>
+      <c r="L50" s="288" t="n"/>
       <c r="M50" s="151" t="n"/>
       <c r="N50" s="151" t="n"/>
       <c r="O50" s="151" t="n"/>
@@ -5024,44 +5022,44 @@
     </row>
     <row r="51" ht="16.5" customHeight="1" s="254">
       <c r="A51" s="151" t="n"/>
-      <c r="B51" s="299" t="inlineStr">
+      <c r="B51" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C51" s="300" t="inlineStr">
+      <c r="C51" s="282" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D51" s="301" t="inlineStr">
+      <c r="D51" s="283" t="inlineStr">
         <is>
           <t>EAZI COLOR PERMANENT HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E51" s="302" t="n">
+      <c r="E51" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F51" s="303" t="n">
+      <c r="F51" s="285" t="n">
         <v>2909</v>
       </c>
-      <c r="G51" s="303" t="n">
+      <c r="G51" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="304">
+      <c r="H51" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F51)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I51" s="303">
+      <c r="I51" s="285">
         <f>G51-H51</f>
         <v/>
       </c>
-      <c r="J51" s="305">
+      <c r="J51" s="287">
         <f>IF(G51=0,"-",H51/G51)</f>
         <v/>
       </c>
-      <c r="K51" s="304" t="n"/>
-      <c r="L51" s="306" t="n"/>
+      <c r="K51" s="286" t="n"/>
+      <c r="L51" s="288" t="n"/>
       <c r="M51" s="151" t="n"/>
       <c r="N51" s="151" t="n"/>
       <c r="O51" s="151" t="n"/>
@@ -5082,44 +5080,44 @@
     </row>
     <row r="52" ht="16.5" customHeight="1" s="254">
       <c r="A52" s="151" t="n"/>
-      <c r="B52" s="299" t="inlineStr">
+      <c r="B52" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C52" s="300" t="inlineStr">
+      <c r="C52" s="282" t="inlineStr">
         <is>
           <t>Mateen Sons</t>
         </is>
       </c>
-      <c r="D52" s="301" t="inlineStr">
+      <c r="D52" s="283" t="inlineStr">
         <is>
           <t>GP DIA 30MM</t>
         </is>
       </c>
-      <c r="E52" s="302" t="n">
+      <c r="E52" s="284" t="n">
         <v>30</v>
       </c>
-      <c r="F52" s="303" t="n">
+      <c r="F52" s="285" t="n">
         <v>6151</v>
       </c>
-      <c r="G52" s="303" t="n">
+      <c r="G52" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="304">
+      <c r="H52" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F52)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I52" s="303">
+      <c r="I52" s="285">
         <f>G52-H52</f>
         <v/>
       </c>
-      <c r="J52" s="305">
+      <c r="J52" s="287">
         <f>IF(G52=0,"-",H52/G52)</f>
         <v/>
       </c>
-      <c r="K52" s="304" t="n"/>
-      <c r="L52" s="306" t="n"/>
+      <c r="K52" s="286" t="n"/>
+      <c r="L52" s="288" t="n"/>
       <c r="M52" s="151" t="n"/>
       <c r="N52" s="151" t="n"/>
       <c r="O52" s="151" t="n"/>
@@ -5140,44 +5138,44 @@
     </row>
     <row r="53" ht="16.5" customHeight="1" s="254">
       <c r="A53" s="151" t="n"/>
-      <c r="B53" s="299" t="inlineStr">
+      <c r="B53" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C53" s="300" t="inlineStr">
+      <c r="C53" s="282" t="inlineStr">
         <is>
           <t>Hola Hair</t>
         </is>
       </c>
-      <c r="D53" s="301" t="inlineStr">
+      <c r="D53" s="283" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E53" s="302" t="n">
+      <c r="E53" s="284" t="n">
         <v>32</v>
       </c>
-      <c r="F53" s="303" t="n">
+      <c r="F53" s="285" t="n">
         <v>6515</v>
       </c>
-      <c r="G53" s="303" t="n">
+      <c r="G53" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="304">
+      <c r="H53" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F53)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I53" s="303">
+      <c r="I53" s="285">
         <f>G53-H53</f>
         <v/>
       </c>
-      <c r="J53" s="305">
+      <c r="J53" s="287">
         <f>IF(G53=0,"-",H53/G53)</f>
         <v/>
       </c>
-      <c r="K53" s="304" t="n"/>
-      <c r="L53" s="306" t="n"/>
+      <c r="K53" s="286" t="n"/>
+      <c r="L53" s="288" t="n"/>
       <c r="M53" s="151" t="n"/>
       <c r="N53" s="151" t="n"/>
       <c r="O53" s="151" t="n"/>
@@ -5198,44 +5196,44 @@
     </row>
     <row r="54" ht="16.5" customHeight="1" s="254">
       <c r="A54" s="151" t="n"/>
-      <c r="B54" s="299" t="inlineStr">
+      <c r="B54" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C54" s="300" t="inlineStr">
+      <c r="C54" s="282" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D54" s="301" t="inlineStr">
+      <c r="D54" s="283" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E54" s="302" t="n">
+      <c r="E54" s="284" t="n">
         <v>32</v>
       </c>
-      <c r="F54" s="303" t="n">
+      <c r="F54" s="285" t="n">
         <v>5782</v>
       </c>
-      <c r="G54" s="303" t="n">
+      <c r="G54" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="304">
+      <c r="H54" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F54)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I54" s="303">
+      <c r="I54" s="285">
         <f>G54-H54</f>
         <v/>
       </c>
-      <c r="J54" s="305">
+      <c r="J54" s="287">
         <f>IF(G54=0,"-",H54/G54)</f>
         <v/>
       </c>
-      <c r="K54" s="304" t="n"/>
-      <c r="L54" s="306" t="n"/>
+      <c r="K54" s="286" t="n"/>
+      <c r="L54" s="288" t="n"/>
       <c r="M54" s="151" t="n"/>
       <c r="N54" s="151" t="n"/>
       <c r="O54" s="151" t="n"/>
@@ -5256,44 +5254,44 @@
     </row>
     <row r="55" ht="16.5" customHeight="1" s="254">
       <c r="A55" s="151" t="n"/>
-      <c r="B55" s="299" t="inlineStr">
+      <c r="B55" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C55" s="300" t="inlineStr">
+      <c r="C55" s="282" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D55" s="301" t="inlineStr">
+      <c r="D55" s="283" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E55" s="302" t="n">
+      <c r="E55" s="284" t="n">
         <v>35</v>
       </c>
-      <c r="F55" s="303" t="n">
+      <c r="F55" s="285" t="n">
         <v>6531</v>
       </c>
-      <c r="G55" s="303" t="n">
+      <c r="G55" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="304">
+      <c r="H55" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F55)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I55" s="303">
+      <c r="I55" s="285">
         <f>G55-H55</f>
         <v/>
       </c>
-      <c r="J55" s="305">
+      <c r="J55" s="287">
         <f>IF(G55=0,"-",H55/G55)</f>
         <v/>
       </c>
-      <c r="K55" s="304" t="n"/>
-      <c r="L55" s="306" t="n"/>
+      <c r="K55" s="286" t="n"/>
+      <c r="L55" s="288" t="n"/>
       <c r="P55" s="151" t="n"/>
       <c r="Q55" s="151" t="n"/>
       <c r="R55" s="151" t="n"/>
@@ -5309,44 +5307,44 @@
     </row>
     <row r="56" ht="16.5" customHeight="1" s="254">
       <c r="A56" s="151" t="n"/>
-      <c r="B56" s="299" t="inlineStr">
+      <c r="B56" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C56" s="300" t="inlineStr">
+      <c r="C56" s="282" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D56" s="301" t="inlineStr">
+      <c r="D56" s="283" t="inlineStr">
         <is>
           <t>ANVIL 43</t>
         </is>
       </c>
-      <c r="E56" s="302" t="n">
+      <c r="E56" s="284" t="n">
         <v>35</v>
       </c>
-      <c r="F56" s="303" t="n">
+      <c r="F56" s="285" t="n">
         <v>6020</v>
       </c>
-      <c r="G56" s="303" t="n">
+      <c r="G56" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="304">
+      <c r="H56" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F56)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I56" s="303">
+      <c r="I56" s="285">
         <f>G56-H56</f>
         <v/>
       </c>
-      <c r="J56" s="305">
+      <c r="J56" s="287">
         <f>IF(G56=0,"-",H56/G56)</f>
         <v/>
       </c>
-      <c r="K56" s="304" t="n"/>
-      <c r="L56" s="306" t="n"/>
+      <c r="K56" s="286" t="n"/>
+      <c r="L56" s="288" t="n"/>
       <c r="M56" s="151" t="n"/>
       <c r="N56" s="151" t="n"/>
       <c r="O56" s="151" t="n"/>
@@ -5367,44 +5365,44 @@
     </row>
     <row r="57" ht="16.5" customHeight="1" s="254">
       <c r="A57" s="151" t="n"/>
-      <c r="B57" s="299" t="inlineStr">
+      <c r="B57" s="281" t="inlineStr">
         <is>
           <t>TUBE</t>
         </is>
       </c>
-      <c r="C57" s="300" t="inlineStr">
+      <c r="C57" s="282" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D57" s="301" t="inlineStr">
+      <c r="D57" s="283" t="inlineStr">
         <is>
           <t>ANVIL 45</t>
         </is>
       </c>
-      <c r="E57" s="302" t="n">
+      <c r="E57" s="284" t="n">
         <v>35</v>
       </c>
-      <c r="F57" s="303" t="n">
+      <c r="F57" s="285" t="n">
         <v>6021</v>
       </c>
-      <c r="G57" s="303" t="n">
+      <c r="G57" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="304">
+      <c r="H57" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F57)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I57" s="303">
+      <c r="I57" s="285">
         <f>G57-H57</f>
         <v/>
       </c>
-      <c r="J57" s="305">
+      <c r="J57" s="287">
         <f>IF(G57=0,"-",H57/G57)</f>
         <v/>
       </c>
-      <c r="K57" s="304" t="n"/>
-      <c r="L57" s="306" t="n"/>
+      <c r="K57" s="286" t="n"/>
+      <c r="L57" s="288" t="n"/>
       <c r="M57" s="151" t="n"/>
       <c r="N57" s="151" t="n"/>
       <c r="O57" s="151" t="n"/>
@@ -5425,46 +5423,46 @@
     </row>
     <row r="58" ht="16.5" customHeight="1" s="254">
       <c r="A58" s="151" t="n"/>
-      <c r="B58" s="299" t="inlineStr">
+      <c r="B58" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C58" s="300" t="inlineStr">
+      <c r="C58" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D58" s="301" t="inlineStr">
+      <c r="D58" s="283" t="inlineStr">
         <is>
           <t>BLACK SMALL BOTTLE 120ML</t>
         </is>
       </c>
-      <c r="E58" s="302" t="inlineStr">
+      <c r="E58" s="284" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="F58" s="303" t="n">
+      <c r="F58" s="285" t="n">
         <v>8011</v>
       </c>
-      <c r="G58" s="303" t="n">
+      <c r="G58" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="304">
+      <c r="H58" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F58)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I58" s="303">
+      <c r="I58" s="285">
         <f>G58-H58</f>
         <v/>
       </c>
-      <c r="J58" s="305">
+      <c r="J58" s="287">
         <f>IF(G58=0,"-",H58/G58)</f>
         <v/>
       </c>
-      <c r="K58" s="304" t="n"/>
-      <c r="L58" s="306" t="n"/>
+      <c r="K58" s="286" t="n"/>
+      <c r="L58" s="288" t="n"/>
       <c r="M58" s="151" t="n"/>
       <c r="N58" s="151" t="n"/>
       <c r="O58" s="151" t="n"/>
@@ -5485,46 +5483,46 @@
     </row>
     <row r="59" ht="16.5" customHeight="1" s="254">
       <c r="A59" s="151" t="n"/>
-      <c r="B59" s="299" t="inlineStr">
+      <c r="B59" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C59" s="300" t="inlineStr">
+      <c r="C59" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D59" s="301" t="inlineStr">
+      <c r="D59" s="283" t="inlineStr">
         <is>
           <t>WHITE SMALL BOTTLE 120ML</t>
         </is>
       </c>
-      <c r="E59" s="302" t="inlineStr">
+      <c r="E59" s="284" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="F59" s="303" t="n">
+      <c r="F59" s="285" t="n">
         <v>8012</v>
       </c>
-      <c r="G59" s="303" t="n">
+      <c r="G59" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="304">
+      <c r="H59" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F59)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I59" s="303">
+      <c r="I59" s="285">
         <f>G59-H59</f>
         <v/>
       </c>
-      <c r="J59" s="305">
+      <c r="J59" s="287">
         <f>IF(G59=0,"-",H59/G59)</f>
         <v/>
       </c>
-      <c r="K59" s="304" t="n"/>
-      <c r="L59" s="306" t="n"/>
+      <c r="K59" s="286" t="n"/>
+      <c r="L59" s="288" t="n"/>
       <c r="M59" s="151" t="n"/>
       <c r="N59" s="151" t="n"/>
       <c r="O59" s="151" t="n"/>
@@ -5545,46 +5543,46 @@
     </row>
     <row r="60" ht="15" customHeight="1" s="254">
       <c r="A60" s="151" t="n"/>
-      <c r="B60" s="299" t="inlineStr">
+      <c r="B60" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C60" s="300" t="inlineStr">
+      <c r="C60" s="282" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D60" s="301" t="inlineStr">
+      <c r="D60" s="283" t="inlineStr">
         <is>
           <t>PET BOTTLE SMALL (130ML) TRANSPARENT</t>
         </is>
       </c>
-      <c r="E60" s="302" t="inlineStr">
+      <c r="E60" s="284" t="inlineStr">
         <is>
           <t>130 ml</t>
         </is>
       </c>
-      <c r="F60" s="303" t="n">
+      <c r="F60" s="285" t="n">
         <v>8010</v>
       </c>
-      <c r="G60" s="303" t="n">
+      <c r="G60" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="304">
+      <c r="H60" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F60)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I60" s="303">
+      <c r="I60" s="285">
         <f>G60-H60</f>
         <v/>
       </c>
-      <c r="J60" s="305">
+      <c r="J60" s="287">
         <f>IF(G60=0,"-",H60/G60)</f>
         <v/>
       </c>
-      <c r="K60" s="304" t="n"/>
-      <c r="L60" s="306" t="n"/>
+      <c r="K60" s="286" t="n"/>
+      <c r="L60" s="288" t="n"/>
       <c r="M60" s="151" t="n"/>
       <c r="N60" s="151" t="n"/>
       <c r="O60" s="151" t="n"/>
@@ -5604,221 +5602,221 @@
       <c r="AC60" s="153" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="299" t="inlineStr">
+      <c r="B61" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C61" s="300" t="inlineStr">
+      <c r="C61" s="282" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D61" s="301" t="inlineStr">
+      <c r="D61" s="283" t="inlineStr">
         <is>
           <t>BLACK BOTTLE 200ML</t>
         </is>
       </c>
-      <c r="E61" s="302" t="inlineStr">
+      <c r="E61" s="284" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F61" s="303" t="n">
+      <c r="F61" s="285" t="n">
         <v>8008</v>
       </c>
-      <c r="G61" s="303" t="n">
+      <c r="G61" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="304">
+      <c r="H61" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F61)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I61" s="303">
+      <c r="I61" s="285">
         <f>G61-H61</f>
         <v/>
       </c>
-      <c r="J61" s="305">
+      <c r="J61" s="287">
         <f>IF(G61=0,"-",H61/G61)</f>
         <v/>
       </c>
-      <c r="K61" s="304" t="n"/>
-      <c r="L61" s="306" t="n"/>
+      <c r="K61" s="286" t="n"/>
+      <c r="L61" s="288" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="299" t="inlineStr">
+      <c r="B62" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C62" s="300" t="inlineStr">
+      <c r="C62" s="282" t="inlineStr">
         <is>
           <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
-      <c r="D62" s="301" t="inlineStr">
+      <c r="D62" s="283" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 300ML</t>
         </is>
       </c>
-      <c r="E62" s="302" t="inlineStr">
+      <c r="E62" s="284" t="inlineStr">
         <is>
           <t>300 ml</t>
         </is>
       </c>
-      <c r="F62" s="303" t="n">
+      <c r="F62" s="285" t="n">
         <v>8009</v>
       </c>
-      <c r="G62" s="303" t="n">
+      <c r="G62" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="304">
+      <c r="H62" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F62)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I62" s="303">
+      <c r="I62" s="285">
         <f>G62-H62</f>
         <v/>
       </c>
-      <c r="J62" s="305">
+      <c r="J62" s="287">
         <f>IF(G62=0,"-",H62/G62)</f>
         <v/>
       </c>
-      <c r="K62" s="304" t="n"/>
-      <c r="L62" s="306" t="n"/>
+      <c r="K62" s="286" t="n"/>
+      <c r="L62" s="288" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="299" t="inlineStr">
+      <c r="B63" s="281" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="C63" s="300" t="inlineStr">
+      <c r="C63" s="282" t="inlineStr">
         <is>
           <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
-      <c r="D63" s="301" t="inlineStr">
+      <c r="D63" s="283" t="inlineStr">
         <is>
           <t>TRANSPARENT JAR 500ML</t>
         </is>
       </c>
-      <c r="E63" s="302" t="inlineStr">
+      <c r="E63" s="284" t="inlineStr">
         <is>
           <t>500 ml</t>
         </is>
       </c>
-      <c r="F63" s="303" t="n">
+      <c r="F63" s="285" t="n">
         <v>8013</v>
       </c>
-      <c r="G63" s="303" t="n">
+      <c r="G63" s="285" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="304">
+      <c r="H63" s="286">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F63)*Production_Log!$H$3:$H$8963)</f>
         <v/>
       </c>
-      <c r="I63" s="303">
+      <c r="I63" s="285">
         <f>G63-H63</f>
         <v/>
       </c>
-      <c r="J63" s="305">
+      <c r="J63" s="287">
         <f>IF(G63=0,"-",H63/G63)</f>
         <v/>
       </c>
-      <c r="K63" s="304" t="n"/>
-      <c r="L63" s="306" t="n"/>
+      <c r="K63" s="286" t="n"/>
+      <c r="L63" s="288" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="311" t="n"/>
-      <c r="C64" s="311" t="n"/>
-      <c r="D64" s="311" t="n"/>
-      <c r="E64" s="311" t="n"/>
-      <c r="F64" s="311" t="n"/>
-      <c r="G64" s="311" t="n"/>
-      <c r="H64" s="311" t="n"/>
-      <c r="I64" s="311" t="n"/>
-      <c r="J64" s="311" t="n"/>
-      <c r="K64" s="311" t="n"/>
-      <c r="L64" s="311" t="n"/>
+      <c r="B64" s="293" t="n"/>
+      <c r="C64" s="293" t="n"/>
+      <c r="D64" s="293" t="n"/>
+      <c r="E64" s="293" t="n"/>
+      <c r="F64" s="293" t="n"/>
+      <c r="G64" s="293" t="n"/>
+      <c r="H64" s="293" t="n"/>
+      <c r="I64" s="293" t="n"/>
+      <c r="J64" s="293" t="n"/>
+      <c r="K64" s="293" t="n"/>
+      <c r="L64" s="293" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="311" t="n"/>
-      <c r="C65" s="311" t="n"/>
-      <c r="D65" s="311" t="n"/>
-      <c r="E65" s="311" t="n"/>
-      <c r="F65" s="311" t="n"/>
-      <c r="G65" s="311" t="n"/>
-      <c r="H65" s="311" t="n"/>
-      <c r="I65" s="311" t="n"/>
-      <c r="J65" s="311" t="n"/>
-      <c r="K65" s="311" t="n"/>
-      <c r="L65" s="311" t="n"/>
+      <c r="B65" s="293" t="n"/>
+      <c r="C65" s="293" t="n"/>
+      <c r="D65" s="293" t="n"/>
+      <c r="E65" s="293" t="n"/>
+      <c r="F65" s="293" t="n"/>
+      <c r="G65" s="293" t="n"/>
+      <c r="H65" s="293" t="n"/>
+      <c r="I65" s="293" t="n"/>
+      <c r="J65" s="293" t="n"/>
+      <c r="K65" s="293" t="n"/>
+      <c r="L65" s="293" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="311" t="n"/>
-      <c r="C66" s="311" t="n"/>
-      <c r="D66" s="311" t="n"/>
-      <c r="E66" s="311" t="n"/>
-      <c r="F66" s="311" t="n"/>
-      <c r="G66" s="311" t="n"/>
-      <c r="H66" s="311" t="n"/>
-      <c r="I66" s="311" t="n"/>
-      <c r="J66" s="311" t="n"/>
-      <c r="K66" s="311" t="n"/>
-      <c r="L66" s="311" t="n"/>
+      <c r="B66" s="293" t="n"/>
+      <c r="C66" s="293" t="n"/>
+      <c r="D66" s="293" t="n"/>
+      <c r="E66" s="293" t="n"/>
+      <c r="F66" s="293" t="n"/>
+      <c r="G66" s="293" t="n"/>
+      <c r="H66" s="293" t="n"/>
+      <c r="I66" s="293" t="n"/>
+      <c r="J66" s="293" t="n"/>
+      <c r="K66" s="293" t="n"/>
+      <c r="L66" s="293" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="254">
-      <c r="B67" s="311" t="n"/>
-      <c r="C67" s="311" t="n"/>
-      <c r="D67" s="311" t="n"/>
-      <c r="E67" s="311" t="n"/>
-      <c r="F67" s="311" t="n"/>
-      <c r="G67" s="311" t="n"/>
-      <c r="H67" s="311" t="n"/>
-      <c r="I67" s="311" t="n"/>
-      <c r="J67" s="311" t="n"/>
-      <c r="K67" s="311" t="n"/>
-      <c r="L67" s="311" t="n"/>
+      <c r="B67" s="293" t="n"/>
+      <c r="C67" s="293" t="n"/>
+      <c r="D67" s="293" t="n"/>
+      <c r="E67" s="293" t="n"/>
+      <c r="F67" s="293" t="n"/>
+      <c r="G67" s="293" t="n"/>
+      <c r="H67" s="293" t="n"/>
+      <c r="I67" s="293" t="n"/>
+      <c r="J67" s="293" t="n"/>
+      <c r="K67" s="293" t="n"/>
+      <c r="L67" s="293" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="254">
-      <c r="B68" s="311" t="n"/>
-      <c r="C68" s="311" t="n"/>
-      <c r="D68" s="311" t="n"/>
-      <c r="E68" s="311" t="n"/>
-      <c r="F68" s="311" t="n"/>
-      <c r="G68" s="311" t="n"/>
-      <c r="H68" s="311" t="n"/>
-      <c r="I68" s="311" t="n"/>
-      <c r="J68" s="311" t="n"/>
-      <c r="K68" s="311" t="n"/>
-      <c r="L68" s="311" t="n"/>
+      <c r="B68" s="293" t="n"/>
+      <c r="C68" s="293" t="n"/>
+      <c r="D68" s="293" t="n"/>
+      <c r="E68" s="293" t="n"/>
+      <c r="F68" s="293" t="n"/>
+      <c r="G68" s="293" t="n"/>
+      <c r="H68" s="293" t="n"/>
+      <c r="I68" s="293" t="n"/>
+      <c r="J68" s="293" t="n"/>
+      <c r="K68" s="293" t="n"/>
+      <c r="L68" s="293" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="254">
-      <c r="B69" s="311" t="n"/>
-      <c r="C69" s="311" t="n"/>
-      <c r="D69" s="311" t="n"/>
-      <c r="E69" s="311" t="n"/>
-      <c r="F69" s="311" t="n"/>
-      <c r="G69" s="311" t="n"/>
-      <c r="H69" s="311" t="n"/>
-      <c r="I69" s="311" t="n"/>
-      <c r="J69" s="311" t="n"/>
-      <c r="K69" s="311" t="n"/>
-      <c r="L69" s="311" t="n"/>
+      <c r="B69" s="293" t="n"/>
+      <c r="C69" s="293" t="n"/>
+      <c r="D69" s="293" t="n"/>
+      <c r="E69" s="293" t="n"/>
+      <c r="F69" s="293" t="n"/>
+      <c r="G69" s="293" t="n"/>
+      <c r="H69" s="293" t="n"/>
+      <c r="I69" s="293" t="n"/>
+      <c r="J69" s="293" t="n"/>
+      <c r="K69" s="293" t="n"/>
+      <c r="L69" s="293" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="254">
-      <c r="B70" s="311" t="n"/>
-      <c r="C70" s="311" t="n"/>
-      <c r="D70" s="311" t="n"/>
-      <c r="E70" s="311" t="n"/>
-      <c r="F70" s="311" t="n"/>
-      <c r="G70" s="311" t="n"/>
-      <c r="H70" s="311" t="n"/>
-      <c r="I70" s="311" t="n"/>
-      <c r="J70" s="311" t="n"/>
-      <c r="K70" s="311" t="n"/>
-      <c r="L70" s="311" t="n"/>
+      <c r="B70" s="293" t="n"/>
+      <c r="C70" s="293" t="n"/>
+      <c r="D70" s="293" t="n"/>
+      <c r="E70" s="293" t="n"/>
+      <c r="F70" s="293" t="n"/>
+      <c r="G70" s="293" t="n"/>
+      <c r="H70" s="293" t="n"/>
+      <c r="I70" s="293" t="n"/>
+      <c r="J70" s="293" t="n"/>
+      <c r="K70" s="293" t="n"/>
+      <c r="L70" s="293" t="n"/>
     </row>
     <row r="71"/>
     <row r="72"/>
@@ -9154,7 +9152,7 @@
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A63,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A63,TableInventory[Item ID],0)),0)</f>
         <v/>
       </c>
-      <c r="G63" s="220">
+      <c r="G63" s="203">
         <f>F63-E63</f>
         <v/>
       </c>
@@ -9346,7 +9344,7 @@
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A67,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A67,TableInventory[Item ID],0)),0)</f>
         <v/>
       </c>
-      <c r="G67" s="221">
+      <c r="G67" s="204">
         <f>F67-E67</f>
         <v/>
       </c>
@@ -10688,7 +10686,7 @@
       <c r="I96" s="30" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1" s="254">
-      <c r="A97" s="223" t="inlineStr">
+      <c r="A97" s="206" t="inlineStr">
         <is>
           <t>June 2026 PET Required Pet Orders</t>
         </is>
@@ -10698,7 +10696,7 @@
       <c r="D97" s="239" t="n"/>
       <c r="E97" s="239" t="n"/>
       <c r="F97" s="239" t="n"/>
-      <c r="G97" s="222" t="n"/>
+      <c r="G97" s="205" t="n"/>
       <c r="H97" s="239" t="n"/>
       <c r="I97" s="240" t="n"/>
     </row>
@@ -10950,7 +10948,7 @@
       <c r="I104" s="29" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1" s="254">
-      <c r="A105" s="224" t="inlineStr">
+      <c r="A105" s="207" t="inlineStr">
         <is>
           <t>JUNE PET MATERIAL REQUIREMENT PLAN</t>
         </is>
@@ -10960,7 +10958,7 @@
       <c r="D105" s="239" t="n"/>
       <c r="E105" s="239" t="n"/>
       <c r="F105" s="239" t="n"/>
-      <c r="G105" s="222" t="n"/>
+      <c r="G105" s="205" t="n"/>
       <c r="H105" s="239" t="n"/>
       <c r="I105" s="239" t="n"/>
     </row>
@@ -11348,7 +11346,7 @@
       <c r="D115" s="239" t="n"/>
       <c r="E115" s="239" t="n"/>
       <c r="F115" s="239" t="n"/>
-      <c r="G115" s="222" t="n"/>
+      <c r="G115" s="205" t="n"/>
       <c r="H115" s="239" t="n"/>
       <c r="I115" s="240" t="n"/>
     </row>
@@ -40327,7 +40325,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -40466,2059 +40464,2059 @@
         </is>
       </c>
     </row>
-    <row r="3" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A3" s="285" t="n">
+    <row r="3" ht="15" customHeight="1" s="254">
+      <c r="A3" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B3" s="276" t="inlineStr">
+      <c r="B3" s="295" t="inlineStr">
         <is>
           <t>Lacquer-02</t>
         </is>
       </c>
-      <c r="C3" s="276" t="inlineStr">
+      <c r="C3" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D3" s="276" t="inlineStr">
+      <c r="D3" s="295" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E3" s="276" t="n">
+      <c r="E3" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F3" s="276" t="n">
+      <c r="F3" s="295" t="n">
         <v>3726</v>
       </c>
-      <c r="G3" s="277" t="n">
+      <c r="G3" s="296" t="n">
         <v>14000</v>
       </c>
-      <c r="H3" s="277" t="n">
+      <c r="H3" s="296" t="n">
         <v>13770</v>
       </c>
-      <c r="I3" s="277" t="n">
+      <c r="I3" s="296" t="n">
         <v>230</v>
       </c>
-      <c r="J3" s="278">
+      <c r="J3" s="297">
         <f>IFERROR(I3/(H3+I3),"")</f>
         <v/>
       </c>
-      <c r="K3" s="276" t="n"/>
-      <c r="L3" s="276" t="n"/>
-      <c r="M3" s="276" t="n">
+      <c r="K3" s="295" t="n"/>
+      <c r="L3" s="295" t="n"/>
+      <c r="M3" s="295" t="n">
         <v>120</v>
       </c>
-      <c r="N3" s="276" t="n"/>
-      <c r="O3" s="276" t="n"/>
-      <c r="P3" s="276" t="n"/>
-      <c r="Q3" s="276" t="n"/>
-      <c r="R3" s="276" t="n"/>
-      <c r="S3" s="276" t="n"/>
-    </row>
-    <row r="4" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A4" s="285" t="n">
+      <c r="N3" s="295" t="n"/>
+      <c r="O3" s="295" t="n"/>
+      <c r="P3" s="295" t="n"/>
+      <c r="Q3" s="295" t="n"/>
+      <c r="R3" s="295" t="n"/>
+      <c r="S3" s="295" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="254">
+      <c r="A4" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B4" s="276" t="inlineStr">
+      <c r="B4" s="295" t="inlineStr">
         <is>
           <t>Lacquer-04</t>
         </is>
       </c>
-      <c r="C4" s="276" t="inlineStr">
+      <c r="C4" s="295" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D4" s="276" t="inlineStr">
+      <c r="D4" s="295" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E4" s="276" t="n">
+      <c r="E4" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="276" t="n">
+      <c r="F4" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="G4" s="277" t="n">
+      <c r="G4" s="296" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" s="277" t="n">
+      <c r="H4" s="296" t="n">
         <v>2940</v>
       </c>
-      <c r="I4" s="277" t="n">
+      <c r="I4" s="296" t="n">
         <v>60</v>
       </c>
-      <c r="J4" s="278">
+      <c r="J4" s="297">
         <f>IFERROR(I4/(H4+I4),"")</f>
         <v/>
       </c>
-      <c r="K4" s="276" t="n"/>
-      <c r="L4" s="276" t="n"/>
-      <c r="M4" s="276" t="n"/>
-      <c r="N4" s="276" t="n"/>
-      <c r="O4" s="276" t="n"/>
-      <c r="P4" s="276" t="n"/>
-      <c r="Q4" s="276" t="n"/>
-      <c r="R4" s="276" t="n"/>
-      <c r="S4" s="276" t="n"/>
-    </row>
-    <row r="5" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A5" s="285" t="n">
+      <c r="K4" s="295" t="n"/>
+      <c r="L4" s="295" t="n"/>
+      <c r="M4" s="295" t="n"/>
+      <c r="N4" s="295" t="n"/>
+      <c r="O4" s="295" t="n"/>
+      <c r="P4" s="295" t="n"/>
+      <c r="Q4" s="295" t="n"/>
+      <c r="R4" s="295" t="n"/>
+      <c r="S4" s="295" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="254">
+      <c r="A5" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B5" s="276" t="inlineStr">
+      <c r="B5" s="295" t="inlineStr">
         <is>
           <t>Latex-01</t>
         </is>
       </c>
-      <c r="C5" s="276" t="inlineStr">
+      <c r="C5" s="295" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D5" s="276" t="inlineStr">
+      <c r="D5" s="295" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E5" s="276" t="n">
+      <c r="E5" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="276" t="n">
+      <c r="F5" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="G5" s="277" t="n">
+      <c r="G5" s="296" t="n">
         <v>26000</v>
       </c>
-      <c r="H5" s="277" t="n">
+      <c r="H5" s="296" t="n">
         <v>25990</v>
       </c>
-      <c r="I5" s="277" t="n">
+      <c r="I5" s="296" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="278">
+      <c r="J5" s="297">
         <f>IFERROR(I5/(H5+I5),"")</f>
         <v/>
       </c>
-      <c r="K5" s="276" t="n"/>
-      <c r="L5" s="276" t="n"/>
-      <c r="M5" s="276" t="n"/>
-      <c r="N5" s="276" t="n"/>
-      <c r="O5" s="276" t="n"/>
-      <c r="P5" s="276" t="n"/>
-      <c r="Q5" s="276" t="n"/>
-      <c r="R5" s="276" t="n"/>
-      <c r="S5" s="276" t="n"/>
-    </row>
-    <row r="6" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A6" s="285" t="n">
+      <c r="K5" s="295" t="n"/>
+      <c r="L5" s="295" t="n"/>
+      <c r="M5" s="295" t="n"/>
+      <c r="N5" s="295" t="n"/>
+      <c r="O5" s="295" t="n"/>
+      <c r="P5" s="295" t="n"/>
+      <c r="Q5" s="295" t="n"/>
+      <c r="R5" s="295" t="n"/>
+      <c r="S5" s="295" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="254">
+      <c r="A6" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B6" s="276" t="inlineStr">
+      <c r="B6" s="295" t="inlineStr">
         <is>
           <t>PF Machine</t>
         </is>
       </c>
-      <c r="C6" s="276" t="inlineStr">
+      <c r="C6" s="295" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D6" s="276" t="inlineStr">
+      <c r="D6" s="295" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E6" s="276" t="inlineStr">
+      <c r="E6" s="295" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F6" s="276" t="n">
+      <c r="F6" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="G6" s="277" t="n">
+      <c r="G6" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="277" t="n">
+      <c r="H6" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="277" t="n">
+      <c r="I6" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="278">
+      <c r="J6" s="297">
         <f>IFERROR(I6/(H6+I6),"")</f>
         <v/>
       </c>
-      <c r="K6" s="276" t="n"/>
-      <c r="L6" s="276" t="n"/>
-      <c r="M6" s="276" t="n"/>
-      <c r="N6" s="276" t="n"/>
-      <c r="O6" s="276" t="n">
+      <c r="K6" s="295" t="n"/>
+      <c r="L6" s="295" t="n"/>
+      <c r="M6" s="295" t="n"/>
+      <c r="N6" s="295" t="n"/>
+      <c r="O6" s="295" t="n">
         <v>480</v>
       </c>
-      <c r="P6" s="276" t="n"/>
-      <c r="Q6" s="276" t="n"/>
-      <c r="R6" s="276" t="n"/>
-      <c r="S6" s="276" t="n"/>
-    </row>
-    <row r="7" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A7" s="285" t="n">
+      <c r="P6" s="295" t="n"/>
+      <c r="Q6" s="295" t="n"/>
+      <c r="R6" s="295" t="n"/>
+      <c r="S6" s="295" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="254">
+      <c r="A7" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B7" s="276" t="inlineStr">
+      <c r="B7" s="295" t="inlineStr">
         <is>
           <t>Press-04</t>
         </is>
       </c>
-      <c r="C7" s="276" t="inlineStr">
+      <c r="C7" s="295" t="inlineStr">
         <is>
           <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
-      <c r="D7" s="276" t="inlineStr">
+      <c r="D7" s="295" t="inlineStr">
         <is>
           <t>VINCE NURTURAL</t>
         </is>
       </c>
-      <c r="E7" s="276" t="n">
+      <c r="E7" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="276" t="n">
+      <c r="F7" s="295" t="n">
         <v>5814</v>
       </c>
-      <c r="G7" s="277" t="n">
+      <c r="G7" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="277" t="n">
+      <c r="H7" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="277" t="n">
+      <c r="I7" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="278">
+      <c r="J7" s="297">
         <f>IFERROR(I7/(H7+I7),"")</f>
         <v/>
       </c>
-      <c r="K7" s="276" t="n"/>
-      <c r="L7" s="276" t="n"/>
-      <c r="M7" s="276" t="n"/>
-      <c r="N7" s="276" t="n"/>
-      <c r="O7" s="276" t="n"/>
-      <c r="P7" s="276" t="n"/>
-      <c r="Q7" s="276" t="n"/>
-      <c r="R7" s="276" t="n"/>
-      <c r="S7" s="276" t="n"/>
-    </row>
-    <row r="8" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A8" s="285" t="n">
+      <c r="K7" s="295" t="n"/>
+      <c r="L7" s="295" t="n"/>
+      <c r="M7" s="295" t="n"/>
+      <c r="N7" s="295" t="n"/>
+      <c r="O7" s="295" t="n"/>
+      <c r="P7" s="295" t="n"/>
+      <c r="Q7" s="295" t="n"/>
+      <c r="R7" s="295" t="n"/>
+      <c r="S7" s="295" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="254">
+      <c r="A8" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B8" s="276" t="inlineStr">
+      <c r="B8" s="295" t="inlineStr">
         <is>
           <t>Press-06</t>
         </is>
       </c>
-      <c r="C8" s="276" t="inlineStr">
+      <c r="C8" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D8" s="276" t="inlineStr">
+      <c r="D8" s="295" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E8" s="276" t="n">
+      <c r="E8" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="276" t="n">
+      <c r="F8" s="295" t="n">
         <v>3726</v>
       </c>
-      <c r="G8" s="277" t="n">
+      <c r="G8" s="296" t="n">
         <v>20000</v>
       </c>
-      <c r="H8" s="277" t="n">
+      <c r="H8" s="296" t="n">
         <v>19890</v>
       </c>
-      <c r="I8" s="277" t="n">
+      <c r="I8" s="296" t="n">
         <v>110</v>
       </c>
-      <c r="J8" s="278">
+      <c r="J8" s="297">
         <f>IFERROR(I8/(H8+I8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="276" t="n"/>
-      <c r="L8" s="276" t="n"/>
-      <c r="M8" s="276" t="n"/>
-      <c r="N8" s="276" t="n"/>
-      <c r="O8" s="276" t="n"/>
-      <c r="P8" s="276" t="n"/>
-      <c r="Q8" s="276" t="n"/>
-      <c r="R8" s="276" t="n"/>
-      <c r="S8" s="276" t="n"/>
+      <c r="K8" s="295" t="n"/>
+      <c r="L8" s="295" t="n"/>
+      <c r="M8" s="295" t="n"/>
+      <c r="N8" s="295" t="n"/>
+      <c r="O8" s="295" t="n"/>
+      <c r="P8" s="295" t="n"/>
+      <c r="Q8" s="295" t="n"/>
+      <c r="R8" s="295" t="n"/>
+      <c r="S8" s="295" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="254">
-      <c r="A9" s="285" t="n">
+      <c r="A9" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B9" s="276" t="inlineStr">
+      <c r="B9" s="295" t="inlineStr">
         <is>
           <t>Printing-03</t>
         </is>
       </c>
-      <c r="C9" s="276" t="inlineStr">
+      <c r="C9" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D9" s="276" t="inlineStr">
+      <c r="D9" s="295" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E9" s="276" t="n">
+      <c r="E9" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F9" s="276" t="n">
+      <c r="F9" s="295" t="n">
         <v>3726</v>
       </c>
-      <c r="G9" s="277" t="n">
+      <c r="G9" s="296" t="n">
         <v>9999</v>
       </c>
-      <c r="H9" s="277" t="n">
+      <c r="H9" s="296" t="n">
         <v>9744</v>
       </c>
-      <c r="I9" s="277" t="n">
+      <c r="I9" s="296" t="n">
         <v>255</v>
       </c>
-      <c r="J9" s="278">
+      <c r="J9" s="297">
         <f>IFERROR(I9/(H9+I9),"")</f>
         <v/>
       </c>
-      <c r="K9" s="276" t="n"/>
-      <c r="L9" s="276" t="n">
+      <c r="K9" s="295" t="n"/>
+      <c r="L9" s="295" t="n">
         <v>60</v>
       </c>
-      <c r="M9" s="276" t="n">
+      <c r="M9" s="295" t="n">
         <v>180</v>
       </c>
-      <c r="N9" s="276" t="n"/>
-      <c r="O9" s="276" t="n"/>
-      <c r="P9" s="276" t="n"/>
-      <c r="Q9" s="276" t="n"/>
-      <c r="R9" s="276" t="n"/>
-      <c r="S9" s="276" t="n"/>
-    </row>
-    <row r="10" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A10" s="285" t="n">
+      <c r="N9" s="295" t="n"/>
+      <c r="O9" s="295" t="n"/>
+      <c r="P9" s="295" t="n"/>
+      <c r="Q9" s="295" t="n"/>
+      <c r="R9" s="295" t="n"/>
+      <c r="S9" s="295" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="254">
+      <c r="A10" s="298" t="n">
         <v>46174</v>
       </c>
-      <c r="B10" s="276" t="inlineStr">
+      <c r="B10" s="295" t="inlineStr">
         <is>
           <t>Printing-04</t>
         </is>
       </c>
-      <c r="C10" s="276" t="inlineStr">
+      <c r="C10" s="295" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D10" s="276" t="inlineStr">
+      <c r="D10" s="295" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E10" s="276" t="n">
+      <c r="E10" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F10" s="276" t="n">
+      <c r="F10" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="G10" s="277" t="n">
+      <c r="G10" s="296" t="n">
         <v>2728</v>
       </c>
-      <c r="H10" s="277" t="n">
+      <c r="H10" s="296" t="n">
         <v>2618</v>
       </c>
-      <c r="I10" s="277" t="n">
+      <c r="I10" s="296" t="n">
         <v>110</v>
       </c>
-      <c r="J10" s="278">
+      <c r="J10" s="297">
         <f>IFERROR(I10/(H10+I10),"")</f>
         <v/>
       </c>
-      <c r="K10" s="276" t="n"/>
-      <c r="L10" s="276" t="n"/>
-      <c r="M10" s="276" t="n"/>
-      <c r="N10" s="276" t="n"/>
-      <c r="O10" s="276" t="n"/>
-      <c r="P10" s="276" t="n"/>
-      <c r="Q10" s="276" t="n"/>
-      <c r="R10" s="276" t="n"/>
-      <c r="S10" s="276" t="n"/>
-    </row>
-    <row r="11" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A11" s="285" t="n">
+      <c r="K10" s="295" t="n"/>
+      <c r="L10" s="295" t="n"/>
+      <c r="M10" s="295" t="n"/>
+      <c r="N10" s="295" t="n"/>
+      <c r="O10" s="295" t="n"/>
+      <c r="P10" s="295" t="n"/>
+      <c r="Q10" s="295" t="n"/>
+      <c r="R10" s="295" t="n"/>
+      <c r="S10" s="295" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="254">
+      <c r="A11" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B11" s="276" t="inlineStr">
+      <c r="B11" s="295" t="inlineStr">
         <is>
           <t>Lacquer-02</t>
         </is>
       </c>
-      <c r="C11" s="276" t="inlineStr">
+      <c r="C11" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D11" s="276" t="inlineStr">
+      <c r="D11" s="295" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E11" s="276" t="n">
+      <c r="E11" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F11" s="276" t="n">
+      <c r="F11" s="295" t="n">
         <v>3726</v>
       </c>
-      <c r="G11" s="277" t="n">
+      <c r="G11" s="296" t="n">
         <v>8000</v>
       </c>
-      <c r="H11" s="277" t="n">
+      <c r="H11" s="296" t="n">
         <v>7880</v>
       </c>
-      <c r="I11" s="277" t="n">
+      <c r="I11" s="296" t="n">
         <v>120</v>
       </c>
-      <c r="J11" s="278">
+      <c r="J11" s="297">
         <f>IFERROR(I11/(H11+I11),"")</f>
         <v/>
       </c>
-      <c r="K11" s="276" t="n"/>
-      <c r="L11" s="276" t="n"/>
-      <c r="M11" s="276" t="n"/>
-      <c r="N11" s="276" t="n"/>
-      <c r="O11" s="276" t="n"/>
-      <c r="P11" s="276" t="n">
+      <c r="K11" s="295" t="n"/>
+      <c r="L11" s="295" t="n"/>
+      <c r="M11" s="295" t="n"/>
+      <c r="N11" s="295" t="n"/>
+      <c r="O11" s="295" t="n"/>
+      <c r="P11" s="295" t="n">
         <v>60</v>
       </c>
-      <c r="Q11" s="276" t="n"/>
-      <c r="R11" s="276" t="n"/>
-      <c r="S11" s="276" t="n"/>
-    </row>
-    <row r="12" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A12" s="285" t="n">
+      <c r="Q11" s="295" t="n"/>
+      <c r="R11" s="295" t="n"/>
+      <c r="S11" s="295" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="254">
+      <c r="A12" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B12" s="276" t="inlineStr">
+      <c r="B12" s="295" t="inlineStr">
         <is>
           <t>Lacquer-04</t>
         </is>
       </c>
-      <c r="C12" s="276" t="inlineStr">
+      <c r="C12" s="295" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D12" s="276" t="inlineStr">
+      <c r="D12" s="295" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E12" s="276" t="n">
+      <c r="E12" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F12" s="276" t="n">
+      <c r="F12" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="G12" s="277" t="n">
+      <c r="G12" s="296" t="n">
         <v>4000</v>
       </c>
-      <c r="H12" s="277" t="n">
+      <c r="H12" s="296" t="n">
         <v>3905</v>
       </c>
-      <c r="I12" s="277" t="n">
+      <c r="I12" s="296" t="n">
         <v>95</v>
       </c>
-      <c r="J12" s="278">
+      <c r="J12" s="297">
         <f>IFERROR(I12/(H12+I12),"")</f>
         <v/>
       </c>
-      <c r="K12" s="276" t="n"/>
-      <c r="L12" s="276" t="n"/>
-      <c r="M12" s="276" t="n"/>
-      <c r="N12" s="276" t="n"/>
-      <c r="O12" s="276" t="n"/>
-      <c r="P12" s="276" t="n"/>
-      <c r="Q12" s="276" t="n"/>
-      <c r="R12" s="276" t="n"/>
-      <c r="S12" s="276" t="n"/>
-    </row>
-    <row r="13" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A13" s="285" t="n">
+      <c r="K12" s="295" t="n"/>
+      <c r="L12" s="295" t="n"/>
+      <c r="M12" s="295" t="n"/>
+      <c r="N12" s="295" t="n"/>
+      <c r="O12" s="295" t="n"/>
+      <c r="P12" s="295" t="n"/>
+      <c r="Q12" s="295" t="n"/>
+      <c r="R12" s="295" t="n"/>
+      <c r="S12" s="295" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="254">
+      <c r="A13" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B13" s="276" t="inlineStr">
+      <c r="B13" s="295" t="inlineStr">
         <is>
           <t>Latex-01</t>
         </is>
       </c>
-      <c r="C13" s="276" t="inlineStr">
+      <c r="C13" s="295" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="276" t="inlineStr">
+      <c r="D13" s="295" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="276" t="n">
+      <c r="E13" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="276" t="n">
+      <c r="F13" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="G13" s="277" t="n">
+      <c r="G13" s="296" t="n">
         <v>22134</v>
       </c>
-      <c r="H13" s="277" t="n">
+      <c r="H13" s="296" t="n">
         <v>22124</v>
       </c>
-      <c r="I13" s="277" t="n">
+      <c r="I13" s="296" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="278">
+      <c r="J13" s="297">
         <f>IFERROR(I13/(H13+I13),"")</f>
         <v/>
       </c>
-      <c r="K13" s="276" t="n"/>
-      <c r="L13" s="276" t="n"/>
-      <c r="M13" s="276" t="n"/>
-      <c r="N13" s="276" t="n"/>
-      <c r="O13" s="276" t="n"/>
-      <c r="P13" s="276" t="n">
+      <c r="K13" s="295" t="n"/>
+      <c r="L13" s="295" t="n"/>
+      <c r="M13" s="295" t="n"/>
+      <c r="N13" s="295" t="n"/>
+      <c r="O13" s="295" t="n"/>
+      <c r="P13" s="295" t="n">
         <v>60</v>
       </c>
-      <c r="Q13" s="276" t="n"/>
-      <c r="R13" s="276" t="n"/>
-      <c r="S13" s="276" t="n"/>
-    </row>
-    <row r="14" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A14" s="285" t="n">
+      <c r="Q13" s="295" t="n"/>
+      <c r="R13" s="295" t="n"/>
+      <c r="S13" s="295" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="254">
+      <c r="A14" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B14" s="276" t="inlineStr">
+      <c r="B14" s="295" t="inlineStr">
         <is>
           <t>PF Machine</t>
         </is>
       </c>
-      <c r="C14" s="276" t="inlineStr">
+      <c r="C14" s="295" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D14" s="276" t="inlineStr">
+      <c r="D14" s="295" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E14" s="276" t="inlineStr">
+      <c r="E14" s="295" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F14" s="276" t="n">
+      <c r="F14" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="G14" s="277" t="n">
+      <c r="G14" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="277" t="n">
+      <c r="H14" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="277" t="n">
+      <c r="I14" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="278">
+      <c r="J14" s="297">
         <f>IFERROR(I14/(H14+I14),"")</f>
         <v/>
       </c>
-      <c r="K14" s="276" t="n"/>
-      <c r="L14" s="276" t="n"/>
-      <c r="M14" s="276" t="n"/>
-      <c r="N14" s="276" t="n"/>
-      <c r="O14" s="276" t="n">
+      <c r="K14" s="295" t="n"/>
+      <c r="L14" s="295" t="n"/>
+      <c r="M14" s="295" t="n"/>
+      <c r="N14" s="295" t="n"/>
+      <c r="O14" s="295" t="n">
         <v>480</v>
       </c>
-      <c r="P14" s="276" t="n"/>
-      <c r="Q14" s="276" t="n"/>
-      <c r="R14" s="276" t="n"/>
-      <c r="S14" s="276" t="n"/>
-    </row>
-    <row r="15" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A15" s="285" t="n">
+      <c r="P14" s="295" t="n"/>
+      <c r="Q14" s="295" t="n"/>
+      <c r="R14" s="295" t="n"/>
+      <c r="S14" s="295" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="254">
+      <c r="A15" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B15" s="276" t="inlineStr">
+      <c r="B15" s="295" t="inlineStr">
         <is>
           <t>Press-04</t>
         </is>
       </c>
-      <c r="C15" s="276" t="inlineStr">
+      <c r="C15" s="295" t="inlineStr">
         <is>
           <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
-      <c r="D15" s="276" t="inlineStr">
+      <c r="D15" s="295" t="inlineStr">
         <is>
           <t>VINCE NURTURAL</t>
         </is>
       </c>
-      <c r="E15" s="276" t="n">
+      <c r="E15" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F15" s="276" t="n">
+      <c r="F15" s="295" t="n">
         <v>5814</v>
       </c>
-      <c r="G15" s="277" t="n">
+      <c r="G15" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="277" t="n">
+      <c r="H15" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="277" t="n">
+      <c r="I15" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="278">
+      <c r="J15" s="297">
         <f>IFERROR(I15/(H15+I15),"")</f>
         <v/>
       </c>
-      <c r="K15" s="276" t="n"/>
-      <c r="L15" s="276" t="n"/>
-      <c r="M15" s="276" t="n"/>
-      <c r="N15" s="276" t="n"/>
-      <c r="O15" s="276" t="n"/>
-      <c r="P15" s="276" t="n"/>
-      <c r="Q15" s="276" t="n"/>
-      <c r="R15" s="276" t="n"/>
-      <c r="S15" s="276" t="n"/>
-    </row>
-    <row r="16" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A16" s="285" t="n">
+      <c r="K15" s="295" t="n"/>
+      <c r="L15" s="295" t="n"/>
+      <c r="M15" s="295" t="n"/>
+      <c r="N15" s="295" t="n"/>
+      <c r="O15" s="295" t="n"/>
+      <c r="P15" s="295" t="n"/>
+      <c r="Q15" s="295" t="n"/>
+      <c r="R15" s="295" t="n"/>
+      <c r="S15" s="295" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="254">
+      <c r="A16" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B16" s="276" t="inlineStr">
+      <c r="B16" s="295" t="inlineStr">
         <is>
           <t>Press-06</t>
         </is>
       </c>
-      <c r="C16" s="276" t="inlineStr">
+      <c r="C16" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D16" s="276" t="inlineStr">
+      <c r="D16" s="295" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E16" s="276" t="n">
+      <c r="E16" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F16" s="276" t="n">
+      <c r="F16" s="295" t="n">
         <v>3726</v>
       </c>
-      <c r="G16" s="277" t="n">
+      <c r="G16" s="296" t="n">
         <v>1000</v>
       </c>
-      <c r="H16" s="277" t="n">
+      <c r="H16" s="296" t="n">
         <v>980</v>
       </c>
-      <c r="I16" s="277" t="n">
+      <c r="I16" s="296" t="n">
         <v>20</v>
       </c>
-      <c r="J16" s="278">
+      <c r="J16" s="297">
         <f>IFERROR(I16/(H16+I16),"")</f>
         <v/>
       </c>
-      <c r="K16" s="276" t="n"/>
-      <c r="L16" s="276" t="n"/>
-      <c r="M16" s="276" t="n"/>
-      <c r="N16" s="276" t="n"/>
-      <c r="O16" s="276" t="n"/>
-      <c r="P16" s="276" t="n"/>
-      <c r="Q16" s="276" t="n"/>
-      <c r="R16" s="276" t="n"/>
-      <c r="S16" s="276" t="n"/>
+      <c r="K16" s="295" t="n"/>
+      <c r="L16" s="295" t="n"/>
+      <c r="M16" s="295" t="n"/>
+      <c r="N16" s="295" t="n"/>
+      <c r="O16" s="295" t="n"/>
+      <c r="P16" s="295" t="n"/>
+      <c r="Q16" s="295" t="n"/>
+      <c r="R16" s="295" t="n"/>
+      <c r="S16" s="295" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="254">
-      <c r="A17" s="285" t="n">
+      <c r="A17" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B17" s="276" t="inlineStr">
+      <c r="B17" s="295" t="inlineStr">
         <is>
           <t>Printing-03</t>
         </is>
       </c>
-      <c r="C17" s="276" t="inlineStr">
+      <c r="C17" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D17" s="276" t="inlineStr">
+      <c r="D17" s="295" t="inlineStr">
         <is>
           <t>TUBES</t>
         </is>
       </c>
-      <c r="E17" s="276" t="n">
+      <c r="E17" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F17" s="276" t="n">
+      <c r="F17" s="295" t="n">
         <v>3726</v>
       </c>
-      <c r="G17" s="277" t="n">
+      <c r="G17" s="296" t="n">
         <v>12687</v>
       </c>
-      <c r="H17" s="277" t="n">
+      <c r="H17" s="296" t="n">
         <v>12432</v>
       </c>
-      <c r="I17" s="277" t="n">
+      <c r="I17" s="296" t="n">
         <v>255</v>
       </c>
-      <c r="J17" s="278">
+      <c r="J17" s="297">
         <f>IFERROR(I17/(H17+I17),"")</f>
         <v/>
       </c>
-      <c r="K17" s="276" t="n"/>
-      <c r="L17" s="276" t="n"/>
-      <c r="M17" s="276" t="n"/>
-      <c r="N17" s="276" t="n"/>
-      <c r="O17" s="276" t="n"/>
-      <c r="P17" s="276" t="n">
+      <c r="K17" s="295" t="n"/>
+      <c r="L17" s="295" t="n"/>
+      <c r="M17" s="295" t="n"/>
+      <c r="N17" s="295" t="n"/>
+      <c r="O17" s="295" t="n"/>
+      <c r="P17" s="295" t="n">
         <v>60</v>
       </c>
-      <c r="Q17" s="276" t="n"/>
-      <c r="R17" s="276" t="n"/>
-      <c r="S17" s="276" t="n"/>
-    </row>
-    <row r="18" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A18" s="285" t="n">
+      <c r="Q17" s="295" t="n"/>
+      <c r="R17" s="295" t="n"/>
+      <c r="S17" s="295" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="254">
+      <c r="A18" s="298" t="n">
         <v>46175</v>
       </c>
-      <c r="B18" s="276" t="inlineStr">
+      <c r="B18" s="295" t="inlineStr">
         <is>
           <t>Printing-04</t>
         </is>
       </c>
-      <c r="C18" s="276" t="inlineStr">
+      <c r="C18" s="295" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D18" s="276" t="inlineStr">
+      <c r="D18" s="295" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E18" s="276" t="n">
+      <c r="E18" s="295" t="n">
         <v>30</v>
       </c>
-      <c r="F18" s="276" t="n">
+      <c r="F18" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="G18" s="277" t="n">
+      <c r="G18" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="277" t="n">
+      <c r="H18" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="277" t="n">
+      <c r="I18" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="278">
+      <c r="J18" s="297">
         <f>IFERROR(I18/(H18+I18),"")</f>
         <v/>
       </c>
-      <c r="K18" s="276" t="n"/>
-      <c r="L18" s="276" t="n"/>
-      <c r="M18" s="276" t="n"/>
-      <c r="N18" s="276" t="n"/>
-      <c r="O18" s="276" t="n"/>
-      <c r="P18" s="276" t="n"/>
-      <c r="Q18" s="276" t="n"/>
-      <c r="R18" s="276" t="n"/>
-      <c r="S18" s="276" t="n"/>
-    </row>
-    <row r="19" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A19" s="285" t="n">
+      <c r="K18" s="295" t="n"/>
+      <c r="L18" s="295" t="n"/>
+      <c r="M18" s="295" t="n"/>
+      <c r="N18" s="295" t="n"/>
+      <c r="O18" s="295" t="n"/>
+      <c r="P18" s="295" t="n"/>
+      <c r="Q18" s="295" t="n"/>
+      <c r="R18" s="295" t="n"/>
+      <c r="S18" s="295" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="254">
+      <c r="A19" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B19" s="276" t="inlineStr">
+      <c r="B19" s="295" t="inlineStr">
         <is>
           <t>Lacquer-02</t>
         </is>
       </c>
-      <c r="C19" s="276" t="inlineStr"/>
-      <c r="D19" s="276" t="inlineStr"/>
-      <c r="E19" s="276" t="inlineStr"/>
-      <c r="F19" s="276" t="n"/>
-      <c r="G19" s="277" t="n">
+      <c r="C19" s="295" t="inlineStr"/>
+      <c r="D19" s="295" t="inlineStr"/>
+      <c r="E19" s="295" t="inlineStr"/>
+      <c r="F19" s="295" t="n"/>
+      <c r="G19" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="277" t="n">
+      <c r="H19" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="277" t="n">
+      <c r="I19" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="278">
+      <c r="J19" s="297">
         <f>IFERROR(I19/(H19+I19),"")</f>
         <v/>
       </c>
-      <c r="K19" s="276" t="n"/>
-      <c r="L19" s="276" t="n"/>
-      <c r="M19" s="276" t="n"/>
-      <c r="N19" s="276" t="n"/>
-      <c r="O19" s="276" t="n"/>
-      <c r="P19" s="276" t="n"/>
-      <c r="Q19" s="276" t="n"/>
-      <c r="R19" s="276" t="n"/>
-      <c r="S19" s="276" t="n"/>
-    </row>
-    <row r="20" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A20" s="285" t="n">
+      <c r="K19" s="295" t="n"/>
+      <c r="L19" s="295" t="n"/>
+      <c r="M19" s="295" t="n"/>
+      <c r="N19" s="295" t="n"/>
+      <c r="O19" s="295" t="n"/>
+      <c r="P19" s="295" t="n"/>
+      <c r="Q19" s="295" t="n"/>
+      <c r="R19" s="295" t="n"/>
+      <c r="S19" s="295" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="254">
+      <c r="A20" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B20" s="276" t="inlineStr">
+      <c r="B20" s="295" t="inlineStr">
         <is>
           <t>Lacquer-04</t>
         </is>
       </c>
-      <c r="C20" s="276" t="inlineStr"/>
-      <c r="D20" s="276" t="inlineStr"/>
-      <c r="E20" s="276" t="inlineStr"/>
-      <c r="F20" s="276" t="n"/>
-      <c r="G20" s="277" t="n">
+      <c r="C20" s="295" t="inlineStr"/>
+      <c r="D20" s="295" t="inlineStr"/>
+      <c r="E20" s="295" t="inlineStr"/>
+      <c r="F20" s="295" t="n"/>
+      <c r="G20" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="277" t="n">
+      <c r="H20" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="277" t="n">
+      <c r="I20" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="278">
+      <c r="J20" s="297">
         <f>IFERROR(I20/(H20+I20),"")</f>
         <v/>
       </c>
-      <c r="K20" s="276" t="n"/>
-      <c r="L20" s="276" t="n"/>
-      <c r="M20" s="276" t="n"/>
-      <c r="N20" s="276" t="n"/>
-      <c r="O20" s="276" t="n"/>
-      <c r="P20" s="276" t="n"/>
-      <c r="Q20" s="276" t="n"/>
-      <c r="R20" s="276" t="n"/>
-      <c r="S20" s="276" t="n"/>
-    </row>
-    <row r="21" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A21" s="285" t="n">
+      <c r="K20" s="295" t="n"/>
+      <c r="L20" s="295" t="n"/>
+      <c r="M20" s="295" t="n"/>
+      <c r="N20" s="295" t="n"/>
+      <c r="O20" s="295" t="n"/>
+      <c r="P20" s="295" t="n"/>
+      <c r="Q20" s="295" t="n"/>
+      <c r="R20" s="295" t="n"/>
+      <c r="S20" s="295" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="254">
+      <c r="A21" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B21" s="276" t="inlineStr">
+      <c r="B21" s="295" t="inlineStr">
         <is>
           <t>Latex-01</t>
         </is>
       </c>
-      <c r="C21" s="276" t="inlineStr"/>
-      <c r="D21" s="276" t="inlineStr"/>
-      <c r="E21" s="276" t="inlineStr"/>
-      <c r="F21" s="276" t="n"/>
-      <c r="G21" s="277" t="n">
+      <c r="C21" s="295" t="inlineStr"/>
+      <c r="D21" s="295" t="inlineStr"/>
+      <c r="E21" s="295" t="inlineStr"/>
+      <c r="F21" s="295" t="n"/>
+      <c r="G21" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="277" t="n">
+      <c r="H21" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="277" t="n">
+      <c r="I21" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="278">
+      <c r="J21" s="297">
         <f>IFERROR(I21/(H21+I21),"")</f>
         <v/>
       </c>
-      <c r="K21" s="276" t="n"/>
-      <c r="L21" s="276" t="n"/>
-      <c r="M21" s="276" t="n"/>
-      <c r="N21" s="276" t="n"/>
-      <c r="O21" s="276" t="n"/>
-      <c r="P21" s="276" t="n"/>
-      <c r="Q21" s="276" t="n"/>
-      <c r="R21" s="276" t="n"/>
-      <c r="S21" s="276" t="n"/>
-    </row>
-    <row r="22" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A22" s="285" t="n">
+      <c r="K21" s="295" t="n"/>
+      <c r="L21" s="295" t="n"/>
+      <c r="M21" s="295" t="n"/>
+      <c r="N21" s="295" t="n"/>
+      <c r="O21" s="295" t="n"/>
+      <c r="P21" s="295" t="n"/>
+      <c r="Q21" s="295" t="n"/>
+      <c r="R21" s="295" t="n"/>
+      <c r="S21" s="295" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="254">
+      <c r="A22" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B22" s="276" t="inlineStr">
+      <c r="B22" s="295" t="inlineStr">
         <is>
           <t>PF Machine</t>
         </is>
       </c>
-      <c r="C22" s="276" t="inlineStr">
+      <c r="C22" s="295" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D22" s="276" t="inlineStr">
+      <c r="D22" s="295" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E22" s="276" t="inlineStr">
+      <c r="E22" s="295" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F22" s="276" t="n">
+      <c r="F22" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="G22" s="277" t="n">
+      <c r="G22" s="296" t="n">
         <v>4525</v>
       </c>
-      <c r="H22" s="277" t="n">
+      <c r="H22" s="296" t="n">
         <v>4025</v>
       </c>
-      <c r="I22" s="277" t="n">
+      <c r="I22" s="296" t="n">
         <v>500</v>
       </c>
-      <c r="J22" s="278">
+      <c r="J22" s="297">
         <f>IFERROR(I22/(H22+I22),"")</f>
         <v/>
       </c>
-      <c r="K22" s="276" t="n"/>
-      <c r="L22" s="276" t="n">
+      <c r="K22" s="295" t="n"/>
+      <c r="L22" s="295" t="n">
         <v>580</v>
       </c>
-      <c r="M22" s="276" t="n"/>
-      <c r="N22" s="276" t="n"/>
-      <c r="O22" s="276" t="n"/>
-      <c r="P22" s="276" t="n">
+      <c r="M22" s="295" t="n"/>
+      <c r="N22" s="295" t="n"/>
+      <c r="O22" s="295" t="n"/>
+      <c r="P22" s="295" t="n">
         <v>80</v>
       </c>
-      <c r="Q22" s="276" t="n"/>
-      <c r="R22" s="276" t="n"/>
-      <c r="S22" s="276" t="n"/>
-    </row>
-    <row r="23" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A23" s="285" t="n">
+      <c r="Q22" s="295" t="n"/>
+      <c r="R22" s="295" t="n"/>
+      <c r="S22" s="295" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="254">
+      <c r="A23" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B23" s="276" t="inlineStr">
+      <c r="B23" s="295" t="inlineStr">
         <is>
           <t>Press-04</t>
         </is>
       </c>
-      <c r="C23" s="276" t="inlineStr"/>
-      <c r="D23" s="276" t="inlineStr"/>
-      <c r="E23" s="276" t="inlineStr"/>
-      <c r="F23" s="276" t="n"/>
-      <c r="G23" s="277" t="n">
+      <c r="C23" s="295" t="inlineStr"/>
+      <c r="D23" s="295" t="inlineStr"/>
+      <c r="E23" s="295" t="inlineStr"/>
+      <c r="F23" s="295" t="n"/>
+      <c r="G23" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="277" t="n">
+      <c r="H23" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="277" t="n">
+      <c r="I23" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="297">
         <f>IFERROR(I23/(H23+I23),"")</f>
         <v/>
       </c>
-      <c r="K23" s="276" t="n"/>
-      <c r="L23" s="276" t="n"/>
-      <c r="M23" s="276" t="n"/>
-      <c r="N23" s="276" t="n"/>
-      <c r="O23" s="276" t="n"/>
-      <c r="P23" s="276" t="n"/>
-      <c r="Q23" s="276" t="n"/>
-      <c r="R23" s="276" t="n"/>
-      <c r="S23" s="276" t="n"/>
-    </row>
-    <row r="24" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A24" s="285" t="n">
+      <c r="K23" s="295" t="n"/>
+      <c r="L23" s="295" t="n"/>
+      <c r="M23" s="295" t="n"/>
+      <c r="N23" s="295" t="n"/>
+      <c r="O23" s="295" t="n"/>
+      <c r="P23" s="295" t="n"/>
+      <c r="Q23" s="295" t="n"/>
+      <c r="R23" s="295" t="n"/>
+      <c r="S23" s="295" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="254">
+      <c r="A24" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B24" s="276" t="inlineStr">
+      <c r="B24" s="295" t="inlineStr">
         <is>
           <t>Press-06</t>
         </is>
       </c>
-      <c r="C24" s="276" t="inlineStr"/>
-      <c r="D24" s="276" t="inlineStr"/>
-      <c r="E24" s="276" t="inlineStr"/>
-      <c r="F24" s="276" t="n"/>
-      <c r="G24" s="277" t="n">
+      <c r="C24" s="295" t="inlineStr"/>
+      <c r="D24" s="295" t="inlineStr"/>
+      <c r="E24" s="295" t="inlineStr"/>
+      <c r="F24" s="295" t="n"/>
+      <c r="G24" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="277" t="n">
+      <c r="H24" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="277" t="n">
+      <c r="I24" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="278">
+      <c r="J24" s="297">
         <f>IFERROR(I24/(H24+I24),"")</f>
         <v/>
       </c>
-      <c r="K24" s="276" t="n"/>
-      <c r="L24" s="276" t="n"/>
-      <c r="M24" s="276" t="n"/>
-      <c r="N24" s="276" t="n"/>
-      <c r="O24" s="276" t="n"/>
-      <c r="P24" s="276" t="n"/>
-      <c r="Q24" s="276" t="n"/>
-      <c r="R24" s="276" t="n"/>
-      <c r="S24" s="276" t="n"/>
-    </row>
-    <row r="25" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A25" s="285" t="n">
+      <c r="K24" s="295" t="n"/>
+      <c r="L24" s="295" t="n"/>
+      <c r="M24" s="295" t="n"/>
+      <c r="N24" s="295" t="n"/>
+      <c r="O24" s="295" t="n"/>
+      <c r="P24" s="295" t="n"/>
+      <c r="Q24" s="295" t="n"/>
+      <c r="R24" s="295" t="n"/>
+      <c r="S24" s="295" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="254">
+      <c r="A25" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B25" s="276" t="inlineStr">
+      <c r="B25" s="295" t="inlineStr">
         <is>
           <t>Printing-03</t>
         </is>
       </c>
-      <c r="C25" s="276" t="inlineStr"/>
-      <c r="D25" s="276" t="inlineStr"/>
-      <c r="E25" s="276" t="inlineStr"/>
-      <c r="F25" s="276" t="n"/>
-      <c r="G25" s="277" t="n">
+      <c r="C25" s="295" t="inlineStr"/>
+      <c r="D25" s="295" t="inlineStr"/>
+      <c r="E25" s="295" t="inlineStr"/>
+      <c r="F25" s="295" t="n"/>
+      <c r="G25" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="277" t="n">
+      <c r="H25" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="277" t="n">
+      <c r="I25" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="278">
+      <c r="J25" s="297">
         <f>IFERROR(I25/(H25+I25),"")</f>
         <v/>
       </c>
-      <c r="K25" s="276" t="n"/>
-      <c r="L25" s="276" t="n"/>
-      <c r="M25" s="276" t="n"/>
-      <c r="N25" s="276" t="n"/>
-      <c r="O25" s="276" t="n"/>
-      <c r="P25" s="276" t="n"/>
-      <c r="Q25" s="276" t="n"/>
-      <c r="R25" s="276" t="n"/>
-      <c r="S25" s="276" t="n"/>
-    </row>
-    <row r="26" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A26" s="285" t="n">
+      <c r="K25" s="295" t="n"/>
+      <c r="L25" s="295" t="n"/>
+      <c r="M25" s="295" t="n"/>
+      <c r="N25" s="295" t="n"/>
+      <c r="O25" s="295" t="n"/>
+      <c r="P25" s="295" t="n"/>
+      <c r="Q25" s="295" t="n"/>
+      <c r="R25" s="295" t="n"/>
+      <c r="S25" s="295" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="254">
+      <c r="A26" s="298" t="n">
         <v>46177</v>
       </c>
-      <c r="B26" s="276" t="inlineStr">
+      <c r="B26" s="295" t="inlineStr">
         <is>
           <t>Printing-04</t>
         </is>
       </c>
-      <c r="C26" s="276" t="inlineStr"/>
-      <c r="D26" s="276" t="inlineStr"/>
-      <c r="E26" s="276" t="inlineStr"/>
-      <c r="F26" s="276" t="n"/>
-      <c r="G26" s="277" t="n">
+      <c r="C26" s="295" t="inlineStr"/>
+      <c r="D26" s="295" t="inlineStr"/>
+      <c r="E26" s="295" t="inlineStr"/>
+      <c r="F26" s="295" t="n"/>
+      <c r="G26" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="277" t="n">
+      <c r="H26" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="277" t="n">
+      <c r="I26" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="278">
+      <c r="J26" s="297">
         <f>IFERROR(I26/(H26+I26),"")</f>
         <v/>
       </c>
-      <c r="K26" s="276" t="n"/>
-      <c r="L26" s="276" t="n"/>
-      <c r="M26" s="276" t="n"/>
-      <c r="N26" s="276" t="n"/>
-      <c r="O26" s="276" t="n"/>
-      <c r="P26" s="276" t="n"/>
-      <c r="Q26" s="276" t="n"/>
-      <c r="R26" s="276" t="n"/>
-      <c r="S26" s="276" t="n"/>
-    </row>
-    <row r="27" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A27" s="285" t="n">
+      <c r="K26" s="295" t="n"/>
+      <c r="L26" s="295" t="n"/>
+      <c r="M26" s="295" t="n"/>
+      <c r="N26" s="295" t="n"/>
+      <c r="O26" s="295" t="n"/>
+      <c r="P26" s="295" t="n"/>
+      <c r="Q26" s="295" t="n"/>
+      <c r="R26" s="295" t="n"/>
+      <c r="S26" s="295" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="254">
+      <c r="A27" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B27" s="276" t="inlineStr">
+      <c r="B27" s="295" t="inlineStr">
         <is>
           <t>Lacquer-02</t>
         </is>
       </c>
-      <c r="C27" s="276" t="inlineStr"/>
-      <c r="D27" s="276" t="inlineStr"/>
-      <c r="E27" s="276" t="inlineStr"/>
-      <c r="F27" s="276" t="n"/>
-      <c r="G27" s="277" t="n">
+      <c r="C27" s="295" t="inlineStr"/>
+      <c r="D27" s="295" t="inlineStr"/>
+      <c r="E27" s="295" t="inlineStr"/>
+      <c r="F27" s="295" t="n"/>
+      <c r="G27" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="277" t="n">
+      <c r="H27" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="277" t="n">
+      <c r="I27" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="278">
+      <c r="J27" s="297">
         <f>IFERROR(I27/(H27+I27),"")</f>
         <v/>
       </c>
-      <c r="K27" s="276" t="n"/>
-      <c r="L27" s="276" t="n"/>
-      <c r="M27" s="276" t="n"/>
-      <c r="N27" s="276" t="n"/>
-      <c r="O27" s="276" t="n"/>
-      <c r="P27" s="276" t="n"/>
-      <c r="Q27" s="276" t="n"/>
-      <c r="R27" s="276" t="n"/>
-      <c r="S27" s="276" t="n"/>
-    </row>
-    <row r="28" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A28" s="285" t="n">
+      <c r="K27" s="295" t="n"/>
+      <c r="L27" s="295" t="n"/>
+      <c r="M27" s="295" t="n"/>
+      <c r="N27" s="295" t="n"/>
+      <c r="O27" s="295" t="n"/>
+      <c r="P27" s="295" t="n"/>
+      <c r="Q27" s="295" t="n"/>
+      <c r="R27" s="295" t="n"/>
+      <c r="S27" s="295" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="254">
+      <c r="A28" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B28" s="276" t="inlineStr">
+      <c r="B28" s="295" t="inlineStr">
         <is>
           <t>Lacquer-04</t>
         </is>
       </c>
-      <c r="C28" s="276" t="inlineStr"/>
-      <c r="D28" s="276" t="inlineStr"/>
-      <c r="E28" s="276" t="inlineStr"/>
-      <c r="F28" s="276" t="n"/>
-      <c r="G28" s="277" t="n">
+      <c r="C28" s="295" t="inlineStr"/>
+      <c r="D28" s="295" t="inlineStr"/>
+      <c r="E28" s="295" t="inlineStr"/>
+      <c r="F28" s="295" t="n"/>
+      <c r="G28" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="277" t="n">
+      <c r="H28" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="277" t="n">
+      <c r="I28" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="278">
+      <c r="J28" s="297">
         <f>IFERROR(I28/(H28+I28),"")</f>
         <v/>
       </c>
-      <c r="K28" s="276" t="n"/>
-      <c r="L28" s="276" t="n"/>
-      <c r="M28" s="276" t="n"/>
-      <c r="N28" s="276" t="n"/>
-      <c r="O28" s="276" t="n"/>
-      <c r="P28" s="276" t="n"/>
-      <c r="Q28" s="276" t="n"/>
-      <c r="R28" s="276" t="n"/>
-      <c r="S28" s="276" t="n"/>
-    </row>
-    <row r="29" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A29" s="285" t="n">
+      <c r="K28" s="295" t="n"/>
+      <c r="L28" s="295" t="n"/>
+      <c r="M28" s="295" t="n"/>
+      <c r="N28" s="295" t="n"/>
+      <c r="O28" s="295" t="n"/>
+      <c r="P28" s="295" t="n"/>
+      <c r="Q28" s="295" t="n"/>
+      <c r="R28" s="295" t="n"/>
+      <c r="S28" s="295" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="254">
+      <c r="A29" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B29" s="276" t="inlineStr">
+      <c r="B29" s="295" t="inlineStr">
         <is>
           <t>Latex-01</t>
         </is>
       </c>
-      <c r="C29" s="276" t="inlineStr"/>
-      <c r="D29" s="276" t="inlineStr"/>
-      <c r="E29" s="276" t="inlineStr"/>
-      <c r="F29" s="276" t="n"/>
-      <c r="G29" s="277" t="n">
+      <c r="C29" s="295" t="inlineStr"/>
+      <c r="D29" s="295" t="inlineStr"/>
+      <c r="E29" s="295" t="inlineStr"/>
+      <c r="F29" s="295" t="n"/>
+      <c r="G29" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="277" t="n">
+      <c r="H29" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="277" t="n">
+      <c r="I29" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="278">
+      <c r="J29" s="297">
         <f>IFERROR(I29/(H29+I29),"")</f>
         <v/>
       </c>
-      <c r="K29" s="276" t="n"/>
-      <c r="L29" s="276" t="n"/>
-      <c r="M29" s="276" t="n"/>
-      <c r="N29" s="276" t="n"/>
-      <c r="O29" s="276" t="n"/>
-      <c r="P29" s="276" t="n"/>
-      <c r="Q29" s="276" t="n"/>
-      <c r="R29" s="276" t="n"/>
-      <c r="S29" s="276" t="n"/>
-    </row>
-    <row r="30" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A30" s="285" t="n">
+      <c r="K29" s="295" t="n"/>
+      <c r="L29" s="295" t="n"/>
+      <c r="M29" s="295" t="n"/>
+      <c r="N29" s="295" t="n"/>
+      <c r="O29" s="295" t="n"/>
+      <c r="P29" s="295" t="n"/>
+      <c r="Q29" s="295" t="n"/>
+      <c r="R29" s="295" t="n"/>
+      <c r="S29" s="295" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="254">
+      <c r="A30" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B30" s="276" t="inlineStr">
+      <c r="B30" s="295" t="inlineStr">
         <is>
           <t>PF Machine</t>
         </is>
       </c>
-      <c r="C30" s="276" t="inlineStr">
+      <c r="C30" s="295" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D30" s="276" t="inlineStr">
+      <c r="D30" s="295" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E30" s="276" t="inlineStr">
+      <c r="E30" s="295" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F30" s="276" t="n">
+      <c r="F30" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="G30" s="277" t="n">
+      <c r="G30" s="296" t="n">
         <v>14005</v>
       </c>
-      <c r="H30" s="277" t="n">
+      <c r="H30" s="296" t="n">
         <v>12535</v>
       </c>
-      <c r="I30" s="277" t="n">
+      <c r="I30" s="296" t="n">
         <v>1470</v>
       </c>
-      <c r="J30" s="278">
+      <c r="J30" s="297">
         <f>IFERROR(I30/(H30+I30),"")</f>
         <v/>
       </c>
-      <c r="K30" s="276" t="n">
+      <c r="K30" s="295" t="n">
         <v>140</v>
       </c>
-      <c r="L30" s="276" t="n"/>
-      <c r="M30" s="276" t="n"/>
-      <c r="N30" s="276" t="n"/>
-      <c r="O30" s="276" t="n"/>
-      <c r="P30" s="276" t="n">
+      <c r="L30" s="295" t="n"/>
+      <c r="M30" s="295" t="n"/>
+      <c r="N30" s="295" t="n"/>
+      <c r="O30" s="295" t="n"/>
+      <c r="P30" s="295" t="n">
         <v>80</v>
       </c>
-      <c r="Q30" s="276" t="n"/>
-      <c r="R30" s="276" t="n"/>
-      <c r="S30" s="276" t="n"/>
-    </row>
-    <row r="31" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A31" s="285" t="n">
+      <c r="Q30" s="295" t="n"/>
+      <c r="R30" s="295" t="n"/>
+      <c r="S30" s="295" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="254">
+      <c r="A31" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B31" s="276" t="inlineStr">
+      <c r="B31" s="295" t="inlineStr">
         <is>
           <t>Press-04</t>
         </is>
       </c>
-      <c r="C31" s="276" t="inlineStr"/>
-      <c r="D31" s="276" t="inlineStr"/>
-      <c r="E31" s="276" t="inlineStr"/>
-      <c r="F31" s="276" t="n"/>
-      <c r="G31" s="277" t="n">
+      <c r="C31" s="295" t="inlineStr"/>
+      <c r="D31" s="295" t="inlineStr"/>
+      <c r="E31" s="295" t="inlineStr"/>
+      <c r="F31" s="295" t="n"/>
+      <c r="G31" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="277" t="n">
+      <c r="H31" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="277" t="n">
+      <c r="I31" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="278">
+      <c r="J31" s="297">
         <f>IFERROR(I31/(H31+I31),"")</f>
         <v/>
       </c>
-      <c r="K31" s="276" t="n"/>
-      <c r="L31" s="276" t="n"/>
-      <c r="M31" s="276" t="n"/>
-      <c r="N31" s="276" t="n"/>
-      <c r="O31" s="276" t="n"/>
-      <c r="P31" s="276" t="n"/>
-      <c r="Q31" s="276" t="n"/>
-      <c r="R31" s="276" t="n"/>
-      <c r="S31" s="276" t="n"/>
-    </row>
-    <row r="32" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A32" s="285" t="n">
+      <c r="K31" s="295" t="n"/>
+      <c r="L31" s="295" t="n"/>
+      <c r="M31" s="295" t="n"/>
+      <c r="N31" s="295" t="n"/>
+      <c r="O31" s="295" t="n"/>
+      <c r="P31" s="295" t="n"/>
+      <c r="Q31" s="295" t="n"/>
+      <c r="R31" s="295" t="n"/>
+      <c r="S31" s="295" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="254">
+      <c r="A32" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B32" s="276" t="inlineStr">
+      <c r="B32" s="295" t="inlineStr">
         <is>
           <t>Press-06</t>
         </is>
       </c>
-      <c r="C32" s="276" t="inlineStr"/>
-      <c r="D32" s="276" t="inlineStr"/>
-      <c r="E32" s="276" t="inlineStr"/>
-      <c r="F32" s="276" t="n"/>
-      <c r="G32" s="277" t="n">
+      <c r="C32" s="295" t="inlineStr"/>
+      <c r="D32" s="295" t="inlineStr"/>
+      <c r="E32" s="295" t="inlineStr"/>
+      <c r="F32" s="295" t="n"/>
+      <c r="G32" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="277" t="n">
+      <c r="H32" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="277" t="n">
+      <c r="I32" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="278">
+      <c r="J32" s="297">
         <f>IFERROR(I32/(H32+I32),"")</f>
         <v/>
       </c>
-      <c r="K32" s="276" t="n"/>
-      <c r="L32" s="276" t="n"/>
-      <c r="M32" s="276" t="n"/>
-      <c r="N32" s="276" t="n"/>
-      <c r="O32" s="276" t="n"/>
-      <c r="P32" s="276" t="n"/>
-      <c r="Q32" s="276" t="n"/>
-      <c r="R32" s="276" t="n"/>
-      <c r="S32" s="276" t="n"/>
-    </row>
-    <row r="33" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A33" s="285" t="n">
+      <c r="K32" s="295" t="n"/>
+      <c r="L32" s="295" t="n"/>
+      <c r="M32" s="295" t="n"/>
+      <c r="N32" s="295" t="n"/>
+      <c r="O32" s="295" t="n"/>
+      <c r="P32" s="295" t="n"/>
+      <c r="Q32" s="295" t="n"/>
+      <c r="R32" s="295" t="n"/>
+      <c r="S32" s="295" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="254">
+      <c r="A33" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B33" s="276" t="inlineStr">
+      <c r="B33" s="295" t="inlineStr">
         <is>
           <t>Printing-03</t>
         </is>
       </c>
-      <c r="C33" s="276" t="inlineStr"/>
-      <c r="D33" s="276" t="inlineStr"/>
-      <c r="E33" s="276" t="inlineStr"/>
-      <c r="F33" s="276" t="n"/>
-      <c r="G33" s="277" t="n">
+      <c r="C33" s="295" t="inlineStr"/>
+      <c r="D33" s="295" t="inlineStr"/>
+      <c r="E33" s="295" t="inlineStr"/>
+      <c r="F33" s="295" t="n"/>
+      <c r="G33" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="277" t="n">
+      <c r="H33" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="277" t="n">
+      <c r="I33" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="278">
+      <c r="J33" s="297">
         <f>IFERROR(I33/(H33+I33),"")</f>
         <v/>
       </c>
-      <c r="K33" s="276" t="n"/>
-      <c r="L33" s="276" t="n"/>
-      <c r="M33" s="276" t="n"/>
-      <c r="N33" s="276" t="n"/>
-      <c r="O33" s="276" t="n"/>
-      <c r="P33" s="276" t="n"/>
-      <c r="Q33" s="276" t="n"/>
-      <c r="R33" s="276" t="n"/>
-      <c r="S33" s="276" t="n"/>
-    </row>
-    <row r="34" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A34" s="285" t="n">
+      <c r="K33" s="295" t="n"/>
+      <c r="L33" s="295" t="n"/>
+      <c r="M33" s="295" t="n"/>
+      <c r="N33" s="295" t="n"/>
+      <c r="O33" s="295" t="n"/>
+      <c r="P33" s="295" t="n"/>
+      <c r="Q33" s="295" t="n"/>
+      <c r="R33" s="295" t="n"/>
+      <c r="S33" s="295" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="254">
+      <c r="A34" s="298" t="n">
         <v>46178</v>
       </c>
-      <c r="B34" s="276" t="inlineStr">
+      <c r="B34" s="295" t="inlineStr">
         <is>
           <t>Printing-04</t>
         </is>
       </c>
-      <c r="C34" s="276" t="inlineStr"/>
-      <c r="D34" s="276" t="inlineStr"/>
-      <c r="E34" s="276" t="inlineStr"/>
-      <c r="F34" s="276" t="n"/>
-      <c r="G34" s="277" t="n">
+      <c r="C34" s="295" t="inlineStr"/>
+      <c r="D34" s="295" t="inlineStr"/>
+      <c r="E34" s="295" t="inlineStr"/>
+      <c r="F34" s="295" t="n"/>
+      <c r="G34" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="277" t="n">
+      <c r="H34" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="277" t="n">
+      <c r="I34" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="278">
+      <c r="J34" s="297">
         <f>IFERROR(I34/(H34+I34),"")</f>
         <v/>
       </c>
-      <c r="K34" s="276" t="n"/>
-      <c r="L34" s="276" t="n"/>
-      <c r="M34" s="276" t="n"/>
-      <c r="N34" s="276" t="n"/>
-      <c r="O34" s="276" t="n"/>
-      <c r="P34" s="276" t="n"/>
-      <c r="Q34" s="276" t="n"/>
-      <c r="R34" s="276" t="n"/>
-      <c r="S34" s="276" t="n"/>
-    </row>
-    <row r="35" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A35" s="285" t="n">
+      <c r="K34" s="295" t="n"/>
+      <c r="L34" s="295" t="n"/>
+      <c r="M34" s="295" t="n"/>
+      <c r="N34" s="295" t="n"/>
+      <c r="O34" s="295" t="n"/>
+      <c r="P34" s="295" t="n"/>
+      <c r="Q34" s="295" t="n"/>
+      <c r="R34" s="295" t="n"/>
+      <c r="S34" s="295" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="254">
+      <c r="A35" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B35" s="276" t="inlineStr">
+      <c r="B35" s="295" t="inlineStr">
         <is>
           <t>Lacquer-02</t>
         </is>
       </c>
-      <c r="C35" s="276" t="inlineStr"/>
-      <c r="D35" s="276" t="inlineStr"/>
-      <c r="E35" s="276" t="inlineStr"/>
-      <c r="F35" s="276" t="n"/>
-      <c r="G35" s="277" t="n">
+      <c r="C35" s="295" t="inlineStr"/>
+      <c r="D35" s="295" t="inlineStr"/>
+      <c r="E35" s="295" t="inlineStr"/>
+      <c r="F35" s="295" t="n"/>
+      <c r="G35" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="277" t="n">
+      <c r="H35" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="277" t="n">
+      <c r="I35" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="278">
+      <c r="J35" s="297">
         <f>IFERROR(I35/(H35+I35),"")</f>
         <v/>
       </c>
-      <c r="K35" s="276" t="n"/>
-      <c r="L35" s="276" t="n"/>
-      <c r="M35" s="276" t="n"/>
-      <c r="N35" s="276" t="n"/>
-      <c r="O35" s="276" t="n"/>
-      <c r="P35" s="276" t="n"/>
-      <c r="Q35" s="276" t="n"/>
-      <c r="R35" s="276" t="n"/>
-      <c r="S35" s="276" t="n"/>
-    </row>
-    <row r="36" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A36" s="285" t="n">
+      <c r="K35" s="295" t="n"/>
+      <c r="L35" s="295" t="n"/>
+      <c r="M35" s="295" t="n"/>
+      <c r="N35" s="295" t="n"/>
+      <c r="O35" s="295" t="n"/>
+      <c r="P35" s="295" t="n"/>
+      <c r="Q35" s="295" t="n"/>
+      <c r="R35" s="295" t="n"/>
+      <c r="S35" s="295" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="254">
+      <c r="A36" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B36" s="276" t="inlineStr">
+      <c r="B36" s="295" t="inlineStr">
         <is>
           <t>Lacquer-04</t>
         </is>
       </c>
-      <c r="C36" s="276" t="inlineStr"/>
-      <c r="D36" s="276" t="inlineStr"/>
-      <c r="E36" s="276" t="inlineStr"/>
-      <c r="F36" s="276" t="n"/>
-      <c r="G36" s="277" t="n">
+      <c r="C36" s="295" t="inlineStr"/>
+      <c r="D36" s="295" t="inlineStr"/>
+      <c r="E36" s="295" t="inlineStr"/>
+      <c r="F36" s="295" t="n"/>
+      <c r="G36" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="277" t="n">
+      <c r="H36" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="277" t="n">
+      <c r="I36" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="278">
+      <c r="J36" s="297">
         <f>IFERROR(I36/(H36+I36),"")</f>
         <v/>
       </c>
-      <c r="K36" s="276" t="n"/>
-      <c r="L36" s="276" t="n"/>
-      <c r="M36" s="276" t="n"/>
-      <c r="N36" s="276" t="n"/>
-      <c r="O36" s="276" t="n"/>
-      <c r="P36" s="276" t="n"/>
-      <c r="Q36" s="276" t="n"/>
-      <c r="R36" s="276" t="n"/>
-      <c r="S36" s="276" t="n"/>
-    </row>
-    <row r="37" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A37" s="285" t="n">
+      <c r="K36" s="295" t="n"/>
+      <c r="L36" s="295" t="n"/>
+      <c r="M36" s="295" t="n"/>
+      <c r="N36" s="295" t="n"/>
+      <c r="O36" s="295" t="n"/>
+      <c r="P36" s="295" t="n"/>
+      <c r="Q36" s="295" t="n"/>
+      <c r="R36" s="295" t="n"/>
+      <c r="S36" s="295" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="254">
+      <c r="A37" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B37" s="276" t="inlineStr">
+      <c r="B37" s="295" t="inlineStr">
         <is>
           <t>Latex-01</t>
         </is>
       </c>
-      <c r="C37" s="276" t="inlineStr"/>
-      <c r="D37" s="276" t="inlineStr"/>
-      <c r="E37" s="276" t="inlineStr"/>
-      <c r="F37" s="276" t="n"/>
-      <c r="G37" s="277" t="n">
+      <c r="C37" s="295" t="inlineStr"/>
+      <c r="D37" s="295" t="inlineStr"/>
+      <c r="E37" s="295" t="inlineStr"/>
+      <c r="F37" s="295" t="n"/>
+      <c r="G37" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="277" t="n">
+      <c r="H37" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="277" t="n">
+      <c r="I37" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="278">
+      <c r="J37" s="297">
         <f>IFERROR(I37/(H37+I37),"")</f>
         <v/>
       </c>
-      <c r="K37" s="276" t="n"/>
-      <c r="L37" s="276" t="n"/>
-      <c r="M37" s="276" t="n"/>
-      <c r="N37" s="276" t="n"/>
-      <c r="O37" s="276" t="n"/>
-      <c r="P37" s="276" t="n"/>
-      <c r="Q37" s="276" t="n"/>
-      <c r="R37" s="276" t="n"/>
-      <c r="S37" s="276" t="n"/>
-    </row>
-    <row r="38" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A38" s="285" t="n">
+      <c r="K37" s="295" t="n"/>
+      <c r="L37" s="295" t="n"/>
+      <c r="M37" s="295" t="n"/>
+      <c r="N37" s="295" t="n"/>
+      <c r="O37" s="295" t="n"/>
+      <c r="P37" s="295" t="n"/>
+      <c r="Q37" s="295" t="n"/>
+      <c r="R37" s="295" t="n"/>
+      <c r="S37" s="295" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="254">
+      <c r="A38" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B38" s="276" t="inlineStr">
+      <c r="B38" s="295" t="inlineStr">
         <is>
           <t>PF Machine</t>
         </is>
       </c>
-      <c r="C38" s="276" t="inlineStr">
+      <c r="C38" s="295" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D38" s="276" t="inlineStr">
+      <c r="D38" s="295" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E38" s="276" t="inlineStr">
+      <c r="E38" s="295" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F38" s="276" t="n">
+      <c r="F38" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="G38" s="277" t="n">
+      <c r="G38" s="296" t="n">
         <v>12550</v>
       </c>
-      <c r="H38" s="277" t="n">
+      <c r="H38" s="296" t="n">
         <v>11500</v>
       </c>
-      <c r="I38" s="277" t="n">
+      <c r="I38" s="296" t="n">
         <v>1050</v>
       </c>
-      <c r="J38" s="278">
+      <c r="J38" s="297">
         <f>IFERROR(I38/(H38+I38),"")</f>
         <v/>
       </c>
-      <c r="K38" s="276" t="n">
+      <c r="K38" s="295" t="n">
         <v>70</v>
       </c>
-      <c r="L38" s="276" t="n">
+      <c r="L38" s="295" t="n">
         <v>180</v>
       </c>
-      <c r="M38" s="276" t="n"/>
-      <c r="N38" s="276" t="n"/>
-      <c r="O38" s="276" t="n"/>
-      <c r="P38" s="276" t="n">
+      <c r="M38" s="295" t="n"/>
+      <c r="N38" s="295" t="n"/>
+      <c r="O38" s="295" t="n"/>
+      <c r="P38" s="295" t="n">
         <v>50</v>
       </c>
-      <c r="Q38" s="276" t="n"/>
-      <c r="R38" s="276" t="n"/>
-      <c r="S38" s="276" t="n"/>
-    </row>
-    <row r="39" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A39" s="285" t="n">
+      <c r="Q38" s="295" t="n"/>
+      <c r="R38" s="295" t="n"/>
+      <c r="S38" s="295" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="254">
+      <c r="A39" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B39" s="276" t="inlineStr">
+      <c r="B39" s="295" t="inlineStr">
         <is>
           <t>Press-04</t>
         </is>
       </c>
-      <c r="C39" s="276" t="inlineStr"/>
-      <c r="D39" s="276" t="inlineStr"/>
-      <c r="E39" s="276" t="inlineStr"/>
-      <c r="F39" s="276" t="n"/>
-      <c r="G39" s="277" t="n">
+      <c r="C39" s="295" t="inlineStr"/>
+      <c r="D39" s="295" t="inlineStr"/>
+      <c r="E39" s="295" t="inlineStr"/>
+      <c r="F39" s="295" t="n"/>
+      <c r="G39" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="277" t="n">
+      <c r="H39" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="277" t="n">
+      <c r="I39" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="278">
+      <c r="J39" s="297">
         <f>IFERROR(I39/(H39+I39),"")</f>
         <v/>
       </c>
-      <c r="K39" s="276" t="n"/>
-      <c r="L39" s="276" t="n"/>
-      <c r="M39" s="276" t="n"/>
-      <c r="N39" s="276" t="n"/>
-      <c r="O39" s="276" t="n"/>
-      <c r="P39" s="276" t="n"/>
-      <c r="Q39" s="276" t="n"/>
-      <c r="R39" s="276" t="n"/>
-      <c r="S39" s="276" t="n"/>
-    </row>
-    <row r="40" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A40" s="285" t="n">
+      <c r="K39" s="295" t="n"/>
+      <c r="L39" s="295" t="n"/>
+      <c r="M39" s="295" t="n"/>
+      <c r="N39" s="295" t="n"/>
+      <c r="O39" s="295" t="n"/>
+      <c r="P39" s="295" t="n"/>
+      <c r="Q39" s="295" t="n"/>
+      <c r="R39" s="295" t="n"/>
+      <c r="S39" s="295" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="254">
+      <c r="A40" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B40" s="276" t="inlineStr">
+      <c r="B40" s="295" t="inlineStr">
         <is>
           <t>Press-06</t>
         </is>
       </c>
-      <c r="C40" s="276" t="inlineStr"/>
-      <c r="D40" s="276" t="inlineStr"/>
-      <c r="E40" s="276" t="inlineStr"/>
-      <c r="F40" s="276" t="n"/>
-      <c r="G40" s="277" t="n">
+      <c r="C40" s="295" t="inlineStr"/>
+      <c r="D40" s="295" t="inlineStr"/>
+      <c r="E40" s="295" t="inlineStr"/>
+      <c r="F40" s="295" t="n"/>
+      <c r="G40" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="277" t="n">
+      <c r="H40" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="277" t="n">
+      <c r="I40" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="278">
+      <c r="J40" s="297">
         <f>IFERROR(I40/(H40+I40),"")</f>
         <v/>
       </c>
-      <c r="K40" s="276" t="n"/>
-      <c r="L40" s="276" t="n"/>
-      <c r="M40" s="276" t="n"/>
-      <c r="N40" s="276" t="n"/>
-      <c r="O40" s="276" t="n"/>
-      <c r="P40" s="276" t="n"/>
-      <c r="Q40" s="276" t="n"/>
-      <c r="R40" s="276" t="n"/>
-      <c r="S40" s="276" t="n"/>
-    </row>
-    <row r="41" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A41" s="285" t="n">
+      <c r="K40" s="295" t="n"/>
+      <c r="L40" s="295" t="n"/>
+      <c r="M40" s="295" t="n"/>
+      <c r="N40" s="295" t="n"/>
+      <c r="O40" s="295" t="n"/>
+      <c r="P40" s="295" t="n"/>
+      <c r="Q40" s="295" t="n"/>
+      <c r="R40" s="295" t="n"/>
+      <c r="S40" s="295" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="254">
+      <c r="A41" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B41" s="276" t="inlineStr">
+      <c r="B41" s="295" t="inlineStr">
         <is>
           <t>Printing-03</t>
         </is>
       </c>
-      <c r="C41" s="276" t="inlineStr"/>
-      <c r="D41" s="276" t="inlineStr"/>
-      <c r="E41" s="276" t="inlineStr"/>
-      <c r="F41" s="276" t="n"/>
-      <c r="G41" s="277" t="n">
+      <c r="C41" s="295" t="inlineStr"/>
+      <c r="D41" s="295" t="inlineStr"/>
+      <c r="E41" s="295" t="inlineStr"/>
+      <c r="F41" s="295" t="n"/>
+      <c r="G41" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="277" t="n">
+      <c r="H41" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="277" t="n">
+      <c r="I41" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="278">
+      <c r="J41" s="297">
         <f>IFERROR(I41/(H41+I41),"")</f>
         <v/>
       </c>
-      <c r="K41" s="276" t="n"/>
-      <c r="L41" s="276" t="n"/>
-      <c r="M41" s="276" t="n"/>
-      <c r="N41" s="276" t="n"/>
-      <c r="O41" s="276" t="n"/>
-      <c r="P41" s="276" t="n"/>
-      <c r="Q41" s="276" t="n"/>
-      <c r="R41" s="276" t="n"/>
-      <c r="S41" s="276" t="n"/>
-    </row>
-    <row r="42" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A42" s="285" t="n">
+      <c r="K41" s="295" t="n"/>
+      <c r="L41" s="295" t="n"/>
+      <c r="M41" s="295" t="n"/>
+      <c r="N41" s="295" t="n"/>
+      <c r="O41" s="295" t="n"/>
+      <c r="P41" s="295" t="n"/>
+      <c r="Q41" s="295" t="n"/>
+      <c r="R41" s="295" t="n"/>
+      <c r="S41" s="295" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="254">
+      <c r="A42" s="298" t="n">
         <v>46179</v>
       </c>
-      <c r="B42" s="276" t="inlineStr">
+      <c r="B42" s="295" t="inlineStr">
         <is>
           <t>Printing-04</t>
         </is>
       </c>
-      <c r="C42" s="276" t="inlineStr"/>
-      <c r="D42" s="276" t="inlineStr"/>
-      <c r="E42" s="276" t="inlineStr"/>
-      <c r="F42" s="276" t="n"/>
-      <c r="G42" s="277" t="n">
+      <c r="C42" s="295" t="inlineStr"/>
+      <c r="D42" s="295" t="inlineStr"/>
+      <c r="E42" s="295" t="inlineStr"/>
+      <c r="F42" s="295" t="n"/>
+      <c r="G42" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="277" t="n">
+      <c r="H42" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="277" t="n">
+      <c r="I42" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="278">
+      <c r="J42" s="297">
         <f>IFERROR(I42/(H42+I42),"")</f>
         <v/>
       </c>
-      <c r="K42" s="276" t="n"/>
-      <c r="L42" s="276" t="n"/>
-      <c r="M42" s="276" t="n"/>
-      <c r="N42" s="276" t="n"/>
-      <c r="O42" s="276" t="n"/>
-      <c r="P42" s="276" t="n"/>
-      <c r="Q42" s="276" t="n"/>
-      <c r="R42" s="276" t="n"/>
-      <c r="S42" s="276" t="n"/>
-    </row>
-    <row r="43" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A43" s="285" t="n">
+      <c r="K42" s="295" t="n"/>
+      <c r="L42" s="295" t="n"/>
+      <c r="M42" s="295" t="n"/>
+      <c r="N42" s="295" t="n"/>
+      <c r="O42" s="295" t="n"/>
+      <c r="P42" s="295" t="n"/>
+      <c r="Q42" s="295" t="n"/>
+      <c r="R42" s="295" t="n"/>
+      <c r="S42" s="295" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="254">
+      <c r="A43" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B43" s="276" t="inlineStr">
+      <c r="B43" s="295" t="inlineStr">
         <is>
           <t>Lacquer-02</t>
         </is>
       </c>
-      <c r="C43" s="276" t="inlineStr"/>
-      <c r="D43" s="276" t="inlineStr"/>
-      <c r="E43" s="276" t="inlineStr"/>
-      <c r="F43" s="276" t="n"/>
-      <c r="G43" s="277" t="n">
+      <c r="C43" s="295" t="inlineStr"/>
+      <c r="D43" s="295" t="inlineStr"/>
+      <c r="E43" s="295" t="inlineStr"/>
+      <c r="F43" s="295" t="n"/>
+      <c r="G43" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="277" t="n">
+      <c r="H43" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="277" t="n">
+      <c r="I43" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="278">
+      <c r="J43" s="297">
         <f>IFERROR(I43/(H43+I43),"")</f>
         <v/>
       </c>
-      <c r="K43" s="276" t="n"/>
-      <c r="L43" s="276" t="n"/>
-      <c r="M43" s="276" t="n"/>
-      <c r="N43" s="276" t="n"/>
-      <c r="O43" s="276" t="n"/>
-      <c r="P43" s="276" t="n"/>
-      <c r="Q43" s="276" t="n"/>
-      <c r="R43" s="276" t="n"/>
-      <c r="S43" s="276" t="n"/>
-    </row>
-    <row r="44" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A44" s="285" t="n">
+      <c r="K43" s="295" t="n"/>
+      <c r="L43" s="295" t="n"/>
+      <c r="M43" s="295" t="n"/>
+      <c r="N43" s="295" t="n"/>
+      <c r="O43" s="295" t="n"/>
+      <c r="P43" s="295" t="n"/>
+      <c r="Q43" s="295" t="n"/>
+      <c r="R43" s="295" t="n"/>
+      <c r="S43" s="295" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="254">
+      <c r="A44" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B44" s="276" t="inlineStr">
+      <c r="B44" s="295" t="inlineStr">
         <is>
           <t>Lacquer-04</t>
         </is>
       </c>
-      <c r="C44" s="276" t="inlineStr">
+      <c r="C44" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D44" s="276" t="inlineStr">
+      <c r="D44" s="295" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E44" s="276" t="n">
+      <c r="E44" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F44" s="276" t="n">
+      <c r="F44" s="295" t="n">
         <v>6470</v>
       </c>
-      <c r="G44" s="277" t="n">
+      <c r="G44" s="296" t="n">
         <v>21000</v>
       </c>
-      <c r="H44" s="277" t="n">
+      <c r="H44" s="296" t="n">
         <v>20735</v>
       </c>
-      <c r="I44" s="277" t="n">
+      <c r="I44" s="296" t="n">
         <v>265</v>
       </c>
-      <c r="J44" s="278">
+      <c r="J44" s="297">
         <f>IFERROR(I44/(H44+I44),"")</f>
         <v/>
       </c>
-      <c r="K44" s="276" t="n"/>
-      <c r="L44" s="276" t="n"/>
-      <c r="M44" s="276" t="n"/>
-      <c r="N44" s="276" t="n"/>
-      <c r="O44" s="276" t="n"/>
-      <c r="P44" s="276" t="n"/>
-      <c r="Q44" s="276" t="n"/>
-      <c r="R44" s="276" t="n"/>
-      <c r="S44" s="276" t="n"/>
-    </row>
-    <row r="45" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A45" s="285" t="n">
+      <c r="K44" s="295" t="n"/>
+      <c r="L44" s="295" t="n"/>
+      <c r="M44" s="295" t="n"/>
+      <c r="N44" s="295" t="n"/>
+      <c r="O44" s="295" t="n"/>
+      <c r="P44" s="295" t="n"/>
+      <c r="Q44" s="295" t="n"/>
+      <c r="R44" s="295" t="n"/>
+      <c r="S44" s="295" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="254">
+      <c r="A45" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B45" s="276" t="inlineStr">
+      <c r="B45" s="295" t="inlineStr">
         <is>
           <t>Latex-01</t>
         </is>
       </c>
-      <c r="C45" s="276" t="inlineStr"/>
-      <c r="D45" s="276" t="inlineStr"/>
-      <c r="E45" s="276" t="inlineStr"/>
-      <c r="F45" s="276" t="n"/>
-      <c r="G45" s="277" t="n">
+      <c r="C45" s="295" t="inlineStr"/>
+      <c r="D45" s="295" t="inlineStr"/>
+      <c r="E45" s="295" t="inlineStr"/>
+      <c r="F45" s="295" t="n"/>
+      <c r="G45" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="277" t="n">
+      <c r="H45" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="277" t="n">
+      <c r="I45" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="278">
+      <c r="J45" s="297">
         <f>IFERROR(I45/(H45+I45),"")</f>
         <v/>
       </c>
-      <c r="K45" s="276" t="n"/>
-      <c r="L45" s="276" t="n"/>
-      <c r="M45" s="276" t="n"/>
-      <c r="N45" s="276" t="n"/>
-      <c r="O45" s="276" t="n"/>
-      <c r="P45" s="276" t="n"/>
-      <c r="Q45" s="276" t="n"/>
-      <c r="R45" s="276" t="n"/>
-      <c r="S45" s="276" t="n"/>
-    </row>
-    <row r="46" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A46" s="285" t="n">
+      <c r="K45" s="295" t="n"/>
+      <c r="L45" s="295" t="n"/>
+      <c r="M45" s="295" t="n"/>
+      <c r="N45" s="295" t="n"/>
+      <c r="O45" s="295" t="n"/>
+      <c r="P45" s="295" t="n"/>
+      <c r="Q45" s="295" t="n"/>
+      <c r="R45" s="295" t="n"/>
+      <c r="S45" s="295" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="254">
+      <c r="A46" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B46" s="276" t="inlineStr">
+      <c r="B46" s="295" t="inlineStr">
         <is>
           <t>PF Machine</t>
         </is>
       </c>
-      <c r="C46" s="276" t="inlineStr">
+      <c r="C46" s="295" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D46" s="276" t="inlineStr">
+      <c r="D46" s="295" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E46" s="276" t="inlineStr">
+      <c r="E46" s="295" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F46" s="276" t="n">
+      <c r="F46" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="G46" s="277" t="n">
+      <c r="G46" s="296" t="n">
         <v>4080</v>
       </c>
-      <c r="H46" s="277" t="n">
+      <c r="H46" s="296" t="n">
         <v>3680</v>
       </c>
-      <c r="I46" s="277" t="n">
+      <c r="I46" s="296" t="n">
         <v>400</v>
       </c>
-      <c r="J46" s="278">
+      <c r="J46" s="297">
         <f>IFERROR(I46/(H46+I46),"")</f>
         <v/>
       </c>
-      <c r="K46" s="276" t="n">
+      <c r="K46" s="295" t="n">
         <v>150</v>
       </c>
-      <c r="L46" s="276" t="n">
+      <c r="L46" s="295" t="n">
         <v>210</v>
       </c>
-      <c r="M46" s="276" t="n"/>
-      <c r="N46" s="276" t="n"/>
-      <c r="O46" s="276" t="n"/>
-      <c r="P46" s="276" t="n"/>
-      <c r="Q46" s="276" t="n"/>
-      <c r="R46" s="276" t="n"/>
-      <c r="S46" s="276" t="n"/>
-    </row>
-    <row r="47" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A47" s="285" t="n">
+      <c r="M46" s="295" t="n"/>
+      <c r="N46" s="295" t="n"/>
+      <c r="O46" s="295" t="n"/>
+      <c r="P46" s="295" t="n"/>
+      <c r="Q46" s="295" t="n"/>
+      <c r="R46" s="295" t="n"/>
+      <c r="S46" s="295" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="254">
+      <c r="A47" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B47" s="276" t="inlineStr">
+      <c r="B47" s="295" t="inlineStr">
         <is>
           <t>Press-04</t>
         </is>
       </c>
-      <c r="C47" s="276" t="inlineStr"/>
-      <c r="D47" s="276" t="inlineStr"/>
-      <c r="E47" s="276" t="inlineStr"/>
-      <c r="F47" s="276" t="n"/>
-      <c r="G47" s="277" t="n">
+      <c r="C47" s="295" t="inlineStr"/>
+      <c r="D47" s="295" t="inlineStr"/>
+      <c r="E47" s="295" t="inlineStr"/>
+      <c r="F47" s="295" t="n"/>
+      <c r="G47" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="277" t="n">
+      <c r="H47" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="277" t="n">
+      <c r="I47" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="278">
+      <c r="J47" s="297">
         <f>IFERROR(I47/(H47+I47),"")</f>
         <v/>
       </c>
-      <c r="K47" s="276" t="n"/>
-      <c r="L47" s="276" t="n"/>
-      <c r="M47" s="276" t="n"/>
-      <c r="N47" s="276" t="n"/>
-      <c r="O47" s="276" t="n"/>
-      <c r="P47" s="276" t="n"/>
-      <c r="Q47" s="276" t="n"/>
-      <c r="R47" s="276" t="n"/>
-      <c r="S47" s="276" t="n"/>
-    </row>
-    <row r="48" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A48" s="285" t="n">
+      <c r="K47" s="295" t="n"/>
+      <c r="L47" s="295" t="n"/>
+      <c r="M47" s="295" t="n"/>
+      <c r="N47" s="295" t="n"/>
+      <c r="O47" s="295" t="n"/>
+      <c r="P47" s="295" t="n"/>
+      <c r="Q47" s="295" t="n"/>
+      <c r="R47" s="295" t="n"/>
+      <c r="S47" s="295" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="254">
+      <c r="A48" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B48" s="276" t="inlineStr">
+      <c r="B48" s="295" t="inlineStr">
         <is>
           <t>Press-06</t>
         </is>
       </c>
-      <c r="C48" s="276" t="inlineStr">
+      <c r="C48" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D48" s="276" t="inlineStr">
+      <c r="D48" s="295" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E48" s="276" t="n">
+      <c r="E48" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F48" s="276" t="n">
+      <c r="F48" s="295" t="n">
         <v>6470</v>
       </c>
-      <c r="G48" s="277" t="n">
+      <c r="G48" s="296" t="n">
         <v>24000</v>
       </c>
-      <c r="H48" s="277" t="n">
+      <c r="H48" s="296" t="n">
         <v>23850</v>
       </c>
-      <c r="I48" s="277" t="n">
+      <c r="I48" s="296" t="n">
         <v>150</v>
       </c>
-      <c r="J48" s="278">
+      <c r="J48" s="297">
         <f>IFERROR(I48/(H48+I48),"")</f>
         <v/>
       </c>
-      <c r="K48" s="276" t="n"/>
-      <c r="L48" s="276" t="n"/>
-      <c r="M48" s="276" t="n"/>
-      <c r="N48" s="276" t="n"/>
-      <c r="O48" s="276" t="n"/>
-      <c r="P48" s="276" t="n"/>
-      <c r="Q48" s="276" t="n"/>
-      <c r="R48" s="276" t="n"/>
-      <c r="S48" s="276" t="n"/>
-    </row>
-    <row r="49" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A49" s="285" t="n">
+      <c r="K48" s="295" t="n"/>
+      <c r="L48" s="295" t="n"/>
+      <c r="M48" s="295" t="n"/>
+      <c r="N48" s="295" t="n"/>
+      <c r="O48" s="295" t="n"/>
+      <c r="P48" s="295" t="n"/>
+      <c r="Q48" s="295" t="n"/>
+      <c r="R48" s="295" t="n"/>
+      <c r="S48" s="295" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="254">
+      <c r="A49" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B49" s="276" t="inlineStr">
+      <c r="B49" s="295" t="inlineStr">
         <is>
           <t>Printing-03</t>
         </is>
       </c>
-      <c r="C49" s="276" t="inlineStr">
+      <c r="C49" s="295" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D49" s="276" t="inlineStr">
+      <c r="D49" s="295" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E49" s="276" t="n">
+      <c r="E49" s="295" t="n">
         <v>25</v>
       </c>
-      <c r="F49" s="276" t="n">
+      <c r="F49" s="295" t="n">
         <v>6470</v>
       </c>
-      <c r="G49" s="277" t="n">
+      <c r="G49" s="296" t="n">
         <v>15816</v>
       </c>
-      <c r="H49" s="277" t="n">
+      <c r="H49" s="296" t="n">
         <v>15456</v>
       </c>
-      <c r="I49" s="277" t="n">
+      <c r="I49" s="296" t="n">
         <v>360</v>
       </c>
-      <c r="J49" s="278">
+      <c r="J49" s="297">
         <f>IFERROR(I49/(H49+I49),"")</f>
         <v/>
       </c>
-      <c r="K49" s="276" t="n"/>
-      <c r="L49" s="276" t="n"/>
-      <c r="M49" s="276" t="n">
+      <c r="K49" s="295" t="n"/>
+      <c r="L49" s="295" t="n"/>
+      <c r="M49" s="295" t="n">
         <v>120</v>
       </c>
-      <c r="N49" s="276" t="n"/>
-      <c r="O49" s="276" t="n"/>
-      <c r="P49" s="276" t="n"/>
-      <c r="Q49" s="276" t="n"/>
-      <c r="R49" s="276" t="n"/>
-      <c r="S49" s="276" t="n"/>
-    </row>
-    <row r="50" hidden="1" ht="15" customHeight="1" s="254">
-      <c r="A50" s="285" t="n">
+      <c r="N49" s="295" t="n"/>
+      <c r="O49" s="295" t="n"/>
+      <c r="P49" s="295" t="n"/>
+      <c r="Q49" s="295" t="n"/>
+      <c r="R49" s="295" t="n"/>
+      <c r="S49" s="295" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="254">
+      <c r="A50" s="298" t="n">
         <v>46181</v>
       </c>
-      <c r="B50" s="276" t="inlineStr">
+      <c r="B50" s="295" t="inlineStr">
         <is>
           <t>Printing-04</t>
         </is>
       </c>
-      <c r="C50" s="276" t="inlineStr"/>
-      <c r="D50" s="276" t="inlineStr"/>
-      <c r="E50" s="276" t="inlineStr"/>
-      <c r="F50" s="276" t="n"/>
-      <c r="G50" s="277" t="n">
+      <c r="C50" s="295" t="inlineStr"/>
+      <c r="D50" s="295" t="inlineStr"/>
+      <c r="E50" s="295" t="inlineStr"/>
+      <c r="F50" s="295" t="n"/>
+      <c r="G50" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="277" t="n">
+      <c r="H50" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="I50" s="277" t="n">
+      <c r="I50" s="296" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="278">
+      <c r="J50" s="297">
         <f>IFERROR(I50/(H50+I50),"")</f>
         <v/>
       </c>
-      <c r="K50" s="276" t="n"/>
-      <c r="L50" s="276" t="n"/>
-      <c r="M50" s="276" t="n"/>
-      <c r="N50" s="276" t="n"/>
-      <c r="O50" s="276" t="n"/>
-      <c r="P50" s="276" t="n"/>
-      <c r="Q50" s="276" t="n"/>
-      <c r="R50" s="276" t="n"/>
-      <c r="S50" s="276" t="n"/>
-    </row>
-    <row r="51" hidden="1" ht="15" customHeight="1" s="254">
+      <c r="K50" s="295" t="n"/>
+      <c r="L50" s="295" t="n"/>
+      <c r="M50" s="295" t="n"/>
+      <c r="N50" s="295" t="n"/>
+      <c r="O50" s="295" t="n"/>
+      <c r="P50" s="295" t="n"/>
+      <c r="Q50" s="295" t="n"/>
+      <c r="R50" s="295" t="n"/>
+      <c r="S50" s="295" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="254">
       <c r="A51" s="191" t="n"/>
       <c r="B51" s="192" t="n"/>
       <c r="C51" s="192" t="n"/>
@@ -42539,7 +42537,7 @@
       <c r="R51" s="192" t="n"/>
       <c r="S51" s="192" t="n"/>
     </row>
-    <row r="52" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="52" ht="15" customHeight="1" s="254">
       <c r="A52" s="191" t="n"/>
       <c r="B52" s="192" t="n"/>
       <c r="C52" s="192" t="n"/>
@@ -42560,7 +42558,7 @@
       <c r="R52" s="192" t="n"/>
       <c r="S52" s="192" t="n"/>
     </row>
-    <row r="53" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="53" ht="15" customHeight="1" s="254">
       <c r="A53" s="191" t="n"/>
       <c r="B53" s="192" t="n"/>
       <c r="C53" s="192" t="n"/>
@@ -42581,7 +42579,7 @@
       <c r="R53" s="192" t="n"/>
       <c r="S53" s="192" t="n"/>
     </row>
-    <row r="54" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="54" ht="15" customHeight="1" s="254">
       <c r="A54" s="191" t="n"/>
       <c r="B54" s="192" t="n"/>
       <c r="C54" s="192" t="n"/>
@@ -42602,7 +42600,7 @@
       <c r="R54" s="192" t="n"/>
       <c r="S54" s="192" t="n"/>
     </row>
-    <row r="55" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="55" ht="15" customHeight="1" s="254">
       <c r="A55" s="191" t="n"/>
       <c r="B55" s="192" t="n"/>
       <c r="C55" s="192" t="n"/>
@@ -42623,7 +42621,7 @@
       <c r="R55" s="192" t="n"/>
       <c r="S55" s="192" t="n"/>
     </row>
-    <row r="56" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="56" ht="15" customHeight="1" s="254">
       <c r="A56" s="191" t="n"/>
       <c r="B56" s="192" t="n"/>
       <c r="C56" s="192" t="n"/>
@@ -42644,7 +42642,7 @@
       <c r="R56" s="192" t="n"/>
       <c r="S56" s="192" t="n"/>
     </row>
-    <row r="57" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="57" ht="15" customHeight="1" s="254">
       <c r="A57" s="191" t="n"/>
       <c r="B57" s="192" t="n"/>
       <c r="C57" s="192" t="n"/>
@@ -42665,7 +42663,7 @@
       <c r="R57" s="192" t="n"/>
       <c r="S57" s="192" t="n"/>
     </row>
-    <row r="58" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="58" ht="15" customHeight="1" s="254">
       <c r="A58" s="191" t="n"/>
       <c r="B58" s="192" t="n"/>
       <c r="C58" s="192" t="n"/>
@@ -42686,7 +42684,7 @@
       <c r="R58" s="192" t="n"/>
       <c r="S58" s="192" t="n"/>
     </row>
-    <row r="59" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="59" ht="15" customHeight="1" s="254">
       <c r="A59" s="191" t="n"/>
       <c r="B59" s="192" t="n"/>
       <c r="C59" s="192" t="n"/>
@@ -42707,7 +42705,7 @@
       <c r="R59" s="192" t="n"/>
       <c r="S59" s="192" t="n"/>
     </row>
-    <row r="60" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="60" ht="15" customHeight="1" s="254">
       <c r="A60" s="191" t="n"/>
       <c r="B60" s="192" t="n"/>
       <c r="C60" s="192" t="n"/>
@@ -42728,7 +42726,7 @@
       <c r="R60" s="192" t="n"/>
       <c r="S60" s="192" t="n"/>
     </row>
-    <row r="61" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="61" ht="15" customHeight="1" s="254">
       <c r="A61" s="191" t="n"/>
       <c r="B61" s="192" t="n"/>
       <c r="C61" s="192" t="n"/>
@@ -42749,7 +42747,7 @@
       <c r="R61" s="192" t="n"/>
       <c r="S61" s="192" t="n"/>
     </row>
-    <row r="62" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="62" ht="15" customHeight="1" s="254">
       <c r="A62" s="191" t="n"/>
       <c r="B62" s="192" t="n"/>
       <c r="C62" s="192" t="n"/>
@@ -42770,7 +42768,7 @@
       <c r="R62" s="192" t="n"/>
       <c r="S62" s="192" t="n"/>
     </row>
-    <row r="63" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="63" ht="15" customHeight="1" s="254">
       <c r="A63" s="191" t="n"/>
       <c r="B63" s="192" t="n"/>
       <c r="C63" s="192" t="n"/>
@@ -42791,7 +42789,7 @@
       <c r="R63" s="192" t="n"/>
       <c r="S63" s="192" t="n"/>
     </row>
-    <row r="64" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="64" ht="15" customHeight="1" s="254">
       <c r="A64" s="191" t="n"/>
       <c r="B64" s="192" t="n"/>
       <c r="C64" s="192" t="n"/>
@@ -42812,7 +42810,7 @@
       <c r="R64" s="192" t="n"/>
       <c r="S64" s="192" t="n"/>
     </row>
-    <row r="65" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="65" ht="15" customHeight="1" s="254">
       <c r="A65" s="191" t="n"/>
       <c r="B65" s="192" t="n"/>
       <c r="C65" s="192" t="n"/>
@@ -42833,7 +42831,7 @@
       <c r="R65" s="192" t="n"/>
       <c r="S65" s="192" t="n"/>
     </row>
-    <row r="66" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="66" ht="15" customHeight="1" s="254">
       <c r="A66" s="191" t="n"/>
       <c r="B66" s="192" t="n"/>
       <c r="C66" s="192" t="n"/>
@@ -42854,7 +42852,7 @@
       <c r="R66" s="192" t="n"/>
       <c r="S66" s="192" t="n"/>
     </row>
-    <row r="67" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="67" ht="15" customHeight="1" s="254">
       <c r="A67" s="191" t="n"/>
       <c r="B67" s="192" t="n"/>
       <c r="C67" s="192" t="n"/>
@@ -42875,7 +42873,7 @@
       <c r="R67" s="192" t="n"/>
       <c r="S67" s="192" t="n"/>
     </row>
-    <row r="68" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="68" ht="15" customHeight="1" s="254">
       <c r="A68" s="191" t="n"/>
       <c r="B68" s="192" t="n"/>
       <c r="C68" s="192" t="n"/>
@@ -42896,7 +42894,7 @@
       <c r="R68" s="192" t="n"/>
       <c r="S68" s="192" t="n"/>
     </row>
-    <row r="69" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="69" ht="15" customHeight="1" s="254">
       <c r="A69" s="191" t="n"/>
       <c r="B69" s="192" t="n"/>
       <c r="C69" s="192" t="n"/>
@@ -42917,7 +42915,7 @@
       <c r="R69" s="192" t="n"/>
       <c r="S69" s="192" t="n"/>
     </row>
-    <row r="70" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="70" ht="15" customHeight="1" s="254">
       <c r="A70" s="191" t="n"/>
       <c r="B70" s="192" t="n"/>
       <c r="C70" s="192" t="n"/>
@@ -42938,7 +42936,7 @@
       <c r="R70" s="192" t="n"/>
       <c r="S70" s="192" t="n"/>
     </row>
-    <row r="71" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="71" ht="15" customHeight="1" s="254">
       <c r="A71" s="191" t="n"/>
       <c r="B71" s="192" t="n"/>
       <c r="C71" s="192" t="n"/>
@@ -42959,7 +42957,7 @@
       <c r="R71" s="192" t="n"/>
       <c r="S71" s="192" t="n"/>
     </row>
-    <row r="72" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="72" ht="15" customHeight="1" s="254">
       <c r="A72" s="191" t="n"/>
       <c r="B72" s="192" t="n"/>
       <c r="C72" s="192" t="n"/>
@@ -42980,7 +42978,7 @@
       <c r="R72" s="192" t="n"/>
       <c r="S72" s="192" t="n"/>
     </row>
-    <row r="73" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="73" ht="15" customHeight="1" s="254">
       <c r="A73" s="191" t="n"/>
       <c r="B73" s="192" t="n"/>
       <c r="C73" s="192" t="n"/>
@@ -43001,7 +42999,7 @@
       <c r="R73" s="192" t="n"/>
       <c r="S73" s="192" t="n"/>
     </row>
-    <row r="74" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="74" ht="15" customHeight="1" s="254">
       <c r="A74" s="191" t="n"/>
       <c r="B74" s="192" t="n"/>
       <c r="C74" s="192" t="n"/>
@@ -43022,7 +43020,7 @@
       <c r="R74" s="192" t="n"/>
       <c r="S74" s="192" t="n"/>
     </row>
-    <row r="75" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="75" ht="15" customHeight="1" s="254">
       <c r="A75" s="191" t="n"/>
       <c r="B75" s="192" t="n"/>
       <c r="C75" s="192" t="n"/>
@@ -43043,7 +43041,7 @@
       <c r="R75" s="192" t="n"/>
       <c r="S75" s="192" t="n"/>
     </row>
-    <row r="76" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="76" ht="15" customHeight="1" s="254">
       <c r="A76" s="191" t="n"/>
       <c r="B76" s="192" t="n"/>
       <c r="C76" s="192" t="n"/>
@@ -43064,7 +43062,7 @@
       <c r="R76" s="192" t="n"/>
       <c r="S76" s="192" t="n"/>
     </row>
-    <row r="77" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="77" ht="15" customHeight="1" s="254">
       <c r="A77" s="191" t="n"/>
       <c r="B77" s="192" t="n"/>
       <c r="C77" s="192" t="n"/>
@@ -43085,7 +43083,7 @@
       <c r="R77" s="192" t="n"/>
       <c r="S77" s="192" t="n"/>
     </row>
-    <row r="78" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="78" ht="15" customHeight="1" s="254">
       <c r="A78" s="191" t="n"/>
       <c r="B78" s="192" t="n"/>
       <c r="C78" s="192" t="n"/>
@@ -43106,7 +43104,7 @@
       <c r="R78" s="192" t="n"/>
       <c r="S78" s="192" t="n"/>
     </row>
-    <row r="79" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="79" ht="15" customHeight="1" s="254">
       <c r="A79" s="191" t="n"/>
       <c r="B79" s="192" t="n"/>
       <c r="C79" s="192" t="n"/>
@@ -43127,7 +43125,7 @@
       <c r="R79" s="192" t="n"/>
       <c r="S79" s="192" t="n"/>
     </row>
-    <row r="80" hidden="1" ht="15" customHeight="1" s="254">
+    <row r="80" ht="15" customHeight="1" s="254">
       <c r="A80" s="191" t="n"/>
       <c r="B80" s="192" t="n"/>
       <c r="C80" s="192" t="n"/>
@@ -45550,18 +45548,6 @@
       <c r="J247" s="106" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S80">
-    <filterColumn colId="1" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="Printing-03"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="25"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -45587,7 +45573,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="254">
-      <c r="A1" s="279" t="inlineStr">
+      <c r="A1" s="275" t="inlineStr">
         <is>
           <t>BOM ISSUES — ERP Action Register (v10.21 · May 2026)</t>
         </is>
@@ -45624,7 +45610,7 @@
       <c r="K3" s="116" t="n"/>
     </row>
     <row r="4" ht="21.95" customHeight="1" s="254">
-      <c r="A4" s="279" t="inlineStr">
+      <c r="A4" s="275" t="inlineStr">
         <is>
           <t>S1 — NEW ERP BOMs REQUIRED: TUBE PRODUCTS</t>
         </is>
@@ -45880,7 +45866,7 @@
       <c r="K11" s="125" t="n"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" s="254">
-      <c r="A12" s="279" t="inlineStr">
+      <c r="A12" s="275" t="inlineStr">
         <is>
           <t>S3 — BOM RATE CORRECTIONS: Fix quantities in existing ERP BOMs</t>
         </is>
@@ -46289,7 +46275,7 @@
       <c r="K22" s="126" t="n"/>
     </row>
     <row r="23" ht="21.95" customHeight="1" s="254">
-      <c r="A23" s="279" t="inlineStr">
+      <c r="A23" s="275" t="inlineStr">
         <is>
           <t>S4 — MISSING MATERIAL LINES: Add to existing ERP BOMs</t>
         </is>
@@ -46652,7 +46638,7 @@
       <c r="K33" s="125" t="n"/>
     </row>
     <row r="34" ht="21.95" customHeight="1" s="254">
-      <c r="A34" s="279" t="inlineStr">
+      <c r="A34" s="275" t="inlineStr">
         <is>
           <t>S5 — ITEM ID CHANGES: Applied in local BOM. Must be replicated in ERP (delete old line, add new line)</t>
         </is>
@@ -47869,7 +47855,7 @@
       <c r="K64" s="131" t="n"/>
     </row>
     <row r="65" ht="21.95" customHeight="1" s="254">
-      <c r="A65" s="279" t="inlineStr">
+      <c r="A65" s="275" t="inlineStr">
         <is>
           <t>S6 — ITEM ID QUERIES: Confirm with Rehan before finalising</t>
         </is>
@@ -48217,7 +48203,7 @@
       <c r="K74" s="116" t="n"/>
     </row>
     <row r="75" ht="21.95" customHeight="1" s="254">
-      <c r="A75" s="279" t="inlineStr">
+      <c r="A75" s="275" t="inlineStr">
         <is>
           <t>S7 — ERP ITEM NAME CORRECTIONS: LACQUER spelling (LACQUAR → LACQUER). Fixed in local BOM. ERP item master still incorrect.</t>
         </is>
@@ -48375,7 +48361,7 @@
       <c r="K80" s="116" t="n"/>
     </row>
     <row r="81" ht="21.95" customHeight="1" s="254">
-      <c r="A81" s="279" t="inlineStr">
+      <c r="A81" s="275" t="inlineStr">
         <is>
           <t>S8 — SLUG CHANGE: 30mm diameter products — 30×4.3 (Item 2) → 30×4.5 S/M (Item 406). Effective 21-Apr-2026. Local BOM updated. ERP pending.</t>
         </is>
@@ -48732,7 +48718,7 @@
       <c r="K91" s="116" t="n"/>
     </row>
     <row r="92" ht="21.95" customHeight="1" s="254">
-      <c r="A92" s="279" t="inlineStr">
+      <c r="A92" s="275" t="inlineStr">
         <is>
           <t>S9 — INK MANAGEMENT (Historical Average Method — BOM-based tracking not applicable)</t>
         </is>
@@ -49977,11 +49963,11 @@
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -50008,14 +49994,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="254">
-      <c r="A1" s="280" t="inlineStr">
+      <c r="A1" s="276" t="inlineStr">
         <is>
           <t>FG STOCK IN HAND — Last Updated: 09-Jun-2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="254">
-      <c r="A2" s="281" t="inlineStr">
+      <c r="A2" s="277" t="inlineStr">
         <is>
           <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
         </is>
@@ -50098,7 +50084,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H4" s="289" t="inlineStr">
+      <c r="H4" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50138,7 +50124,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H5" s="289" t="inlineStr">
+      <c r="H5" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50178,7 +50164,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H6" s="289" t="inlineStr">
+      <c r="H6" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50218,7 +50204,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H7" s="289" t="inlineStr">
+      <c r="H7" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50258,7 +50244,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H8" s="289" t="inlineStr">
+      <c r="H8" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50298,7 +50284,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H9" s="289" t="inlineStr">
+      <c r="H9" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50338,7 +50324,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H10" s="289" t="inlineStr">
+      <c r="H10" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50378,7 +50364,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H11" s="289" t="inlineStr">
+      <c r="H11" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50418,7 +50404,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H12" s="289" t="inlineStr">
+      <c r="H12" s="302" t="inlineStr">
         <is>
           <t>Ready for dispatch</t>
         </is>
@@ -50458,7 +50444,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H13" s="289" t="inlineStr">
+      <c r="H13" s="302" t="inlineStr">
         <is>
           <t>No JOF</t>
         </is>
@@ -50498,7 +50484,7 @@
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="H14" s="293" t="inlineStr">
+      <c r="H14" s="306" t="inlineStr">
         <is>
           <t>To be dispatch after packing</t>
         </is>
@@ -50538,7 +50524,7 @@
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="H15" s="293" t="inlineStr">
+      <c r="H15" s="306" t="inlineStr">
         <is>
           <t>To be dispatch after packing</t>
         </is>
@@ -50578,7 +50564,7 @@
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="H16" s="293" t="inlineStr">
+      <c r="H16" s="306" t="inlineStr">
         <is>
           <t>To be dispatch after packing</t>
         </is>
@@ -50618,7 +50604,7 @@
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="H17" s="293" t="inlineStr">
+      <c r="H17" s="306" t="inlineStr">
         <is>
           <t>Cap Not Available</t>
         </is>
@@ -50658,7 +50644,7 @@
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="H18" s="293" t="inlineStr">
+      <c r="H18" s="306" t="inlineStr">
         <is>
           <t>Cap Not Available</t>
         </is>
@@ -50698,7 +50684,7 @@
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="H19" s="293" t="inlineStr">
+      <c r="H19" s="306" t="inlineStr">
         <is>
           <t>Cap Not Available</t>
         </is>
@@ -50709,1120 +50695,1120 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="254">
-      <c r="A20" s="294" t="n"/>
-      <c r="B20" s="294" t="n"/>
-      <c r="C20" s="295" t="n"/>
-      <c r="D20" s="295" t="n"/>
-      <c r="E20" s="294" t="n"/>
-      <c r="F20" s="296" t="n"/>
-      <c r="G20" s="294" t="n"/>
-      <c r="H20" s="297" t="n"/>
+      <c r="A20" s="307" t="n"/>
+      <c r="B20" s="307" t="n"/>
+      <c r="C20" s="308" t="n"/>
+      <c r="D20" s="308" t="n"/>
+      <c r="E20" s="307" t="n"/>
+      <c r="F20" s="309" t="n"/>
+      <c r="G20" s="307" t="n"/>
+      <c r="H20" s="310" t="n"/>
       <c r="I20" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B20)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="254">
-      <c r="A21" s="294" t="n"/>
-      <c r="B21" s="294" t="n"/>
-      <c r="C21" s="295" t="n"/>
-      <c r="D21" s="295" t="n"/>
-      <c r="E21" s="294" t="n"/>
-      <c r="F21" s="296" t="n"/>
-      <c r="G21" s="294" t="n"/>
-      <c r="H21" s="297" t="n"/>
+      <c r="A21" s="307" t="n"/>
+      <c r="B21" s="307" t="n"/>
+      <c r="C21" s="308" t="n"/>
+      <c r="D21" s="308" t="n"/>
+      <c r="E21" s="307" t="n"/>
+      <c r="F21" s="309" t="n"/>
+      <c r="G21" s="307" t="n"/>
+      <c r="H21" s="310" t="n"/>
       <c r="I21" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B21)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="254">
-      <c r="A22" s="294" t="n"/>
-      <c r="B22" s="294" t="n"/>
-      <c r="C22" s="295" t="n"/>
-      <c r="D22" s="295" t="n"/>
-      <c r="E22" s="294" t="n"/>
-      <c r="F22" s="296" t="n"/>
-      <c r="G22" s="294" t="n"/>
-      <c r="H22" s="297" t="n"/>
+      <c r="A22" s="307" t="n"/>
+      <c r="B22" s="307" t="n"/>
+      <c r="C22" s="308" t="n"/>
+      <c r="D22" s="308" t="n"/>
+      <c r="E22" s="307" t="n"/>
+      <c r="F22" s="309" t="n"/>
+      <c r="G22" s="307" t="n"/>
+      <c r="H22" s="310" t="n"/>
       <c r="I22" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B22)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="254">
-      <c r="A23" s="294" t="n"/>
-      <c r="B23" s="294" t="n"/>
-      <c r="C23" s="295" t="n"/>
-      <c r="D23" s="295" t="n"/>
-      <c r="E23" s="294" t="n"/>
-      <c r="F23" s="296" t="n"/>
-      <c r="G23" s="294" t="n"/>
-      <c r="H23" s="297" t="n"/>
+      <c r="A23" s="307" t="n"/>
+      <c r="B23" s="307" t="n"/>
+      <c r="C23" s="308" t="n"/>
+      <c r="D23" s="308" t="n"/>
+      <c r="E23" s="307" t="n"/>
+      <c r="F23" s="309" t="n"/>
+      <c r="G23" s="307" t="n"/>
+      <c r="H23" s="310" t="n"/>
       <c r="I23" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B23)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="254">
-      <c r="A24" s="294" t="n"/>
-      <c r="B24" s="294" t="n"/>
-      <c r="C24" s="295" t="n"/>
-      <c r="D24" s="295" t="n"/>
-      <c r="E24" s="294" t="n"/>
-      <c r="F24" s="296" t="n"/>
-      <c r="G24" s="294" t="n"/>
-      <c r="H24" s="297" t="n"/>
+      <c r="A24" s="307" t="n"/>
+      <c r="B24" s="307" t="n"/>
+      <c r="C24" s="308" t="n"/>
+      <c r="D24" s="308" t="n"/>
+      <c r="E24" s="307" t="n"/>
+      <c r="F24" s="309" t="n"/>
+      <c r="G24" s="307" t="n"/>
+      <c r="H24" s="310" t="n"/>
       <c r="I24" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B24)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="254">
-      <c r="A25" s="294" t="n"/>
-      <c r="B25" s="294" t="n"/>
-      <c r="C25" s="295" t="n"/>
-      <c r="D25" s="295" t="n"/>
-      <c r="E25" s="294" t="n"/>
-      <c r="F25" s="296" t="n"/>
-      <c r="G25" s="294" t="n"/>
-      <c r="H25" s="297" t="n"/>
+      <c r="A25" s="307" t="n"/>
+      <c r="B25" s="307" t="n"/>
+      <c r="C25" s="308" t="n"/>
+      <c r="D25" s="308" t="n"/>
+      <c r="E25" s="307" t="n"/>
+      <c r="F25" s="309" t="n"/>
+      <c r="G25" s="307" t="n"/>
+      <c r="H25" s="310" t="n"/>
       <c r="I25" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B25)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="254">
-      <c r="A26" s="294" t="n"/>
-      <c r="B26" s="294" t="n"/>
-      <c r="C26" s="295" t="n"/>
-      <c r="D26" s="295" t="n"/>
-      <c r="E26" s="294" t="n"/>
-      <c r="F26" s="296" t="n"/>
-      <c r="G26" s="294" t="n"/>
-      <c r="H26" s="297" t="n"/>
+      <c r="A26" s="307" t="n"/>
+      <c r="B26" s="307" t="n"/>
+      <c r="C26" s="308" t="n"/>
+      <c r="D26" s="308" t="n"/>
+      <c r="E26" s="307" t="n"/>
+      <c r="F26" s="309" t="n"/>
+      <c r="G26" s="307" t="n"/>
+      <c r="H26" s="310" t="n"/>
       <c r="I26" s="110">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B26)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="254">
-      <c r="A27" s="294" t="n"/>
-      <c r="B27" s="294" t="n"/>
-      <c r="C27" s="295" t="n"/>
-      <c r="D27" s="295" t="n"/>
-      <c r="E27" s="294" t="n"/>
-      <c r="F27" s="296" t="n"/>
-      <c r="G27" s="294" t="n"/>
-      <c r="H27" s="297" t="n"/>
+      <c r="A27" s="307" t="n"/>
+      <c r="B27" s="307" t="n"/>
+      <c r="C27" s="308" t="n"/>
+      <c r="D27" s="308" t="n"/>
+      <c r="E27" s="307" t="n"/>
+      <c r="F27" s="309" t="n"/>
+      <c r="G27" s="307" t="n"/>
+      <c r="H27" s="310" t="n"/>
       <c r="I27" s="111">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B27)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="254">
-      <c r="A28" s="298" t="n"/>
-      <c r="B28" s="298" t="n"/>
-      <c r="C28" s="298" t="n"/>
-      <c r="D28" s="298" t="n"/>
-      <c r="E28" s="298" t="n"/>
-      <c r="F28" s="298" t="n"/>
-      <c r="G28" s="298" t="n"/>
-      <c r="H28" s="298" t="n"/>
+      <c r="A28" s="311" t="n"/>
+      <c r="B28" s="311" t="n"/>
+      <c r="C28" s="311" t="n"/>
+      <c r="D28" s="311" t="n"/>
+      <c r="E28" s="311" t="n"/>
+      <c r="F28" s="311" t="n"/>
+      <c r="G28" s="311" t="n"/>
+      <c r="H28" s="311" t="n"/>
       <c r="I28" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B28)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="254">
-      <c r="A29" s="298" t="n"/>
-      <c r="B29" s="298" t="n"/>
-      <c r="C29" s="298" t="n"/>
-      <c r="D29" s="298" t="n"/>
-      <c r="E29" s="298" t="n"/>
-      <c r="F29" s="298" t="n"/>
-      <c r="G29" s="298" t="n"/>
-      <c r="H29" s="298" t="n"/>
+      <c r="A29" s="311" t="n"/>
+      <c r="B29" s="311" t="n"/>
+      <c r="C29" s="311" t="n"/>
+      <c r="D29" s="311" t="n"/>
+      <c r="E29" s="311" t="n"/>
+      <c r="F29" s="311" t="n"/>
+      <c r="G29" s="311" t="n"/>
+      <c r="H29" s="311" t="n"/>
       <c r="I29" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B29)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="254">
-      <c r="A30" s="298" t="n"/>
-      <c r="B30" s="298" t="n"/>
-      <c r="C30" s="298" t="n"/>
-      <c r="D30" s="298" t="n"/>
-      <c r="E30" s="298" t="n"/>
-      <c r="F30" s="298" t="n"/>
-      <c r="G30" s="298" t="n"/>
-      <c r="H30" s="298" t="n"/>
+      <c r="A30" s="311" t="n"/>
+      <c r="B30" s="311" t="n"/>
+      <c r="C30" s="311" t="n"/>
+      <c r="D30" s="311" t="n"/>
+      <c r="E30" s="311" t="n"/>
+      <c r="F30" s="311" t="n"/>
+      <c r="G30" s="311" t="n"/>
+      <c r="H30" s="311" t="n"/>
       <c r="I30" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B30)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="254">
-      <c r="A31" s="298" t="n"/>
-      <c r="B31" s="298" t="n"/>
-      <c r="C31" s="298" t="n"/>
-      <c r="D31" s="298" t="n"/>
-      <c r="E31" s="298" t="n"/>
-      <c r="F31" s="298" t="n"/>
-      <c r="G31" s="298" t="n"/>
-      <c r="H31" s="298" t="n"/>
+      <c r="A31" s="311" t="n"/>
+      <c r="B31" s="311" t="n"/>
+      <c r="C31" s="311" t="n"/>
+      <c r="D31" s="311" t="n"/>
+      <c r="E31" s="311" t="n"/>
+      <c r="F31" s="311" t="n"/>
+      <c r="G31" s="311" t="n"/>
+      <c r="H31" s="311" t="n"/>
       <c r="I31" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B31)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="254">
-      <c r="A32" s="298" t="n"/>
-      <c r="B32" s="298" t="n"/>
-      <c r="C32" s="298" t="n"/>
-      <c r="D32" s="298" t="n"/>
-      <c r="E32" s="298" t="n"/>
-      <c r="F32" s="298" t="n"/>
-      <c r="G32" s="298" t="n"/>
-      <c r="H32" s="298" t="n"/>
+      <c r="A32" s="311" t="n"/>
+      <c r="B32" s="311" t="n"/>
+      <c r="C32" s="311" t="n"/>
+      <c r="D32" s="311" t="n"/>
+      <c r="E32" s="311" t="n"/>
+      <c r="F32" s="311" t="n"/>
+      <c r="G32" s="311" t="n"/>
+      <c r="H32" s="311" t="n"/>
       <c r="I32" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B32)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="254">
-      <c r="A33" s="298" t="n"/>
-      <c r="B33" s="298" t="n"/>
-      <c r="C33" s="298" t="n"/>
-      <c r="D33" s="298" t="n"/>
-      <c r="E33" s="298" t="n"/>
-      <c r="F33" s="298" t="n"/>
-      <c r="G33" s="298" t="n"/>
-      <c r="H33" s="298" t="n"/>
+      <c r="A33" s="311" t="n"/>
+      <c r="B33" s="311" t="n"/>
+      <c r="C33" s="311" t="n"/>
+      <c r="D33" s="311" t="n"/>
+      <c r="E33" s="311" t="n"/>
+      <c r="F33" s="311" t="n"/>
+      <c r="G33" s="311" t="n"/>
+      <c r="H33" s="311" t="n"/>
       <c r="I33" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B33)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="254">
-      <c r="A34" s="298" t="n"/>
-      <c r="B34" s="298" t="n"/>
-      <c r="C34" s="298" t="n"/>
-      <c r="D34" s="298" t="n"/>
-      <c r="E34" s="298" t="n"/>
-      <c r="F34" s="298" t="n"/>
-      <c r="G34" s="298" t="n"/>
-      <c r="H34" s="298" t="n"/>
+      <c r="A34" s="311" t="n"/>
+      <c r="B34" s="311" t="n"/>
+      <c r="C34" s="311" t="n"/>
+      <c r="D34" s="311" t="n"/>
+      <c r="E34" s="311" t="n"/>
+      <c r="F34" s="311" t="n"/>
+      <c r="G34" s="311" t="n"/>
+      <c r="H34" s="311" t="n"/>
       <c r="I34" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B34)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="254">
-      <c r="A35" s="298" t="n"/>
-      <c r="B35" s="298" t="n"/>
-      <c r="C35" s="298" t="n"/>
-      <c r="D35" s="298" t="n"/>
-      <c r="E35" s="298" t="n"/>
-      <c r="F35" s="298" t="n"/>
-      <c r="G35" s="298" t="n"/>
-      <c r="H35" s="298" t="n"/>
+      <c r="A35" s="311" t="n"/>
+      <c r="B35" s="311" t="n"/>
+      <c r="C35" s="311" t="n"/>
+      <c r="D35" s="311" t="n"/>
+      <c r="E35" s="311" t="n"/>
+      <c r="F35" s="311" t="n"/>
+      <c r="G35" s="311" t="n"/>
+      <c r="H35" s="311" t="n"/>
       <c r="I35" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B35)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="254">
-      <c r="A36" s="298" t="n"/>
-      <c r="B36" s="298" t="n"/>
-      <c r="C36" s="298" t="n"/>
-      <c r="D36" s="298" t="n"/>
-      <c r="E36" s="298" t="n"/>
-      <c r="F36" s="298" t="n"/>
-      <c r="G36" s="298" t="n"/>
-      <c r="H36" s="298" t="n"/>
+      <c r="A36" s="311" t="n"/>
+      <c r="B36" s="311" t="n"/>
+      <c r="C36" s="311" t="n"/>
+      <c r="D36" s="311" t="n"/>
+      <c r="E36" s="311" t="n"/>
+      <c r="F36" s="311" t="n"/>
+      <c r="G36" s="311" t="n"/>
+      <c r="H36" s="311" t="n"/>
       <c r="I36" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B36)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="254">
-      <c r="A37" s="298" t="n"/>
-      <c r="B37" s="298" t="n"/>
-      <c r="C37" s="298" t="n"/>
-      <c r="D37" s="298" t="n"/>
-      <c r="E37" s="298" t="n"/>
-      <c r="F37" s="298" t="n"/>
-      <c r="G37" s="298" t="n"/>
-      <c r="H37" s="298" t="n"/>
+      <c r="A37" s="311" t="n"/>
+      <c r="B37" s="311" t="n"/>
+      <c r="C37" s="311" t="n"/>
+      <c r="D37" s="311" t="n"/>
+      <c r="E37" s="311" t="n"/>
+      <c r="F37" s="311" t="n"/>
+      <c r="G37" s="311" t="n"/>
+      <c r="H37" s="311" t="n"/>
       <c r="I37" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B37)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="254">
-      <c r="A38" s="298" t="n"/>
-      <c r="B38" s="298" t="n"/>
-      <c r="C38" s="298" t="n"/>
-      <c r="D38" s="298" t="n"/>
-      <c r="E38" s="298" t="n"/>
-      <c r="F38" s="298" t="n"/>
-      <c r="G38" s="298" t="n"/>
-      <c r="H38" s="298" t="n"/>
+      <c r="A38" s="311" t="n"/>
+      <c r="B38" s="311" t="n"/>
+      <c r="C38" s="311" t="n"/>
+      <c r="D38" s="311" t="n"/>
+      <c r="E38" s="311" t="n"/>
+      <c r="F38" s="311" t="n"/>
+      <c r="G38" s="311" t="n"/>
+      <c r="H38" s="311" t="n"/>
       <c r="I38" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B38)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="254">
-      <c r="A39" s="298" t="n"/>
-      <c r="B39" s="298" t="n"/>
-      <c r="C39" s="298" t="n"/>
-      <c r="D39" s="298" t="n"/>
-      <c r="E39" s="298" t="n"/>
-      <c r="F39" s="298" t="n"/>
-      <c r="G39" s="298" t="n"/>
-      <c r="H39" s="298" t="n"/>
+      <c r="A39" s="311" t="n"/>
+      <c r="B39" s="311" t="n"/>
+      <c r="C39" s="311" t="n"/>
+      <c r="D39" s="311" t="n"/>
+      <c r="E39" s="311" t="n"/>
+      <c r="F39" s="311" t="n"/>
+      <c r="G39" s="311" t="n"/>
+      <c r="H39" s="311" t="n"/>
       <c r="I39" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B39)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="254">
-      <c r="A40" s="298" t="n"/>
-      <c r="B40" s="298" t="n"/>
-      <c r="C40" s="298" t="n"/>
-      <c r="D40" s="298" t="n"/>
-      <c r="E40" s="298" t="n"/>
-      <c r="F40" s="298" t="n"/>
-      <c r="G40" s="298" t="n"/>
-      <c r="H40" s="298" t="n"/>
+      <c r="A40" s="311" t="n"/>
+      <c r="B40" s="311" t="n"/>
+      <c r="C40" s="311" t="n"/>
+      <c r="D40" s="311" t="n"/>
+      <c r="E40" s="311" t="n"/>
+      <c r="F40" s="311" t="n"/>
+      <c r="G40" s="311" t="n"/>
+      <c r="H40" s="311" t="n"/>
       <c r="I40" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B40)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="254">
-      <c r="A41" s="298" t="n"/>
-      <c r="B41" s="298" t="n"/>
-      <c r="C41" s="298" t="n"/>
-      <c r="D41" s="298" t="n"/>
-      <c r="E41" s="298" t="n"/>
-      <c r="F41" s="298" t="n"/>
-      <c r="G41" s="298" t="n"/>
-      <c r="H41" s="298" t="n"/>
+      <c r="A41" s="311" t="n"/>
+      <c r="B41" s="311" t="n"/>
+      <c r="C41" s="311" t="n"/>
+      <c r="D41" s="311" t="n"/>
+      <c r="E41" s="311" t="n"/>
+      <c r="F41" s="311" t="n"/>
+      <c r="G41" s="311" t="n"/>
+      <c r="H41" s="311" t="n"/>
       <c r="I41" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B41)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="254">
-      <c r="A42" s="298" t="n"/>
-      <c r="B42" s="298" t="n"/>
-      <c r="C42" s="298" t="n"/>
-      <c r="D42" s="298" t="n"/>
-      <c r="E42" s="298" t="n"/>
-      <c r="F42" s="298" t="n"/>
-      <c r="G42" s="298" t="n"/>
-      <c r="H42" s="298" t="n"/>
+      <c r="A42" s="311" t="n"/>
+      <c r="B42" s="311" t="n"/>
+      <c r="C42" s="311" t="n"/>
+      <c r="D42" s="311" t="n"/>
+      <c r="E42" s="311" t="n"/>
+      <c r="F42" s="311" t="n"/>
+      <c r="G42" s="311" t="n"/>
+      <c r="H42" s="311" t="n"/>
       <c r="I42" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B42)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="254">
-      <c r="A43" s="298" t="n"/>
-      <c r="B43" s="298" t="n"/>
-      <c r="C43" s="298" t="n"/>
-      <c r="D43" s="298" t="n"/>
-      <c r="E43" s="298" t="n"/>
-      <c r="F43" s="298" t="n"/>
-      <c r="G43" s="298" t="n"/>
-      <c r="H43" s="298" t="n"/>
+      <c r="A43" s="311" t="n"/>
+      <c r="B43" s="311" t="n"/>
+      <c r="C43" s="311" t="n"/>
+      <c r="D43" s="311" t="n"/>
+      <c r="E43" s="311" t="n"/>
+      <c r="F43" s="311" t="n"/>
+      <c r="G43" s="311" t="n"/>
+      <c r="H43" s="311" t="n"/>
       <c r="I43" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B43)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="254">
-      <c r="A44" s="298" t="n"/>
-      <c r="B44" s="298" t="n"/>
-      <c r="C44" s="298" t="n"/>
-      <c r="D44" s="298" t="n"/>
-      <c r="E44" s="298" t="n"/>
-      <c r="F44" s="298" t="n"/>
-      <c r="G44" s="298" t="n"/>
-      <c r="H44" s="298" t="n"/>
+      <c r="A44" s="311" t="n"/>
+      <c r="B44" s="311" t="n"/>
+      <c r="C44" s="311" t="n"/>
+      <c r="D44" s="311" t="n"/>
+      <c r="E44" s="311" t="n"/>
+      <c r="F44" s="311" t="n"/>
+      <c r="G44" s="311" t="n"/>
+      <c r="H44" s="311" t="n"/>
       <c r="I44" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B44)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="254">
-      <c r="A45" s="298" t="n"/>
-      <c r="B45" s="298" t="n"/>
-      <c r="C45" s="298" t="n"/>
-      <c r="D45" s="298" t="n"/>
-      <c r="E45" s="298" t="n"/>
-      <c r="F45" s="298" t="n"/>
-      <c r="G45" s="298" t="n"/>
-      <c r="H45" s="298" t="n"/>
+      <c r="A45" s="311" t="n"/>
+      <c r="B45" s="311" t="n"/>
+      <c r="C45" s="311" t="n"/>
+      <c r="D45" s="311" t="n"/>
+      <c r="E45" s="311" t="n"/>
+      <c r="F45" s="311" t="n"/>
+      <c r="G45" s="311" t="n"/>
+      <c r="H45" s="311" t="n"/>
       <c r="I45" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B45)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="254">
-      <c r="A46" s="298" t="n"/>
-      <c r="B46" s="298" t="n"/>
-      <c r="C46" s="298" t="n"/>
-      <c r="D46" s="298" t="n"/>
-      <c r="E46" s="298" t="n"/>
-      <c r="F46" s="298" t="n"/>
-      <c r="G46" s="298" t="n"/>
-      <c r="H46" s="298" t="n"/>
+      <c r="A46" s="311" t="n"/>
+      <c r="B46" s="311" t="n"/>
+      <c r="C46" s="311" t="n"/>
+      <c r="D46" s="311" t="n"/>
+      <c r="E46" s="311" t="n"/>
+      <c r="F46" s="311" t="n"/>
+      <c r="G46" s="311" t="n"/>
+      <c r="H46" s="311" t="n"/>
       <c r="I46" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B46)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="254">
-      <c r="A47" s="298" t="n"/>
-      <c r="B47" s="298" t="n"/>
-      <c r="C47" s="298" t="n"/>
-      <c r="D47" s="298" t="n"/>
-      <c r="E47" s="298" t="n"/>
-      <c r="F47" s="298" t="n"/>
-      <c r="G47" s="298" t="n"/>
-      <c r="H47" s="298" t="n"/>
+      <c r="A47" s="311" t="n"/>
+      <c r="B47" s="311" t="n"/>
+      <c r="C47" s="311" t="n"/>
+      <c r="D47" s="311" t="n"/>
+      <c r="E47" s="311" t="n"/>
+      <c r="F47" s="311" t="n"/>
+      <c r="G47" s="311" t="n"/>
+      <c r="H47" s="311" t="n"/>
       <c r="I47" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B47)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="254">
-      <c r="A48" s="298" t="n"/>
-      <c r="B48" s="298" t="n"/>
-      <c r="C48" s="298" t="n"/>
-      <c r="D48" s="298" t="n"/>
-      <c r="E48" s="298" t="n"/>
-      <c r="F48" s="298" t="n"/>
-      <c r="G48" s="298" t="n"/>
-      <c r="H48" s="298" t="n"/>
+      <c r="A48" s="311" t="n"/>
+      <c r="B48" s="311" t="n"/>
+      <c r="C48" s="311" t="n"/>
+      <c r="D48" s="311" t="n"/>
+      <c r="E48" s="311" t="n"/>
+      <c r="F48" s="311" t="n"/>
+      <c r="G48" s="311" t="n"/>
+      <c r="H48" s="311" t="n"/>
       <c r="I48" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B48)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="254">
-      <c r="A49" s="298" t="n"/>
-      <c r="B49" s="298" t="n"/>
-      <c r="C49" s="298" t="n"/>
-      <c r="D49" s="298" t="n"/>
-      <c r="E49" s="298" t="n"/>
-      <c r="F49" s="298" t="n"/>
-      <c r="G49" s="298" t="n"/>
-      <c r="H49" s="298" t="n"/>
+      <c r="A49" s="311" t="n"/>
+      <c r="B49" s="311" t="n"/>
+      <c r="C49" s="311" t="n"/>
+      <c r="D49" s="311" t="n"/>
+      <c r="E49" s="311" t="n"/>
+      <c r="F49" s="311" t="n"/>
+      <c r="G49" s="311" t="n"/>
+      <c r="H49" s="311" t="n"/>
       <c r="I49" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B49)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="254">
-      <c r="A50" s="298" t="n"/>
-      <c r="B50" s="298" t="n"/>
-      <c r="C50" s="298" t="n"/>
-      <c r="D50" s="298" t="n"/>
-      <c r="E50" s="298" t="n"/>
-      <c r="F50" s="298" t="n"/>
-      <c r="G50" s="298" t="n"/>
-      <c r="H50" s="298" t="n"/>
+      <c r="A50" s="311" t="n"/>
+      <c r="B50" s="311" t="n"/>
+      <c r="C50" s="311" t="n"/>
+      <c r="D50" s="311" t="n"/>
+      <c r="E50" s="311" t="n"/>
+      <c r="F50" s="311" t="n"/>
+      <c r="G50" s="311" t="n"/>
+      <c r="H50" s="311" t="n"/>
       <c r="I50" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B50)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="254">
-      <c r="A51" s="298" t="n"/>
-      <c r="B51" s="298" t="n"/>
-      <c r="C51" s="298" t="n"/>
-      <c r="D51" s="298" t="n"/>
-      <c r="E51" s="298" t="n"/>
-      <c r="F51" s="298" t="n"/>
-      <c r="G51" s="298" t="n"/>
-      <c r="H51" s="298" t="n"/>
+      <c r="A51" s="311" t="n"/>
+      <c r="B51" s="311" t="n"/>
+      <c r="C51" s="311" t="n"/>
+      <c r="D51" s="311" t="n"/>
+      <c r="E51" s="311" t="n"/>
+      <c r="F51" s="311" t="n"/>
+      <c r="G51" s="311" t="n"/>
+      <c r="H51" s="311" t="n"/>
       <c r="I51" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B51)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="254">
-      <c r="A52" s="298" t="n"/>
-      <c r="B52" s="298" t="n"/>
-      <c r="C52" s="298" t="n"/>
-      <c r="D52" s="298" t="n"/>
-      <c r="E52" s="298" t="n"/>
-      <c r="F52" s="298" t="n"/>
-      <c r="G52" s="298" t="n"/>
-      <c r="H52" s="298" t="n"/>
+      <c r="A52" s="311" t="n"/>
+      <c r="B52" s="311" t="n"/>
+      <c r="C52" s="311" t="n"/>
+      <c r="D52" s="311" t="n"/>
+      <c r="E52" s="311" t="n"/>
+      <c r="F52" s="311" t="n"/>
+      <c r="G52" s="311" t="n"/>
+      <c r="H52" s="311" t="n"/>
       <c r="I52" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B52)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="254">
-      <c r="A53" s="298" t="n"/>
-      <c r="B53" s="298" t="n"/>
-      <c r="C53" s="298" t="n"/>
-      <c r="D53" s="298" t="n"/>
-      <c r="E53" s="298" t="n"/>
-      <c r="F53" s="298" t="n"/>
-      <c r="G53" s="298" t="n"/>
-      <c r="H53" s="298" t="n"/>
+      <c r="A53" s="311" t="n"/>
+      <c r="B53" s="311" t="n"/>
+      <c r="C53" s="311" t="n"/>
+      <c r="D53" s="311" t="n"/>
+      <c r="E53" s="311" t="n"/>
+      <c r="F53" s="311" t="n"/>
+      <c r="G53" s="311" t="n"/>
+      <c r="H53" s="311" t="n"/>
       <c r="I53" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B53)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="254">
-      <c r="A54" s="298" t="n"/>
-      <c r="B54" s="298" t="n"/>
-      <c r="C54" s="298" t="n"/>
-      <c r="D54" s="298" t="n"/>
-      <c r="E54" s="298" t="n"/>
-      <c r="F54" s="298" t="n"/>
-      <c r="G54" s="298" t="n"/>
-      <c r="H54" s="298" t="n"/>
+      <c r="A54" s="311" t="n"/>
+      <c r="B54" s="311" t="n"/>
+      <c r="C54" s="311" t="n"/>
+      <c r="D54" s="311" t="n"/>
+      <c r="E54" s="311" t="n"/>
+      <c r="F54" s="311" t="n"/>
+      <c r="G54" s="311" t="n"/>
+      <c r="H54" s="311" t="n"/>
       <c r="I54" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B54)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="254">
-      <c r="A55" s="298" t="n"/>
-      <c r="B55" s="298" t="n"/>
-      <c r="C55" s="298" t="n"/>
-      <c r="D55" s="298" t="n"/>
-      <c r="E55" s="298" t="n"/>
-      <c r="F55" s="298" t="n"/>
-      <c r="G55" s="298" t="n"/>
-      <c r="H55" s="298" t="n"/>
+      <c r="A55" s="311" t="n"/>
+      <c r="B55" s="311" t="n"/>
+      <c r="C55" s="311" t="n"/>
+      <c r="D55" s="311" t="n"/>
+      <c r="E55" s="311" t="n"/>
+      <c r="F55" s="311" t="n"/>
+      <c r="G55" s="311" t="n"/>
+      <c r="H55" s="311" t="n"/>
       <c r="I55" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B55)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="254">
-      <c r="A56" s="298" t="n"/>
-      <c r="B56" s="298" t="n"/>
-      <c r="C56" s="298" t="n"/>
-      <c r="D56" s="298" t="n"/>
-      <c r="E56" s="298" t="n"/>
-      <c r="F56" s="298" t="n"/>
-      <c r="G56" s="298" t="n"/>
-      <c r="H56" s="298" t="n"/>
+      <c r="A56" s="311" t="n"/>
+      <c r="B56" s="311" t="n"/>
+      <c r="C56" s="311" t="n"/>
+      <c r="D56" s="311" t="n"/>
+      <c r="E56" s="311" t="n"/>
+      <c r="F56" s="311" t="n"/>
+      <c r="G56" s="311" t="n"/>
+      <c r="H56" s="311" t="n"/>
       <c r="I56" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B56)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="254">
-      <c r="A57" s="298" t="n"/>
-      <c r="B57" s="298" t="n"/>
-      <c r="C57" s="298" t="n"/>
-      <c r="D57" s="298" t="n"/>
-      <c r="E57" s="298" t="n"/>
-      <c r="F57" s="298" t="n"/>
-      <c r="G57" s="298" t="n"/>
-      <c r="H57" s="298" t="n"/>
+      <c r="A57" s="311" t="n"/>
+      <c r="B57" s="311" t="n"/>
+      <c r="C57" s="311" t="n"/>
+      <c r="D57" s="311" t="n"/>
+      <c r="E57" s="311" t="n"/>
+      <c r="F57" s="311" t="n"/>
+      <c r="G57" s="311" t="n"/>
+      <c r="H57" s="311" t="n"/>
       <c r="I57" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B57)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="254">
-      <c r="A58" s="298" t="n"/>
-      <c r="B58" s="298" t="n"/>
-      <c r="C58" s="298" t="n"/>
-      <c r="D58" s="298" t="n"/>
-      <c r="E58" s="298" t="n"/>
-      <c r="F58" s="298" t="n"/>
-      <c r="G58" s="298" t="n"/>
-      <c r="H58" s="298" t="n"/>
+      <c r="A58" s="311" t="n"/>
+      <c r="B58" s="311" t="n"/>
+      <c r="C58" s="311" t="n"/>
+      <c r="D58" s="311" t="n"/>
+      <c r="E58" s="311" t="n"/>
+      <c r="F58" s="311" t="n"/>
+      <c r="G58" s="311" t="n"/>
+      <c r="H58" s="311" t="n"/>
       <c r="I58" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B58)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="254">
-      <c r="A59" s="298" t="n"/>
-      <c r="B59" s="298" t="n"/>
-      <c r="C59" s="298" t="n"/>
-      <c r="D59" s="298" t="n"/>
-      <c r="E59" s="298" t="n"/>
-      <c r="F59" s="298" t="n"/>
-      <c r="G59" s="298" t="n"/>
-      <c r="H59" s="298" t="n"/>
+      <c r="A59" s="311" t="n"/>
+      <c r="B59" s="311" t="n"/>
+      <c r="C59" s="311" t="n"/>
+      <c r="D59" s="311" t="n"/>
+      <c r="E59" s="311" t="n"/>
+      <c r="F59" s="311" t="n"/>
+      <c r="G59" s="311" t="n"/>
+      <c r="H59" s="311" t="n"/>
       <c r="I59" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B59)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="254">
-      <c r="A60" s="298" t="n"/>
-      <c r="B60" s="298" t="n"/>
-      <c r="C60" s="298" t="n"/>
-      <c r="D60" s="298" t="n"/>
-      <c r="E60" s="298" t="n"/>
-      <c r="F60" s="298" t="n"/>
-      <c r="G60" s="298" t="n"/>
-      <c r="H60" s="298" t="n"/>
+      <c r="A60" s="311" t="n"/>
+      <c r="B60" s="311" t="n"/>
+      <c r="C60" s="311" t="n"/>
+      <c r="D60" s="311" t="n"/>
+      <c r="E60" s="311" t="n"/>
+      <c r="F60" s="311" t="n"/>
+      <c r="G60" s="311" t="n"/>
+      <c r="H60" s="311" t="n"/>
       <c r="I60" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B60)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="254">
-      <c r="A61" s="298" t="n"/>
-      <c r="B61" s="298" t="n"/>
-      <c r="C61" s="298" t="n"/>
-      <c r="D61" s="298" t="n"/>
-      <c r="E61" s="298" t="n"/>
-      <c r="F61" s="298" t="n"/>
-      <c r="G61" s="298" t="n"/>
-      <c r="H61" s="298" t="n"/>
+      <c r="A61" s="311" t="n"/>
+      <c r="B61" s="311" t="n"/>
+      <c r="C61" s="311" t="n"/>
+      <c r="D61" s="311" t="n"/>
+      <c r="E61" s="311" t="n"/>
+      <c r="F61" s="311" t="n"/>
+      <c r="G61" s="311" t="n"/>
+      <c r="H61" s="311" t="n"/>
       <c r="I61" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B61)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="254">
-      <c r="A62" s="298" t="n"/>
-      <c r="B62" s="298" t="n"/>
-      <c r="C62" s="298" t="n"/>
-      <c r="D62" s="298" t="n"/>
-      <c r="E62" s="298" t="n"/>
-      <c r="F62" s="298" t="n"/>
-      <c r="G62" s="298" t="n"/>
-      <c r="H62" s="298" t="n"/>
+      <c r="A62" s="311" t="n"/>
+      <c r="B62" s="311" t="n"/>
+      <c r="C62" s="311" t="n"/>
+      <c r="D62" s="311" t="n"/>
+      <c r="E62" s="311" t="n"/>
+      <c r="F62" s="311" t="n"/>
+      <c r="G62" s="311" t="n"/>
+      <c r="H62" s="311" t="n"/>
       <c r="I62" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B62)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="254">
-      <c r="A63" s="298" t="n"/>
-      <c r="B63" s="298" t="n"/>
-      <c r="C63" s="298" t="n"/>
-      <c r="D63" s="298" t="n"/>
-      <c r="E63" s="298" t="n"/>
-      <c r="F63" s="298" t="n"/>
-      <c r="G63" s="298" t="n"/>
-      <c r="H63" s="298" t="n"/>
+      <c r="A63" s="311" t="n"/>
+      <c r="B63" s="311" t="n"/>
+      <c r="C63" s="311" t="n"/>
+      <c r="D63" s="311" t="n"/>
+      <c r="E63" s="311" t="n"/>
+      <c r="F63" s="311" t="n"/>
+      <c r="G63" s="311" t="n"/>
+      <c r="H63" s="311" t="n"/>
       <c r="I63" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B63)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="254">
-      <c r="A64" s="298" t="n"/>
-      <c r="B64" s="298" t="n"/>
-      <c r="C64" s="298" t="n"/>
-      <c r="D64" s="298" t="n"/>
-      <c r="E64" s="298" t="n"/>
-      <c r="F64" s="298" t="n"/>
-      <c r="G64" s="298" t="n"/>
-      <c r="H64" s="298" t="n"/>
+      <c r="A64" s="311" t="n"/>
+      <c r="B64" s="311" t="n"/>
+      <c r="C64" s="311" t="n"/>
+      <c r="D64" s="311" t="n"/>
+      <c r="E64" s="311" t="n"/>
+      <c r="F64" s="311" t="n"/>
+      <c r="G64" s="311" t="n"/>
+      <c r="H64" s="311" t="n"/>
       <c r="I64" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B64)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="254">
-      <c r="A65" s="298" t="n"/>
-      <c r="B65" s="298" t="n"/>
-      <c r="C65" s="298" t="n"/>
-      <c r="D65" s="298" t="n"/>
-      <c r="E65" s="298" t="n"/>
-      <c r="F65" s="298" t="n"/>
-      <c r="G65" s="298" t="n"/>
-      <c r="H65" s="298" t="n"/>
+      <c r="A65" s="311" t="n"/>
+      <c r="B65" s="311" t="n"/>
+      <c r="C65" s="311" t="n"/>
+      <c r="D65" s="311" t="n"/>
+      <c r="E65" s="311" t="n"/>
+      <c r="F65" s="311" t="n"/>
+      <c r="G65" s="311" t="n"/>
+      <c r="H65" s="311" t="n"/>
       <c r="I65" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B65)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="254">
-      <c r="A66" s="298" t="n"/>
-      <c r="B66" s="298" t="n"/>
-      <c r="C66" s="298" t="n"/>
-      <c r="D66" s="298" t="n"/>
-      <c r="E66" s="298" t="n"/>
-      <c r="F66" s="298" t="n"/>
-      <c r="G66" s="298" t="n"/>
-      <c r="H66" s="298" t="n"/>
+      <c r="A66" s="311" t="n"/>
+      <c r="B66" s="311" t="n"/>
+      <c r="C66" s="311" t="n"/>
+      <c r="D66" s="311" t="n"/>
+      <c r="E66" s="311" t="n"/>
+      <c r="F66" s="311" t="n"/>
+      <c r="G66" s="311" t="n"/>
+      <c r="H66" s="311" t="n"/>
       <c r="I66" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B66)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="254">
-      <c r="A67" s="298" t="n"/>
-      <c r="B67" s="298" t="n"/>
-      <c r="C67" s="298" t="n"/>
-      <c r="D67" s="298" t="n"/>
-      <c r="E67" s="298" t="n"/>
-      <c r="F67" s="298" t="n"/>
-      <c r="G67" s="298" t="n"/>
-      <c r="H67" s="298" t="n"/>
+      <c r="A67" s="311" t="n"/>
+      <c r="B67" s="311" t="n"/>
+      <c r="C67" s="311" t="n"/>
+      <c r="D67" s="311" t="n"/>
+      <c r="E67" s="311" t="n"/>
+      <c r="F67" s="311" t="n"/>
+      <c r="G67" s="311" t="n"/>
+      <c r="H67" s="311" t="n"/>
       <c r="I67" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B67)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="254">
-      <c r="A68" s="298" t="n"/>
-      <c r="B68" s="298" t="n"/>
-      <c r="C68" s="298" t="n"/>
-      <c r="D68" s="298" t="n"/>
-      <c r="E68" s="298" t="n"/>
-      <c r="F68" s="298" t="n"/>
-      <c r="G68" s="298" t="n"/>
-      <c r="H68" s="298" t="n"/>
+      <c r="A68" s="311" t="n"/>
+      <c r="B68" s="311" t="n"/>
+      <c r="C68" s="311" t="n"/>
+      <c r="D68" s="311" t="n"/>
+      <c r="E68" s="311" t="n"/>
+      <c r="F68" s="311" t="n"/>
+      <c r="G68" s="311" t="n"/>
+      <c r="H68" s="311" t="n"/>
       <c r="I68" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B68)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="254">
-      <c r="A69" s="298" t="n"/>
-      <c r="B69" s="298" t="n"/>
-      <c r="C69" s="298" t="n"/>
-      <c r="D69" s="298" t="n"/>
-      <c r="E69" s="298" t="n"/>
-      <c r="F69" s="298" t="n"/>
-      <c r="G69" s="298" t="n"/>
-      <c r="H69" s="298" t="n"/>
+      <c r="A69" s="311" t="n"/>
+      <c r="B69" s="311" t="n"/>
+      <c r="C69" s="311" t="n"/>
+      <c r="D69" s="311" t="n"/>
+      <c r="E69" s="311" t="n"/>
+      <c r="F69" s="311" t="n"/>
+      <c r="G69" s="311" t="n"/>
+      <c r="H69" s="311" t="n"/>
       <c r="I69" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B69)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="254">
-      <c r="A70" s="298" t="n"/>
-      <c r="B70" s="298" t="n"/>
-      <c r="C70" s="298" t="n"/>
-      <c r="D70" s="298" t="n"/>
-      <c r="E70" s="298" t="n"/>
-      <c r="F70" s="298" t="n"/>
-      <c r="G70" s="298" t="n"/>
-      <c r="H70" s="298" t="n"/>
+      <c r="A70" s="311" t="n"/>
+      <c r="B70" s="311" t="n"/>
+      <c r="C70" s="311" t="n"/>
+      <c r="D70" s="311" t="n"/>
+      <c r="E70" s="311" t="n"/>
+      <c r="F70" s="311" t="n"/>
+      <c r="G70" s="311" t="n"/>
+      <c r="H70" s="311" t="n"/>
       <c r="I70" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B70)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="254">
-      <c r="A71" s="298" t="n"/>
-      <c r="B71" s="298" t="n"/>
-      <c r="C71" s="298" t="n"/>
-      <c r="D71" s="298" t="n"/>
-      <c r="E71" s="298" t="n"/>
-      <c r="F71" s="298" t="n"/>
-      <c r="G71" s="298" t="n"/>
-      <c r="H71" s="298" t="n"/>
+      <c r="A71" s="311" t="n"/>
+      <c r="B71" s="311" t="n"/>
+      <c r="C71" s="311" t="n"/>
+      <c r="D71" s="311" t="n"/>
+      <c r="E71" s="311" t="n"/>
+      <c r="F71" s="311" t="n"/>
+      <c r="G71" s="311" t="n"/>
+      <c r="H71" s="311" t="n"/>
       <c r="I71" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B71)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="254">
-      <c r="A72" s="298" t="n"/>
-      <c r="B72" s="298" t="n"/>
-      <c r="C72" s="298" t="n"/>
-      <c r="D72" s="298" t="n"/>
-      <c r="E72" s="298" t="n"/>
-      <c r="F72" s="298" t="n"/>
-      <c r="G72" s="298" t="n"/>
-      <c r="H72" s="298" t="n"/>
+      <c r="A72" s="311" t="n"/>
+      <c r="B72" s="311" t="n"/>
+      <c r="C72" s="311" t="n"/>
+      <c r="D72" s="311" t="n"/>
+      <c r="E72" s="311" t="n"/>
+      <c r="F72" s="311" t="n"/>
+      <c r="G72" s="311" t="n"/>
+      <c r="H72" s="311" t="n"/>
       <c r="I72" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B72)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="254">
-      <c r="A73" s="298" t="n"/>
-      <c r="B73" s="298" t="n"/>
-      <c r="C73" s="298" t="n"/>
-      <c r="D73" s="298" t="n"/>
-      <c r="E73" s="298" t="n"/>
-      <c r="F73" s="298" t="n"/>
-      <c r="G73" s="298" t="n"/>
-      <c r="H73" s="298" t="n"/>
+      <c r="A73" s="311" t="n"/>
+      <c r="B73" s="311" t="n"/>
+      <c r="C73" s="311" t="n"/>
+      <c r="D73" s="311" t="n"/>
+      <c r="E73" s="311" t="n"/>
+      <c r="F73" s="311" t="n"/>
+      <c r="G73" s="311" t="n"/>
+      <c r="H73" s="311" t="n"/>
       <c r="I73" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B73)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="254">
-      <c r="A74" s="298" t="n"/>
-      <c r="B74" s="298" t="n"/>
-      <c r="C74" s="298" t="n"/>
-      <c r="D74" s="298" t="n"/>
-      <c r="E74" s="298" t="n"/>
-      <c r="F74" s="298" t="n"/>
-      <c r="G74" s="298" t="n"/>
-      <c r="H74" s="298" t="n"/>
+      <c r="A74" s="311" t="n"/>
+      <c r="B74" s="311" t="n"/>
+      <c r="C74" s="311" t="n"/>
+      <c r="D74" s="311" t="n"/>
+      <c r="E74" s="311" t="n"/>
+      <c r="F74" s="311" t="n"/>
+      <c r="G74" s="311" t="n"/>
+      <c r="H74" s="311" t="n"/>
       <c r="I74" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B74)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="254">
-      <c r="A75" s="298" t="n"/>
-      <c r="B75" s="298" t="n"/>
-      <c r="C75" s="298" t="n"/>
-      <c r="D75" s="298" t="n"/>
-      <c r="E75" s="298" t="n"/>
-      <c r="F75" s="298" t="n"/>
-      <c r="G75" s="298" t="n"/>
-      <c r="H75" s="298" t="n"/>
+      <c r="A75" s="311" t="n"/>
+      <c r="B75" s="311" t="n"/>
+      <c r="C75" s="311" t="n"/>
+      <c r="D75" s="311" t="n"/>
+      <c r="E75" s="311" t="n"/>
+      <c r="F75" s="311" t="n"/>
+      <c r="G75" s="311" t="n"/>
+      <c r="H75" s="311" t="n"/>
       <c r="I75" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B75)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="254">
-      <c r="A76" s="298" t="n"/>
-      <c r="B76" s="298" t="n"/>
-      <c r="C76" s="298" t="n"/>
-      <c r="D76" s="298" t="n"/>
-      <c r="E76" s="298" t="n"/>
-      <c r="F76" s="298" t="n"/>
-      <c r="G76" s="298" t="n"/>
-      <c r="H76" s="298" t="n"/>
+      <c r="A76" s="311" t="n"/>
+      <c r="B76" s="311" t="n"/>
+      <c r="C76" s="311" t="n"/>
+      <c r="D76" s="311" t="n"/>
+      <c r="E76" s="311" t="n"/>
+      <c r="F76" s="311" t="n"/>
+      <c r="G76" s="311" t="n"/>
+      <c r="H76" s="311" t="n"/>
       <c r="I76" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B76)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="254">
-      <c r="A77" s="298" t="n"/>
-      <c r="B77" s="298" t="n"/>
-      <c r="C77" s="298" t="n"/>
-      <c r="D77" s="298" t="n"/>
-      <c r="E77" s="298" t="n"/>
-      <c r="F77" s="298" t="n"/>
-      <c r="G77" s="298" t="n"/>
-      <c r="H77" s="298" t="n"/>
+      <c r="A77" s="311" t="n"/>
+      <c r="B77" s="311" t="n"/>
+      <c r="C77" s="311" t="n"/>
+      <c r="D77" s="311" t="n"/>
+      <c r="E77" s="311" t="n"/>
+      <c r="F77" s="311" t="n"/>
+      <c r="G77" s="311" t="n"/>
+      <c r="H77" s="311" t="n"/>
       <c r="I77" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B77)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="254">
-      <c r="A78" s="298" t="n"/>
-      <c r="B78" s="298" t="n"/>
-      <c r="C78" s="298" t="n"/>
-      <c r="D78" s="298" t="n"/>
-      <c r="E78" s="298" t="n"/>
-      <c r="F78" s="298" t="n"/>
-      <c r="G78" s="298" t="n"/>
-      <c r="H78" s="298" t="n"/>
+      <c r="A78" s="311" t="n"/>
+      <c r="B78" s="311" t="n"/>
+      <c r="C78" s="311" t="n"/>
+      <c r="D78" s="311" t="n"/>
+      <c r="E78" s="311" t="n"/>
+      <c r="F78" s="311" t="n"/>
+      <c r="G78" s="311" t="n"/>
+      <c r="H78" s="311" t="n"/>
       <c r="I78" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B78)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="254">
-      <c r="A79" s="298" t="n"/>
-      <c r="B79" s="298" t="n"/>
-      <c r="C79" s="298" t="n"/>
-      <c r="D79" s="298" t="n"/>
-      <c r="E79" s="298" t="n"/>
-      <c r="F79" s="298" t="n"/>
-      <c r="G79" s="298" t="n"/>
-      <c r="H79" s="298" t="n"/>
+      <c r="A79" s="311" t="n"/>
+      <c r="B79" s="311" t="n"/>
+      <c r="C79" s="311" t="n"/>
+      <c r="D79" s="311" t="n"/>
+      <c r="E79" s="311" t="n"/>
+      <c r="F79" s="311" t="n"/>
+      <c r="G79" s="311" t="n"/>
+      <c r="H79" s="311" t="n"/>
       <c r="I79" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B79)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="254">
-      <c r="A80" s="298" t="n"/>
-      <c r="B80" s="298" t="n"/>
-      <c r="C80" s="298" t="n"/>
-      <c r="D80" s="298" t="n"/>
-      <c r="E80" s="298" t="n"/>
-      <c r="F80" s="298" t="n"/>
-      <c r="G80" s="298" t="n"/>
-      <c r="H80" s="298" t="n"/>
+      <c r="A80" s="311" t="n"/>
+      <c r="B80" s="311" t="n"/>
+      <c r="C80" s="311" t="n"/>
+      <c r="D80" s="311" t="n"/>
+      <c r="E80" s="311" t="n"/>
+      <c r="F80" s="311" t="n"/>
+      <c r="G80" s="311" t="n"/>
+      <c r="H80" s="311" t="n"/>
       <c r="I80" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B80)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="254">
-      <c r="A81" s="298" t="n"/>
-      <c r="B81" s="298" t="n"/>
-      <c r="C81" s="298" t="n"/>
-      <c r="D81" s="298" t="n"/>
-      <c r="E81" s="298" t="n"/>
-      <c r="F81" s="298" t="n"/>
-      <c r="G81" s="298" t="n"/>
-      <c r="H81" s="298" t="n"/>
+      <c r="A81" s="311" t="n"/>
+      <c r="B81" s="311" t="n"/>
+      <c r="C81" s="311" t="n"/>
+      <c r="D81" s="311" t="n"/>
+      <c r="E81" s="311" t="n"/>
+      <c r="F81" s="311" t="n"/>
+      <c r="G81" s="311" t="n"/>
+      <c r="H81" s="311" t="n"/>
       <c r="I81" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B81)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="254">
-      <c r="A82" s="298" t="n"/>
-      <c r="B82" s="298" t="n"/>
-      <c r="C82" s="298" t="n"/>
-      <c r="D82" s="298" t="n"/>
-      <c r="E82" s="298" t="n"/>
-      <c r="F82" s="298" t="n"/>
-      <c r="G82" s="298" t="n"/>
-      <c r="H82" s="298" t="n"/>
+      <c r="A82" s="311" t="n"/>
+      <c r="B82" s="311" t="n"/>
+      <c r="C82" s="311" t="n"/>
+      <c r="D82" s="311" t="n"/>
+      <c r="E82" s="311" t="n"/>
+      <c r="F82" s="311" t="n"/>
+      <c r="G82" s="311" t="n"/>
+      <c r="H82" s="311" t="n"/>
       <c r="I82" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B82)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="254">
-      <c r="A83" s="298" t="n"/>
-      <c r="B83" s="298" t="n"/>
-      <c r="C83" s="298" t="n"/>
-      <c r="D83" s="298" t="n"/>
-      <c r="E83" s="298" t="n"/>
-      <c r="F83" s="298" t="n"/>
-      <c r="G83" s="298" t="n"/>
-      <c r="H83" s="298" t="n"/>
+      <c r="A83" s="311" t="n"/>
+      <c r="B83" s="311" t="n"/>
+      <c r="C83" s="311" t="n"/>
+      <c r="D83" s="311" t="n"/>
+      <c r="E83" s="311" t="n"/>
+      <c r="F83" s="311" t="n"/>
+      <c r="G83" s="311" t="n"/>
+      <c r="H83" s="311" t="n"/>
       <c r="I83" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B83)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="254">
-      <c r="A84" s="298" t="n"/>
-      <c r="B84" s="298" t="n"/>
-      <c r="C84" s="298" t="n"/>
-      <c r="D84" s="298" t="n"/>
-      <c r="E84" s="298" t="n"/>
-      <c r="F84" s="298" t="n"/>
-      <c r="G84" s="298" t="n"/>
-      <c r="H84" s="298" t="n"/>
+      <c r="A84" s="311" t="n"/>
+      <c r="B84" s="311" t="n"/>
+      <c r="C84" s="311" t="n"/>
+      <c r="D84" s="311" t="n"/>
+      <c r="E84" s="311" t="n"/>
+      <c r="F84" s="311" t="n"/>
+      <c r="G84" s="311" t="n"/>
+      <c r="H84" s="311" t="n"/>
       <c r="I84" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B84)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="254">
-      <c r="A85" s="298" t="n"/>
-      <c r="B85" s="298" t="n"/>
-      <c r="C85" s="298" t="n"/>
-      <c r="D85" s="298" t="n"/>
-      <c r="E85" s="298" t="n"/>
-      <c r="F85" s="298" t="n"/>
-      <c r="G85" s="298" t="n"/>
-      <c r="H85" s="298" t="n"/>
+      <c r="A85" s="311" t="n"/>
+      <c r="B85" s="311" t="n"/>
+      <c r="C85" s="311" t="n"/>
+      <c r="D85" s="311" t="n"/>
+      <c r="E85" s="311" t="n"/>
+      <c r="F85" s="311" t="n"/>
+      <c r="G85" s="311" t="n"/>
+      <c r="H85" s="311" t="n"/>
       <c r="I85" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B85)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="254">
-      <c r="A86" s="298" t="n"/>
-      <c r="B86" s="298" t="n"/>
-      <c r="C86" s="298" t="n"/>
-      <c r="D86" s="298" t="n"/>
-      <c r="E86" s="298" t="n"/>
-      <c r="F86" s="298" t="n"/>
-      <c r="G86" s="298" t="n"/>
-      <c r="H86" s="298" t="n"/>
+      <c r="A86" s="311" t="n"/>
+      <c r="B86" s="311" t="n"/>
+      <c r="C86" s="311" t="n"/>
+      <c r="D86" s="311" t="n"/>
+      <c r="E86" s="311" t="n"/>
+      <c r="F86" s="311" t="n"/>
+      <c r="G86" s="311" t="n"/>
+      <c r="H86" s="311" t="n"/>
       <c r="I86" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B86)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="254">
-      <c r="A87" s="298" t="n"/>
-      <c r="B87" s="298" t="n"/>
-      <c r="C87" s="298" t="n"/>
-      <c r="D87" s="298" t="n"/>
-      <c r="E87" s="298" t="n"/>
-      <c r="F87" s="298" t="n"/>
-      <c r="G87" s="298" t="n"/>
-      <c r="H87" s="298" t="n"/>
+      <c r="A87" s="311" t="n"/>
+      <c r="B87" s="311" t="n"/>
+      <c r="C87" s="311" t="n"/>
+      <c r="D87" s="311" t="n"/>
+      <c r="E87" s="311" t="n"/>
+      <c r="F87" s="311" t="n"/>
+      <c r="G87" s="311" t="n"/>
+      <c r="H87" s="311" t="n"/>
       <c r="I87" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B87)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="254">
-      <c r="A88" s="298" t="n"/>
-      <c r="B88" s="298" t="n"/>
-      <c r="C88" s="298" t="n"/>
-      <c r="D88" s="298" t="n"/>
-      <c r="E88" s="298" t="n"/>
-      <c r="F88" s="298" t="n"/>
-      <c r="G88" s="298" t="n"/>
-      <c r="H88" s="298" t="n"/>
+      <c r="A88" s="311" t="n"/>
+      <c r="B88" s="311" t="n"/>
+      <c r="C88" s="311" t="n"/>
+      <c r="D88" s="311" t="n"/>
+      <c r="E88" s="311" t="n"/>
+      <c r="F88" s="311" t="n"/>
+      <c r="G88" s="311" t="n"/>
+      <c r="H88" s="311" t="n"/>
       <c r="I88" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B88)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="254">
-      <c r="A89" s="298" t="n"/>
-      <c r="B89" s="298" t="n"/>
-      <c r="C89" s="298" t="n"/>
-      <c r="D89" s="298" t="n"/>
-      <c r="E89" s="298" t="n"/>
-      <c r="F89" s="298" t="n"/>
-      <c r="G89" s="298" t="n"/>
-      <c r="H89" s="298" t="n"/>
+      <c r="A89" s="311" t="n"/>
+      <c r="B89" s="311" t="n"/>
+      <c r="C89" s="311" t="n"/>
+      <c r="D89" s="311" t="n"/>
+      <c r="E89" s="311" t="n"/>
+      <c r="F89" s="311" t="n"/>
+      <c r="G89" s="311" t="n"/>
+      <c r="H89" s="311" t="n"/>
       <c r="I89" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B89)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="254">
-      <c r="A90" s="298" t="n"/>
-      <c r="B90" s="298" t="n"/>
-      <c r="C90" s="298" t="n"/>
-      <c r="D90" s="298" t="n"/>
-      <c r="E90" s="298" t="n"/>
-      <c r="F90" s="298" t="n"/>
-      <c r="G90" s="298" t="n"/>
-      <c r="H90" s="298" t="n"/>
+      <c r="A90" s="311" t="n"/>
+      <c r="B90" s="311" t="n"/>
+      <c r="C90" s="311" t="n"/>
+      <c r="D90" s="311" t="n"/>
+      <c r="E90" s="311" t="n"/>
+      <c r="F90" s="311" t="n"/>
+      <c r="G90" s="311" t="n"/>
+      <c r="H90" s="311" t="n"/>
       <c r="I90" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B90)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="254">
-      <c r="A91" s="298" t="n"/>
-      <c r="B91" s="298" t="n"/>
-      <c r="C91" s="298" t="n"/>
-      <c r="D91" s="298" t="n"/>
-      <c r="E91" s="298" t="n"/>
-      <c r="F91" s="298" t="n"/>
-      <c r="G91" s="298" t="n"/>
-      <c r="H91" s="298" t="n"/>
+      <c r="A91" s="311" t="n"/>
+      <c r="B91" s="311" t="n"/>
+      <c r="C91" s="311" t="n"/>
+      <c r="D91" s="311" t="n"/>
+      <c r="E91" s="311" t="n"/>
+      <c r="F91" s="311" t="n"/>
+      <c r="G91" s="311" t="n"/>
+      <c r="H91" s="311" t="n"/>
       <c r="I91" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B91)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="254">
-      <c r="A92" s="298" t="n"/>
-      <c r="B92" s="298" t="n"/>
-      <c r="C92" s="298" t="n"/>
-      <c r="D92" s="298" t="n"/>
-      <c r="E92" s="298" t="n"/>
-      <c r="F92" s="298" t="n"/>
-      <c r="G92" s="298" t="n"/>
-      <c r="H92" s="298" t="n"/>
+      <c r="A92" s="311" t="n"/>
+      <c r="B92" s="311" t="n"/>
+      <c r="C92" s="311" t="n"/>
+      <c r="D92" s="311" t="n"/>
+      <c r="E92" s="311" t="n"/>
+      <c r="F92" s="311" t="n"/>
+      <c r="G92" s="311" t="n"/>
+      <c r="H92" s="311" t="n"/>
       <c r="I92" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B92)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="254">
-      <c r="A93" s="298" t="n"/>
-      <c r="B93" s="298" t="n"/>
-      <c r="C93" s="298" t="n"/>
-      <c r="D93" s="298" t="n"/>
-      <c r="E93" s="298" t="n"/>
-      <c r="F93" s="298" t="n"/>
-      <c r="G93" s="298" t="n"/>
-      <c r="H93" s="298" t="n"/>
+      <c r="A93" s="311" t="n"/>
+      <c r="B93" s="311" t="n"/>
+      <c r="C93" s="311" t="n"/>
+      <c r="D93" s="311" t="n"/>
+      <c r="E93" s="311" t="n"/>
+      <c r="F93" s="311" t="n"/>
+      <c r="G93" s="311" t="n"/>
+      <c r="H93" s="311" t="n"/>
       <c r="I93" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B93)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="254">
-      <c r="A94" s="298" t="n"/>
-      <c r="B94" s="298" t="n"/>
-      <c r="C94" s="298" t="n"/>
-      <c r="D94" s="298" t="n"/>
-      <c r="E94" s="298" t="n"/>
-      <c r="F94" s="298" t="n"/>
-      <c r="G94" s="298" t="n"/>
-      <c r="H94" s="298" t="n"/>
+      <c r="A94" s="311" t="n"/>
+      <c r="B94" s="311" t="n"/>
+      <c r="C94" s="311" t="n"/>
+      <c r="D94" s="311" t="n"/>
+      <c r="E94" s="311" t="n"/>
+      <c r="F94" s="311" t="n"/>
+      <c r="G94" s="311" t="n"/>
+      <c r="H94" s="311" t="n"/>
       <c r="I94" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B94)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="254">
-      <c r="A95" s="298" t="n"/>
-      <c r="B95" s="298" t="n"/>
-      <c r="C95" s="298" t="n"/>
-      <c r="D95" s="298" t="n"/>
-      <c r="E95" s="298" t="n"/>
-      <c r="F95" s="298" t="n"/>
-      <c r="G95" s="298" t="n"/>
-      <c r="H95" s="298" t="n"/>
+      <c r="A95" s="311" t="n"/>
+      <c r="B95" s="311" t="n"/>
+      <c r="C95" s="311" t="n"/>
+      <c r="D95" s="311" t="n"/>
+      <c r="E95" s="311" t="n"/>
+      <c r="F95" s="311" t="n"/>
+      <c r="G95" s="311" t="n"/>
+      <c r="H95" s="311" t="n"/>
       <c r="I95" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B95)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="254">
-      <c r="A96" s="298" t="n"/>
-      <c r="B96" s="298" t="n"/>
-      <c r="C96" s="298" t="n"/>
-      <c r="D96" s="298" t="n"/>
-      <c r="E96" s="298" t="n"/>
-      <c r="F96" s="298" t="n"/>
-      <c r="G96" s="298" t="n"/>
-      <c r="H96" s="298" t="n"/>
+      <c r="A96" s="311" t="n"/>
+      <c r="B96" s="311" t="n"/>
+      <c r="C96" s="311" t="n"/>
+      <c r="D96" s="311" t="n"/>
+      <c r="E96" s="311" t="n"/>
+      <c r="F96" s="311" t="n"/>
+      <c r="G96" s="311" t="n"/>
+      <c r="H96" s="311" t="n"/>
       <c r="I96" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B96)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="254">
-      <c r="A97" s="298" t="n"/>
-      <c r="B97" s="298" t="n"/>
-      <c r="C97" s="298" t="n"/>
-      <c r="D97" s="298" t="n"/>
-      <c r="E97" s="298" t="n"/>
-      <c r="F97" s="298" t="n"/>
-      <c r="G97" s="298" t="n"/>
-      <c r="H97" s="298" t="n"/>
+      <c r="A97" s="311" t="n"/>
+      <c r="B97" s="311" t="n"/>
+      <c r="C97" s="311" t="n"/>
+      <c r="D97" s="311" t="n"/>
+      <c r="E97" s="311" t="n"/>
+      <c r="F97" s="311" t="n"/>
+      <c r="G97" s="311" t="n"/>
+      <c r="H97" s="311" t="n"/>
       <c r="I97" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B97)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="254">
-      <c r="A98" s="298" t="n"/>
-      <c r="B98" s="298" t="n"/>
-      <c r="C98" s="298" t="n"/>
-      <c r="D98" s="298" t="n"/>
-      <c r="E98" s="298" t="n"/>
-      <c r="F98" s="298" t="n"/>
-      <c r="G98" s="298" t="n"/>
-      <c r="H98" s="298" t="n"/>
+      <c r="A98" s="311" t="n"/>
+      <c r="B98" s="311" t="n"/>
+      <c r="C98" s="311" t="n"/>
+      <c r="D98" s="311" t="n"/>
+      <c r="E98" s="311" t="n"/>
+      <c r="F98" s="311" t="n"/>
+      <c r="G98" s="311" t="n"/>
+      <c r="H98" s="311" t="n"/>
       <c r="I98" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B98)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="254">
-      <c r="A99" s="298" t="n"/>
-      <c r="B99" s="298" t="n"/>
-      <c r="C99" s="298" t="n"/>
-      <c r="D99" s="298" t="n"/>
-      <c r="E99" s="298" t="n"/>
-      <c r="F99" s="298" t="n"/>
-      <c r="G99" s="298" t="n"/>
-      <c r="H99" s="298" t="n"/>
+      <c r="A99" s="311" t="n"/>
+      <c r="B99" s="311" t="n"/>
+      <c r="C99" s="311" t="n"/>
+      <c r="D99" s="311" t="n"/>
+      <c r="E99" s="311" t="n"/>
+      <c r="F99" s="311" t="n"/>
+      <c r="G99" s="311" t="n"/>
+      <c r="H99" s="311" t="n"/>
       <c r="I99" s="112">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B99)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>
@@ -51855,14 +51841,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.1" customHeight="1" s="254">
-      <c r="A1" s="282" t="inlineStr">
+      <c r="A1" s="278" t="inlineStr">
         <is>
           <t>ALPHA CONTAINERS — PROJECT REFERENCE GUIDE</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="254">
-      <c r="A2" s="283" t="inlineStr">
+      <c r="A2" s="279" t="inlineStr">
         <is>
           <t>Last Updated: 16-May-2026 | File: AlphaContainers_v10_27.xlsx | 9 sheets</t>
         </is>
@@ -51877,14 +51863,14 @@
       <c r="F3" s="140" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1" s="254">
-      <c r="A4" s="279" t="inlineStr">
+      <c r="A4" s="275" t="inlineStr">
         <is>
           <t>S0 — DAILY WORKFLOW</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15.95" customHeight="1" s="254">
-      <c r="A5" s="284" t="inlineStr">
+      <c r="A5" s="280" t="inlineStr">
         <is>
           <t>Automated pipeline via Run_All_Updates.bat or individual scripts.</t>
         </is>
@@ -52227,21 +52213,21 @@
       <c r="F17" s="140" t="n"/>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="263">
-      <c r="A18" s="284" t="inlineStr">
+      <c r="A18" s="280" t="inlineStr">
         <is>
           <t>Individual scripts: update_production.py also runs sort_dashboard automatically at the end.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="263">
-      <c r="A19" s="284" t="inlineStr">
+      <c r="A19" s="280" t="inlineStr">
         <is>
           <t>Safety: All scripts check if Excel file is open (lock guard) and warn if source files are stale (&gt;26 hours).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="263">
-      <c r="A20" s="284" t="inlineStr">
+      <c r="A20" s="280" t="inlineStr">
         <is>
           <t>Logging: All output saved to Logs/ folder with timestamps. Mismatches logged to Logs/mismatches.log.</t>
         </is>
@@ -52256,7 +52242,7 @@
       <c r="F21" s="140" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1" s="254">
-      <c r="A22" s="279" t="inlineStr">
+      <c r="A22" s="275" t="inlineStr">
         <is>
           <t>S1 — PEOPLE</t>
         </is>
@@ -52435,7 +52421,7 @@
       <c r="F30" s="140" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1" s="254">
-      <c r="A31" s="279" t="inlineStr">
+      <c r="A31" s="275" t="inlineStr">
         <is>
           <t>S2 — PLANTS &amp; MACHINES</t>
         </is>
@@ -52634,7 +52620,7 @@
       <c r="F43" s="140" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1" s="254">
-      <c r="A44" s="279" t="inlineStr">
+      <c r="A44" s="275" t="inlineStr">
         <is>
           <t>S3 — SHEET MAP (9 sheets)</t>
         </is>
@@ -52829,7 +52815,7 @@
       <c r="F55" s="140" t="n"/>
     </row>
     <row r="56" ht="24" customHeight="1" s="254">
-      <c r="A56" s="279" t="inlineStr">
+      <c r="A56" s="275" t="inlineStr">
         <is>
           <t>S4 — AUTOMATION SCRIPTS</t>
         </is>
@@ -53072,7 +53058,7 @@
       <c r="F67" s="140" t="n"/>
     </row>
     <row r="68" ht="24" customHeight="1" s="254">
-      <c r="A68" s="279" t="inlineStr">
+      <c r="A68" s="275" t="inlineStr">
         <is>
           <t>S5 — DASHBOARD SORT RULES (sort_dashboard.py)</t>
         </is>
@@ -53247,7 +53233,7 @@
       <c r="F79" s="140" t="n"/>
     </row>
     <row r="80" ht="24" customHeight="1" s="254">
-      <c r="A80" s="279" t="inlineStr">
+      <c r="A80" s="275" t="inlineStr">
         <is>
           <t>S6 — CRITICAL RULES (DO NOT BREAK)</t>
         </is>
@@ -53454,7 +53440,7 @@
       <c r="F93" s="140" t="n"/>
     </row>
     <row r="94" ht="24" customHeight="1" s="254">
-      <c r="A94" s="279" t="inlineStr">
+      <c r="A94" s="275" t="inlineStr">
         <is>
           <t>S7 — CUSTOMER &amp; ERP CONTEXT</t>
         </is>
@@ -53701,7 +53687,7 @@
       <c r="F109" s="140" t="n"/>
     </row>
     <row r="110" ht="24" customHeight="1" s="254">
-      <c r="A110" s="279" t="inlineStr">
+      <c r="A110" s="275" t="inlineStr">
         <is>
           <t>S8 — COATING CONSUMPTION STUDY</t>
         </is>
@@ -53824,14 +53810,14 @@
       <c r="F117" s="140" t="n"/>
     </row>
     <row r="118" ht="24" customHeight="1" s="254">
-      <c r="A118" s="279" t="inlineStr">
+      <c r="A118" s="275" t="inlineStr">
         <is>
           <t>S9 — INK MANAGEMENT (Historical Average Method)</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15.95" customHeight="1" s="254">
-      <c r="A119" s="284" t="inlineStr">
+      <c r="A119" s="280" t="inlineStr">
         <is>
           <t>Ink consumption tracked via MRP sheet ink section using 12-month ERP averages (May 2025-Apr 2026). DO NOT create ink BOMs in ERP — Aurangzeb custom-mixes every batch. Refresh quarterly.</t>
         </is>
@@ -53958,7 +53944,7 @@
       <c r="F127" s="140" t="n"/>
     </row>
     <row r="128" ht="24" customHeight="1" s="254">
-      <c r="A128" s="279" t="inlineStr">
+      <c r="A128" s="275" t="inlineStr">
         <is>
           <t>S10 — OPEN ACTION ITEMS</t>
         </is>
@@ -54501,7 +54487,7 @@
       <c r="F151" s="140" t="n"/>
     </row>
     <row r="152" ht="24" customHeight="1" s="254">
-      <c r="A152" s="279" t="inlineStr">
+      <c r="A152" s="275" t="inlineStr">
         <is>
           <t>S11 — FUTURE TASKS (Sikander)</t>
         </is>
@@ -54580,7 +54566,7 @@
       <c r="F155" s="147" t="n"/>
     </row>
     <row r="156" ht="24" customHeight="1" s="254">
-      <c r="A156" s="279" t="inlineStr">
+      <c r="A156" s="275" t="inlineStr">
         <is>
           <t>S12 — RESOLVED ITEMS (for reference)</t>
         </is>
@@ -54724,8 +54710,8 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
   </mergeCells>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tubex_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,6 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MRP'!$A$12:$J$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Product_Catalog'!$A$2:$S$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Production_Log'!$A$2:$R$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BOM Issues'!$A$52:$J$64</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -1382,12 +1383,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1397,19 +1411,6 @@
     <xf numFmtId="0" fontId="42" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1431,6 +1432,9 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1438,9 +1442,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2041,23 +2042,23 @@
   <dimension ref="A1:AC199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="16.5"/>
   <cols>
-    <col width="1.5703125" customWidth="1" style="225" min="1" max="1"/>
-    <col width="7" customWidth="1" style="225" min="2" max="2"/>
-    <col width="32.7109375" customWidth="1" style="225" min="3" max="3"/>
-    <col width="38.7109375" customWidth="1" style="225" min="4" max="4"/>
-    <col width="8.85546875" customWidth="1" style="226" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="225" min="6" max="6"/>
-    <col width="11" customWidth="1" style="227" min="7" max="7"/>
-    <col width="11.140625" customWidth="1" style="225" min="8" max="8"/>
-    <col width="10.28515625" customWidth="1" style="225" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="225" min="10" max="10"/>
-    <col width="9.28515625" customWidth="1" style="225" min="11" max="11"/>
-    <col width="33.85546875" customWidth="1" style="225" min="12" max="12"/>
-    <col width="14.7109375" customWidth="1" style="225" min="13" max="13"/>
-    <col width="13.28515625" customWidth="1" style="225" min="14" max="14"/>
-    <col width="9.5703125" customWidth="1" style="225" min="15" max="15"/>
-    <col width="8.7109375" customWidth="1" style="225" min="16" max="49"/>
-    <col width="8.7109375" customWidth="1" style="225" min="50" max="16384"/>
+    <col width="1.5703125" customWidth="1" style="227" min="1" max="1"/>
+    <col width="7" customWidth="1" style="227" min="2" max="2"/>
+    <col width="32.7109375" customWidth="1" style="227" min="3" max="3"/>
+    <col width="38.7109375" customWidth="1" style="227" min="4" max="4"/>
+    <col width="8.85546875" customWidth="1" style="228" min="5" max="5"/>
+    <col width="9.140625" customWidth="1" style="227" min="6" max="6"/>
+    <col width="11" customWidth="1" style="229" min="7" max="7"/>
+    <col width="11.140625" customWidth="1" style="227" min="8" max="8"/>
+    <col width="10.28515625" customWidth="1" style="227" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="227" min="10" max="10"/>
+    <col width="9.28515625" customWidth="1" style="227" min="11" max="11"/>
+    <col width="33.85546875" customWidth="1" style="227" min="12" max="12"/>
+    <col width="14.7109375" customWidth="1" style="227" min="13" max="13"/>
+    <col width="13.28515625" customWidth="1" style="227" min="14" max="14"/>
+    <col width="9.5703125" customWidth="1" style="227" min="15" max="15"/>
+    <col width="8.7109375" customWidth="1" style="227" min="16" max="50"/>
+    <col width="8.7109375" customWidth="1" style="227" min="51" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1" s="237">
@@ -2373,21 +2374,21 @@
     </row>
     <row r="9" ht="20.25" customHeight="1" s="237">
       <c r="A9" s="136" t="n"/>
-      <c r="B9" s="234" t="inlineStr">
+      <c r="B9" s="224" t="inlineStr">
         <is>
           <t>Summary of Production &amp; Dispatch - MTD</t>
         </is>
       </c>
-      <c r="C9" s="235" t="n"/>
-      <c r="D9" s="235" t="n"/>
-      <c r="E9" s="235" t="n"/>
-      <c r="F9" s="235" t="n"/>
-      <c r="G9" s="235" t="n"/>
-      <c r="H9" s="235" t="n"/>
-      <c r="I9" s="235" t="n"/>
-      <c r="J9" s="235" t="n"/>
-      <c r="K9" s="235" t="n"/>
-      <c r="L9" s="235" t="n"/>
+      <c r="C9" s="225" t="n"/>
+      <c r="D9" s="225" t="n"/>
+      <c r="E9" s="225" t="n"/>
+      <c r="F9" s="225" t="n"/>
+      <c r="G9" s="225" t="n"/>
+      <c r="H9" s="225" t="n"/>
+      <c r="I9" s="225" t="n"/>
+      <c r="J9" s="225" t="n"/>
+      <c r="K9" s="225" t="n"/>
+      <c r="L9" s="225" t="n"/>
       <c r="M9" s="157">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,3),$U$9:$U$23,0)),"")</f>
         <v/>
@@ -2710,7 +2711,9 @@
         <f>IF(G13=0,"-",H13/G13)</f>
         <v/>
       </c>
-      <c r="K13" s="287" t="n"/>
+      <c r="K13" s="287" t="n">
+        <v>62496</v>
+      </c>
       <c r="L13" s="289" t="n"/>
       <c r="M13" s="157">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,7),$U$9:$U$23,0)),"")</f>
@@ -2898,23 +2901,22 @@
       </c>
       <c r="C16" s="283" t="inlineStr">
         <is>
-          <t>Golden Pearl Cosmetics (PVT) LTD</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D16" s="284" t="inlineStr">
         <is>
-          <t>HELLO HAIR COLOR</t>
+          <t>TUBES</t>
         </is>
       </c>
       <c r="E16" s="285" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F16" s="286" t="n">
-        <v>6206</v>
-      </c>
-      <c r="G16" s="286">
-        <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F16,MRP!$D$3:$D$9,0)),0)</f>
-        <v/>
+        <v>3726</v>
+      </c>
+      <c r="G16" s="286" t="n">
+        <v>0</v>
       </c>
       <c r="H16" s="287">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F16)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
@@ -2928,12 +2930,10 @@
         <f>IF(G16=0,"-",H16/G16)</f>
         <v/>
       </c>
-      <c r="K16" s="287" t="n"/>
-      <c r="L16" s="289" t="inlineStr">
-        <is>
-          <t>Advance Production</t>
-        </is>
-      </c>
+      <c r="K16" s="287" t="n">
+        <v>55776</v>
+      </c>
+      <c r="L16" s="289" t="n"/>
       <c r="M16" s="136" t="n"/>
       <c r="N16" s="136" t="n"/>
       <c r="O16" s="136" t="n"/>
@@ -2971,19 +2971,19 @@
       </c>
       <c r="C17" s="283" t="inlineStr">
         <is>
-          <t>Mablay Beauty PVT LTD.</t>
+          <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
       <c r="D17" s="284" t="inlineStr">
         <is>
-          <t>VINCE NURTURAL</t>
+          <t>HELLO HAIR COLOR</t>
         </is>
       </c>
       <c r="E17" s="285" t="n">
         <v>30</v>
       </c>
       <c r="F17" s="286" t="n">
-        <v>5814</v>
+        <v>6206</v>
       </c>
       <c r="G17" s="286">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F17,MRP!$D$3:$D$9,0)),0)</f>
@@ -3002,7 +3002,11 @@
         <v/>
       </c>
       <c r="K17" s="287" t="n"/>
-      <c r="L17" s="289" t="n"/>
+      <c r="L17" s="289" t="inlineStr">
+        <is>
+          <t>Advance Production</t>
+        </is>
+      </c>
       <c r="P17" s="136" t="n"/>
       <c r="Q17" s="136" t="n"/>
       <c r="R17" s="136" t="n"/>
@@ -3027,19 +3031,19 @@
       </c>
       <c r="C18" s="283" t="inlineStr">
         <is>
-          <t>Adore</t>
+          <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
       <c r="D18" s="284" t="inlineStr">
         <is>
-          <t>V- HC BROWN</t>
+          <t>VINCE NURTURAL</t>
         </is>
       </c>
       <c r="E18" s="285" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F18" s="286" t="n">
-        <v>6530</v>
+        <v>5814</v>
       </c>
       <c r="G18" s="286">
         <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F18,MRP!$D$3:$D$9,0)),0)</f>
@@ -3058,11 +3062,7 @@
         <v/>
       </c>
       <c r="K18" s="287" t="n"/>
-      <c r="L18" s="289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hold </t>
-        </is>
-      </c>
+      <c r="L18" s="289" t="n"/>
       <c r="P18" s="136" t="n"/>
       <c r="Q18" s="136" t="n"/>
       <c r="R18" s="136" t="n"/>
@@ -3090,33 +3090,49 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" s="237">
       <c r="A19" s="136" t="n"/>
-      <c r="B19" s="290" t="n"/>
-      <c r="C19" s="291" t="n"/>
-      <c r="D19" s="292" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E19" s="290" t="n"/>
-      <c r="F19" s="291" t="n"/>
-      <c r="G19" s="293">
-        <f>SUM(G11:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="293">
-        <f>SUM(H11:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="293">
-        <f>SUMIF(I11:I18,"&gt;"&amp;0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="293" t="n"/>
-      <c r="K19" s="293">
-        <f>SUM(K11:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="293" t="n"/>
+      <c r="B19" s="282" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="C19" s="283" t="inlineStr">
+        <is>
+          <t>Adore</t>
+        </is>
+      </c>
+      <c r="D19" s="284" t="inlineStr">
+        <is>
+          <t>V- HC BROWN</t>
+        </is>
+      </c>
+      <c r="E19" s="285" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="286" t="n">
+        <v>6530</v>
+      </c>
+      <c r="G19" s="286">
+        <f>IFERROR(INDEX(MRP!$F$3:$F$9,MATCH(Tubex_Dashboard!F19,MRP!$D$3:$D$9,0)),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="287">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F19)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
+        <v/>
+      </c>
+      <c r="I19" s="286">
+        <f>G19-H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="288">
+        <f>IF(G19=0,"-",H19/G19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="287" t="n"/>
+      <c r="L19" s="289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hold </t>
+        </is>
+      </c>
       <c r="M19" s="136" t="n"/>
       <c r="N19" s="136" t="n"/>
       <c r="O19" s="136" t="n"/>
@@ -3147,46 +3163,33 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" s="237">
       <c r="A20" s="136" t="n"/>
-      <c r="B20" s="282" t="inlineStr">
-        <is>
-          <t>PET</t>
-        </is>
-      </c>
-      <c r="C20" s="283" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="284" t="inlineStr">
-        <is>
-          <t>PET BOTTLE SMALL (120ML) YELLOW</t>
-        </is>
-      </c>
-      <c r="E20" s="285" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
-      <c r="F20" s="286" t="n">
-        <v>8005</v>
-      </c>
-      <c r="G20" s="286" t="n">
-        <v>19840</v>
-      </c>
-      <c r="H20" s="287">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F20)*Production_Log!$H$3:$H$8963)</f>
-        <v/>
-      </c>
-      <c r="I20" s="286">
-        <f>G20-H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="288">
-        <f>IF(G20=0,"-",H20/G20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="287" t="n"/>
-      <c r="L20" s="289" t="n"/>
+      <c r="B20" s="290" t="n"/>
+      <c r="C20" s="291" t="n"/>
+      <c r="D20" s="292" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E20" s="290" t="n"/>
+      <c r="F20" s="291" t="n"/>
+      <c r="G20" s="293">
+        <f>SUM(G11:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="293">
+        <f>SUM(H11:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="293">
+        <f>SUMIF(I11:I19,"&gt;"&amp;0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="293" t="n"/>
+      <c r="K20" s="293">
+        <f>SUM(K11:K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="293" t="n"/>
       <c r="M20" s="136" t="n"/>
       <c r="N20" s="136" t="n"/>
       <c r="O20" s="136" t="n"/>
@@ -3212,24 +3215,24 @@
       </c>
       <c r="C21" s="283" t="inlineStr">
         <is>
-          <t>Alpha Labs PVT LTD</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D21" s="284" t="inlineStr">
         <is>
-          <t>TRANSPARENT BOTTLE 150ML</t>
+          <t>PET BOTTLE SMALL (120ML) YELLOW</t>
         </is>
       </c>
       <c r="E21" s="285" t="inlineStr">
         <is>
-          <t>150 ml</t>
+          <t>120 ml</t>
         </is>
       </c>
       <c r="F21" s="286" t="n">
-        <v>8001</v>
+        <v>8005</v>
       </c>
       <c r="G21" s="286" t="n">
-        <v>249997</v>
+        <v>19840</v>
       </c>
       <c r="H21" s="287">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F21)*Production_Log!$H$3:$H$8963)</f>
@@ -3243,9 +3246,7 @@
         <f>IF(G21=0,"-",H21/G21)</f>
         <v/>
       </c>
-      <c r="K21" s="287" t="n">
-        <v>63480</v>
-      </c>
+      <c r="K21" s="287" t="n"/>
       <c r="L21" s="289" t="n"/>
       <c r="M21" s="136" t="n"/>
       <c r="N21" s="136" t="n"/>
@@ -3272,24 +3273,24 @@
       </c>
       <c r="C22" s="283" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
       <c r="D22" s="284" t="inlineStr">
         <is>
-          <t>PET BOTTLE LARGE 200ML WHITE</t>
+          <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
       <c r="E22" s="285" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>150 ml</t>
         </is>
       </c>
       <c r="F22" s="286" t="n">
-        <v>8007</v>
+        <v>8001</v>
       </c>
       <c r="G22" s="286" t="n">
-        <v>10000</v>
+        <v>249997</v>
       </c>
       <c r="H22" s="287">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F22)*Production_Log!$H$3:$H$8963)</f>
@@ -3303,7 +3304,9 @@
         <f>IF(G22=0,"-",H22/G22)</f>
         <v/>
       </c>
-      <c r="K22" s="287" t="n"/>
+      <c r="K22" s="287" t="n">
+        <v>63480</v>
+      </c>
       <c r="L22" s="289" t="n"/>
       <c r="M22" s="136" t="n"/>
       <c r="N22" s="136" t="n"/>
@@ -3335,7 +3338,7 @@
       </c>
       <c r="D23" s="284" t="inlineStr">
         <is>
-          <t>BT-200 ML YELLOW</t>
+          <t>PET BOTTLE LARGE 200ML WHITE</t>
         </is>
       </c>
       <c r="E23" s="285" t="inlineStr">
@@ -3344,10 +3347,10 @@
         </is>
       </c>
       <c r="F23" s="286" t="n">
-        <v>8006</v>
+        <v>8007</v>
       </c>
       <c r="G23" s="286" t="n">
-        <v>42400</v>
+        <v>10000</v>
       </c>
       <c r="H23" s="287">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F23)*Production_Log!$H$3:$H$8963)</f>
@@ -3393,7 +3396,7 @@
       </c>
       <c r="D24" s="284" t="inlineStr">
         <is>
-          <t>BT-200ML MUSTARD OIL (TRANSPARENT)</t>
+          <t>BT-200 ML YELLOW</t>
         </is>
       </c>
       <c r="E24" s="285" t="inlineStr">
@@ -3402,10 +3405,10 @@
         </is>
       </c>
       <c r="F24" s="286" t="n">
-        <v>8014</v>
+        <v>8006</v>
       </c>
       <c r="G24" s="286" t="n">
-        <v>10000</v>
+        <v>42400</v>
       </c>
       <c r="H24" s="287">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F24)*Production_Log!$H$3:$H$8963)</f>
@@ -3441,33 +3444,46 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="237">
       <c r="A25" s="136" t="n"/>
-      <c r="B25" s="290" t="n"/>
-      <c r="C25" s="291" t="n"/>
-      <c r="D25" s="292" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E25" s="290" t="n"/>
-      <c r="F25" s="291" t="n"/>
-      <c r="G25" s="293">
-        <f>SUM(G20:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="293">
-        <f>SUM(H20:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="293">
-        <f>SUMIF(I20:I24,"&gt;"&amp;0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="293" t="n"/>
-      <c r="K25" s="293">
-        <f>SUM(K20:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="293" t="n"/>
+      <c r="B25" s="282" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="C25" s="283" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="284" t="inlineStr">
+        <is>
+          <t>BT-200ML MUSTARD OIL (TRANSPARENT)</t>
+        </is>
+      </c>
+      <c r="E25" s="285" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="F25" s="286" t="n">
+        <v>8014</v>
+      </c>
+      <c r="G25" s="286" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H25" s="287">
+        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F25)*Production_Log!$H$3:$H$8963)</f>
+        <v/>
+      </c>
+      <c r="I25" s="286">
+        <f>G25-H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="288">
+        <f>IF(G25=0,"-",H25/G25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="287" t="n"/>
+      <c r="L25" s="289" t="n"/>
       <c r="M25" s="136" t="n"/>
       <c r="N25" s="136" t="n"/>
       <c r="O25" s="136" t="n"/>
@@ -3488,44 +3504,33 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="237">
       <c r="A26" s="136" t="n"/>
-      <c r="B26" s="282" t="inlineStr">
-        <is>
-          <t>TUBE</t>
-        </is>
-      </c>
-      <c r="C26" s="283" t="inlineStr">
-        <is>
-          <t>Bahadur</t>
-        </is>
-      </c>
-      <c r="D26" s="284" t="inlineStr">
-        <is>
-          <t>BAHADUR TUBE 12.5MM</t>
-        </is>
-      </c>
-      <c r="E26" s="285" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F26" s="286" t="n">
-        <v>9004</v>
-      </c>
-      <c r="G26" s="286" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="287">
-        <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F26)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v/>
-      </c>
-      <c r="I26" s="286">
-        <f>G26-H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="288">
-        <f>IF(G26=0,"-",H26/G26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="287" t="n"/>
-      <c r="L26" s="289" t="n"/>
+      <c r="B26" s="290" t="n"/>
+      <c r="C26" s="291" t="n"/>
+      <c r="D26" s="292" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E26" s="290" t="n"/>
+      <c r="F26" s="291" t="n"/>
+      <c r="G26" s="293">
+        <f>SUM(G21:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="293">
+        <f>SUM(H21:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="293">
+        <f>SUMIF(I21:I25,"&gt;"&amp;0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="293" t="n"/>
+      <c r="K26" s="293">
+        <f>SUM(K21:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="293" t="n"/>
       <c r="M26" s="136" t="n"/>
       <c r="N26" s="136" t="n"/>
       <c r="O26" s="136" t="n"/>
@@ -3553,19 +3558,19 @@
       </c>
       <c r="C27" s="283" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Bahadur</t>
         </is>
       </c>
       <c r="D27" s="284" t="inlineStr">
         <is>
-          <t>S-45 DIA 19MM</t>
+          <t>BAHADUR TUBE 12.5MM</t>
         </is>
       </c>
       <c r="E27" s="285" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="F27" s="286" t="n">
-        <v>6624</v>
+        <v>9004</v>
       </c>
       <c r="G27" s="286" t="n">
         <v>0</v>
@@ -3616,14 +3621,14 @@
       </c>
       <c r="D28" s="284" t="inlineStr">
         <is>
-          <t>S-43 DIA 19MM</t>
+          <t>S-45 DIA 19MM</t>
         </is>
       </c>
       <c r="E28" s="285" t="n">
         <v>19</v>
       </c>
       <c r="F28" s="286" t="n">
-        <v>6623</v>
+        <v>6624</v>
       </c>
       <c r="G28" s="286" t="n">
         <v>0</v>
@@ -3667,19 +3672,19 @@
       </c>
       <c r="C29" s="283" t="inlineStr">
         <is>
-          <t>Brookes Pharma Private Limited</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D29" s="284" t="inlineStr">
         <is>
-          <t>PHLOGIN GEL 20G</t>
+          <t>S-43 DIA 19MM</t>
         </is>
       </c>
       <c r="E29" s="285" t="n">
         <v>19</v>
       </c>
       <c r="F29" s="286" t="n">
-        <v>6559</v>
+        <v>6623</v>
       </c>
       <c r="G29" s="286" t="n">
         <v>0</v>
@@ -3728,14 +3733,14 @@
       </c>
       <c r="D30" s="284" t="inlineStr">
         <is>
-          <t>PYODINE GEL 20GM</t>
+          <t>PHLOGIN GEL 20G</t>
         </is>
       </c>
       <c r="E30" s="285" t="n">
         <v>19</v>
       </c>
       <c r="F30" s="286" t="n">
-        <v>1085</v>
+        <v>6559</v>
       </c>
       <c r="G30" s="286" t="n">
         <v>0</v>
@@ -3786,14 +3791,14 @@
       </c>
       <c r="D31" s="284" t="inlineStr">
         <is>
-          <t>CONTRATUBEX GEL 20G</t>
+          <t>PYODINE GEL 20GM</t>
         </is>
       </c>
       <c r="E31" s="285" t="n">
         <v>19</v>
       </c>
       <c r="F31" s="286" t="n">
-        <v>6560</v>
+        <v>1085</v>
       </c>
       <c r="G31" s="286" t="n">
         <v>0</v>
@@ -3839,19 +3844,19 @@
       </c>
       <c r="C32" s="283" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Brookes Pharma Private Limited</t>
         </is>
       </c>
       <c r="D32" s="284" t="inlineStr">
         <is>
-          <t>S-43 DIA 20.5</t>
+          <t>CONTRATUBEX GEL 20G</t>
         </is>
       </c>
       <c r="E32" s="285" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="F32" s="286" t="n">
-        <v>5699</v>
+        <v>6560</v>
       </c>
       <c r="G32" s="286" t="n">
         <v>0</v>
@@ -3897,19 +3902,19 @@
       </c>
       <c r="C33" s="283" t="inlineStr">
         <is>
-          <t>Mablay Beauty PVT LTD.</t>
+          <t>Samsol International Private Limited</t>
         </is>
       </c>
       <c r="D33" s="284" t="inlineStr">
         <is>
-          <t>VINCE HIS ONLY BEARD &amp; MUSTACHE COLOR CREAM</t>
+          <t>S-43 DIA 20.5</t>
         </is>
       </c>
       <c r="E33" s="285" t="n">
         <v>20.5</v>
       </c>
       <c r="F33" s="286" t="n">
-        <v>6077</v>
+        <v>5699</v>
       </c>
       <c r="G33" s="286" t="n">
         <v>0</v>
@@ -3953,19 +3958,19 @@
       </c>
       <c r="C34" s="283" t="inlineStr">
         <is>
-          <t>Samsol International Private Limited</t>
+          <t>Mablay Beauty PVT LTD.</t>
         </is>
       </c>
       <c r="D34" s="284" t="inlineStr">
         <is>
-          <t>S-45 DIA 20.5</t>
+          <t>VINCE HIS ONLY BEARD &amp; MUSTACHE COLOR CREAM</t>
         </is>
       </c>
       <c r="E34" s="285" t="n">
         <v>20.5</v>
       </c>
       <c r="F34" s="286" t="n">
-        <v>5698</v>
+        <v>6077</v>
       </c>
       <c r="G34" s="286" t="n">
         <v>0</v>
@@ -4014,14 +4019,14 @@
       </c>
       <c r="D35" s="284" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
+          <t>S-45 DIA 20.5</t>
         </is>
       </c>
       <c r="E35" s="285" t="n">
         <v>20.5</v>
       </c>
       <c r="F35" s="286" t="n">
-        <v>5731</v>
+        <v>5698</v>
       </c>
       <c r="G35" s="286" t="n">
         <v>0</v>
@@ -4070,14 +4075,14 @@
       </c>
       <c r="D36" s="284" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 43 DIA 20.5 MM</t>
+          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
       <c r="E36" s="285" t="n">
         <v>20.5</v>
       </c>
       <c r="F36" s="286" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="G36" s="286" t="n">
         <v>0</v>
@@ -4099,7 +4104,7 @@
       <c r="P36" s="136" t="n"/>
       <c r="Q36" s="136" t="n"/>
       <c r="R36" s="136" t="n"/>
-      <c r="S36" s="225" t="inlineStr">
+      <c r="S36" s="227" t="inlineStr">
         <is>
           <t>Gas Shutdown</t>
         </is>
@@ -4108,7 +4113,7 @@
         <f>SUMPRODUCT((MONTH(Production_Log!$A$3:$A$8963)=MONTH(TODAY()))*(YEAR(Production_Log!$A$3:$A$8963)=YEAR(TODAY()))*Production_Log!$Q$3:$Q$8963)</f>
         <v/>
       </c>
-      <c r="U36" s="225">
+      <c r="U36" s="227">
         <f>T36+0.00006</f>
         <v/>
       </c>
@@ -4135,14 +4140,14 @@
       </c>
       <c r="D37" s="284" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 39 SMALL PURPLE</t>
+          <t>SAMSOL HAIR COLOR 43 DIA 20.5 MM</t>
         </is>
       </c>
       <c r="E37" s="285" t="n">
         <v>20.5</v>
       </c>
       <c r="F37" s="286" t="n">
-        <v>6556</v>
+        <v>5732</v>
       </c>
       <c r="G37" s="286" t="n">
         <v>0</v>
@@ -4193,14 +4198,14 @@
       </c>
       <c r="D38" s="284" t="inlineStr">
         <is>
-          <t>SAMSOL HAIR COLOR 41 SMALL PURPLE</t>
+          <t>SAMSOL HAIR COLOR 39 SMALL PURPLE</t>
         </is>
       </c>
       <c r="E38" s="285" t="n">
         <v>20.5</v>
       </c>
       <c r="F38" s="286" t="n">
-        <v>6557</v>
+        <v>6556</v>
       </c>
       <c r="G38" s="286" t="n">
         <v>0</v>
@@ -4251,14 +4256,14 @@
       </c>
       <c r="D39" s="284" t="inlineStr">
         <is>
-          <t>TUBES</t>
+          <t>SAMSOL HAIR COLOR 41 SMALL PURPLE</t>
         </is>
       </c>
       <c r="E39" s="285" t="n">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="F39" s="286" t="n">
-        <v>3726</v>
+        <v>6557</v>
       </c>
       <c r="G39" s="286" t="n">
         <v>0</v>
@@ -6820,9 +6825,10 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A20)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A20)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A20)&gt;0)*($H$9&gt;0),$C$9&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A20)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A20)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A20)&gt;0)*($H$9&gt;0),$C$9&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A20)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A20)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A20)&gt;0)*($H$9&gt;0),$C$9&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I20" s="30">
-        <f>IF(E20=0,"Not needed",IF(G20&lt;0,"SHORTAGE",IF(G20&lt;F20*0.1,"LOW","OK")))</f>
-        <v/>
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>100kg Shortage (13k tubes WIP)</t>
+        </is>
       </c>
       <c r="J20" s="30">
         <f>IF(B20&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A20)*'FG Stock'!$F$4:$F$100))</f>
@@ -13159,22 +13165,22 @@
       <filters>
         <filter val="1"/>
         <filter val="10"/>
-        <filter val="110"/>
-        <filter val="114,655"/>
         <filter val="138"/>
         <filter val="15"/>
-        <filter val="172"/>
+        <filter val="170"/>
         <filter val="188"/>
         <filter val="194"/>
         <filter val="2"/>
         <filter val="25,500"/>
+        <filter val="289"/>
         <filter val="3"/>
+        <filter val="36"/>
         <filter val="36,006"/>
-        <filter val="361"/>
-        <filter val="43"/>
+        <filter val="574"/>
         <filter val="69"/>
-        <filter val="718"/>
         <filter val="89"/>
+        <filter val="92,036"/>
+        <filter val="95"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -32247,13 +32253,13 @@
           <t>Slugs Inventory — June 2026 MONTH TO DATE</t>
         </is>
       </c>
-      <c r="B1" s="235" t="n"/>
-      <c r="C1" s="235" t="n"/>
-      <c r="D1" s="235" t="n"/>
-      <c r="E1" s="235" t="n"/>
-      <c r="F1" s="235" t="n"/>
-      <c r="G1" s="235" t="n"/>
-      <c r="H1" s="235" t="n"/>
+      <c r="B1" s="225" t="n"/>
+      <c r="C1" s="225" t="n"/>
+      <c r="D1" s="225" t="n"/>
+      <c r="E1" s="225" t="n"/>
+      <c r="F1" s="225" t="n"/>
+      <c r="G1" s="225" t="n"/>
+      <c r="H1" s="225" t="n"/>
       <c r="I1" s="69" t="inlineStr">
         <is>
           <t>Date:</t>
@@ -32501,7 +32507,7 @@
         <v/>
       </c>
       <c r="I7" s="37" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="J7" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -40263,7 +40269,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -40402,7 +40408,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="237">
+    <row r="3" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A3" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40452,7 +40458,7 @@
       <c r="R3" s="265" t="n"/>
       <c r="S3" s="265" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="237">
+    <row r="4" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A4" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40500,7 +40506,7 @@
       <c r="R4" s="265" t="n"/>
       <c r="S4" s="265" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="237">
+    <row r="5" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A5" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40548,7 +40554,7 @@
       <c r="R5" s="265" t="n"/>
       <c r="S5" s="265" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="237">
+    <row r="6" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A6" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40600,7 +40606,7 @@
       <c r="R6" s="265" t="n"/>
       <c r="S6" s="265" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="237">
+    <row r="7" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A7" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40648,7 +40654,7 @@
       <c r="R7" s="265" t="n"/>
       <c r="S7" s="265" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="237">
+    <row r="8" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A8" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40748,7 +40754,7 @@
       <c r="R9" s="265" t="n"/>
       <c r="S9" s="265" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="237">
+    <row r="10" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A10" s="268" t="n">
         <v>46174</v>
       </c>
@@ -40796,7 +40802,7 @@
       <c r="R10" s="265" t="n"/>
       <c r="S10" s="265" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="237">
+    <row r="11" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A11" s="268" t="n">
         <v>46175</v>
       </c>
@@ -40846,7 +40852,7 @@
       <c r="R11" s="265" t="n"/>
       <c r="S11" s="265" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="237">
+    <row r="12" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A12" s="268" t="n">
         <v>46175</v>
       </c>
@@ -40894,7 +40900,7 @@
       <c r="R12" s="265" t="n"/>
       <c r="S12" s="265" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="237">
+    <row r="13" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A13" s="268" t="n">
         <v>46175</v>
       </c>
@@ -40944,7 +40950,7 @@
       <c r="R13" s="265" t="n"/>
       <c r="S13" s="265" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="237">
+    <row r="14" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A14" s="268" t="n">
         <v>46175</v>
       </c>
@@ -40996,7 +41002,7 @@
       <c r="R14" s="265" t="n"/>
       <c r="S14" s="265" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="237">
+    <row r="15" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A15" s="268" t="n">
         <v>46175</v>
       </c>
@@ -41044,7 +41050,7 @@
       <c r="R15" s="265" t="n"/>
       <c r="S15" s="265" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="237">
+    <row r="16" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A16" s="268" t="n">
         <v>46175</v>
       </c>
@@ -41142,7 +41148,7 @@
       <c r="R17" s="265" t="n"/>
       <c r="S17" s="265" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="237">
+    <row r="18" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A18" s="268" t="n">
         <v>46175</v>
       </c>
@@ -41190,7 +41196,7 @@
       <c r="R18" s="265" t="n"/>
       <c r="S18" s="265" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="237">
+    <row r="19" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A19" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41226,7 +41232,7 @@
       <c r="R19" s="265" t="n"/>
       <c r="S19" s="265" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="237">
+    <row r="20" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A20" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41262,7 +41268,7 @@
       <c r="R20" s="265" t="n"/>
       <c r="S20" s="265" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="237">
+    <row r="21" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A21" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41298,7 +41304,7 @@
       <c r="R21" s="265" t="n"/>
       <c r="S21" s="265" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="237">
+    <row r="22" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A22" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41352,7 +41358,7 @@
       <c r="R22" s="265" t="n"/>
       <c r="S22" s="265" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1" s="237">
+    <row r="23" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A23" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41388,7 +41394,7 @@
       <c r="R23" s="265" t="n"/>
       <c r="S23" s="265" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="237">
+    <row r="24" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A24" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41424,7 +41430,7 @@
       <c r="R24" s="265" t="n"/>
       <c r="S24" s="265" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="237">
+    <row r="25" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A25" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41460,7 +41466,7 @@
       <c r="R25" s="265" t="n"/>
       <c r="S25" s="265" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="237">
+    <row r="26" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A26" s="268" t="n">
         <v>46177</v>
       </c>
@@ -41496,7 +41502,7 @@
       <c r="R26" s="265" t="n"/>
       <c r="S26" s="265" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="237">
+    <row r="27" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A27" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41532,7 +41538,7 @@
       <c r="R27" s="265" t="n"/>
       <c r="S27" s="265" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="237">
+    <row r="28" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A28" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41568,7 +41574,7 @@
       <c r="R28" s="265" t="n"/>
       <c r="S28" s="265" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="237">
+    <row r="29" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A29" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41604,7 +41610,7 @@
       <c r="R29" s="265" t="n"/>
       <c r="S29" s="265" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="237">
+    <row r="30" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A30" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41658,7 +41664,7 @@
       <c r="R30" s="265" t="n"/>
       <c r="S30" s="265" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="237">
+    <row r="31" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A31" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41694,7 +41700,7 @@
       <c r="R31" s="265" t="n"/>
       <c r="S31" s="265" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1" s="237">
+    <row r="32" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A32" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41730,7 +41736,7 @@
       <c r="R32" s="265" t="n"/>
       <c r="S32" s="265" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="237">
+    <row r="33" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A33" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41766,7 +41772,7 @@
       <c r="R33" s="265" t="n"/>
       <c r="S33" s="265" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="237">
+    <row r="34" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A34" s="268" t="n">
         <v>46178</v>
       </c>
@@ -41802,7 +41808,7 @@
       <c r="R34" s="265" t="n"/>
       <c r="S34" s="265" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1" s="237">
+    <row r="35" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A35" s="268" t="n">
         <v>46179</v>
       </c>
@@ -41838,7 +41844,7 @@
       <c r="R35" s="265" t="n"/>
       <c r="S35" s="265" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="237">
+    <row r="36" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A36" s="268" t="n">
         <v>46179</v>
       </c>
@@ -41874,7 +41880,7 @@
       <c r="R36" s="265" t="n"/>
       <c r="S36" s="265" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1" s="237">
+    <row r="37" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A37" s="268" t="n">
         <v>46179</v>
       </c>
@@ -41910,7 +41916,7 @@
       <c r="R37" s="265" t="n"/>
       <c r="S37" s="265" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="237">
+    <row r="38" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A38" s="268" t="n">
         <v>46179</v>
       </c>
@@ -41966,7 +41972,7 @@
       <c r="R38" s="265" t="n"/>
       <c r="S38" s="265" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="237">
+    <row r="39" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A39" s="268" t="n">
         <v>46179</v>
       </c>
@@ -42002,7 +42008,7 @@
       <c r="R39" s="265" t="n"/>
       <c r="S39" s="265" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1" s="237">
+    <row r="40" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A40" s="268" t="n">
         <v>46179</v>
       </c>
@@ -42038,7 +42044,7 @@
       <c r="R40" s="265" t="n"/>
       <c r="S40" s="265" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="237">
+    <row r="41" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A41" s="268" t="n">
         <v>46179</v>
       </c>
@@ -42074,7 +42080,7 @@
       <c r="R41" s="265" t="n"/>
       <c r="S41" s="265" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1" s="237">
+    <row r="42" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A42" s="268" t="n">
         <v>46179</v>
       </c>
@@ -42110,7 +42116,7 @@
       <c r="R42" s="265" t="n"/>
       <c r="S42" s="265" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1" s="237">
+    <row r="43" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A43" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42146,7 +42152,7 @@
       <c r="R43" s="265" t="n"/>
       <c r="S43" s="265" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1" s="237">
+    <row r="44" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A44" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42194,7 +42200,7 @@
       <c r="R44" s="265" t="n"/>
       <c r="S44" s="265" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1" s="237">
+    <row r="45" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A45" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42230,7 +42236,7 @@
       <c r="R45" s="265" t="n"/>
       <c r="S45" s="265" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1" s="237">
+    <row r="46" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A46" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42284,7 +42290,7 @@
       <c r="R46" s="265" t="n"/>
       <c r="S46" s="265" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1" s="237">
+    <row r="47" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A47" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42320,7 +42326,7 @@
       <c r="R47" s="265" t="n"/>
       <c r="S47" s="265" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1" s="237">
+    <row r="48" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A48" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42418,7 +42424,7 @@
       <c r="R49" s="265" t="n"/>
       <c r="S49" s="265" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1" s="237">
+    <row r="50" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A50" s="268" t="n">
         <v>46181</v>
       </c>
@@ -42454,7 +42460,7 @@
       <c r="R50" s="265" t="n"/>
       <c r="S50" s="265" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="237">
+    <row r="51" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A51" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42490,7 +42496,7 @@
       <c r="R51" s="265" t="n"/>
       <c r="S51" s="265" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1" s="237">
+    <row r="52" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A52" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42538,7 +42544,7 @@
       <c r="R52" s="265" t="n"/>
       <c r="S52" s="265" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1" s="237">
+    <row r="53" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A53" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42574,7 +42580,7 @@
       <c r="R53" s="265" t="n"/>
       <c r="S53" s="265" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="237">
+    <row r="54" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A54" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42628,7 +42634,7 @@
       <c r="R54" s="265" t="n"/>
       <c r="S54" s="265" t="n"/>
     </row>
-    <row r="55" ht="15" customHeight="1" s="237">
+    <row r="55" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A55" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42664,7 +42670,7 @@
       <c r="R55" s="265" t="n"/>
       <c r="S55" s="265" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1" s="237">
+    <row r="56" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A56" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42760,7 +42766,7 @@
       <c r="R57" s="265" t="n"/>
       <c r="S57" s="265" t="n"/>
     </row>
-    <row r="58" ht="15" customHeight="1" s="237">
+    <row r="58" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A58" s="268" t="n">
         <v>46182</v>
       </c>
@@ -42796,7 +42802,7 @@
       <c r="R58" s="265" t="n"/>
       <c r="S58" s="265" t="n"/>
     </row>
-    <row r="59" ht="15" customHeight="1" s="237">
+    <row r="59" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A59" s="268" t="n">
         <v>46183</v>
       </c>
@@ -42832,7 +42838,7 @@
       <c r="R59" s="265" t="n"/>
       <c r="S59" s="265" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1" s="237">
+    <row r="60" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A60" s="268" t="n">
         <v>46183</v>
       </c>
@@ -42880,7 +42886,7 @@
       <c r="R60" s="265" t="n"/>
       <c r="S60" s="265" t="n"/>
     </row>
-    <row r="61" ht="15" customHeight="1" s="237">
+    <row r="61" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A61" s="268" t="n">
         <v>46183</v>
       </c>
@@ -42916,7 +42922,7 @@
       <c r="R61" s="265" t="n"/>
       <c r="S61" s="265" t="n"/>
     </row>
-    <row r="62" ht="15" customHeight="1" s="237">
+    <row r="62" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A62" s="268" t="n">
         <v>46183</v>
       </c>
@@ -42968,7 +42974,7 @@
       <c r="R62" s="265" t="n"/>
       <c r="S62" s="265" t="n"/>
     </row>
-    <row r="63" ht="15" customHeight="1" s="237">
+    <row r="63" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A63" s="268" t="n">
         <v>46183</v>
       </c>
@@ -43004,7 +43010,7 @@
       <c r="R63" s="265" t="n"/>
       <c r="S63" s="265" t="n"/>
     </row>
-    <row r="64" ht="15" customHeight="1" s="237">
+    <row r="64" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A64" s="268" t="n">
         <v>46183</v>
       </c>
@@ -43100,7 +43106,7 @@
       <c r="R65" s="265" t="n"/>
       <c r="S65" s="265" t="n"/>
     </row>
-    <row r="66" ht="15" customHeight="1" s="237">
+    <row r="66" hidden="1" ht="15" customHeight="1" s="237">
       <c r="A66" s="268" t="n">
         <v>46183</v>
       </c>
@@ -45832,6 +45838,18 @@
       <c r="J247" s="91" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:R66">
+    <filterColumn colId="1" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="Printing-03"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="25"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -52250,7 +52268,7 @@
         </is>
       </c>
     </row>
-    <row r="8" customFormat="1" s="246">
+    <row r="8" customFormat="1" s="247">
       <c r="A8" s="127" t="inlineStr">
         <is>
           <t>2</t>
@@ -52282,7 +52300,7 @@
         </is>
       </c>
     </row>
-    <row r="9" customFormat="1" s="246">
+    <row r="9" customFormat="1" s="247">
       <c r="A9" s="126" t="inlineStr">
         <is>
           <t>3</t>
@@ -52314,7 +52332,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customFormat="1" customHeight="1" s="246">
+    <row r="10" ht="24" customFormat="1" customHeight="1" s="247">
       <c r="A10" s="106" t="n"/>
       <c r="B10" s="107" t="inlineStr">
         <is>
@@ -52454,7 +52472,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customFormat="1" customHeight="1" s="246">
+    <row r="15" ht="24" customFormat="1" customHeight="1" s="247">
       <c r="A15" s="126" t="inlineStr">
         <is>
           <t>4</t>
@@ -52514,7 +52532,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="8.1" customFormat="1" customHeight="1" s="246">
+    <row r="17" ht="8.1" customFormat="1" customHeight="1" s="247">
       <c r="A17" s="128" t="n"/>
       <c r="B17" s="129" t="n"/>
       <c r="C17" s="129" t="n"/>
@@ -52522,21 +52540,21 @@
       <c r="E17" s="125" t="n"/>
       <c r="F17" s="125" t="n"/>
     </row>
-    <row r="18" ht="15.95" customFormat="1" customHeight="1" s="246">
+    <row r="18" ht="15.95" customFormat="1" customHeight="1" s="247">
       <c r="A18" s="263" t="inlineStr">
         <is>
           <t>Individual scripts: update_production.py also runs sort_dashboard automatically at the end.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.95" customFormat="1" customHeight="1" s="246">
+    <row r="19" ht="15.95" customFormat="1" customHeight="1" s="247">
       <c r="A19" s="263" t="inlineStr">
         <is>
           <t>Safety: All scripts check if Excel file is open (lock guard) and warn if source files are stale (&gt;26 hours).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.95" customFormat="1" customHeight="1" s="246">
+    <row r="20" ht="15.95" customFormat="1" customHeight="1" s="247">
       <c r="A20" s="263" t="inlineStr">
         <is>
           <t>Logging: All output saved to Logs/ folder with timestamps. Mismatches logged to Logs/mismatches.log.</t>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -802,7 +802,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1566,6 +1566,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32500,7 +32518,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="H7" s="38">
         <f>E7+F7-G7</f>
@@ -33040,7 +33058,7 @@
         <v>210</v>
       </c>
       <c r="G22" s="37" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H22" s="38">
         <f>E22+F22-G22</f>
@@ -34050,7 +34068,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="37" t="n">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="H46" s="38">
         <f>E46+F46-G46</f>
@@ -36082,7 +36100,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="38">
         <f>E94+F94-G94</f>
@@ -50357,31 +50375,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="237">
-      <c r="A4" s="269" t="n">
+      <c r="A4" s="295" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="269" t="n">
+      <c r="B4" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="296" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="296" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="269" t="inlineStr">
+      <c r="E4" s="295" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="271" t="n">
+      <c r="F4" s="297" t="n">
         <v>10580</v>
       </c>
-      <c r="G4" s="269" t="inlineStr">
+      <c r="G4" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50397,31 +50415,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="237">
-      <c r="A5" s="269" t="n">
+      <c r="A5" s="295" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="269" t="n">
+      <c r="B5" s="295" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="270" t="inlineStr">
+      <c r="C5" s="296" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="270" t="inlineStr">
+      <c r="D5" s="296" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="269" t="inlineStr">
+      <c r="E5" s="295" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="271" t="n">
+      <c r="F5" s="297" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="269" t="inlineStr">
+      <c r="G5" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50437,31 +50455,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="237">
-      <c r="A6" s="269" t="n">
+      <c r="A6" s="295" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="269" t="n">
+      <c r="B6" s="295" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="270" t="inlineStr">
+      <c r="C6" s="296" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="270" t="inlineStr">
+      <c r="D6" s="296" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="269" t="inlineStr">
+      <c r="E6" s="295" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="271" t="n">
+      <c r="F6" s="297" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="269" t="inlineStr">
+      <c r="G6" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50477,31 +50495,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="237">
-      <c r="A7" s="269" t="n">
+      <c r="A7" s="295" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="269" t="n">
+      <c r="B7" s="295" t="n">
         <v>6470</v>
       </c>
-      <c r="C7" s="270" t="inlineStr">
+      <c r="C7" s="296" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="270" t="inlineStr">
+      <c r="D7" s="296" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E7" s="269" t="inlineStr">
+      <c r="E7" s="295" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="271" t="n">
+      <c r="F7" s="297" t="n">
         <v>60000</v>
       </c>
-      <c r="G7" s="269" t="inlineStr">
+      <c r="G7" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50517,31 +50535,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="237">
-      <c r="A8" s="269" t="n">
+      <c r="A8" s="295" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="269" t="n">
+      <c r="B8" s="295" t="n">
         <v>4050</v>
       </c>
-      <c r="C8" s="270" t="inlineStr">
+      <c r="C8" s="296" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D8" s="270" t="inlineStr">
+      <c r="D8" s="296" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E8" s="269" t="inlineStr">
+      <c r="E8" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="271" t="n">
+      <c r="F8" s="297" t="n">
         <v>9450</v>
       </c>
-      <c r="G8" s="269" t="inlineStr">
+      <c r="G8" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50557,31 +50575,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="237">
-      <c r="A9" s="269" t="n">
+      <c r="A9" s="295" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="269" t="n">
+      <c r="B9" s="295" t="n">
         <v>6337</v>
       </c>
-      <c r="C9" s="270" t="inlineStr">
+      <c r="C9" s="296" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="270" t="inlineStr">
+      <c r="D9" s="296" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="269" t="inlineStr">
+      <c r="E9" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="271" t="n">
+      <c r="F9" s="297" t="n">
         <v>15680</v>
       </c>
-      <c r="G9" s="269" t="inlineStr">
+      <c r="G9" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50597,31 +50615,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="237">
-      <c r="A10" s="269" t="n">
+      <c r="A10" s="295" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="269" t="n">
+      <c r="B10" s="295" t="n">
         <v>6416</v>
       </c>
-      <c r="C10" s="270" t="inlineStr">
+      <c r="C10" s="296" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D10" s="270" t="inlineStr">
+      <c r="D10" s="296" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E10" s="269" t="inlineStr">
+      <c r="E10" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="271" t="n">
+      <c r="F10" s="297" t="n">
         <v>15435</v>
       </c>
-      <c r="G10" s="269" t="inlineStr">
+      <c r="G10" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50637,31 +50655,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="237">
-      <c r="A11" s="269" t="n">
+      <c r="A11" s="295" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="269" t="n">
+      <c r="B11" s="295" t="n">
         <v>5782</v>
       </c>
-      <c r="C11" s="270" t="inlineStr">
+      <c r="C11" s="296" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D11" s="270" t="inlineStr">
+      <c r="D11" s="296" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E11" s="269" t="inlineStr">
+      <c r="E11" s="295" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F11" s="271" t="n">
+      <c r="F11" s="297" t="n">
         <v>63648</v>
       </c>
-      <c r="G11" s="269" t="inlineStr">
+      <c r="G11" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50677,31 +50695,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="237">
-      <c r="A12" s="269" t="n">
+      <c r="A12" s="295" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="269" t="n">
+      <c r="B12" s="295" t="n">
         <v>6531</v>
       </c>
-      <c r="C12" s="270" t="inlineStr">
+      <c r="C12" s="296" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D12" s="270" t="inlineStr">
+      <c r="D12" s="296" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E12" s="269" t="inlineStr">
+      <c r="E12" s="295" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F12" s="271" t="n">
+      <c r="F12" s="297" t="n">
         <v>4380</v>
       </c>
-      <c r="G12" s="269" t="inlineStr">
+      <c r="G12" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50717,31 +50735,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="237">
-      <c r="A13" s="269" t="n">
+      <c r="A13" s="295" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="269" t="n">
+      <c r="B13" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="270" t="inlineStr">
+      <c r="C13" s="296" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="270" t="inlineStr">
+      <c r="D13" s="296" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="269" t="inlineStr">
+      <c r="E13" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="271" t="n">
+      <c r="F13" s="297" t="n">
         <v>95000</v>
       </c>
-      <c r="G13" s="269" t="inlineStr">
+      <c r="G13" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50757,31 +50775,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="237">
-      <c r="A14" s="273" t="n">
+      <c r="A14" s="298" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="273" t="n">
+      <c r="B14" s="298" t="n">
         <v>6470</v>
       </c>
-      <c r="C14" s="274" t="inlineStr">
+      <c r="C14" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="274" t="inlineStr">
+      <c r="D14" s="299" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E14" s="273" t="inlineStr">
+      <c r="E14" s="298" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F14" s="275" t="n">
+      <c r="F14" s="300" t="n">
         <v>7632</v>
       </c>
-      <c r="G14" s="273" t="inlineStr">
+      <c r="G14" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50797,31 +50815,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="237">
-      <c r="A15" s="273" t="n">
+      <c r="A15" s="298" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="273" t="n">
+      <c r="B15" s="298" t="n">
         <v>6515</v>
       </c>
-      <c r="C15" s="274" t="inlineStr">
+      <c r="C15" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D15" s="274" t="inlineStr">
+      <c r="D15" s="299" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E15" s="273" t="inlineStr">
+      <c r="E15" s="298" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F15" s="275" t="n">
+      <c r="F15" s="300" t="n">
         <v>38896</v>
       </c>
-      <c r="G15" s="273" t="inlineStr">
+      <c r="G15" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50837,31 +50855,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="237">
-      <c r="A16" s="273" t="n">
+      <c r="A16" s="298" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="273" t="n">
+      <c r="B16" s="298" t="n">
         <v>6530</v>
       </c>
-      <c r="C16" s="274" t="inlineStr">
+      <c r="C16" s="299" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D16" s="274" t="inlineStr">
+      <c r="D16" s="299" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E16" s="273" t="inlineStr">
+      <c r="E16" s="298" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F16" s="275" t="n">
+      <c r="F16" s="300" t="n">
         <v>15000</v>
       </c>
-      <c r="G16" s="273" t="inlineStr">
+      <c r="G16" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50877,31 +50895,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="237">
-      <c r="A17" s="273" t="n">
+      <c r="A17" s="298" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="273" t="n">
+      <c r="B17" s="298" t="n">
         <v>6206</v>
       </c>
-      <c r="C17" s="274" t="inlineStr">
+      <c r="C17" s="299" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D17" s="274" t="inlineStr">
+      <c r="D17" s="299" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E17" s="273" t="inlineStr">
+      <c r="E17" s="298" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F17" s="275" t="n">
+      <c r="F17" s="300" t="n">
         <v>3674</v>
       </c>
-      <c r="G17" s="273" t="inlineStr">
+      <c r="G17" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50917,31 +50935,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="237">
-      <c r="A18" s="273" t="n">
+      <c r="A18" s="298" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="273" t="n">
+      <c r="B18" s="298" t="n">
         <v>5782</v>
       </c>
-      <c r="C18" s="274" t="inlineStr">
+      <c r="C18" s="299" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D18" s="274" t="inlineStr">
+      <c r="D18" s="299" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E18" s="273" t="inlineStr">
+      <c r="E18" s="298" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F18" s="275" t="n">
+      <c r="F18" s="300" t="n">
         <v>10500</v>
       </c>
-      <c r="G18" s="273" t="inlineStr">
+      <c r="G18" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50957,31 +50975,31 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="237">
-      <c r="A19" s="273" t="n">
+      <c r="A19" s="298" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="273" t="n">
+      <c r="B19" s="298" t="n">
         <v>6624</v>
       </c>
-      <c r="C19" s="274" t="inlineStr">
+      <c r="C19" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D19" s="274" t="inlineStr">
+      <c r="D19" s="299" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E19" s="273" t="inlineStr">
+      <c r="E19" s="298" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F19" s="275" t="n">
+      <c r="F19" s="300" t="n">
         <v>15288</v>
       </c>
-      <c r="G19" s="273" t="inlineStr">
+      <c r="G19" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -50997,31 +51015,31 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="237">
-      <c r="A20" s="273" t="n">
+      <c r="A20" s="298" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="273" t="n">
+      <c r="B20" s="298" t="n">
         <v>5731</v>
       </c>
-      <c r="C20" s="274" t="inlineStr">
+      <c r="C20" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D20" s="274" t="inlineStr">
+      <c r="D20" s="299" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E20" s="273" t="inlineStr">
+      <c r="E20" s="298" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F20" s="275" t="n">
+      <c r="F20" s="300" t="n">
         <v>37030</v>
       </c>
-      <c r="G20" s="273" t="inlineStr">
+      <c r="G20" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tubex_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -685,6 +685,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -697,13 +704,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1299,10 +1299,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1364,20 +1364,20 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1386,7 +1386,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1394,23 +1394,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1422,25 +1422,25 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2049,8 +2049,8 @@
     <col width="14.7109375" customWidth="1" style="227" min="13" max="13"/>
     <col width="13.28515625" customWidth="1" style="227" min="14" max="14"/>
     <col width="9.5703125" customWidth="1" style="227" min="15" max="15"/>
-    <col width="8.7109375" customWidth="1" style="227" min="16" max="53"/>
-    <col width="8.7109375" customWidth="1" style="227" min="54" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="227" min="16" max="54"/>
+    <col width="8.7109375" customWidth="1" style="227" min="55" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1" s="237">
@@ -6819,10 +6819,9 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A20)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A20)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A20)&gt;0)*($H$9&gt;0),$C$9&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A20)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A20)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A20)&gt;0)*($H$9&gt;0),$C$9&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A20)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A20)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A20)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A20)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A20)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A20)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A20)&gt;0)*($H$9&gt;0),$C$9&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I20" s="30" t="inlineStr">
-        <is>
-          <t>100kg Shortage (16k tubes WIP)</t>
-        </is>
+      <c r="I20" s="30">
+        <f>IF(E20=0,"Not needed",IF(G20&lt;0,"SHORTAGE",IF(G20&lt;F20*0.1,"LOW","OK")))</f>
+        <v/>
       </c>
       <c r="J20" s="30">
         <f>IF(B20&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A20)*'FG Stock'!$F$4:$F$100))</f>
@@ -13161,19 +13160,19 @@
         <filter val="10"/>
         <filter val="138"/>
         <filter val="15"/>
-        <filter val="169"/>
+        <filter val="167"/>
+        <filter val="183"/>
         <filter val="188"/>
         <filter val="194"/>
         <filter val="2"/>
-        <filter val="232"/>
+        <filter val="25"/>
         <filter val="25,500"/>
         <filter val="3"/>
-        <filter val="30"/>
         <filter val="36,006"/>
-        <filter val="460"/>
+        <filter val="364"/>
+        <filter val="59,135"/>
         <filter val="69"/>
-        <filter val="74,214"/>
-        <filter val="83"/>
+        <filter val="73"/>
         <filter val="89"/>
       </filters>
     </filterColumn>
@@ -38202,7 +38201,7 @@
     <col width="8.85546875" customWidth="1" style="67" min="6" max="6"/>
     <col width="11.140625" customWidth="1" style="67" min="7" max="7"/>
     <col width="8.5703125" customWidth="1" style="68" min="8" max="8"/>
-    <col hidden="1" width="7.7109375" customWidth="1" style="67" min="9" max="9"/>
+    <col width="7.7109375" customWidth="1" style="67" min="9" max="9"/>
     <col width="16.140625" customWidth="1" style="67" min="10" max="10"/>
     <col width="18" customWidth="1" style="237" min="11" max="11"/>
   </cols>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -801,7 +801,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1565,6 +1565,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -50723,31 +50741,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="237">
-      <c r="A4" s="269" t="n">
+      <c r="A4" s="295" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="269" t="n">
+      <c r="B4" s="295" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="270" t="inlineStr">
+      <c r="C4" s="296" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="270" t="inlineStr">
+      <c r="D4" s="296" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="269" t="inlineStr">
+      <c r="E4" s="295" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="271" t="n">
+      <c r="F4" s="297" t="n">
         <v>10580</v>
       </c>
-      <c r="G4" s="269" t="inlineStr">
+      <c r="G4" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50763,31 +50781,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="237">
-      <c r="A5" s="269" t="n">
+      <c r="A5" s="295" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="269" t="n">
+      <c r="B5" s="295" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="270" t="inlineStr">
+      <c r="C5" s="296" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="270" t="inlineStr">
+      <c r="D5" s="296" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="269" t="inlineStr">
+      <c r="E5" s="295" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="271" t="n">
+      <c r="F5" s="297" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="269" t="inlineStr">
+      <c r="G5" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50803,31 +50821,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="237">
-      <c r="A6" s="269" t="n">
+      <c r="A6" s="295" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="269" t="n">
+      <c r="B6" s="295" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="270" t="inlineStr">
+      <c r="C6" s="296" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="270" t="inlineStr">
+      <c r="D6" s="296" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="269" t="inlineStr">
+      <c r="E6" s="295" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="271" t="n">
+      <c r="F6" s="297" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="269" t="inlineStr">
+      <c r="G6" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50843,31 +50861,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="237">
-      <c r="A7" s="269" t="n">
+      <c r="A7" s="295" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="269" t="n">
+      <c r="B7" s="295" t="n">
         <v>4050</v>
       </c>
-      <c r="C7" s="270" t="inlineStr">
+      <c r="C7" s="296" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D7" s="270" t="inlineStr">
+      <c r="D7" s="296" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E7" s="269" t="inlineStr">
+      <c r="E7" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F7" s="271" t="n">
+      <c r="F7" s="297" t="n">
         <v>9450</v>
       </c>
-      <c r="G7" s="269" t="inlineStr">
+      <c r="G7" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50883,31 +50901,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="237">
-      <c r="A8" s="269" t="n">
+      <c r="A8" s="295" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="269" t="n">
+      <c r="B8" s="295" t="n">
         <v>6337</v>
       </c>
-      <c r="C8" s="270" t="inlineStr">
+      <c r="C8" s="296" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D8" s="270" t="inlineStr">
+      <c r="D8" s="296" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E8" s="269" t="inlineStr">
+      <c r="E8" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="271" t="n">
+      <c r="F8" s="297" t="n">
         <v>15680</v>
       </c>
-      <c r="G8" s="269" t="inlineStr">
+      <c r="G8" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50923,31 +50941,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="237">
-      <c r="A9" s="269" t="n">
+      <c r="A9" s="295" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="269" t="n">
+      <c r="B9" s="295" t="n">
         <v>6416</v>
       </c>
-      <c r="C9" s="270" t="inlineStr">
+      <c r="C9" s="296" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="270" t="inlineStr">
+      <c r="D9" s="296" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="269" t="inlineStr">
+      <c r="E9" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="271" t="n">
+      <c r="F9" s="297" t="n">
         <v>15435</v>
       </c>
-      <c r="G9" s="269" t="inlineStr">
+      <c r="G9" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50963,31 +50981,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="237">
-      <c r="A10" s="269" t="n">
+      <c r="A10" s="295" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="269" t="n">
+      <c r="B10" s="295" t="n">
         <v>5782</v>
       </c>
-      <c r="C10" s="270" t="inlineStr">
+      <c r="C10" s="296" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D10" s="270" t="inlineStr">
+      <c r="D10" s="296" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E10" s="269" t="inlineStr">
+      <c r="E10" s="295" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F10" s="271" t="n">
+      <c r="F10" s="297" t="n">
         <v>63648</v>
       </c>
-      <c r="G10" s="269" t="inlineStr">
+      <c r="G10" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51003,31 +51021,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="237">
-      <c r="A11" s="269" t="n">
+      <c r="A11" s="295" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="269" t="n">
+      <c r="B11" s="295" t="n">
         <v>6531</v>
       </c>
-      <c r="C11" s="270" t="inlineStr">
+      <c r="C11" s="296" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D11" s="270" t="inlineStr">
+      <c r="D11" s="296" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E11" s="269" t="inlineStr">
+      <c r="E11" s="295" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F11" s="271" t="n">
+      <c r="F11" s="297" t="n">
         <v>4380</v>
       </c>
-      <c r="G11" s="269" t="inlineStr">
+      <c r="G11" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51043,31 +51061,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="237">
-      <c r="A12" s="269" t="n">
+      <c r="A12" s="295" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="269" t="n">
+      <c r="B12" s="295" t="n">
         <v>6532</v>
       </c>
-      <c r="C12" s="270" t="inlineStr">
+      <c r="C12" s="296" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D12" s="270" t="inlineStr">
+      <c r="D12" s="296" t="inlineStr">
         <is>
           <t>TUBE COMMON PURPLE</t>
         </is>
       </c>
-      <c r="E12" s="269" t="inlineStr">
+      <c r="E12" s="295" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F12" s="271" t="n">
+      <c r="F12" s="297" t="n">
         <v>31248</v>
       </c>
-      <c r="G12" s="269" t="inlineStr">
+      <c r="G12" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51083,31 +51101,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="237">
-      <c r="A13" s="269" t="n">
+      <c r="A13" s="295" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="269" t="n">
+      <c r="B13" s="295" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="270" t="inlineStr">
+      <c r="C13" s="296" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="270" t="inlineStr">
+      <c r="D13" s="296" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="269" t="inlineStr">
+      <c r="E13" s="295" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="271" t="n">
+      <c r="F13" s="297" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="269" t="inlineStr">
+      <c r="G13" s="295" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51123,31 +51141,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="237">
-      <c r="A14" s="273" t="n">
+      <c r="A14" s="298" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="273" t="n">
+      <c r="B14" s="298" t="n">
         <v>6470</v>
       </c>
-      <c r="C14" s="274" t="inlineStr">
+      <c r="C14" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="274" t="inlineStr">
+      <c r="D14" s="299" t="inlineStr">
         <is>
           <t>TUBES COMMON RED</t>
         </is>
       </c>
-      <c r="E14" s="273" t="inlineStr">
+      <c r="E14" s="298" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F14" s="275" t="n">
+      <c r="F14" s="300" t="n">
         <v>7632</v>
       </c>
-      <c r="G14" s="273" t="inlineStr">
+      <c r="G14" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51163,31 +51181,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="237">
-      <c r="A15" s="273" t="n">
+      <c r="A15" s="298" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="273" t="n">
+      <c r="B15" s="298" t="n">
         <v>6515</v>
       </c>
-      <c r="C15" s="274" t="inlineStr">
+      <c r="C15" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D15" s="274" t="inlineStr">
+      <c r="D15" s="299" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E15" s="273" t="inlineStr">
+      <c r="E15" s="298" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F15" s="275" t="n">
+      <c r="F15" s="300" t="n">
         <v>38896</v>
       </c>
-      <c r="G15" s="273" t="inlineStr">
+      <c r="G15" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51203,31 +51221,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="237">
-      <c r="A16" s="273" t="n">
+      <c r="A16" s="298" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="273" t="n">
+      <c r="B16" s="298" t="n">
         <v>6530</v>
       </c>
-      <c r="C16" s="274" t="inlineStr">
+      <c r="C16" s="299" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D16" s="274" t="inlineStr">
+      <c r="D16" s="299" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E16" s="273" t="inlineStr">
+      <c r="E16" s="298" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F16" s="275" t="n">
+      <c r="F16" s="300" t="n">
         <v>15000</v>
       </c>
-      <c r="G16" s="273" t="inlineStr">
+      <c r="G16" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51243,31 +51261,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="237">
-      <c r="A17" s="273" t="n">
+      <c r="A17" s="298" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="273" t="n">
+      <c r="B17" s="298" t="n">
         <v>5782</v>
       </c>
-      <c r="C17" s="274" t="inlineStr">
+      <c r="C17" s="299" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D17" s="274" t="inlineStr">
+      <c r="D17" s="299" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E17" s="273" t="inlineStr">
+      <c r="E17" s="298" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F17" s="275" t="n">
+      <c r="F17" s="300" t="n">
         <v>10500</v>
       </c>
-      <c r="G17" s="273" t="inlineStr">
+      <c r="G17" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51283,31 +51301,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="237">
-      <c r="A18" s="273" t="n">
+      <c r="A18" s="298" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="273" t="n">
+      <c r="B18" s="298" t="n">
         <v>6624</v>
       </c>
-      <c r="C18" s="274" t="inlineStr">
+      <c r="C18" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="274" t="inlineStr">
+      <c r="D18" s="299" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E18" s="273" t="inlineStr">
+      <c r="E18" s="298" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F18" s="275" t="n">
+      <c r="F18" s="300" t="n">
         <v>15288</v>
       </c>
-      <c r="G18" s="273" t="inlineStr">
+      <c r="G18" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51323,31 +51341,31 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="237">
-      <c r="A19" s="273" t="n">
+      <c r="A19" s="298" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="273" t="n">
+      <c r="B19" s="298" t="n">
         <v>5731</v>
       </c>
-      <c r="C19" s="274" t="inlineStr">
+      <c r="C19" s="299" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D19" s="274" t="inlineStr">
+      <c r="D19" s="299" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E19" s="273" t="inlineStr">
+      <c r="E19" s="298" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F19" s="275" t="n">
+      <c r="F19" s="300" t="n">
         <v>37030</v>
       </c>
-      <c r="G19" s="273" t="inlineStr">
+      <c r="G19" s="298" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -801,7 +801,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1583,6 +1583,24 @@
     <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16872,193 +16890,398 @@
       <c r="S83" s="265" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="237">
-      <c r="A84" s="176" t="n"/>
-      <c r="B84" s="177" t="n"/>
-      <c r="C84" s="177" t="n"/>
-      <c r="D84" s="177" t="n"/>
-      <c r="E84" s="177" t="n"/>
-      <c r="F84" s="177" t="n"/>
-      <c r="G84" s="178" t="n"/>
-      <c r="H84" s="178" t="n"/>
-      <c r="I84" s="178" t="n"/>
-      <c r="J84" s="179" t="n"/>
-      <c r="K84" s="177" t="n"/>
-      <c r="L84" s="177" t="n"/>
-      <c r="M84" s="177" t="n"/>
-      <c r="N84" s="177" t="n"/>
-      <c r="O84" s="177" t="n"/>
-      <c r="P84" s="177" t="n"/>
-      <c r="Q84" s="177" t="n"/>
-      <c r="R84" s="177" t="n"/>
-      <c r="S84" s="177" t="n"/>
+      <c r="A84" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B84" s="265" t="inlineStr">
+        <is>
+          <t>Lacquer-02</t>
+        </is>
+      </c>
+      <c r="C84" s="265" t="inlineStr"/>
+      <c r="D84" s="265" t="inlineStr"/>
+      <c r="E84" s="265" t="inlineStr"/>
+      <c r="F84" s="265" t="n"/>
+      <c r="G84" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="267">
+        <f>IFERROR(I84/(H84+I84),"")</f>
+        <v/>
+      </c>
+      <c r="K84" s="265" t="n"/>
+      <c r="L84" s="265" t="n"/>
+      <c r="M84" s="265" t="n"/>
+      <c r="N84" s="265" t="n"/>
+      <c r="O84" s="265" t="n"/>
+      <c r="P84" s="265" t="n"/>
+      <c r="Q84" s="265" t="n"/>
+      <c r="R84" s="265" t="n"/>
+      <c r="S84" s="265" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="237">
-      <c r="A85" s="176" t="n"/>
-      <c r="B85" s="177" t="n"/>
-      <c r="C85" s="177" t="n"/>
-      <c r="D85" s="177" t="n"/>
-      <c r="E85" s="177" t="n"/>
-      <c r="F85" s="177" t="n"/>
-      <c r="G85" s="178" t="n"/>
-      <c r="H85" s="178" t="n"/>
-      <c r="I85" s="178" t="n"/>
-      <c r="J85" s="179" t="n"/>
-      <c r="K85" s="177" t="n"/>
-      <c r="L85" s="177" t="n"/>
-      <c r="M85" s="177" t="n"/>
-      <c r="N85" s="177" t="n"/>
-      <c r="O85" s="177" t="n"/>
-      <c r="P85" s="177" t="n"/>
-      <c r="Q85" s="177" t="n"/>
-      <c r="R85" s="177" t="n"/>
-      <c r="S85" s="177" t="n"/>
+      <c r="A85" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B85" s="265" t="inlineStr">
+        <is>
+          <t>Lacquer-04</t>
+        </is>
+      </c>
+      <c r="C85" s="265" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D85" s="265" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E85" s="265" t="n">
+        <v>25</v>
+      </c>
+      <c r="F85" s="265" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G85" s="266" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H85" s="266" t="n">
+        <v>14775</v>
+      </c>
+      <c r="I85" s="266" t="n">
+        <v>225</v>
+      </c>
+      <c r="J85" s="267">
+        <f>IFERROR(I85/(H85+I85),"")</f>
+        <v/>
+      </c>
+      <c r="K85" s="265" t="n"/>
+      <c r="L85" s="265" t="n"/>
+      <c r="M85" s="265" t="n"/>
+      <c r="N85" s="265" t="n"/>
+      <c r="O85" s="265" t="n"/>
+      <c r="P85" s="265" t="n"/>
+      <c r="Q85" s="265" t="n"/>
+      <c r="R85" s="265" t="n"/>
+      <c r="S85" s="265" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1" s="237">
-      <c r="A86" s="176" t="n"/>
-      <c r="B86" s="177" t="n"/>
-      <c r="C86" s="177" t="n"/>
-      <c r="D86" s="177" t="n"/>
-      <c r="E86" s="177" t="n"/>
-      <c r="F86" s="177" t="n"/>
-      <c r="G86" s="178" t="n"/>
-      <c r="H86" s="178" t="n"/>
-      <c r="I86" s="178" t="n"/>
-      <c r="J86" s="179" t="n"/>
-      <c r="K86" s="177" t="n"/>
-      <c r="L86" s="177" t="n"/>
-      <c r="M86" s="177" t="n"/>
-      <c r="N86" s="177" t="n"/>
-      <c r="O86" s="177" t="n"/>
-      <c r="P86" s="177" t="n"/>
-      <c r="Q86" s="177" t="n"/>
-      <c r="R86" s="177" t="n"/>
-      <c r="S86" s="177" t="n"/>
+      <c r="A86" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B86" s="265" t="inlineStr">
+        <is>
+          <t>Latex-01</t>
+        </is>
+      </c>
+      <c r="C86" s="265" t="inlineStr"/>
+      <c r="D86" s="265" t="inlineStr"/>
+      <c r="E86" s="265" t="inlineStr"/>
+      <c r="F86" s="265" t="n"/>
+      <c r="G86" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="267">
+        <f>IFERROR(I86/(H86+I86),"")</f>
+        <v/>
+      </c>
+      <c r="K86" s="265" t="n"/>
+      <c r="L86" s="265" t="n"/>
+      <c r="M86" s="265" t="n"/>
+      <c r="N86" s="265" t="n"/>
+      <c r="O86" s="265" t="n"/>
+      <c r="P86" s="265" t="n"/>
+      <c r="Q86" s="265" t="n"/>
+      <c r="R86" s="265" t="n"/>
+      <c r="S86" s="265" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1" s="237">
-      <c r="A87" s="176" t="n"/>
-      <c r="B87" s="177" t="n"/>
-      <c r="C87" s="177" t="n"/>
-      <c r="D87" s="177" t="n"/>
-      <c r="E87" s="177" t="n"/>
-      <c r="F87" s="177" t="n"/>
-      <c r="G87" s="178" t="n"/>
-      <c r="H87" s="178" t="n"/>
-      <c r="I87" s="178" t="n"/>
-      <c r="J87" s="179" t="n"/>
-      <c r="K87" s="177" t="n"/>
-      <c r="L87" s="177" t="n"/>
-      <c r="M87" s="177" t="n"/>
-      <c r="N87" s="177" t="n"/>
-      <c r="O87" s="177" t="n"/>
-      <c r="P87" s="177" t="n"/>
-      <c r="Q87" s="177" t="n"/>
-      <c r="R87" s="177" t="n"/>
-      <c r="S87" s="177" t="n"/>
+      <c r="A87" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B87" s="265" t="inlineStr">
+        <is>
+          <t>PF Machine</t>
+        </is>
+      </c>
+      <c r="C87" s="265" t="inlineStr">
+        <is>
+          <t>Alpha Labs PVT LTD</t>
+        </is>
+      </c>
+      <c r="D87" s="265" t="inlineStr">
+        <is>
+          <t>TRANSPARENT BOTTLE 150ML</t>
+        </is>
+      </c>
+      <c r="E87" s="265" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="F87" s="265" t="n">
+        <v>8001</v>
+      </c>
+      <c r="G87" s="266" t="n">
+        <v>9030</v>
+      </c>
+      <c r="H87" s="266" t="n">
+        <v>8280</v>
+      </c>
+      <c r="I87" s="266" t="n">
+        <v>750</v>
+      </c>
+      <c r="J87" s="267">
+        <f>IFERROR(I87/(H87+I87),"")</f>
+        <v/>
+      </c>
+      <c r="K87" s="265" t="n"/>
+      <c r="L87" s="265" t="n"/>
+      <c r="M87" s="265" t="n"/>
+      <c r="N87" s="265" t="n"/>
+      <c r="O87" s="265" t="n"/>
+      <c r="P87" s="265" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q87" s="265" t="n"/>
+      <c r="R87" s="265" t="n"/>
+      <c r="S87" s="265" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1" s="237">
-      <c r="A88" s="176" t="n"/>
-      <c r="B88" s="177" t="n"/>
-      <c r="C88" s="177" t="n"/>
-      <c r="D88" s="177" t="n"/>
-      <c r="E88" s="177" t="n"/>
-      <c r="F88" s="177" t="n"/>
-      <c r="G88" s="178" t="n"/>
-      <c r="H88" s="178" t="n"/>
-      <c r="I88" s="178" t="n"/>
-      <c r="J88" s="179" t="n"/>
-      <c r="K88" s="177" t="n"/>
-      <c r="L88" s="177" t="n"/>
-      <c r="M88" s="177" t="n"/>
-      <c r="N88" s="177" t="n"/>
-      <c r="O88" s="177" t="n"/>
-      <c r="P88" s="177" t="n"/>
-      <c r="Q88" s="177" t="n"/>
-      <c r="R88" s="177" t="n"/>
-      <c r="S88" s="177" t="n"/>
+      <c r="A88" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B88" s="265" t="inlineStr">
+        <is>
+          <t>Press-04</t>
+        </is>
+      </c>
+      <c r="C88" s="265" t="inlineStr"/>
+      <c r="D88" s="265" t="inlineStr"/>
+      <c r="E88" s="265" t="inlineStr"/>
+      <c r="F88" s="265" t="n"/>
+      <c r="G88" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="267">
+        <f>IFERROR(I88/(H88+I88),"")</f>
+        <v/>
+      </c>
+      <c r="K88" s="265" t="n"/>
+      <c r="L88" s="265" t="n"/>
+      <c r="M88" s="265" t="n"/>
+      <c r="N88" s="265" t="n"/>
+      <c r="O88" s="265" t="n"/>
+      <c r="P88" s="265" t="n"/>
+      <c r="Q88" s="265" t="n"/>
+      <c r="R88" s="265" t="n"/>
+      <c r="S88" s="265" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1" s="237">
-      <c r="A89" s="176" t="n"/>
-      <c r="B89" s="177" t="n"/>
-      <c r="C89" s="177" t="n"/>
-      <c r="D89" s="177" t="n"/>
-      <c r="E89" s="177" t="n"/>
-      <c r="F89" s="177" t="n"/>
-      <c r="G89" s="178" t="n"/>
-      <c r="H89" s="178" t="n"/>
-      <c r="I89" s="178" t="n"/>
-      <c r="J89" s="179" t="n"/>
-      <c r="K89" s="177" t="n"/>
-      <c r="L89" s="177" t="n"/>
-      <c r="M89" s="177" t="n"/>
-      <c r="N89" s="177" t="n"/>
-      <c r="O89" s="177" t="n"/>
-      <c r="P89" s="177" t="n"/>
-      <c r="Q89" s="177" t="n"/>
-      <c r="R89" s="177" t="n"/>
-      <c r="S89" s="177" t="n"/>
+      <c r="A89" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B89" s="265" t="inlineStr">
+        <is>
+          <t>Press-06</t>
+        </is>
+      </c>
+      <c r="C89" s="265" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D89" s="265" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E89" s="265" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="265" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G89" s="266" t="n">
+        <v>19500</v>
+      </c>
+      <c r="H89" s="266" t="n">
+        <v>19345</v>
+      </c>
+      <c r="I89" s="266" t="n">
+        <v>155</v>
+      </c>
+      <c r="J89" s="267">
+        <f>IFERROR(I89/(H89+I89),"")</f>
+        <v/>
+      </c>
+      <c r="K89" s="265" t="n"/>
+      <c r="L89" s="265" t="n"/>
+      <c r="M89" s="265" t="n"/>
+      <c r="N89" s="265" t="n"/>
+      <c r="O89" s="265" t="n"/>
+      <c r="P89" s="265" t="n"/>
+      <c r="Q89" s="265" t="n"/>
+      <c r="R89" s="265" t="n"/>
+      <c r="S89" s="265" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" s="237">
-      <c r="A90" s="176" t="n"/>
-      <c r="B90" s="177" t="n"/>
-      <c r="C90" s="177" t="n"/>
-      <c r="D90" s="177" t="n"/>
-      <c r="E90" s="177" t="n"/>
-      <c r="F90" s="177" t="n"/>
-      <c r="G90" s="178" t="n"/>
-      <c r="H90" s="178" t="n"/>
-      <c r="I90" s="178" t="n"/>
-      <c r="J90" s="179" t="n"/>
-      <c r="K90" s="177" t="n"/>
-      <c r="L90" s="177" t="n"/>
-      <c r="M90" s="177" t="n"/>
-      <c r="N90" s="177" t="n"/>
-      <c r="O90" s="177" t="n"/>
-      <c r="P90" s="177" t="n"/>
-      <c r="Q90" s="177" t="n"/>
-      <c r="R90" s="177" t="n"/>
-      <c r="S90" s="177" t="n"/>
+      <c r="A90" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B90" s="265" t="inlineStr">
+        <is>
+          <t>Printing-03</t>
+        </is>
+      </c>
+      <c r="C90" s="265" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D90" s="265" t="inlineStr">
+        <is>
+          <t>TUBE COMMON PURPLE</t>
+        </is>
+      </c>
+      <c r="E90" s="265" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" s="265" t="n">
+        <v>6532</v>
+      </c>
+      <c r="G90" s="266" t="n">
+        <v>3188</v>
+      </c>
+      <c r="H90" s="266" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I90" s="266" t="n">
+        <v>164</v>
+      </c>
+      <c r="J90" s="267">
+        <f>IFERROR(I90/(H90+I90),"")</f>
+        <v/>
+      </c>
+      <c r="K90" s="265" t="n"/>
+      <c r="L90" s="265" t="n"/>
+      <c r="M90" s="265" t="n"/>
+      <c r="N90" s="265" t="n">
+        <v>20</v>
+      </c>
+      <c r="O90" s="265" t="n"/>
+      <c r="P90" s="265" t="n"/>
+      <c r="Q90" s="265" t="n"/>
+      <c r="R90" s="265" t="n"/>
+      <c r="S90" s="265" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="237">
-      <c r="A91" s="176" t="n"/>
-      <c r="B91" s="177" t="n"/>
-      <c r="C91" s="177" t="n"/>
-      <c r="D91" s="177" t="n"/>
-      <c r="E91" s="177" t="n"/>
-      <c r="F91" s="177" t="n"/>
-      <c r="G91" s="178" t="n"/>
-      <c r="H91" s="178" t="n"/>
-      <c r="I91" s="178" t="n"/>
-      <c r="J91" s="179" t="n"/>
-      <c r="K91" s="177" t="n"/>
-      <c r="L91" s="177" t="n"/>
-      <c r="M91" s="177" t="n"/>
-      <c r="N91" s="177" t="n"/>
-      <c r="O91" s="177" t="n"/>
-      <c r="P91" s="177" t="n"/>
-      <c r="Q91" s="177" t="n"/>
-      <c r="R91" s="177" t="n"/>
-      <c r="S91" s="177" t="n"/>
+      <c r="A91" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B91" s="265" t="inlineStr">
+        <is>
+          <t>Printing-03</t>
+        </is>
+      </c>
+      <c r="C91" s="265" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D91" s="265" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E91" s="265" t="n">
+        <v>25</v>
+      </c>
+      <c r="F91" s="265" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G91" s="266" t="n">
+        <v>12762</v>
+      </c>
+      <c r="H91" s="266" t="n">
+        <v>12432</v>
+      </c>
+      <c r="I91" s="266" t="n">
+        <v>330</v>
+      </c>
+      <c r="J91" s="267">
+        <f>IFERROR(I91/(H91+I91),"")</f>
+        <v/>
+      </c>
+      <c r="K91" s="265" t="n"/>
+      <c r="L91" s="265" t="n"/>
+      <c r="M91" s="265" t="n"/>
+      <c r="N91" s="265" t="n"/>
+      <c r="O91" s="265" t="n"/>
+      <c r="P91" s="265" t="n"/>
+      <c r="Q91" s="265" t="n"/>
+      <c r="R91" s="265" t="n"/>
+      <c r="S91" s="265" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" s="237">
-      <c r="A92" s="176" t="n"/>
-      <c r="B92" s="177" t="n"/>
-      <c r="C92" s="177" t="n"/>
-      <c r="D92" s="177" t="n"/>
-      <c r="E92" s="177" t="n"/>
-      <c r="F92" s="177" t="n"/>
-      <c r="G92" s="178" t="n"/>
-      <c r="H92" s="178" t="n"/>
-      <c r="I92" s="178" t="n"/>
-      <c r="J92" s="179" t="n"/>
-      <c r="K92" s="177" t="n"/>
-      <c r="L92" s="177" t="n"/>
-      <c r="M92" s="177" t="n"/>
-      <c r="N92" s="177" t="n"/>
-      <c r="O92" s="177" t="n"/>
-      <c r="P92" s="177" t="n"/>
-      <c r="Q92" s="177" t="n"/>
-      <c r="R92" s="177" t="n"/>
-      <c r="S92" s="177" t="n"/>
+      <c r="A92" s="268" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B92" s="265" t="inlineStr">
+        <is>
+          <t>Printing-04</t>
+        </is>
+      </c>
+      <c r="C92" s="265" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D92" s="265" t="inlineStr"/>
+      <c r="E92" s="265" t="inlineStr"/>
+      <c r="F92" s="265" t="n"/>
+      <c r="G92" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="267">
+        <f>IFERROR(I92/(H92+I92),"")</f>
+        <v/>
+      </c>
+      <c r="K92" s="265" t="n"/>
+      <c r="L92" s="265" t="n"/>
+      <c r="M92" s="265" t="n"/>
+      <c r="N92" s="265" t="n"/>
+      <c r="O92" s="265" t="n"/>
+      <c r="P92" s="265" t="n"/>
+      <c r="Q92" s="265" t="n"/>
+      <c r="R92" s="265" t="n"/>
+      <c r="S92" s="265" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1" s="237">
       <c r="A93" s="176" t="n"/>
@@ -50682,7 +50905,7 @@
     <row r="1" ht="30" customHeight="1" s="237">
       <c r="A1" s="259" t="inlineStr">
         <is>
-          <t>FG STOCK IN HAND — Last Updated: 13-Jun-2026</t>
+          <t>FG STOCK IN HAND — Last Updated: 15-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -50741,31 +50964,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="237">
-      <c r="A4" s="295" t="n">
+      <c r="A4" s="301" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="295" t="n">
+      <c r="B4" s="301" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="296" t="inlineStr">
+      <c r="C4" s="302" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="296" t="inlineStr">
+      <c r="D4" s="302" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="295" t="inlineStr">
+      <c r="E4" s="301" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="297" t="n">
-        <v>10580</v>
-      </c>
-      <c r="G4" s="295" t="inlineStr">
+      <c r="F4" s="303" t="n">
+        <v>18860</v>
+      </c>
+      <c r="G4" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50781,31 +51004,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="237">
-      <c r="A5" s="295" t="n">
+      <c r="A5" s="301" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="295" t="n">
+      <c r="B5" s="301" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="296" t="inlineStr">
+      <c r="C5" s="302" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="296" t="inlineStr">
+      <c r="D5" s="302" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="295" t="inlineStr">
+      <c r="E5" s="301" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="297" t="n">
+      <c r="F5" s="303" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="295" t="inlineStr">
+      <c r="G5" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50821,31 +51044,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="237">
-      <c r="A6" s="295" t="n">
+      <c r="A6" s="301" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="295" t="n">
+      <c r="B6" s="301" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="296" t="inlineStr">
+      <c r="C6" s="302" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="296" t="inlineStr">
+      <c r="D6" s="302" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="295" t="inlineStr">
+      <c r="E6" s="301" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="297" t="n">
+      <c r="F6" s="303" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="295" t="inlineStr">
+      <c r="G6" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50861,31 +51084,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="237">
-      <c r="A7" s="295" t="n">
+      <c r="A7" s="301" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="295" t="n">
-        <v>4050</v>
-      </c>
-      <c r="C7" s="296" t="inlineStr">
-        <is>
-          <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
-        </is>
-      </c>
-      <c r="D7" s="296" t="inlineStr">
-        <is>
-          <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
-        </is>
-      </c>
-      <c r="E7" s="295" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F7" s="297" t="n">
-        <v>9450</v>
-      </c>
-      <c r="G7" s="295" t="inlineStr">
+      <c r="B7" s="301" t="n">
+        <v>5389</v>
+      </c>
+      <c r="C7" s="302" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="302" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E7" s="301" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="303" t="n">
+        <v>11088</v>
+      </c>
+      <c r="G7" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50901,31 +51124,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="237">
-      <c r="A8" s="295" t="n">
+      <c r="A8" s="301" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="295" t="n">
-        <v>6337</v>
-      </c>
-      <c r="C8" s="296" t="inlineStr">
-        <is>
-          <t>Al-Rehman Group</t>
-        </is>
-      </c>
-      <c r="D8" s="296" t="inlineStr">
-        <is>
-          <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
-        </is>
-      </c>
-      <c r="E8" s="295" t="inlineStr">
+      <c r="B8" s="301" t="n">
+        <v>4050</v>
+      </c>
+      <c r="C8" s="302" t="inlineStr">
+        <is>
+          <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
+        </is>
+      </c>
+      <c r="D8" s="302" t="inlineStr">
+        <is>
+          <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
+        </is>
+      </c>
+      <c r="E8" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="297" t="n">
-        <v>15680</v>
-      </c>
-      <c r="G8" s="295" t="inlineStr">
+      <c r="F8" s="303" t="n">
+        <v>9450</v>
+      </c>
+      <c r="G8" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50941,31 +51164,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="237">
-      <c r="A9" s="295" t="n">
+      <c r="A9" s="301" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="295" t="n">
-        <v>6416</v>
-      </c>
-      <c r="C9" s="296" t="inlineStr">
+      <c r="B9" s="301" t="n">
+        <v>6337</v>
+      </c>
+      <c r="C9" s="302" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="296" t="inlineStr">
-        <is>
-          <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
-        </is>
-      </c>
-      <c r="E9" s="295" t="inlineStr">
+      <c r="D9" s="302" t="inlineStr">
+        <is>
+          <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
+        </is>
+      </c>
+      <c r="E9" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="297" t="n">
-        <v>15435</v>
-      </c>
-      <c r="G9" s="295" t="inlineStr">
+      <c r="F9" s="303" t="n">
+        <v>15680</v>
+      </c>
+      <c r="G9" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -50981,31 +51204,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="237">
-      <c r="A10" s="295" t="n">
+      <c r="A10" s="301" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="295" t="n">
-        <v>5782</v>
-      </c>
-      <c r="C10" s="296" t="inlineStr">
-        <is>
-          <t>Mega Grey</t>
-        </is>
-      </c>
-      <c r="D10" s="296" t="inlineStr">
-        <is>
-          <t>M.G</t>
-        </is>
-      </c>
-      <c r="E10" s="295" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F10" s="297" t="n">
-        <v>63648</v>
-      </c>
-      <c r="G10" s="295" t="inlineStr">
+      <c r="B10" s="301" t="n">
+        <v>6416</v>
+      </c>
+      <c r="C10" s="302" t="inlineStr">
+        <is>
+          <t>Al-Rehman Group</t>
+        </is>
+      </c>
+      <c r="D10" s="302" t="inlineStr">
+        <is>
+          <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
+        </is>
+      </c>
+      <c r="E10" s="301" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" s="303" t="n">
+        <v>15435</v>
+      </c>
+      <c r="G10" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51021,31 +51244,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="237">
-      <c r="A11" s="295" t="n">
+      <c r="A11" s="301" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="295" t="n">
-        <v>6531</v>
-      </c>
-      <c r="C11" s="296" t="inlineStr">
-        <is>
-          <t>Adore</t>
-        </is>
-      </c>
-      <c r="D11" s="296" t="inlineStr">
-        <is>
-          <t>V-HC BLACK</t>
-        </is>
-      </c>
-      <c r="E11" s="295" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F11" s="297" t="n">
-        <v>4380</v>
-      </c>
-      <c r="G11" s="295" t="inlineStr">
+      <c r="B11" s="301" t="n">
+        <v>5782</v>
+      </c>
+      <c r="C11" s="302" t="inlineStr">
+        <is>
+          <t>Mega Grey</t>
+        </is>
+      </c>
+      <c r="D11" s="302" t="inlineStr">
+        <is>
+          <t>M.G</t>
+        </is>
+      </c>
+      <c r="E11" s="301" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F11" s="303" t="n">
+        <v>63648</v>
+      </c>
+      <c r="G11" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51061,31 +51284,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="237">
-      <c r="A12" s="295" t="n">
+      <c r="A12" s="301" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="295" t="n">
-        <v>6532</v>
-      </c>
-      <c r="C12" s="296" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D12" s="296" t="inlineStr">
-        <is>
-          <t>TUBE COMMON PURPLE</t>
-        </is>
-      </c>
-      <c r="E12" s="295" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F12" s="297" t="n">
-        <v>31248</v>
-      </c>
-      <c r="G12" s="295" t="inlineStr">
+      <c r="B12" s="301" t="n">
+        <v>6531</v>
+      </c>
+      <c r="C12" s="302" t="inlineStr">
+        <is>
+          <t>Adore</t>
+        </is>
+      </c>
+      <c r="D12" s="302" t="inlineStr">
+        <is>
+          <t>V-HC BLACK</t>
+        </is>
+      </c>
+      <c r="E12" s="301" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F12" s="303" t="n">
+        <v>4380</v>
+      </c>
+      <c r="G12" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51101,31 +51324,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="237">
-      <c r="A13" s="295" t="n">
+      <c r="A13" s="301" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="295" t="n">
+      <c r="B13" s="301" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="296" t="inlineStr">
+      <c r="C13" s="302" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="296" t="inlineStr">
+      <c r="D13" s="302" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="295" t="inlineStr">
+      <c r="E13" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="297" t="n">
+      <c r="F13" s="303" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="295" t="inlineStr">
+      <c r="G13" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51141,31 +51364,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="237">
-      <c r="A14" s="298" t="n">
+      <c r="A14" s="304" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="298" t="n">
-        <v>6470</v>
-      </c>
-      <c r="C14" s="299" t="inlineStr">
+      <c r="B14" s="304" t="n">
+        <v>6515</v>
+      </c>
+      <c r="C14" s="305" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="299" t="inlineStr">
-        <is>
-          <t>TUBES COMMON RED</t>
-        </is>
-      </c>
-      <c r="E14" s="298" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F14" s="300" t="n">
-        <v>7632</v>
-      </c>
-      <c r="G14" s="298" t="inlineStr">
+      <c r="D14" s="305" t="inlineStr">
+        <is>
+          <t>H.H 100GM</t>
+        </is>
+      </c>
+      <c r="E14" s="304" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F14" s="306" t="n">
+        <v>38896</v>
+      </c>
+      <c r="G14" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51181,38 +51404,38 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="237">
-      <c r="A15" s="298" t="n">
+      <c r="A15" s="304" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="298" t="n">
-        <v>6515</v>
-      </c>
-      <c r="C15" s="299" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D15" s="299" t="inlineStr">
-        <is>
-          <t>H.H 100GM</t>
-        </is>
-      </c>
-      <c r="E15" s="298" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F15" s="300" t="n">
-        <v>38896</v>
-      </c>
-      <c r="G15" s="298" t="inlineStr">
+      <c r="B15" s="304" t="n">
+        <v>6530</v>
+      </c>
+      <c r="C15" s="305" t="inlineStr">
+        <is>
+          <t>Adore</t>
+        </is>
+      </c>
+      <c r="D15" s="305" t="inlineStr">
+        <is>
+          <t>V- HC BROWN</t>
+        </is>
+      </c>
+      <c r="E15" s="304" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F15" s="306" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G15" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
       </c>
       <c r="H15" s="276" t="inlineStr">
         <is>
-          <t>To be dispatch after packing</t>
+          <t>Cap Not Available</t>
         </is>
       </c>
       <c r="I15" s="95">
@@ -51221,38 +51444,38 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="237">
-      <c r="A16" s="298" t="n">
+      <c r="A16" s="304" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="298" t="n">
-        <v>6530</v>
-      </c>
-      <c r="C16" s="299" t="inlineStr">
-        <is>
-          <t>Adore</t>
-        </is>
-      </c>
-      <c r="D16" s="299" t="inlineStr">
-        <is>
-          <t>V- HC BROWN</t>
-        </is>
-      </c>
-      <c r="E16" s="298" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F16" s="300" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G16" s="298" t="inlineStr">
+      <c r="B16" s="304" t="n">
+        <v>5782</v>
+      </c>
+      <c r="C16" s="305" t="inlineStr">
+        <is>
+          <t>Mega Grey</t>
+        </is>
+      </c>
+      <c r="D16" s="305" t="inlineStr">
+        <is>
+          <t>M.G</t>
+        </is>
+      </c>
+      <c r="E16" s="304" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F16" s="306" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G16" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
       </c>
       <c r="H16" s="276" t="inlineStr">
         <is>
-          <t>To be dispatch after packing</t>
+          <t>Cap Not Available</t>
         </is>
       </c>
       <c r="I16" s="95">
@@ -51261,31 +51484,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="237">
-      <c r="A17" s="298" t="n">
+      <c r="A17" s="304" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="298" t="n">
-        <v>5782</v>
-      </c>
-      <c r="C17" s="299" t="inlineStr">
-        <is>
-          <t>Mega Grey</t>
-        </is>
-      </c>
-      <c r="D17" s="299" t="inlineStr">
-        <is>
-          <t>M.G</t>
-        </is>
-      </c>
-      <c r="E17" s="298" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F17" s="300" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G17" s="298" t="inlineStr">
+      <c r="B17" s="304" t="n">
+        <v>6624</v>
+      </c>
+      <c r="C17" s="305" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D17" s="305" t="inlineStr">
+        <is>
+          <t>S-45 DIA 19MM</t>
+        </is>
+      </c>
+      <c r="E17" s="304" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F17" s="306" t="n">
+        <v>15288</v>
+      </c>
+      <c r="G17" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51301,31 +51524,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="237">
-      <c r="A18" s="298" t="n">
+      <c r="A18" s="304" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="298" t="n">
-        <v>6624</v>
-      </c>
-      <c r="C18" s="299" t="inlineStr">
+      <c r="B18" s="304" t="n">
+        <v>5731</v>
+      </c>
+      <c r="C18" s="305" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="299" t="inlineStr">
-        <is>
-          <t>S-45 DIA 19MM</t>
-        </is>
-      </c>
-      <c r="E18" s="298" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F18" s="300" t="n">
-        <v>15288</v>
-      </c>
-      <c r="G18" s="298" t="inlineStr">
+      <c r="D18" s="305" t="inlineStr">
+        <is>
+          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
+        </is>
+      </c>
+      <c r="E18" s="304" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="F18" s="306" t="n">
+        <v>37030</v>
+      </c>
+      <c r="G18" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51341,40 +51564,14 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="237">
-      <c r="A19" s="298" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="298" t="n">
-        <v>5731</v>
-      </c>
-      <c r="C19" s="299" t="inlineStr">
-        <is>
-          <t>Samsol International Private Limited</t>
-        </is>
-      </c>
-      <c r="D19" s="299" t="inlineStr">
-        <is>
-          <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
-        </is>
-      </c>
-      <c r="E19" s="298" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="F19" s="300" t="n">
-        <v>37030</v>
-      </c>
-      <c r="G19" s="298" t="inlineStr">
-        <is>
-          <t>Not Ready</t>
-        </is>
-      </c>
-      <c r="H19" s="276" t="inlineStr">
-        <is>
-          <t>Cap Not Available</t>
-        </is>
-      </c>
+      <c r="A19" s="277" t="n"/>
+      <c r="B19" s="277" t="n"/>
+      <c r="C19" s="278" t="n"/>
+      <c r="D19" s="278" t="n"/>
+      <c r="E19" s="277" t="n"/>
+      <c r="F19" s="279" t="n"/>
+      <c r="G19" s="277" t="n"/>
+      <c r="H19" s="280" t="n"/>
       <c r="I19" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B19)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
         <v/>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -801,7 +801,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="20"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1601,6 +1601,24 @@
     <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2818,7 +2836,9 @@
         <f>IF(G14=0,"-",H14/G14)</f>
         <v/>
       </c>
-      <c r="K14" s="287" t="n"/>
+      <c r="K14" s="287" t="n">
+        <v>31248</v>
+      </c>
       <c r="L14" s="289" t="n"/>
       <c r="M14" s="155" t="inlineStr">
         <is>
@@ -38700,7 +38720,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="H7" s="38">
         <f>E7+F7-G7</f>
@@ -38968,7 +38988,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H15" s="38">
         <f>E15+F15-G15</f>
@@ -39240,7 +39260,7 @@
         <v>210</v>
       </c>
       <c r="G22" s="37" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H22" s="38">
         <f>E22+F22-G22</f>
@@ -41082,7 +41102,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H65" s="38">
         <f>E65+F65-G65</f>
@@ -50964,31 +50984,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="237">
-      <c r="A4" s="301" t="n">
+      <c r="A4" s="307" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="301" t="n">
+      <c r="B4" s="307" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="302" t="inlineStr">
+      <c r="C4" s="308" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="302" t="inlineStr">
+      <c r="D4" s="308" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="301" t="inlineStr">
+      <c r="E4" s="307" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="303" t="n">
+      <c r="F4" s="309" t="n">
         <v>18860</v>
       </c>
-      <c r="G4" s="301" t="inlineStr">
+      <c r="G4" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51004,31 +51024,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="237">
-      <c r="A5" s="301" t="n">
+      <c r="A5" s="307" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="301" t="n">
+      <c r="B5" s="307" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="302" t="inlineStr">
+      <c r="C5" s="308" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="302" t="inlineStr">
+      <c r="D5" s="308" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="301" t="inlineStr">
+      <c r="E5" s="307" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="303" t="n">
+      <c r="F5" s="309" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="301" t="inlineStr">
+      <c r="G5" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51044,31 +51064,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="237">
-      <c r="A6" s="301" t="n">
+      <c r="A6" s="307" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="301" t="n">
+      <c r="B6" s="307" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="302" t="inlineStr">
+      <c r="C6" s="308" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="302" t="inlineStr">
+      <c r="D6" s="308" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="301" t="inlineStr">
+      <c r="E6" s="307" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="303" t="n">
+      <c r="F6" s="309" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="301" t="inlineStr">
+      <c r="G6" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51084,31 +51104,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="237">
-      <c r="A7" s="301" t="n">
+      <c r="A7" s="307" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="301" t="n">
+      <c r="B7" s="307" t="n">
         <v>5389</v>
       </c>
-      <c r="C7" s="302" t="inlineStr">
+      <c r="C7" s="308" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="302" t="inlineStr">
+      <c r="D7" s="308" t="inlineStr">
         <is>
           <t>S-45</t>
         </is>
       </c>
-      <c r="E7" s="301" t="inlineStr">
+      <c r="E7" s="307" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="303" t="n">
+      <c r="F7" s="309" t="n">
         <v>11088</v>
       </c>
-      <c r="G7" s="301" t="inlineStr">
+      <c r="G7" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51124,31 +51144,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="237">
-      <c r="A8" s="301" t="n">
+      <c r="A8" s="307" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="301" t="n">
+      <c r="B8" s="307" t="n">
         <v>4050</v>
       </c>
-      <c r="C8" s="302" t="inlineStr">
+      <c r="C8" s="308" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D8" s="302" t="inlineStr">
+      <c r="D8" s="308" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E8" s="301" t="inlineStr">
+      <c r="E8" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="303" t="n">
+      <c r="F8" s="309" t="n">
         <v>9450</v>
       </c>
-      <c r="G8" s="301" t="inlineStr">
+      <c r="G8" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51164,31 +51184,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="237">
-      <c r="A9" s="301" t="n">
+      <c r="A9" s="307" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="301" t="n">
+      <c r="B9" s="307" t="n">
         <v>6337</v>
       </c>
-      <c r="C9" s="302" t="inlineStr">
+      <c r="C9" s="308" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="302" t="inlineStr">
+      <c r="D9" s="308" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="301" t="inlineStr">
+      <c r="E9" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="303" t="n">
+      <c r="F9" s="309" t="n">
         <v>15680</v>
       </c>
-      <c r="G9" s="301" t="inlineStr">
+      <c r="G9" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51204,31 +51224,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="237">
-      <c r="A10" s="301" t="n">
+      <c r="A10" s="307" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="301" t="n">
+      <c r="B10" s="307" t="n">
         <v>6416</v>
       </c>
-      <c r="C10" s="302" t="inlineStr">
+      <c r="C10" s="308" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D10" s="302" t="inlineStr">
+      <c r="D10" s="308" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E10" s="301" t="inlineStr">
+      <c r="E10" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="303" t="n">
+      <c r="F10" s="309" t="n">
         <v>15435</v>
       </c>
-      <c r="G10" s="301" t="inlineStr">
+      <c r="G10" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51244,31 +51264,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="237">
-      <c r="A11" s="301" t="n">
+      <c r="A11" s="307" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="301" t="n">
+      <c r="B11" s="307" t="n">
         <v>5782</v>
       </c>
-      <c r="C11" s="302" t="inlineStr">
+      <c r="C11" s="308" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D11" s="302" t="inlineStr">
+      <c r="D11" s="308" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E11" s="301" t="inlineStr">
+      <c r="E11" s="307" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F11" s="303" t="n">
+      <c r="F11" s="309" t="n">
         <v>63648</v>
       </c>
-      <c r="G11" s="301" t="inlineStr">
+      <c r="G11" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51284,31 +51304,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="237">
-      <c r="A12" s="301" t="n">
+      <c r="A12" s="307" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="301" t="n">
+      <c r="B12" s="307" t="n">
         <v>6531</v>
       </c>
-      <c r="C12" s="302" t="inlineStr">
+      <c r="C12" s="308" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D12" s="302" t="inlineStr">
+      <c r="D12" s="308" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E12" s="301" t="inlineStr">
+      <c r="E12" s="307" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F12" s="303" t="n">
+      <c r="F12" s="309" t="n">
         <v>4380</v>
       </c>
-      <c r="G12" s="301" t="inlineStr">
+      <c r="G12" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51324,31 +51344,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="237">
-      <c r="A13" s="301" t="n">
+      <c r="A13" s="307" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="301" t="n">
+      <c r="B13" s="307" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="302" t="inlineStr">
+      <c r="C13" s="308" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="302" t="inlineStr">
+      <c r="D13" s="308" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="301" t="inlineStr">
+      <c r="E13" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="303" t="n">
+      <c r="F13" s="309" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="301" t="inlineStr">
+      <c r="G13" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51364,31 +51384,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="237">
-      <c r="A14" s="304" t="n">
+      <c r="A14" s="310" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="304" t="n">
+      <c r="B14" s="310" t="n">
         <v>6515</v>
       </c>
-      <c r="C14" s="305" t="inlineStr">
+      <c r="C14" s="311" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="305" t="inlineStr">
+      <c r="D14" s="311" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E14" s="304" t="inlineStr">
+      <c r="E14" s="310" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F14" s="306" t="n">
+      <c r="F14" s="312" t="n">
         <v>38896</v>
       </c>
-      <c r="G14" s="304" t="inlineStr">
+      <c r="G14" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51404,31 +51424,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="237">
-      <c r="A15" s="304" t="n">
+      <c r="A15" s="310" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="304" t="n">
+      <c r="B15" s="310" t="n">
         <v>6530</v>
       </c>
-      <c r="C15" s="305" t="inlineStr">
+      <c r="C15" s="311" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D15" s="305" t="inlineStr">
+      <c r="D15" s="311" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E15" s="304" t="inlineStr">
+      <c r="E15" s="310" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F15" s="306" t="n">
+      <c r="F15" s="312" t="n">
         <v>15000</v>
       </c>
-      <c r="G15" s="304" t="inlineStr">
+      <c r="G15" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51444,31 +51464,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="237">
-      <c r="A16" s="304" t="n">
+      <c r="A16" s="310" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="304" t="n">
+      <c r="B16" s="310" t="n">
         <v>5782</v>
       </c>
-      <c r="C16" s="305" t="inlineStr">
+      <c r="C16" s="311" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D16" s="305" t="inlineStr">
+      <c r="D16" s="311" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E16" s="304" t="inlineStr">
+      <c r="E16" s="310" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="306" t="n">
+      <c r="F16" s="312" t="n">
         <v>10500</v>
       </c>
-      <c r="G16" s="304" t="inlineStr">
+      <c r="G16" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51484,31 +51504,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="237">
-      <c r="A17" s="304" t="n">
+      <c r="A17" s="310" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="304" t="n">
+      <c r="B17" s="310" t="n">
         <v>6624</v>
       </c>
-      <c r="C17" s="305" t="inlineStr">
+      <c r="C17" s="311" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D17" s="305" t="inlineStr">
+      <c r="D17" s="311" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E17" s="304" t="inlineStr">
+      <c r="E17" s="310" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F17" s="306" t="n">
+      <c r="F17" s="312" t="n">
         <v>15288</v>
       </c>
-      <c r="G17" s="304" t="inlineStr">
+      <c r="G17" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51524,31 +51544,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="237">
-      <c r="A18" s="304" t="n">
+      <c r="A18" s="310" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="304" t="n">
+      <c r="B18" s="310" t="n">
         <v>5731</v>
       </c>
-      <c r="C18" s="305" t="inlineStr">
+      <c r="C18" s="311" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="305" t="inlineStr">
+      <c r="D18" s="311" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E18" s="304" t="inlineStr">
+      <c r="E18" s="310" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F18" s="306" t="n">
+      <c r="F18" s="312" t="n">
         <v>37030</v>
       </c>
-      <c r="G18" s="304" t="inlineStr">
+      <c r="G18" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Guide" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MRP'!$A$13:$K$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Production_Log'!$A$2:$R$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BOM Issues'!$A$52:$J$64</definedName>
   </definedNames>
@@ -482,7 +483,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -684,6 +685,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -785,20 +801,20 @@
     </border>
   </borders>
   <cellStyleXfs count="10">
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
-    <xf numFmtId="173" fontId="24" fillId="0" borderId="20"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="173" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="20"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="21"/>
   </cellStyleXfs>
   <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1298,136 +1314,136 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="47" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="47" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="48" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="48" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1439,149 +1455,149 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="24" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="24" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="47" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="47" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="48" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="48" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="48" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2051,23 +2067,23 @@
   <dimension ref="A1:AC199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="16.5"/>
   <cols>
-    <col width="1.5703125" customWidth="1" style="231" min="1" max="1"/>
-    <col width="7" customWidth="1" style="231" min="2" max="2"/>
-    <col width="32.7109375" customWidth="1" style="231" min="3" max="3"/>
-    <col width="38.7109375" customWidth="1" style="231" min="4" max="4"/>
-    <col width="8.85546875" customWidth="1" style="232" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="231" min="6" max="6"/>
-    <col width="11" customWidth="1" style="233" min="7" max="7"/>
-    <col width="11.140625" customWidth="1" style="231" min="8" max="8"/>
-    <col width="10.28515625" customWidth="1" style="231" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="231" min="10" max="10"/>
-    <col width="9.28515625" customWidth="1" style="231" min="11" max="11"/>
-    <col width="33.85546875" customWidth="1" style="231" min="12" max="12"/>
-    <col width="14.7109375" customWidth="1" style="231" min="13" max="13"/>
-    <col width="13.28515625" customWidth="1" style="231" min="14" max="14"/>
-    <col width="9.5703125" customWidth="1" style="231" min="15" max="15"/>
-    <col width="8.7109375" customWidth="1" style="231" min="16" max="56"/>
-    <col width="8.7109375" customWidth="1" style="231" min="57" max="16384"/>
+    <col width="1.5703125" customWidth="1" style="228" min="1" max="1"/>
+    <col width="7" customWidth="1" style="228" min="2" max="2"/>
+    <col width="32.7109375" customWidth="1" style="228" min="3" max="3"/>
+    <col width="38.7109375" customWidth="1" style="228" min="4" max="4"/>
+    <col width="8.85546875" customWidth="1" style="229" min="5" max="5"/>
+    <col width="9.140625" customWidth="1" style="228" min="6" max="6"/>
+    <col width="11" customWidth="1" style="230" min="7" max="7"/>
+    <col width="11.140625" customWidth="1" style="228" min="8" max="8"/>
+    <col width="10.28515625" customWidth="1" style="228" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="228" min="10" max="10"/>
+    <col width="9.28515625" customWidth="1" style="228" min="11" max="11"/>
+    <col width="35.140625" customWidth="1" style="228" min="12" max="12"/>
+    <col width="14.7109375" customWidth="1" style="228" min="13" max="13"/>
+    <col width="13.28515625" customWidth="1" style="228" min="14" max="14"/>
+    <col width="9.5703125" customWidth="1" style="228" min="15" max="15"/>
+    <col width="8.7109375" customWidth="1" style="228" min="16" max="57"/>
+    <col width="8.7109375" customWidth="1" style="228" min="58" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1" s="243">
@@ -2383,21 +2399,21 @@
     </row>
     <row r="9" ht="20.25" customHeight="1" s="243">
       <c r="A9" s="136" t="n"/>
-      <c r="B9" s="240" t="inlineStr">
+      <c r="B9" s="237" t="inlineStr">
         <is>
           <t>Summary of Production &amp; Dispatch - MTD</t>
         </is>
       </c>
-      <c r="C9" s="241" t="n"/>
-      <c r="D9" s="241" t="n"/>
-      <c r="E9" s="241" t="n"/>
-      <c r="F9" s="241" t="n"/>
-      <c r="G9" s="241" t="n"/>
-      <c r="H9" s="241" t="n"/>
-      <c r="I9" s="241" t="n"/>
-      <c r="J9" s="241" t="n"/>
-      <c r="K9" s="241" t="n"/>
-      <c r="L9" s="241" t="n"/>
+      <c r="C9" s="238" t="n"/>
+      <c r="D9" s="238" t="n"/>
+      <c r="E9" s="238" t="n"/>
+      <c r="F9" s="238" t="n"/>
+      <c r="G9" s="238" t="n"/>
+      <c r="H9" s="238" t="n"/>
+      <c r="I9" s="238" t="n"/>
+      <c r="J9" s="238" t="n"/>
+      <c r="K9" s="238" t="n"/>
+      <c r="L9" s="238" t="n"/>
       <c r="M9" s="157">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,3),$U$9:$U$23,0)),"")</f>
         <v/>
@@ -3020,7 +3036,7 @@
       <c r="K17" s="293" t="n"/>
       <c r="L17" s="295" t="inlineStr">
         <is>
-          <t>2.6k Advance Production</t>
+          <t>400k Order, 100k Advance Production</t>
         </is>
       </c>
       <c r="P17" s="136" t="n"/>
@@ -4132,7 +4148,7 @@
       <c r="P36" s="136" t="n"/>
       <c r="Q36" s="136" t="n"/>
       <c r="R36" s="136" t="n"/>
-      <c r="S36" s="231" t="inlineStr">
+      <c r="S36" s="228" t="inlineStr">
         <is>
           <t>Gas Shutdown</t>
         </is>
@@ -4141,7 +4157,7 @@
         <f>SUMPRODUCT((MONTH(Production_Log!$A$3:$A$8963)=MONTH(TODAY()))*(YEAR(Production_Log!$A$3:$A$8963)=YEAR(TODAY()))*Production_Log!$Q$3:$Q$8963)</f>
         <v/>
       </c>
-      <c r="U36" s="231">
+      <c r="U36" s="228">
         <f>T36+0.00006</f>
         <v/>
       </c>
@@ -5939,7 +5955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5978,8 +5994,9 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="H1" s="163" t="n">
-        <v>46171</v>
+      <c r="H1" s="163">
+        <f>TODAY()</f>
+        <v/>
       </c>
       <c r="I1" s="10" t="n"/>
       <c r="J1" s="11" t="n"/>
@@ -6198,7 +6215,7 @@
         <v>6894</v>
       </c>
       <c r="F6" s="185" t="n">
-        <v>30000</v>
+        <v>32592</v>
       </c>
       <c r="G6" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$58,MATCH(MRP!D6,Tubex_Dashboard!$F$11:$F$58,0))</f>
@@ -6231,7 +6248,7 @@
         <v>6893</v>
       </c>
       <c r="F7" s="185" t="n">
-        <v>62000</v>
+        <v>62496</v>
       </c>
       <c r="G7" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$58,MATCH(MRP!D7,Tubex_Dashboard!$F$11:$F$58,0))</f>
@@ -6264,7 +6281,7 @@
         <v>6887</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>22000</v>
+        <v>52000</v>
       </c>
       <c r="G8" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$58,MATCH(MRP!D8,Tubex_Dashboard!$F$11:$F$58,0))</f>
@@ -6309,8 +6326,9 @@
           <t>Awaited</t>
         </is>
       </c>
-      <c r="F9" s="193" t="n">
-        <v>300000</v>
+      <c r="F9" s="193">
+        <f>400000-98056</f>
+        <v/>
       </c>
       <c r="G9" s="194">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D9,Tubex_Dashboard!$F$11:$F$100,0))</f>
@@ -6322,7 +6340,7 @@
       </c>
       <c r="I9" s="195" t="inlineStr">
         <is>
-          <t>2.6k Already in FG Stock</t>
+          <t>400k Order, 100k already in FG Stock</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6521,7 @@
       <c r="T13" s="11" t="n"/>
       <c r="U13" s="2" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1" s="243">
+    <row r="14" hidden="1" ht="24" customHeight="1" s="243">
       <c r="A14" s="21" t="n">
         <v>33</v>
       </c>
@@ -6561,7 +6579,7 @@
       <c r="T14" s="11" t="n"/>
       <c r="U14" s="2" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" hidden="1" s="243">
       <c r="A15" s="21" t="n">
         <v>31</v>
       </c>
@@ -6677,7 +6695,7 @@
       <c r="T16" s="11" t="n"/>
       <c r="U16" s="2" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" hidden="1" s="243">
       <c r="A17" s="21" t="n">
         <v>25</v>
       </c>
@@ -6735,7 +6753,7 @@
       <c r="T17" s="11" t="n"/>
       <c r="U17" s="2" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" hidden="1" s="243">
       <c r="A18" s="21" t="n">
         <v>22</v>
       </c>
@@ -6783,7 +6801,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1" s="243">
       <c r="A19" s="21" t="n">
         <v>19</v>
       </c>
@@ -6831,7 +6849,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1" s="243">
       <c r="A20" s="21" t="n">
         <v>4179</v>
       </c>
@@ -6927,7 +6945,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1" s="243">
       <c r="A22" s="21" t="n">
         <v>10</v>
       </c>
@@ -6975,7 +6993,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1" s="243">
       <c r="A23" s="21" t="n">
         <v>2</v>
       </c>
@@ -7081,7 +7099,7 @@
       <c r="T24" s="11" t="n"/>
       <c r="U24" s="2" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" hidden="1" s="243">
       <c r="A25" s="21" t="n">
         <v>6961</v>
       </c>
@@ -7139,7 +7157,7 @@
       <c r="T25" s="11" t="n"/>
       <c r="U25" s="2" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" hidden="1" s="243">
       <c r="A26" s="21" t="n">
         <v>3935</v>
       </c>
@@ -7232,9 +7250,10 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A27)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A27)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A27)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A27)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A27)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A27)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A27)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A27)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A27)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A27)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A27)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A27)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A27)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A27)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A27)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A27)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A27)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A27)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A27)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A27)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A27)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A27)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A27)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A27)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I27" s="30">
-        <f>IF(E27=0,"Not needed",IF(G27&lt;0,"SHORTAGE",IF(G27&lt;F27*0.1,"LOW","OK")))</f>
-        <v/>
+      <c r="I27" s="30" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
       </c>
       <c r="J27" s="30">
         <f>IF(B27&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A27)*'FG Stock'!$F$4:$F$100))</f>
@@ -7245,7 +7264,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1" s="243">
       <c r="A28" s="21" t="n">
         <v>184</v>
       </c>
@@ -7361,7 +7380,7 @@
       <c r="T29" s="11" t="n"/>
       <c r="U29" s="2" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" hidden="1" s="243">
       <c r="A30" s="21" t="n">
         <v>188</v>
       </c>
@@ -7419,7 +7438,7 @@
       <c r="T30" s="11" t="n"/>
       <c r="U30" s="2" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" s="243">
       <c r="A31" s="21" t="n">
         <v>1065</v>
       </c>
@@ -7535,7 +7554,7 @@
       <c r="T32" s="11" t="n"/>
       <c r="U32" s="2" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" hidden="1" s="243">
       <c r="A33" s="21" t="n">
         <v>170</v>
       </c>
@@ -7593,7 +7612,7 @@
       <c r="T33" s="11" t="n"/>
       <c r="U33" s="2" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" hidden="1" s="243">
       <c r="A34" s="21" t="n">
         <v>175</v>
       </c>
@@ -7651,7 +7670,7 @@
       <c r="T34" s="11" t="n"/>
       <c r="U34" s="2" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" hidden="1" s="243">
       <c r="A35" s="21" t="n">
         <v>192</v>
       </c>
@@ -7767,7 +7786,7 @@
       <c r="T36" s="11" t="n"/>
       <c r="U36" s="2" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" hidden="1" s="243">
       <c r="A37" s="21" t="n">
         <v>3869</v>
       </c>
@@ -7825,7 +7844,7 @@
       <c r="T37" s="11" t="n"/>
       <c r="U37" s="2" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" hidden="1" s="243">
       <c r="A38" s="21" t="n">
         <v>4156</v>
       </c>
@@ -7873,7 +7892,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="1" s="243">
       <c r="A39" s="21" t="n">
         <v>4157</v>
       </c>
@@ -7921,7 +7940,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="1" s="243">
       <c r="A40" s="21" t="n">
         <v>5895</v>
       </c>
@@ -7979,7 +7998,7 @@
       <c r="T40" s="11" t="n"/>
       <c r="U40" s="2" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" hidden="1" s="243">
       <c r="A41" s="21" t="n">
         <v>5974</v>
       </c>
@@ -8027,7 +8046,7 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="1" s="243">
       <c r="A42" s="21" t="n">
         <v>177</v>
       </c>
@@ -8075,7 +8094,7 @@
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1" s="243">
       <c r="A43" s="21" t="n">
         <v>6132</v>
       </c>
@@ -8219,7 +8238,7 @@
         <v/>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="1" s="243">
       <c r="A46" s="21" t="n">
         <v>4165</v>
       </c>
@@ -8312,9 +8331,10 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A47)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A47)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A47)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A47)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A47)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A47)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A47)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A47)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A47)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A47)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A47)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A47)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A47)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A47)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A47)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A47)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A47)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A47)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A47)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A47)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A47)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A47)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A47)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A47)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I47" s="30">
-        <f>IF(E47=0,"Not needed",IF(G47&lt;0,"SHORTAGE",IF(G47&lt;F47*0.1,"LOW","OK")))</f>
-        <v/>
+      <c r="I47" s="30" t="inlineStr">
+        <is>
+          <t>Hold. Caps not approved</t>
+        </is>
       </c>
       <c r="J47" s="30">
         <f>IF(B47&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A47)*'FG Stock'!$F$4:$F$100))</f>
@@ -8325,7 +8345,7 @@
         <v/>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="1" s="243">
       <c r="A48" s="21" t="n">
         <v>99</v>
       </c>
@@ -8383,7 +8403,7 @@
       <c r="T48" s="11" t="n"/>
       <c r="U48" s="2" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" hidden="1" s="243">
       <c r="A49" s="21" t="n">
         <v>72</v>
       </c>
@@ -8441,7 +8461,7 @@
       <c r="T49" s="11" t="n"/>
       <c r="U49" s="2" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" hidden="1" s="243">
       <c r="A50" s="21" t="n">
         <v>79</v>
       </c>
@@ -8499,7 +8519,7 @@
       <c r="T50" s="11" t="n"/>
       <c r="U50" s="2" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" hidden="1" s="243">
       <c r="A51" s="21" t="n">
         <v>80</v>
       </c>
@@ -8547,7 +8567,7 @@
         <v/>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="1" s="243">
       <c r="A52" s="21" t="n">
         <v>81</v>
       </c>
@@ -8595,7 +8615,7 @@
         <v/>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" s="243">
       <c r="A53" s="21" t="n">
         <v>1800</v>
       </c>
@@ -8643,7 +8663,7 @@
         <v/>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="1" s="243">
       <c r="A54" s="21" t="n">
         <v>3211</v>
       </c>
@@ -8691,7 +8711,7 @@
         <v/>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1" s="243">
       <c r="A55" s="21" t="n">
         <v>4015</v>
       </c>
@@ -8739,7 +8759,7 @@
         <v/>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1" s="243">
       <c r="A56" s="21" t="n">
         <v>4044</v>
       </c>
@@ -8787,7 +8807,7 @@
         <v/>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" s="243">
       <c r="A57" s="21" t="n">
         <v>4088</v>
       </c>
@@ -8835,7 +8855,7 @@
         <v/>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1" s="243">
       <c r="A58" s="21" t="n">
         <v>4143</v>
       </c>
@@ -8883,7 +8903,7 @@
         <v/>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" s="243">
       <c r="A59" s="21" t="n">
         <v>6971</v>
       </c>
@@ -8931,7 +8951,7 @@
         <v/>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="1" s="243">
       <c r="A60" s="21" t="n">
         <v>7370</v>
       </c>
@@ -9027,7 +9047,7 @@
         <v/>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="1" s="243">
       <c r="A62" s="21" t="n">
         <v>102</v>
       </c>
@@ -9075,7 +9095,7 @@
         <v/>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="1" s="243">
       <c r="A63" s="21" t="n">
         <v>1073</v>
       </c>
@@ -9123,7 +9143,7 @@
         <v/>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="1" s="243">
       <c r="A64" s="21" t="n">
         <v>1285</v>
       </c>
@@ -9171,7 +9191,7 @@
         <v/>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="1" s="243">
       <c r="A65" s="21" t="n">
         <v>3522</v>
       </c>
@@ -9219,7 +9239,7 @@
         <v/>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="1" s="243">
       <c r="A66" s="21" t="n">
         <v>3866</v>
       </c>
@@ -9315,7 +9335,7 @@
         <v/>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="1" s="243">
       <c r="A68" s="21" t="n">
         <v>9902</v>
       </c>
@@ -9363,7 +9383,7 @@
         <v/>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="1" s="243">
       <c r="A69" s="21" t="n">
         <v>9903</v>
       </c>
@@ -9446,9 +9466,10 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A70)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A70)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A70)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A70)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A70)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A70)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A70)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A70)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A70)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A70)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A70)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A70)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A70)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A70)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A70)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A70)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A70)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A70)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A70)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A70)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A70)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A70)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A70)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A70)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I70" s="30">
-        <f>IF(E70=0,"Not needed",IF(G70&lt;0,"SHORTAGE",IF(G70&lt;F70*0.1,"LOW","OK")))</f>
-        <v/>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Hold. Caps not approved</t>
+        </is>
       </c>
       <c r="J70">
         <f>IF(B70&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A70)*'FG Stock'!$F$4:$F$100))</f>
@@ -9494,9 +9515,10 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A71)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A71)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A71)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A71)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A71)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A71)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A71)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A71)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A71)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A71)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A71)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A71)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A71)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A71)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A71)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A71)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A71)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A71)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A71)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A71)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A71)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A71)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A71)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A71)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I71" s="30">
-        <f>IF(E71=0,"Not needed",IF(G71&lt;0,"SHORTAGE",IF(G71&lt;F71*0.1,"LOW","OK")))</f>
-        <v/>
+      <c r="I71" s="30" t="inlineStr">
+        <is>
+          <t>Hold. Caps not approved</t>
+        </is>
       </c>
       <c r="J71" s="30">
         <f>IF(B71&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A71)*'FG Stock'!$F$4:$F$100))</f>
@@ -9507,7 +9529,7 @@
         <v/>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1" s="243">
       <c r="A72" s="21" t="n">
         <v>39</v>
       </c>
@@ -9555,7 +9577,7 @@
         <v/>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="1" s="243">
       <c r="A73" s="21" t="n">
         <v>3619</v>
       </c>
@@ -9651,7 +9673,7 @@
         <v/>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="1" s="243">
       <c r="A75" s="21" t="n">
         <v>45</v>
       </c>
@@ -9747,7 +9769,7 @@
         <v/>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="1" s="243">
       <c r="A77" s="21" t="n">
         <v>5977</v>
       </c>
@@ -9891,7 +9913,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="243">
+    <row r="80" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A80" s="21" t="n">
         <v>191</v>
       </c>
@@ -9939,7 +9961,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="243">
+    <row r="81" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A81" s="21" t="n">
         <v>2680</v>
       </c>
@@ -9987,7 +10009,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="243">
+    <row r="82" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A82" s="21" t="n">
         <v>3492</v>
       </c>
@@ -10035,7 +10057,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="243">
+    <row r="83" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A83" s="21" t="n">
         <v>4002</v>
       </c>
@@ -10083,7 +10105,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="243">
+    <row r="84" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A84" s="21" t="n">
         <v>4070</v>
       </c>
@@ -10131,7 +10153,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="243">
+    <row r="85" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A85" s="21" t="n">
         <v>4310</v>
       </c>
@@ -10179,7 +10201,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="243">
+    <row r="86" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A86" s="21" t="n">
         <v>5625</v>
       </c>
@@ -10227,7 +10249,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="243">
+    <row r="87" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A87" s="21" t="n">
         <v>5816</v>
       </c>
@@ -10275,7 +10297,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="243">
+    <row r="88" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A88" s="21" t="n">
         <v>6135</v>
       </c>
@@ -10323,7 +10345,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="243">
+    <row r="89" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A89" s="21" t="n">
         <v>7133</v>
       </c>
@@ -10371,7 +10393,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="243">
+    <row r="90" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A90" s="21" t="n">
         <v>7412</v>
       </c>
@@ -10419,7 +10441,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="243">
+    <row r="91" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A91" s="21" t="n">
         <v>3752</v>
       </c>
@@ -10467,7 +10489,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="243">
+    <row r="92" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A92" s="21" t="n">
         <v>4248</v>
       </c>
@@ -10515,7 +10537,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" ht="16.5" customHeight="1" s="243">
+    <row r="93" hidden="1" ht="16.5" customHeight="1" s="243">
       <c r="A93" s="21" t="n">
         <v>6042</v>
       </c>
@@ -10563,7 +10585,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="243">
+    <row r="94" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A94" s="21" t="n">
         <v>2267</v>
       </c>
@@ -10611,7 +10633,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" s="243">
+    <row r="95" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A95" s="21" t="n">
         <v>3043</v>
       </c>
@@ -10687,14 +10709,14 @@
           <t>June 2026 PET Required Pet Orders</t>
         </is>
       </c>
-      <c r="B98" s="228" t="n"/>
-      <c r="C98" s="228" t="n"/>
-      <c r="D98" s="228" t="n"/>
-      <c r="E98" s="228" t="n"/>
-      <c r="F98" s="228" t="n"/>
+      <c r="B98" s="240" t="n"/>
+      <c r="C98" s="240" t="n"/>
+      <c r="D98" s="240" t="n"/>
+      <c r="E98" s="240" t="n"/>
+      <c r="F98" s="240" t="n"/>
       <c r="G98" s="188" t="n"/>
-      <c r="H98" s="228" t="n"/>
-      <c r="I98" s="229" t="n"/>
+      <c r="H98" s="240" t="n"/>
+      <c r="I98" s="241" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1" s="243">
       <c r="A99" s="12" t="inlineStr">
@@ -10949,14 +10971,14 @@
           <t>JUNE PET MATERIAL REQUIREMENT PLAN</t>
         </is>
       </c>
-      <c r="B106" s="228" t="n"/>
-      <c r="C106" s="228" t="n"/>
-      <c r="D106" s="228" t="n"/>
-      <c r="E106" s="228" t="n"/>
-      <c r="F106" s="228" t="n"/>
+      <c r="B106" s="240" t="n"/>
+      <c r="C106" s="240" t="n"/>
+      <c r="D106" s="240" t="n"/>
+      <c r="E106" s="240" t="n"/>
+      <c r="F106" s="240" t="n"/>
       <c r="G106" s="188" t="n"/>
-      <c r="H106" s="228" t="n"/>
-      <c r="I106" s="228" t="n"/>
+      <c r="H106" s="240" t="n"/>
+      <c r="I106" s="240" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1" s="243">
       <c r="A107" s="41" t="inlineStr">
@@ -11146,31 +11168,31 @@
       <c r="A111" s="262" t="n">
         <v>5977</v>
       </c>
-      <c r="B111" s="228" t="n"/>
-      <c r="C111" s="228" t="n"/>
-      <c r="D111" s="228" t="n"/>
-      <c r="E111" s="228" t="n"/>
-      <c r="F111" s="228" t="n"/>
-      <c r="G111" s="228" t="n"/>
-      <c r="H111" s="228" t="n"/>
-      <c r="I111" s="229" t="n"/>
+      <c r="B111" s="240" t="n"/>
+      <c r="C111" s="240" t="n"/>
+      <c r="D111" s="240" t="n"/>
+      <c r="E111" s="240" t="n"/>
+      <c r="F111" s="240" t="n"/>
+      <c r="G111" s="240" t="n"/>
+      <c r="H111" s="240" t="n"/>
+      <c r="I111" s="241" t="n"/>
       <c r="K111" s="47">
         <f>IF(E106=0,"",MAX(0,E106-F106))</f>
         <v/>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1" s="243">
-      <c r="A112" s="227" t="n">
+      <c r="A112" s="196" t="n">
         <v>2267</v>
       </c>
-      <c r="B112" s="228" t="n"/>
-      <c r="C112" s="228" t="n"/>
-      <c r="D112" s="228" t="n"/>
-      <c r="E112" s="228" t="n"/>
-      <c r="F112" s="228" t="n"/>
-      <c r="G112" s="228" t="n"/>
-      <c r="H112" s="228" t="n"/>
-      <c r="I112" s="229" t="n"/>
+      <c r="B112" s="240" t="n"/>
+      <c r="C112" s="240" t="n"/>
+      <c r="D112" s="240" t="n"/>
+      <c r="E112" s="240" t="n"/>
+      <c r="F112" s="240" t="n"/>
+      <c r="G112" s="240" t="n"/>
+      <c r="H112" s="240" t="n"/>
+      <c r="I112" s="241" t="n"/>
       <c r="K112" s="48">
         <f>IF(E107=0,"",MAX(0,E107-F107))</f>
         <v/>
@@ -11310,14 +11332,14 @@
     </row>
     <row r="116" ht="15" customHeight="1" s="243">
       <c r="A116" s="187" t="n"/>
-      <c r="B116" s="228" t="n"/>
-      <c r="C116" s="228" t="n"/>
-      <c r="D116" s="228" t="n"/>
-      <c r="E116" s="228" t="n"/>
-      <c r="F116" s="228" t="n"/>
+      <c r="B116" s="240" t="n"/>
+      <c r="C116" s="240" t="n"/>
+      <c r="D116" s="240" t="n"/>
+      <c r="E116" s="240" t="n"/>
+      <c r="F116" s="240" t="n"/>
       <c r="G116" s="188" t="n"/>
-      <c r="H116" s="228" t="n"/>
-      <c r="I116" s="229" t="n"/>
+      <c r="H116" s="240" t="n"/>
+      <c r="I116" s="241" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1" s="243">
       <c r="A117" s="6" t="inlineStr">
@@ -13217,6 +13239,30 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A13:K95">
+    <filterColumn colId="4" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="1,516"/>
+        <filter val="111"/>
+        <filter val="138"/>
+        <filter val="15"/>
+        <filter val="188"/>
+        <filter val="2"/>
+        <filter val="20"/>
+        <filter val="222"/>
+        <filter val="25,500"/>
+        <filter val="263"/>
+        <filter val="3"/>
+        <filter val="3,092"/>
+        <filter val="305"/>
+        <filter val="347,688"/>
+        <filter val="66,606"/>
+        <filter val="69"/>
+        <filter val="89"/>
+        <filter val="99"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A111:I111"/>
   </mergeCells>
@@ -13253,15 +13299,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="F125:G125 H2:I3 H8:I10 H123:H130 I6:I10 I11:I12 I14 I16:I19 I22 I24:I25 I27:I29 I31:I37 I40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F125:G125 H2:I3 H8:I10 H123:H130 I6:I12 I14 I16:I19 I22 I24:I25 I27:I29 I31:I37 I40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Confirmed,1st Week,2nd Week,Tentative,In Process,Initial Stage,Completed,Cancelled"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="B6:B10 B11:B19 B127 B131:B132 B137:B138 C3 C8:C9 C124:C126 C128:C130 C133:C135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B6:B19 B127 B131:B132 B137:B138 C3 C8:C9 C124:C126 C128:C130 C133:C135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alpha Lab,Brookes Pharma,DTM,Golden Pearl,Mabley Beauty,Mega Grey,PBS,Samsol"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="C6:C10 C11:C19 C127 C131:C132 C137:C138 D3 D8:D10 D124:D136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C19 C127 C131:C132 C137:C138 D3 D8:D10 D124:D136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CONTRATUBEX GEL 20G,DTM DIA 25MM,EAZICOLOR PREMIUM 60ML,H.H 100GM,HELLO HAIR COLOR,M.G (Mega Grey),PHLOGIN GEL 20G,PYODINE GEL 20GM,S 43 25MM,S-43 DIA 20.5,S-45 DIA 20.5,TRANSPARENT BOTTLE 150ML,TUBES (Samsol 25),V-HC BLACK (Vince),VINCE NURTURAL (VARNISH"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17288,193 +17334,420 @@
       <c r="S92" s="271" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1" s="243">
-      <c r="A93" s="176" t="n"/>
-      <c r="B93" s="177" t="n"/>
-      <c r="C93" s="177" t="n"/>
-      <c r="D93" s="177" t="n"/>
-      <c r="E93" s="177" t="n"/>
-      <c r="F93" s="177" t="n"/>
-      <c r="G93" s="178" t="n"/>
-      <c r="H93" s="178" t="n"/>
-      <c r="I93" s="178" t="n"/>
-      <c r="J93" s="179" t="n"/>
-      <c r="K93" s="177" t="n"/>
-      <c r="L93" s="177" t="n"/>
-      <c r="M93" s="177" t="n"/>
-      <c r="N93" s="177" t="n"/>
-      <c r="O93" s="177" t="n"/>
-      <c r="P93" s="177" t="n"/>
-      <c r="Q93" s="177" t="n"/>
-      <c r="R93" s="177" t="n"/>
-      <c r="S93" s="177" t="n"/>
+      <c r="A93" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B93" s="271" t="inlineStr">
+        <is>
+          <t>Lacquer-02</t>
+        </is>
+      </c>
+      <c r="C93" s="271" t="inlineStr"/>
+      <c r="D93" s="271" t="inlineStr"/>
+      <c r="E93" s="271" t="inlineStr"/>
+      <c r="F93" s="271" t="n"/>
+      <c r="G93" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="273">
+        <f>IFERROR(I93/(H93+I93),"")</f>
+        <v/>
+      </c>
+      <c r="K93" s="271" t="n"/>
+      <c r="L93" s="271" t="n"/>
+      <c r="M93" s="271" t="n"/>
+      <c r="N93" s="271" t="n"/>
+      <c r="O93" s="271" t="n"/>
+      <c r="P93" s="271" t="n"/>
+      <c r="Q93" s="271" t="n"/>
+      <c r="R93" s="271" t="n"/>
+      <c r="S93" s="271" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1" s="243">
-      <c r="A94" s="176" t="n"/>
-      <c r="B94" s="177" t="n"/>
-      <c r="C94" s="177" t="n"/>
-      <c r="D94" s="177" t="n"/>
-      <c r="E94" s="177" t="n"/>
-      <c r="F94" s="177" t="n"/>
-      <c r="G94" s="178" t="n"/>
-      <c r="H94" s="178" t="n"/>
-      <c r="I94" s="178" t="n"/>
-      <c r="J94" s="179" t="n"/>
-      <c r="K94" s="177" t="n"/>
-      <c r="L94" s="177" t="n"/>
-      <c r="M94" s="177" t="n"/>
-      <c r="N94" s="177" t="n"/>
-      <c r="O94" s="177" t="n"/>
-      <c r="P94" s="177" t="n"/>
-      <c r="Q94" s="177" t="n"/>
-      <c r="R94" s="177" t="n"/>
-      <c r="S94" s="177" t="n"/>
+      <c r="A94" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B94" s="271" t="inlineStr">
+        <is>
+          <t>Lacquer-04</t>
+        </is>
+      </c>
+      <c r="C94" s="271" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D94" s="271" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E94" s="271" t="n">
+        <v>25</v>
+      </c>
+      <c r="F94" s="271" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G94" s="272" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H94" s="272" t="n">
+        <v>15715</v>
+      </c>
+      <c r="I94" s="272" t="n">
+        <v>285</v>
+      </c>
+      <c r="J94" s="273">
+        <f>IFERROR(I94/(H94+I94),"")</f>
+        <v/>
+      </c>
+      <c r="K94" s="271" t="n"/>
+      <c r="L94" s="271" t="n"/>
+      <c r="M94" s="271" t="n">
+        <v>90</v>
+      </c>
+      <c r="N94" s="271" t="n"/>
+      <c r="O94" s="271" t="n"/>
+      <c r="P94" s="271" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q94" s="271" t="n"/>
+      <c r="R94" s="271" t="n"/>
+      <c r="S94" s="271" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1" s="243">
-      <c r="A95" s="176" t="n"/>
-      <c r="B95" s="177" t="n"/>
-      <c r="C95" s="177" t="n"/>
-      <c r="D95" s="177" t="n"/>
-      <c r="E95" s="177" t="n"/>
-      <c r="F95" s="177" t="n"/>
-      <c r="G95" s="178" t="n"/>
-      <c r="H95" s="178" t="n"/>
-      <c r="I95" s="178" t="n"/>
-      <c r="J95" s="179" t="n"/>
-      <c r="K95" s="177" t="n"/>
-      <c r="L95" s="177" t="n"/>
-      <c r="M95" s="177" t="n"/>
-      <c r="N95" s="177" t="n"/>
-      <c r="O95" s="177" t="n"/>
-      <c r="P95" s="177" t="n"/>
-      <c r="Q95" s="177" t="n"/>
-      <c r="R95" s="177" t="n"/>
-      <c r="S95" s="177" t="n"/>
+      <c r="A95" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B95" s="271" t="inlineStr">
+        <is>
+          <t>Latex-01</t>
+        </is>
+      </c>
+      <c r="C95" s="271" t="inlineStr"/>
+      <c r="D95" s="271" t="inlineStr"/>
+      <c r="E95" s="271" t="inlineStr"/>
+      <c r="F95" s="271" t="n"/>
+      <c r="G95" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="273">
+        <f>IFERROR(I95/(H95+I95),"")</f>
+        <v/>
+      </c>
+      <c r="K95" s="271" t="n"/>
+      <c r="L95" s="271" t="n"/>
+      <c r="M95" s="271" t="n"/>
+      <c r="N95" s="271" t="n"/>
+      <c r="O95" s="271" t="n"/>
+      <c r="P95" s="271" t="n"/>
+      <c r="Q95" s="271" t="n"/>
+      <c r="R95" s="271" t="n"/>
+      <c r="S95" s="271" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="243">
-      <c r="A96" s="176" t="n"/>
-      <c r="B96" s="177" t="n"/>
-      <c r="C96" s="177" t="n"/>
-      <c r="D96" s="177" t="n"/>
-      <c r="E96" s="177" t="n"/>
-      <c r="F96" s="177" t="n"/>
-      <c r="G96" s="178" t="n"/>
-      <c r="H96" s="178" t="n"/>
-      <c r="I96" s="178" t="n"/>
-      <c r="J96" s="179" t="n"/>
-      <c r="K96" s="177" t="n"/>
-      <c r="L96" s="177" t="n"/>
-      <c r="M96" s="177" t="n"/>
-      <c r="N96" s="177" t="n"/>
-      <c r="O96" s="177" t="n"/>
-      <c r="P96" s="177" t="n"/>
-      <c r="Q96" s="177" t="n"/>
-      <c r="R96" s="177" t="n"/>
-      <c r="S96" s="177" t="n"/>
+      <c r="A96" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B96" s="271" t="inlineStr">
+        <is>
+          <t>PF Machine</t>
+        </is>
+      </c>
+      <c r="C96" s="271" t="inlineStr">
+        <is>
+          <t>Alpha Labs PVT LTD</t>
+        </is>
+      </c>
+      <c r="D96" s="271" t="inlineStr">
+        <is>
+          <t>TRANSPARENT BOTTLE 150ML</t>
+        </is>
+      </c>
+      <c r="E96" s="271" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="F96" s="271" t="n">
+        <v>8001</v>
+      </c>
+      <c r="G96" s="272" t="n">
+        <v>6020</v>
+      </c>
+      <c r="H96" s="272" t="n">
+        <v>5520</v>
+      </c>
+      <c r="I96" s="272" t="n">
+        <v>500</v>
+      </c>
+      <c r="J96" s="273">
+        <f>IFERROR(I96/(H96+I96),"")</f>
+        <v/>
+      </c>
+      <c r="K96" s="271" t="n"/>
+      <c r="L96" s="271" t="n"/>
+      <c r="M96" s="271" t="n"/>
+      <c r="N96" s="271" t="n"/>
+      <c r="O96" s="271" t="n"/>
+      <c r="P96" s="271" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q96" s="271" t="n"/>
+      <c r="R96" s="271" t="n"/>
+      <c r="S96" s="271" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1" s="243">
-      <c r="A97" s="176" t="n"/>
-      <c r="B97" s="177" t="n"/>
-      <c r="C97" s="177" t="n"/>
-      <c r="D97" s="177" t="n"/>
-      <c r="E97" s="177" t="n"/>
-      <c r="F97" s="177" t="n"/>
-      <c r="G97" s="178" t="n"/>
-      <c r="H97" s="178" t="n"/>
-      <c r="I97" s="178" t="n"/>
-      <c r="J97" s="179" t="n"/>
-      <c r="K97" s="177" t="n"/>
-      <c r="L97" s="177" t="n"/>
-      <c r="M97" s="177" t="n"/>
-      <c r="N97" s="177" t="n"/>
-      <c r="O97" s="177" t="n"/>
-      <c r="P97" s="177" t="n"/>
-      <c r="Q97" s="177" t="n"/>
-      <c r="R97" s="177" t="n"/>
-      <c r="S97" s="177" t="n"/>
+      <c r="A97" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B97" s="271" t="inlineStr">
+        <is>
+          <t>Press-04</t>
+        </is>
+      </c>
+      <c r="C97" s="271" t="inlineStr">
+        <is>
+          <t>Golden Pearl Cosmetics (PVT) LTD</t>
+        </is>
+      </c>
+      <c r="D97" s="271" t="inlineStr">
+        <is>
+          <t>HELLO HAIR COLOR</t>
+        </is>
+      </c>
+      <c r="E97" s="271" t="n">
+        <v>30</v>
+      </c>
+      <c r="F97" s="271" t="n">
+        <v>6206</v>
+      </c>
+      <c r="G97" s="272" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H97" s="272" t="n">
+        <v>9890</v>
+      </c>
+      <c r="I97" s="272" t="n">
+        <v>110</v>
+      </c>
+      <c r="J97" s="273">
+        <f>IFERROR(I97/(H97+I97),"")</f>
+        <v/>
+      </c>
+      <c r="K97" s="271" t="n"/>
+      <c r="L97" s="271" t="n"/>
+      <c r="M97" s="271" t="n"/>
+      <c r="N97" s="271" t="n">
+        <v>210</v>
+      </c>
+      <c r="O97" s="271" t="n"/>
+      <c r="P97" s="271" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q97" s="271" t="n"/>
+      <c r="R97" s="271" t="n"/>
+      <c r="S97" s="271" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1" s="243">
-      <c r="A98" s="176" t="n"/>
-      <c r="B98" s="177" t="n"/>
-      <c r="C98" s="177" t="n"/>
-      <c r="D98" s="177" t="n"/>
-      <c r="E98" s="177" t="n"/>
-      <c r="F98" s="177" t="n"/>
-      <c r="G98" s="178" t="n"/>
-      <c r="H98" s="178" t="n"/>
-      <c r="I98" s="178" t="n"/>
-      <c r="J98" s="179" t="n"/>
-      <c r="K98" s="177" t="n"/>
-      <c r="L98" s="177" t="n"/>
-      <c r="M98" s="177" t="n"/>
-      <c r="N98" s="177" t="n"/>
-      <c r="O98" s="177" t="n"/>
-      <c r="P98" s="177" t="n"/>
-      <c r="Q98" s="177" t="n"/>
-      <c r="R98" s="177" t="n"/>
-      <c r="S98" s="177" t="n"/>
+      <c r="A98" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B98" s="271" t="inlineStr">
+        <is>
+          <t>Press-06</t>
+        </is>
+      </c>
+      <c r="C98" s="271" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D98" s="271" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E98" s="271" t="n">
+        <v>25</v>
+      </c>
+      <c r="F98" s="271" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G98" s="272" t="n">
+        <v>18500</v>
+      </c>
+      <c r="H98" s="272" t="n">
+        <v>18375</v>
+      </c>
+      <c r="I98" s="272" t="n">
+        <v>125</v>
+      </c>
+      <c r="J98" s="273">
+        <f>IFERROR(I98/(H98+I98),"")</f>
+        <v/>
+      </c>
+      <c r="K98" s="271" t="n">
+        <v>60</v>
+      </c>
+      <c r="L98" s="271" t="n"/>
+      <c r="M98" s="271" t="n"/>
+      <c r="N98" s="271" t="n"/>
+      <c r="O98" s="271" t="n"/>
+      <c r="P98" s="271" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q98" s="271" t="n"/>
+      <c r="R98" s="271" t="n"/>
+      <c r="S98" s="271" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1" s="243">
-      <c r="A99" s="176" t="n"/>
-      <c r="B99" s="177" t="n"/>
-      <c r="C99" s="177" t="n"/>
-      <c r="D99" s="177" t="n"/>
-      <c r="E99" s="177" t="n"/>
-      <c r="F99" s="177" t="n"/>
-      <c r="G99" s="178" t="n"/>
-      <c r="H99" s="178" t="n"/>
-      <c r="I99" s="178" t="n"/>
-      <c r="J99" s="179" t="n"/>
-      <c r="K99" s="177" t="n"/>
-      <c r="L99" s="177" t="n"/>
-      <c r="M99" s="177" t="n"/>
-      <c r="N99" s="177" t="n"/>
-      <c r="O99" s="177" t="n"/>
-      <c r="P99" s="177" t="n"/>
-      <c r="Q99" s="177" t="n"/>
-      <c r="R99" s="177" t="n"/>
-      <c r="S99" s="177" t="n"/>
+      <c r="A99" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B99" s="271" t="inlineStr">
+        <is>
+          <t>Printing-03</t>
+        </is>
+      </c>
+      <c r="C99" s="271" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D99" s="271" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="E99" s="271" t="n">
+        <v>25</v>
+      </c>
+      <c r="F99" s="271" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G99" s="272" t="n">
+        <v>14898</v>
+      </c>
+      <c r="H99" s="272" t="n">
+        <v>14448</v>
+      </c>
+      <c r="I99" s="272" t="n">
+        <v>450</v>
+      </c>
+      <c r="J99" s="273">
+        <f>IFERROR(I99/(H99+I99),"")</f>
+        <v/>
+      </c>
+      <c r="K99" s="271" t="n"/>
+      <c r="L99" s="271" t="n"/>
+      <c r="M99" s="271" t="n"/>
+      <c r="N99" s="271" t="n"/>
+      <c r="O99" s="271" t="n"/>
+      <c r="P99" s="271" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q99" s="271" t="n"/>
+      <c r="R99" s="271" t="n"/>
+      <c r="S99" s="271" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="243">
-      <c r="A100" s="176" t="n"/>
-      <c r="B100" s="177" t="n"/>
-      <c r="C100" s="177" t="n"/>
-      <c r="D100" s="177" t="n"/>
-      <c r="E100" s="177" t="n"/>
-      <c r="F100" s="177" t="n"/>
-      <c r="G100" s="178" t="n"/>
-      <c r="H100" s="178" t="n"/>
-      <c r="I100" s="178" t="n"/>
-      <c r="J100" s="179" t="n"/>
-      <c r="K100" s="177" t="n"/>
-      <c r="L100" s="177" t="n"/>
-      <c r="M100" s="177" t="n"/>
-      <c r="N100" s="177" t="n"/>
-      <c r="O100" s="177" t="n"/>
-      <c r="P100" s="177" t="n"/>
-      <c r="Q100" s="177" t="n"/>
-      <c r="R100" s="177" t="n"/>
-      <c r="S100" s="177" t="n"/>
+      <c r="A100" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B100" s="271" t="inlineStr">
+        <is>
+          <t>Printing-03</t>
+        </is>
+      </c>
+      <c r="C100" s="271" t="inlineStr">
+        <is>
+          <t>Samsol International Private Limited</t>
+        </is>
+      </c>
+      <c r="D100" s="271" t="inlineStr">
+        <is>
+          <t>S 43 25MM</t>
+        </is>
+      </c>
+      <c r="E100" s="271" t="n">
+        <v>25</v>
+      </c>
+      <c r="F100" s="271" t="n">
+        <v>3447</v>
+      </c>
+      <c r="G100" s="272" t="n">
+        <v>4864</v>
+      </c>
+      <c r="H100" s="272" t="n">
+        <v>4704</v>
+      </c>
+      <c r="I100" s="272" t="n">
+        <v>160</v>
+      </c>
+      <c r="J100" s="273">
+        <f>IFERROR(I100/(H100+I100),"")</f>
+        <v/>
+      </c>
+      <c r="K100" s="271" t="n"/>
+      <c r="L100" s="271" t="n"/>
+      <c r="M100" s="271" t="n"/>
+      <c r="N100" s="271" t="n">
+        <v>30</v>
+      </c>
+      <c r="O100" s="271" t="n"/>
+      <c r="P100" s="271" t="n"/>
+      <c r="Q100" s="271" t="n"/>
+      <c r="R100" s="271" t="n"/>
+      <c r="S100" s="271" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1" s="243">
-      <c r="A101" s="176" t="n"/>
-      <c r="B101" s="177" t="n"/>
-      <c r="C101" s="177" t="n"/>
-      <c r="D101" s="177" t="n"/>
-      <c r="E101" s="177" t="n"/>
-      <c r="F101" s="177" t="n"/>
-      <c r="G101" s="178" t="n"/>
-      <c r="H101" s="178" t="n"/>
-      <c r="I101" s="178" t="n"/>
-      <c r="J101" s="179" t="n"/>
-      <c r="K101" s="177" t="n"/>
-      <c r="L101" s="177" t="n"/>
-      <c r="M101" s="177" t="n"/>
-      <c r="N101" s="177" t="n"/>
-      <c r="O101" s="177" t="n"/>
-      <c r="P101" s="177" t="n"/>
-      <c r="Q101" s="177" t="n"/>
-      <c r="R101" s="177" t="n"/>
-      <c r="S101" s="177" t="n"/>
+      <c r="A101" s="274" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B101" s="271" t="inlineStr">
+        <is>
+          <t>Printing-04</t>
+        </is>
+      </c>
+      <c r="C101" s="271" t="inlineStr"/>
+      <c r="D101" s="271" t="inlineStr"/>
+      <c r="E101" s="271" t="inlineStr"/>
+      <c r="F101" s="271" t="n"/>
+      <c r="G101" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="273">
+        <f>IFERROR(I101/(H101+I101),"")</f>
+        <v/>
+      </c>
+      <c r="K101" s="271" t="n"/>
+      <c r="L101" s="271" t="n"/>
+      <c r="M101" s="271" t="n"/>
+      <c r="N101" s="271" t="n"/>
+      <c r="O101" s="271" t="n"/>
+      <c r="P101" s="271" t="n"/>
+      <c r="Q101" s="271" t="n"/>
+      <c r="R101" s="271" t="n"/>
+      <c r="S101" s="271" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1" s="243">
       <c r="A102" s="176" t="n"/>
@@ -38440,13 +38713,13 @@
   <cols>
     <col width="10" customWidth="1" style="243" min="1" max="1"/>
     <col width="15.28515625" customWidth="1" style="243" min="2" max="2"/>
-    <col width="16.85546875" customWidth="1" style="243" min="3" max="3"/>
+    <col width="33.140625" customWidth="1" style="243" min="3" max="3"/>
     <col width="6" customWidth="1" style="243" min="4" max="4"/>
     <col width="8.5703125" customWidth="1" style="67" min="5" max="5"/>
     <col width="8.85546875" customWidth="1" style="67" min="6" max="6"/>
     <col width="11.140625" customWidth="1" style="67" min="7" max="7"/>
     <col width="8.5703125" customWidth="1" style="68" min="8" max="8"/>
-    <col width="7.7109375" customWidth="1" style="67" min="9" max="9"/>
+    <col hidden="1" width="7.7109375" customWidth="1" style="67" min="9" max="9"/>
     <col width="16.140625" customWidth="1" style="67" min="10" max="10"/>
     <col width="18" customWidth="1" style="243" min="11" max="11"/>
   </cols>
@@ -38457,13 +38730,13 @@
           <t>Slugs Inventory — June 2026 MONTH TO DATE</t>
         </is>
       </c>
-      <c r="B1" s="241" t="n"/>
-      <c r="C1" s="241" t="n"/>
-      <c r="D1" s="241" t="n"/>
-      <c r="E1" s="241" t="n"/>
-      <c r="F1" s="241" t="n"/>
-      <c r="G1" s="241" t="n"/>
-      <c r="H1" s="241" t="n"/>
+      <c r="B1" s="238" t="n"/>
+      <c r="C1" s="238" t="n"/>
+      <c r="D1" s="238" t="n"/>
+      <c r="E1" s="238" t="n"/>
+      <c r="F1" s="238" t="n"/>
+      <c r="G1" s="238" t="n"/>
+      <c r="H1" s="238" t="n"/>
       <c r="I1" s="69" t="inlineStr">
         <is>
           <t>Date:</t>
@@ -38704,14 +38977,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>1150</v>
+        <v>1215</v>
       </c>
       <c r="H7" s="38">
         <f>E7+F7-G7</f>
         <v/>
       </c>
       <c r="I7" s="37" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="J7" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
@@ -38750,7 +39023,9 @@
         <f>E8+F8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="37" t="n"/>
+      <c r="I8" s="37" t="n">
+        <v>10</v>
+      </c>
       <c r="J8" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
         <v/>
@@ -39088,7 +39363,7 @@
         <v>100</v>
       </c>
       <c r="G18" s="37" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H18" s="38">
         <f>E18+F18-G18</f>
@@ -39244,7 +39519,7 @@
         <v>210</v>
       </c>
       <c r="G22" s="37" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H22" s="38">
         <f>E22+F22-G22</f>
@@ -40251,10 +40526,10 @@
         <v>70000</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G46" s="37" t="n">
-        <v>70000</v>
+        <v>100000</v>
       </c>
       <c r="H46" s="38">
         <f>E46+F46-G46</f>
@@ -40514,13 +40789,13 @@
         </is>
       </c>
       <c r="E52" s="37" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="37" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="37" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="38">
         <f>E52+F52-G52</f>
@@ -40954,7 +41229,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="37" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H62" s="38">
         <f>E62+F62-G62</f>
@@ -41481,7 +41756,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="37" t="n">
         <v>0</v>
@@ -41792,7 +42067,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="38">
         <f>E81+F81-G81</f>
@@ -42245,7 +42520,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G93" s="37" t="n">
         <v>0</v>
@@ -50876,11 +51151,11 @@
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -55597,8 +55872,8 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
   </mergeCells>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tubex_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MRP'!$A$13:$K$95</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Production_Log'!$A$2:$R$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Production_Log'!$A$2:$R$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BOM Issues'!$A$52:$J$64</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -1410,12 +1410,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1425,24 +1443,6 @@
     <xf numFmtId="0" fontId="42" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1464,6 +1464,9 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1471,9 +1474,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2067,23 +2067,23 @@
   <dimension ref="A1:AC199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="16.5"/>
   <cols>
-    <col width="1.5703125" customWidth="1" style="228" min="1" max="1"/>
-    <col width="7" customWidth="1" style="228" min="2" max="2"/>
-    <col width="32.7109375" customWidth="1" style="228" min="3" max="3"/>
-    <col width="38.7109375" customWidth="1" style="228" min="4" max="4"/>
-    <col width="8.85546875" customWidth="1" style="229" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="228" min="6" max="6"/>
-    <col width="11" customWidth="1" style="230" min="7" max="7"/>
-    <col width="11.140625" customWidth="1" style="228" min="8" max="8"/>
-    <col width="10.28515625" customWidth="1" style="228" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="228" min="10" max="10"/>
-    <col width="9.28515625" customWidth="1" style="228" min="11" max="11"/>
-    <col width="35.140625" customWidth="1" style="228" min="12" max="12"/>
-    <col width="14.7109375" customWidth="1" style="228" min="13" max="13"/>
-    <col width="13.28515625" customWidth="1" style="228" min="14" max="14"/>
-    <col width="9.5703125" customWidth="1" style="228" min="15" max="15"/>
-    <col width="8.7109375" customWidth="1" style="228" min="16" max="57"/>
-    <col width="8.7109375" customWidth="1" style="228" min="58" max="16384"/>
+    <col width="1.5703125" customWidth="1" style="233" min="1" max="1"/>
+    <col width="7" customWidth="1" style="233" min="2" max="2"/>
+    <col width="32.7109375" customWidth="1" style="233" min="3" max="3"/>
+    <col width="38.7109375" customWidth="1" style="233" min="4" max="4"/>
+    <col width="8.85546875" customWidth="1" style="234" min="5" max="5"/>
+    <col width="9.140625" customWidth="1" style="233" min="6" max="6"/>
+    <col width="11" customWidth="1" style="235" min="7" max="7"/>
+    <col width="11.140625" customWidth="1" style="233" min="8" max="8"/>
+    <col width="10.28515625" customWidth="1" style="233" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="233" min="10" max="10"/>
+    <col width="9.28515625" customWidth="1" style="233" min="11" max="11"/>
+    <col width="35.140625" customWidth="1" style="233" min="12" max="12"/>
+    <col width="14.7109375" customWidth="1" style="233" min="13" max="13"/>
+    <col width="13.28515625" customWidth="1" style="233" min="14" max="14"/>
+    <col width="9.5703125" customWidth="1" style="233" min="15" max="15"/>
+    <col width="8.7109375" customWidth="1" style="233" min="16" max="58"/>
+    <col width="8.7109375" customWidth="1" style="233" min="59" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1" s="243">
@@ -2399,21 +2399,21 @@
     </row>
     <row r="9" ht="20.25" customHeight="1" s="243">
       <c r="A9" s="136" t="n"/>
-      <c r="B9" s="237" t="inlineStr">
+      <c r="B9" s="230" t="inlineStr">
         <is>
           <t>Summary of Production &amp; Dispatch - MTD</t>
         </is>
       </c>
-      <c r="C9" s="238" t="n"/>
-      <c r="D9" s="238" t="n"/>
-      <c r="E9" s="238" t="n"/>
-      <c r="F9" s="238" t="n"/>
-      <c r="G9" s="238" t="n"/>
-      <c r="H9" s="238" t="n"/>
-      <c r="I9" s="238" t="n"/>
-      <c r="J9" s="238" t="n"/>
-      <c r="K9" s="238" t="n"/>
-      <c r="L9" s="238" t="n"/>
+      <c r="C9" s="231" t="n"/>
+      <c r="D9" s="231" t="n"/>
+      <c r="E9" s="231" t="n"/>
+      <c r="F9" s="231" t="n"/>
+      <c r="G9" s="231" t="n"/>
+      <c r="H9" s="231" t="n"/>
+      <c r="I9" s="231" t="n"/>
+      <c r="J9" s="231" t="n"/>
+      <c r="K9" s="231" t="n"/>
+      <c r="L9" s="231" t="n"/>
       <c r="M9" s="157">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,3),$U$9:$U$23,0)),"")</f>
         <v/>
@@ -2884,9 +2884,8 @@
       <c r="F15" s="292" t="n">
         <v>5389</v>
       </c>
-      <c r="G15" s="292">
-        <f>IFERROR(INDEX(MRP!$F$3:$F$10,MATCH(Tubex_Dashboard!F15,MRP!$D$3:$D$10,0)),0)</f>
-        <v/>
+      <c r="G15" s="292" t="n">
+        <v>49056</v>
       </c>
       <c r="H15" s="293">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F15)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
@@ -4148,7 +4147,7 @@
       <c r="P36" s="136" t="n"/>
       <c r="Q36" s="136" t="n"/>
       <c r="R36" s="136" t="n"/>
-      <c r="S36" s="228" t="inlineStr">
+      <c r="S36" s="233" t="inlineStr">
         <is>
           <t>Gas Shutdown</t>
         </is>
@@ -4157,7 +4156,7 @@
         <f>SUMPRODUCT((MONTH(Production_Log!$A$3:$A$8963)=MONTH(TODAY()))*(YEAR(Production_Log!$A$3:$A$8963)=YEAR(TODAY()))*Production_Log!$Q$3:$Q$8963)</f>
         <v/>
       </c>
-      <c r="U36" s="228">
+      <c r="U36" s="233">
         <f>T36+0.00006</f>
         <v/>
       </c>
@@ -6140,7 +6139,7 @@
         <v>6892</v>
       </c>
       <c r="F4" s="185" t="n">
-        <v>48176</v>
+        <v>49056</v>
       </c>
       <c r="G4" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$58,MATCH(MRP!D4,Tubex_Dashboard!$F$11:$F$58,0))</f>
@@ -6281,7 +6280,7 @@
         <v>6887</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>52000</v>
+        <v>30000</v>
       </c>
       <c r="G8" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$58,MATCH(MRP!D8,Tubex_Dashboard!$F$11:$F$58,0))</f>
@@ -6932,9 +6931,10 @@
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
         <v/>
       </c>
-      <c r="I21" s="30">
-        <f>IF(E21=0,"Not needed",IF(G21&lt;0,"SHORTAGE",IF(G21&lt;F21*0.1,"LOW","OK")))</f>
-        <v/>
+      <c r="I21" s="30" t="inlineStr">
+        <is>
+          <t>100kg Shortage. 15k Tubes WIP</t>
+        </is>
       </c>
       <c r="J21" s="30">
         <f>IF(B21&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A21)*'FG Stock'!$F$4:$F$100))</f>
@@ -10709,14 +10709,14 @@
           <t>June 2026 PET Required Pet Orders</t>
         </is>
       </c>
-      <c r="B98" s="240" t="n"/>
-      <c r="C98" s="240" t="n"/>
-      <c r="D98" s="240" t="n"/>
-      <c r="E98" s="240" t="n"/>
-      <c r="F98" s="240" t="n"/>
+      <c r="B98" s="228" t="n"/>
+      <c r="C98" s="228" t="n"/>
+      <c r="D98" s="228" t="n"/>
+      <c r="E98" s="228" t="n"/>
+      <c r="F98" s="228" t="n"/>
       <c r="G98" s="188" t="n"/>
-      <c r="H98" s="240" t="n"/>
-      <c r="I98" s="241" t="n"/>
+      <c r="H98" s="228" t="n"/>
+      <c r="I98" s="229" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1" s="243">
       <c r="A99" s="12" t="inlineStr">
@@ -10971,14 +10971,14 @@
           <t>JUNE PET MATERIAL REQUIREMENT PLAN</t>
         </is>
       </c>
-      <c r="B106" s="240" t="n"/>
-      <c r="C106" s="240" t="n"/>
-      <c r="D106" s="240" t="n"/>
-      <c r="E106" s="240" t="n"/>
-      <c r="F106" s="240" t="n"/>
+      <c r="B106" s="228" t="n"/>
+      <c r="C106" s="228" t="n"/>
+      <c r="D106" s="228" t="n"/>
+      <c r="E106" s="228" t="n"/>
+      <c r="F106" s="228" t="n"/>
       <c r="G106" s="188" t="n"/>
-      <c r="H106" s="240" t="n"/>
-      <c r="I106" s="240" t="n"/>
+      <c r="H106" s="228" t="n"/>
+      <c r="I106" s="228" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1" s="243">
       <c r="A107" s="41" t="inlineStr">
@@ -11168,14 +11168,14 @@
       <c r="A111" s="262" t="n">
         <v>5977</v>
       </c>
-      <c r="B111" s="240" t="n"/>
-      <c r="C111" s="240" t="n"/>
-      <c r="D111" s="240" t="n"/>
-      <c r="E111" s="240" t="n"/>
-      <c r="F111" s="240" t="n"/>
-      <c r="G111" s="240" t="n"/>
-      <c r="H111" s="240" t="n"/>
-      <c r="I111" s="241" t="n"/>
+      <c r="B111" s="228" t="n"/>
+      <c r="C111" s="228" t="n"/>
+      <c r="D111" s="228" t="n"/>
+      <c r="E111" s="228" t="n"/>
+      <c r="F111" s="228" t="n"/>
+      <c r="G111" s="228" t="n"/>
+      <c r="H111" s="228" t="n"/>
+      <c r="I111" s="229" t="n"/>
       <c r="K111" s="47">
         <f>IF(E106=0,"",MAX(0,E106-F106))</f>
         <v/>
@@ -11185,14 +11185,14 @@
       <c r="A112" s="196" t="n">
         <v>2267</v>
       </c>
-      <c r="B112" s="240" t="n"/>
-      <c r="C112" s="240" t="n"/>
-      <c r="D112" s="240" t="n"/>
-      <c r="E112" s="240" t="n"/>
-      <c r="F112" s="240" t="n"/>
-      <c r="G112" s="240" t="n"/>
-      <c r="H112" s="240" t="n"/>
-      <c r="I112" s="241" t="n"/>
+      <c r="B112" s="228" t="n"/>
+      <c r="C112" s="228" t="n"/>
+      <c r="D112" s="228" t="n"/>
+      <c r="E112" s="228" t="n"/>
+      <c r="F112" s="228" t="n"/>
+      <c r="G112" s="228" t="n"/>
+      <c r="H112" s="228" t="n"/>
+      <c r="I112" s="229" t="n"/>
       <c r="K112" s="48">
         <f>IF(E107=0,"",MAX(0,E107-F107))</f>
         <v/>
@@ -11332,14 +11332,14 @@
     </row>
     <row r="116" ht="15" customHeight="1" s="243">
       <c r="A116" s="187" t="n"/>
-      <c r="B116" s="240" t="n"/>
-      <c r="C116" s="240" t="n"/>
-      <c r="D116" s="240" t="n"/>
-      <c r="E116" s="240" t="n"/>
-      <c r="F116" s="240" t="n"/>
+      <c r="B116" s="228" t="n"/>
+      <c r="C116" s="228" t="n"/>
+      <c r="D116" s="228" t="n"/>
+      <c r="E116" s="228" t="n"/>
+      <c r="F116" s="228" t="n"/>
       <c r="G116" s="188" t="n"/>
-      <c r="H116" s="240" t="n"/>
-      <c r="I116" s="241" t="n"/>
+      <c r="H116" s="228" t="n"/>
+      <c r="I116" s="229" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1" s="243">
       <c r="A117" s="6" t="inlineStr">
@@ -13242,24 +13242,23 @@
   <autoFilter ref="A13:K95">
     <filterColumn colId="4" hiddenButton="0" showButton="1">
       <filters>
-        <filter val="1,516"/>
-        <filter val="111"/>
+        <filter val="1,466"/>
+        <filter val="104"/>
         <filter val="138"/>
         <filter val="15"/>
+        <filter val="165"/>
         <filter val="188"/>
+        <filter val="193"/>
         <filter val="2"/>
-        <filter val="20"/>
-        <filter val="222"/>
+        <filter val="2,898"/>
         <filter val="25,500"/>
-        <filter val="263"/>
+        <filter val="279"/>
         <filter val="3"/>
-        <filter val="3,092"/>
-        <filter val="305"/>
-        <filter val="347,688"/>
-        <filter val="66,606"/>
+        <filter val="331,114"/>
+        <filter val="44,166"/>
         <filter val="69"/>
         <filter val="89"/>
-        <filter val="99"/>
+        <filter val="96"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -13320,7 +13319,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13459,7 +13458,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="243">
+    <row r="3" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A3" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13509,7 +13508,7 @@
       <c r="R3" s="271" t="n"/>
       <c r="S3" s="271" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="243">
+    <row r="4" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A4" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13557,7 +13556,7 @@
       <c r="R4" s="271" t="n"/>
       <c r="S4" s="271" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="243">
+    <row r="5" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A5" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13605,7 +13604,7 @@
       <c r="R5" s="271" t="n"/>
       <c r="S5" s="271" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="243">
+    <row r="6" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A6" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13657,7 +13656,7 @@
       <c r="R6" s="271" t="n"/>
       <c r="S6" s="271" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="243">
+    <row r="7" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A7" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13753,7 +13752,7 @@
       <c r="R8" s="271" t="n"/>
       <c r="S8" s="271" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="243">
+    <row r="9" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A9" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13805,7 +13804,7 @@
       <c r="R9" s="271" t="n"/>
       <c r="S9" s="271" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="243">
+    <row r="10" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A10" s="274" t="n">
         <v>46174</v>
       </c>
@@ -13853,7 +13852,7 @@
       <c r="R10" s="271" t="n"/>
       <c r="S10" s="271" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="243">
+    <row r="11" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A11" s="274" t="n">
         <v>46175</v>
       </c>
@@ -13903,7 +13902,7 @@
       <c r="R11" s="271" t="n"/>
       <c r="S11" s="271" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="243">
+    <row r="12" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A12" s="274" t="n">
         <v>46175</v>
       </c>
@@ -13951,7 +13950,7 @@
       <c r="R12" s="271" t="n"/>
       <c r="S12" s="271" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="243">
+    <row r="13" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A13" s="274" t="n">
         <v>46175</v>
       </c>
@@ -14001,7 +14000,7 @@
       <c r="R13" s="271" t="n"/>
       <c r="S13" s="271" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="243">
+    <row r="14" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A14" s="274" t="n">
         <v>46175</v>
       </c>
@@ -14053,7 +14052,7 @@
       <c r="R14" s="271" t="n"/>
       <c r="S14" s="271" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="243">
+    <row r="15" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A15" s="274" t="n">
         <v>46175</v>
       </c>
@@ -14149,7 +14148,7 @@
       <c r="R16" s="271" t="n"/>
       <c r="S16" s="271" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="243">
+    <row r="17" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A17" s="274" t="n">
         <v>46175</v>
       </c>
@@ -14199,7 +14198,7 @@
       <c r="R17" s="271" t="n"/>
       <c r="S17" s="271" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="243">
+    <row r="18" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A18" s="274" t="n">
         <v>46175</v>
       </c>
@@ -14247,7 +14246,7 @@
       <c r="R18" s="271" t="n"/>
       <c r="S18" s="271" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="243">
+    <row r="19" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A19" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14283,7 +14282,7 @@
       <c r="R19" s="271" t="n"/>
       <c r="S19" s="271" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="243">
+    <row r="20" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A20" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14319,7 +14318,7 @@
       <c r="R20" s="271" t="n"/>
       <c r="S20" s="271" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="243">
+    <row r="21" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A21" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14355,7 +14354,7 @@
       <c r="R21" s="271" t="n"/>
       <c r="S21" s="271" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="243">
+    <row r="22" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A22" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14409,7 +14408,7 @@
       <c r="R22" s="271" t="n"/>
       <c r="S22" s="271" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1" s="243">
+    <row r="23" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A23" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14445,7 +14444,7 @@
       <c r="R23" s="271" t="n"/>
       <c r="S23" s="271" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="243">
+    <row r="24" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A24" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14481,7 +14480,7 @@
       <c r="R24" s="271" t="n"/>
       <c r="S24" s="271" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="243">
+    <row r="25" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A25" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14517,7 +14516,7 @@
       <c r="R25" s="271" t="n"/>
       <c r="S25" s="271" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="243">
+    <row r="26" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A26" s="274" t="n">
         <v>46177</v>
       </c>
@@ -14553,7 +14552,7 @@
       <c r="R26" s="271" t="n"/>
       <c r="S26" s="271" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="243">
+    <row r="27" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A27" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14589,7 +14588,7 @@
       <c r="R27" s="271" t="n"/>
       <c r="S27" s="271" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="243">
+    <row r="28" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A28" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14625,7 +14624,7 @@
       <c r="R28" s="271" t="n"/>
       <c r="S28" s="271" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="243">
+    <row r="29" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A29" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14661,7 +14660,7 @@
       <c r="R29" s="271" t="n"/>
       <c r="S29" s="271" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="243">
+    <row r="30" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A30" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14715,7 +14714,7 @@
       <c r="R30" s="271" t="n"/>
       <c r="S30" s="271" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="243">
+    <row r="31" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A31" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14751,7 +14750,7 @@
       <c r="R31" s="271" t="n"/>
       <c r="S31" s="271" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1" s="243">
+    <row r="32" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A32" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14787,7 +14786,7 @@
       <c r="R32" s="271" t="n"/>
       <c r="S32" s="271" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="243">
+    <row r="33" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A33" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14823,7 +14822,7 @@
       <c r="R33" s="271" t="n"/>
       <c r="S33" s="271" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="243">
+    <row r="34" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A34" s="274" t="n">
         <v>46178</v>
       </c>
@@ -14859,7 +14858,7 @@
       <c r="R34" s="271" t="n"/>
       <c r="S34" s="271" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1" s="243">
+    <row r="35" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A35" s="274" t="n">
         <v>46179</v>
       </c>
@@ -14895,7 +14894,7 @@
       <c r="R35" s="271" t="n"/>
       <c r="S35" s="271" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="243">
+    <row r="36" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A36" s="274" t="n">
         <v>46179</v>
       </c>
@@ -14931,7 +14930,7 @@
       <c r="R36" s="271" t="n"/>
       <c r="S36" s="271" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1" s="243">
+    <row r="37" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A37" s="274" t="n">
         <v>46179</v>
       </c>
@@ -14967,7 +14966,7 @@
       <c r="R37" s="271" t="n"/>
       <c r="S37" s="271" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="243">
+    <row r="38" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A38" s="274" t="n">
         <v>46179</v>
       </c>
@@ -15023,7 +15022,7 @@
       <c r="R38" s="271" t="n"/>
       <c r="S38" s="271" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="243">
+    <row r="39" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A39" s="274" t="n">
         <v>46179</v>
       </c>
@@ -15059,7 +15058,7 @@
       <c r="R39" s="271" t="n"/>
       <c r="S39" s="271" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1" s="243">
+    <row r="40" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A40" s="274" t="n">
         <v>46179</v>
       </c>
@@ -15095,7 +15094,7 @@
       <c r="R40" s="271" t="n"/>
       <c r="S40" s="271" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="243">
+    <row r="41" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A41" s="274" t="n">
         <v>46179</v>
       </c>
@@ -15131,7 +15130,7 @@
       <c r="R41" s="271" t="n"/>
       <c r="S41" s="271" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1" s="243">
+    <row r="42" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A42" s="274" t="n">
         <v>46179</v>
       </c>
@@ -15167,7 +15166,7 @@
       <c r="R42" s="271" t="n"/>
       <c r="S42" s="271" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1" s="243">
+    <row r="43" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A43" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15203,7 +15202,7 @@
       <c r="R43" s="271" t="n"/>
       <c r="S43" s="271" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1" s="243">
+    <row r="44" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A44" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15251,7 +15250,7 @@
       <c r="R44" s="271" t="n"/>
       <c r="S44" s="271" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1" s="243">
+    <row r="45" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A45" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15287,7 +15286,7 @@
       <c r="R45" s="271" t="n"/>
       <c r="S45" s="271" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1" s="243">
+    <row r="46" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A46" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15341,7 +15340,7 @@
       <c r="R46" s="271" t="n"/>
       <c r="S46" s="271" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1" s="243">
+    <row r="47" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A47" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15425,7 +15424,7 @@
       <c r="R48" s="271" t="n"/>
       <c r="S48" s="271" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1" s="243">
+    <row r="49" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A49" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15475,7 +15474,7 @@
       <c r="R49" s="271" t="n"/>
       <c r="S49" s="271" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1" s="243">
+    <row r="50" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A50" s="274" t="n">
         <v>46181</v>
       </c>
@@ -15511,7 +15510,7 @@
       <c r="R50" s="271" t="n"/>
       <c r="S50" s="271" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="243">
+    <row r="51" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A51" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15547,7 +15546,7 @@
       <c r="R51" s="271" t="n"/>
       <c r="S51" s="271" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1" s="243">
+    <row r="52" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A52" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15595,7 +15594,7 @@
       <c r="R52" s="271" t="n"/>
       <c r="S52" s="271" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1" s="243">
+    <row r="53" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A53" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15631,7 +15630,7 @@
       <c r="R53" s="271" t="n"/>
       <c r="S53" s="271" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="243">
+    <row r="54" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A54" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15685,7 +15684,7 @@
       <c r="R54" s="271" t="n"/>
       <c r="S54" s="271" t="n"/>
     </row>
-    <row r="55" ht="15" customHeight="1" s="243">
+    <row r="55" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A55" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15769,7 +15768,7 @@
       <c r="R56" s="271" t="n"/>
       <c r="S56" s="271" t="n"/>
     </row>
-    <row r="57" ht="15" customHeight="1" s="243">
+    <row r="57" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A57" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15817,7 +15816,7 @@
       <c r="R57" s="271" t="n"/>
       <c r="S57" s="271" t="n"/>
     </row>
-    <row r="58" ht="15" customHeight="1" s="243">
+    <row r="58" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A58" s="274" t="n">
         <v>46182</v>
       </c>
@@ -15853,7 +15852,7 @@
       <c r="R58" s="271" t="n"/>
       <c r="S58" s="271" t="n"/>
     </row>
-    <row r="59" ht="15" customHeight="1" s="243">
+    <row r="59" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A59" s="274" t="n">
         <v>46183</v>
       </c>
@@ -15889,7 +15888,7 @@
       <c r="R59" s="271" t="n"/>
       <c r="S59" s="271" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1" s="243">
+    <row r="60" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A60" s="274" t="n">
         <v>46183</v>
       </c>
@@ -15937,7 +15936,7 @@
       <c r="R60" s="271" t="n"/>
       <c r="S60" s="271" t="n"/>
     </row>
-    <row r="61" ht="15" customHeight="1" s="243">
+    <row r="61" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A61" s="274" t="n">
         <v>46183</v>
       </c>
@@ -15973,7 +15972,7 @@
       <c r="R61" s="271" t="n"/>
       <c r="S61" s="271" t="n"/>
     </row>
-    <row r="62" ht="15" customHeight="1" s="243">
+    <row r="62" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A62" s="274" t="n">
         <v>46183</v>
       </c>
@@ -16025,7 +16024,7 @@
       <c r="R62" s="271" t="n"/>
       <c r="S62" s="271" t="n"/>
     </row>
-    <row r="63" ht="15" customHeight="1" s="243">
+    <row r="63" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A63" s="274" t="n">
         <v>46183</v>
       </c>
@@ -16109,7 +16108,7 @@
       <c r="R64" s="271" t="n"/>
       <c r="S64" s="271" t="n"/>
     </row>
-    <row r="65" ht="15" customHeight="1" s="243">
+    <row r="65" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A65" s="274" t="n">
         <v>46183</v>
       </c>
@@ -16157,7 +16156,7 @@
       <c r="R65" s="271" t="n"/>
       <c r="S65" s="271" t="n"/>
     </row>
-    <row r="66" ht="15" customHeight="1" s="243">
+    <row r="66" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A66" s="274" t="n">
         <v>46183</v>
       </c>
@@ -16193,7 +16192,7 @@
       <c r="R66" s="271" t="n"/>
       <c r="S66" s="271" t="n"/>
     </row>
-    <row r="67" ht="15" customHeight="1" s="243">
+    <row r="67" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A67" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16229,7 +16228,7 @@
       <c r="R67" s="271" t="n"/>
       <c r="S67" s="271" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1" s="243">
+    <row r="68" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A68" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16279,7 +16278,7 @@
       <c r="R68" s="271" t="n"/>
       <c r="S68" s="271" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1" s="243">
+    <row r="69" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A69" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16315,7 +16314,7 @@
       <c r="R69" s="271" t="n"/>
       <c r="S69" s="271" t="n"/>
     </row>
-    <row r="70" ht="15" customHeight="1" s="243">
+    <row r="70" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A70" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16367,7 +16366,7 @@
       <c r="R70" s="271" t="n"/>
       <c r="S70" s="271" t="n"/>
     </row>
-    <row r="71" ht="15" customHeight="1" s="243">
+    <row r="71" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A71" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16453,7 +16452,7 @@
       <c r="R72" s="271" t="n"/>
       <c r="S72" s="271" t="n"/>
     </row>
-    <row r="73" ht="15" customHeight="1" s="243">
+    <row r="73" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A73" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16503,7 +16502,7 @@
       <c r="R73" s="271" t="n"/>
       <c r="S73" s="271" t="n"/>
     </row>
-    <row r="74" ht="15" customHeight="1" s="243">
+    <row r="74" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A74" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16553,7 +16552,7 @@
       <c r="R74" s="271" t="n"/>
       <c r="S74" s="271" t="n"/>
     </row>
-    <row r="75" ht="15" customHeight="1" s="243">
+    <row r="75" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A75" s="274" t="n">
         <v>46184</v>
       </c>
@@ -16589,7 +16588,7 @@
       <c r="R75" s="271" t="n"/>
       <c r="S75" s="271" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1" s="243">
+    <row r="76" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A76" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16625,7 +16624,7 @@
       <c r="R76" s="271" t="n"/>
       <c r="S76" s="271" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1" s="243">
+    <row r="77" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A77" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16675,7 +16674,7 @@
       <c r="R77" s="271" t="n"/>
       <c r="S77" s="271" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1" s="243">
+    <row r="78" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A78" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16711,7 +16710,7 @@
       <c r="R78" s="271" t="n"/>
       <c r="S78" s="271" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1" s="243">
+    <row r="79" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A79" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16763,7 +16762,7 @@
       <c r="R79" s="271" t="n"/>
       <c r="S79" s="271" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1" s="243">
+    <row r="80" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A80" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16849,7 +16848,7 @@
       <c r="R81" s="271" t="n"/>
       <c r="S81" s="271" t="n"/>
     </row>
-    <row r="82" ht="15" customHeight="1" s="243">
+    <row r="82" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A82" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16899,7 +16898,7 @@
       <c r="R82" s="271" t="n"/>
       <c r="S82" s="271" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1" s="243">
+    <row r="83" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A83" s="274" t="n">
         <v>46185</v>
       </c>
@@ -16939,7 +16938,7 @@
       <c r="R83" s="271" t="n"/>
       <c r="S83" s="271" t="n"/>
     </row>
-    <row r="84" ht="15" customHeight="1" s="243">
+    <row r="84" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A84" s="274" t="n">
         <v>46186</v>
       </c>
@@ -16975,7 +16974,7 @@
       <c r="R84" s="271" t="n"/>
       <c r="S84" s="271" t="n"/>
     </row>
-    <row r="85" ht="15" customHeight="1" s="243">
+    <row r="85" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A85" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17023,7 +17022,7 @@
       <c r="R85" s="271" t="n"/>
       <c r="S85" s="271" t="n"/>
     </row>
-    <row r="86" ht="15" customHeight="1" s="243">
+    <row r="86" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A86" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17059,7 +17058,7 @@
       <c r="R86" s="271" t="n"/>
       <c r="S86" s="271" t="n"/>
     </row>
-    <row r="87" ht="15" customHeight="1" s="243">
+    <row r="87" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A87" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17111,7 +17110,7 @@
       <c r="R87" s="271" t="n"/>
       <c r="S87" s="271" t="n"/>
     </row>
-    <row r="88" ht="15" customHeight="1" s="243">
+    <row r="88" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A88" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17195,7 +17194,7 @@
       <c r="R89" s="271" t="n"/>
       <c r="S89" s="271" t="n"/>
     </row>
-    <row r="90" ht="15" customHeight="1" s="243">
+    <row r="90" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A90" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17245,7 +17244,7 @@
       <c r="R90" s="271" t="n"/>
       <c r="S90" s="271" t="n"/>
     </row>
-    <row r="91" ht="15" customHeight="1" s="243">
+    <row r="91" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A91" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17293,7 +17292,7 @@
       <c r="R91" s="271" t="n"/>
       <c r="S91" s="271" t="n"/>
     </row>
-    <row r="92" ht="15" customHeight="1" s="243">
+    <row r="92" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A92" s="274" t="n">
         <v>46186</v>
       </c>
@@ -17333,7 +17332,7 @@
       <c r="R92" s="271" t="n"/>
       <c r="S92" s="271" t="n"/>
     </row>
-    <row r="93" ht="15" customHeight="1" s="243">
+    <row r="93" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A93" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17369,7 +17368,7 @@
       <c r="R93" s="271" t="n"/>
       <c r="S93" s="271" t="n"/>
     </row>
-    <row r="94" ht="15" customHeight="1" s="243">
+    <row r="94" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A94" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17421,7 +17420,7 @@
       <c r="R94" s="271" t="n"/>
       <c r="S94" s="271" t="n"/>
     </row>
-    <row r="95" ht="15" customHeight="1" s="243">
+    <row r="95" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A95" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17457,7 +17456,7 @@
       <c r="R95" s="271" t="n"/>
       <c r="S95" s="271" t="n"/>
     </row>
-    <row r="96" ht="15" customHeight="1" s="243">
+    <row r="96" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A96" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17509,7 +17508,7 @@
       <c r="R96" s="271" t="n"/>
       <c r="S96" s="271" t="n"/>
     </row>
-    <row r="97" ht="15" customHeight="1" s="243">
+    <row r="97" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A97" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17613,7 +17612,7 @@
       <c r="R98" s="271" t="n"/>
       <c r="S98" s="271" t="n"/>
     </row>
-    <row r="99" ht="15" customHeight="1" s="243">
+    <row r="99" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A99" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17663,7 +17662,7 @@
       <c r="R99" s="271" t="n"/>
       <c r="S99" s="271" t="n"/>
     </row>
-    <row r="100" ht="15" customHeight="1" s="243">
+    <row r="100" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A100" s="274" t="n">
         <v>46188</v>
       </c>
@@ -17713,7 +17712,7 @@
       <c r="R100" s="271" t="n"/>
       <c r="S100" s="271" t="n"/>
     </row>
-    <row r="101" ht="15" customHeight="1" s="243">
+    <row r="101" hidden="1" ht="15" customHeight="1" s="243">
       <c r="A101" s="274" t="n">
         <v>46188</v>
       </c>
@@ -19710,7 +19709,18 @@
       <c r="J247" s="91" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R83"/>
+  <autoFilter ref="A2:R101">
+    <filterColumn colId="1" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="Press-06"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="25"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -38713,7 +38723,7 @@
   <cols>
     <col width="10" customWidth="1" style="243" min="1" max="1"/>
     <col width="15.28515625" customWidth="1" style="243" min="2" max="2"/>
-    <col width="33.140625" customWidth="1" style="243" min="3" max="3"/>
+    <col width="33.42578125" customWidth="1" style="243" min="3" max="3"/>
     <col width="6" customWidth="1" style="243" min="4" max="4"/>
     <col width="8.5703125" customWidth="1" style="67" min="5" max="5"/>
     <col width="8.85546875" customWidth="1" style="67" min="6" max="6"/>
@@ -38730,13 +38740,13 @@
           <t>Slugs Inventory — June 2026 MONTH TO DATE</t>
         </is>
       </c>
-      <c r="B1" s="238" t="n"/>
-      <c r="C1" s="238" t="n"/>
-      <c r="D1" s="238" t="n"/>
-      <c r="E1" s="238" t="n"/>
-      <c r="F1" s="238" t="n"/>
-      <c r="G1" s="238" t="n"/>
-      <c r="H1" s="238" t="n"/>
+      <c r="B1" s="231" t="n"/>
+      <c r="C1" s="231" t="n"/>
+      <c r="D1" s="231" t="n"/>
+      <c r="E1" s="231" t="n"/>
+      <c r="F1" s="231" t="n"/>
+      <c r="G1" s="231" t="n"/>
+      <c r="H1" s="231" t="n"/>
       <c r="I1" s="69" t="inlineStr">
         <is>
           <t>Date:</t>
@@ -53102,7 +53112,7 @@
         </is>
       </c>
     </row>
-    <row r="8" customFormat="1" s="252">
+    <row r="8" customFormat="1" s="253">
       <c r="A8" s="127" t="inlineStr">
         <is>
           <t>2</t>
@@ -53134,7 +53144,7 @@
         </is>
       </c>
     </row>
-    <row r="9" customFormat="1" s="252">
+    <row r="9" customFormat="1" s="253">
       <c r="A9" s="126" t="inlineStr">
         <is>
           <t>3</t>
@@ -53166,7 +53176,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customFormat="1" customHeight="1" s="252">
+    <row r="10" ht="24" customFormat="1" customHeight="1" s="253">
       <c r="A10" s="106" t="n"/>
       <c r="B10" s="107" t="inlineStr">
         <is>
@@ -53306,7 +53316,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customFormat="1" customHeight="1" s="252">
+    <row r="15" ht="24" customFormat="1" customHeight="1" s="253">
       <c r="A15" s="126" t="inlineStr">
         <is>
           <t>4</t>
@@ -53366,7 +53376,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="8.1" customFormat="1" customHeight="1" s="252">
+    <row r="17" ht="8.1" customFormat="1" customHeight="1" s="253">
       <c r="A17" s="128" t="n"/>
       <c r="B17" s="129" t="n"/>
       <c r="C17" s="129" t="n"/>
@@ -53374,21 +53384,21 @@
       <c r="E17" s="125" t="n"/>
       <c r="F17" s="125" t="n"/>
     </row>
-    <row r="18" ht="15.95" customFormat="1" customHeight="1" s="252">
+    <row r="18" ht="15.95" customFormat="1" customHeight="1" s="253">
       <c r="A18" s="269" t="inlineStr">
         <is>
           <t>Individual scripts: update_production.py also runs sort_dashboard automatically at the end.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.95" customFormat="1" customHeight="1" s="252">
+    <row r="19" ht="15.95" customFormat="1" customHeight="1" s="253">
       <c r="A19" s="269" t="inlineStr">
         <is>
           <t>Safety: All scripts check if Excel file is open (lock guard) and warn if source files are stale (&gt;26 hours).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.95" customFormat="1" customHeight="1" s="252">
+    <row r="20" ht="15.95" customFormat="1" customHeight="1" s="253">
       <c r="A20" s="269" t="inlineStr">
         <is>
           <t>Logging: All output saved to Logs/ folder with timestamps. Mismatches logged to Logs/mismatches.log.</t>
@@ -55872,8 +55882,8 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
   </mergeCells>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -816,7 +816,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1598,6 +1598,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51253,31 +51271,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="243">
-      <c r="A4" s="275" t="n">
+      <c r="A4" s="301" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="275" t="n">
+      <c r="B4" s="301" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="276" t="inlineStr">
+      <c r="C4" s="302" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="276" t="inlineStr">
+      <c r="D4" s="302" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="275" t="inlineStr">
+      <c r="E4" s="301" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="277" t="n">
+      <c r="F4" s="303" t="n">
         <v>18860</v>
       </c>
-      <c r="G4" s="275" t="inlineStr">
+      <c r="G4" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51293,31 +51311,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="243">
-      <c r="A5" s="275" t="n">
+      <c r="A5" s="301" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="275" t="n">
+      <c r="B5" s="301" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="276" t="inlineStr">
+      <c r="C5" s="302" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="276" t="inlineStr">
+      <c r="D5" s="302" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="275" t="inlineStr">
+      <c r="E5" s="301" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="277" t="n">
+      <c r="F5" s="303" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="275" t="inlineStr">
+      <c r="G5" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51333,31 +51351,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="243">
-      <c r="A6" s="275" t="n">
+      <c r="A6" s="301" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="275" t="n">
+      <c r="B6" s="301" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="276" t="inlineStr">
+      <c r="C6" s="302" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="276" t="inlineStr">
+      <c r="D6" s="302" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="275" t="inlineStr">
+      <c r="E6" s="301" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="277" t="n">
+      <c r="F6" s="303" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="275" t="inlineStr">
+      <c r="G6" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51373,31 +51391,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="243">
-      <c r="A7" s="275" t="n">
+      <c r="A7" s="301" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="275" t="n">
+      <c r="B7" s="301" t="n">
         <v>5389</v>
       </c>
-      <c r="C7" s="276" t="inlineStr">
+      <c r="C7" s="302" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="276" t="inlineStr">
+      <c r="D7" s="302" t="inlineStr">
         <is>
           <t>S-45</t>
         </is>
       </c>
-      <c r="E7" s="275" t="inlineStr">
+      <c r="E7" s="301" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="277" t="n">
+      <c r="F7" s="303" t="n">
         <v>11088</v>
       </c>
-      <c r="G7" s="275" t="inlineStr">
+      <c r="G7" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51413,31 +51431,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="243">
-      <c r="A8" s="275" t="n">
+      <c r="A8" s="301" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="275" t="n">
+      <c r="B8" s="301" t="n">
         <v>4050</v>
       </c>
-      <c r="C8" s="276" t="inlineStr">
+      <c r="C8" s="302" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D8" s="276" t="inlineStr">
+      <c r="D8" s="302" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E8" s="275" t="inlineStr">
+      <c r="E8" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="277" t="n">
+      <c r="F8" s="303" t="n">
         <v>9450</v>
       </c>
-      <c r="G8" s="275" t="inlineStr">
+      <c r="G8" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51453,31 +51471,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="243">
-      <c r="A9" s="275" t="n">
+      <c r="A9" s="301" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="275" t="n">
+      <c r="B9" s="301" t="n">
         <v>6337</v>
       </c>
-      <c r="C9" s="276" t="inlineStr">
+      <c r="C9" s="302" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="276" t="inlineStr">
+      <c r="D9" s="302" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="275" t="inlineStr">
+      <c r="E9" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="277" t="n">
+      <c r="F9" s="303" t="n">
         <v>15680</v>
       </c>
-      <c r="G9" s="275" t="inlineStr">
+      <c r="G9" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51493,31 +51511,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="243">
-      <c r="A10" s="275" t="n">
+      <c r="A10" s="301" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="275" t="n">
+      <c r="B10" s="301" t="n">
         <v>6416</v>
       </c>
-      <c r="C10" s="276" t="inlineStr">
+      <c r="C10" s="302" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D10" s="276" t="inlineStr">
+      <c r="D10" s="302" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E10" s="275" t="inlineStr">
+      <c r="E10" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="277" t="n">
+      <c r="F10" s="303" t="n">
         <v>15435</v>
       </c>
-      <c r="G10" s="275" t="inlineStr">
+      <c r="G10" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51533,31 +51551,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="243">
-      <c r="A11" s="275" t="n">
+      <c r="A11" s="301" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="275" t="n">
+      <c r="B11" s="301" t="n">
         <v>5782</v>
       </c>
-      <c r="C11" s="276" t="inlineStr">
+      <c r="C11" s="302" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D11" s="276" t="inlineStr">
+      <c r="D11" s="302" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E11" s="275" t="inlineStr">
+      <c r="E11" s="301" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F11" s="277" t="n">
+      <c r="F11" s="303" t="n">
         <v>63648</v>
       </c>
-      <c r="G11" s="275" t="inlineStr">
+      <c r="G11" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51573,31 +51591,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="243">
-      <c r="A12" s="275" t="n">
+      <c r="A12" s="301" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="275" t="n">
+      <c r="B12" s="301" t="n">
         <v>6531</v>
       </c>
-      <c r="C12" s="276" t="inlineStr">
+      <c r="C12" s="302" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D12" s="276" t="inlineStr">
+      <c r="D12" s="302" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E12" s="275" t="inlineStr">
+      <c r="E12" s="301" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F12" s="277" t="n">
+      <c r="F12" s="303" t="n">
         <v>4380</v>
       </c>
-      <c r="G12" s="275" t="inlineStr">
+      <c r="G12" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51613,31 +51631,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="243">
-      <c r="A13" s="275" t="n">
+      <c r="A13" s="301" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="275" t="n">
+      <c r="B13" s="301" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="276" t="inlineStr">
+      <c r="C13" s="302" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="276" t="inlineStr">
+      <c r="D13" s="302" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="275" t="inlineStr">
+      <c r="E13" s="301" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="277" t="n">
+      <c r="F13" s="303" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="275" t="inlineStr">
+      <c r="G13" s="301" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51653,31 +51671,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="243">
-      <c r="A14" s="279" t="n">
+      <c r="A14" s="304" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="279" t="n">
+      <c r="B14" s="304" t="n">
         <v>6515</v>
       </c>
-      <c r="C14" s="280" t="inlineStr">
+      <c r="C14" s="305" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="280" t="inlineStr">
+      <c r="D14" s="305" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E14" s="279" t="inlineStr">
+      <c r="E14" s="304" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F14" s="281" t="n">
+      <c r="F14" s="306" t="n">
         <v>38896</v>
       </c>
-      <c r="G14" s="279" t="inlineStr">
+      <c r="G14" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51693,31 +51711,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="243">
-      <c r="A15" s="279" t="n">
+      <c r="A15" s="304" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="279" t="n">
+      <c r="B15" s="304" t="n">
         <v>6530</v>
       </c>
-      <c r="C15" s="280" t="inlineStr">
+      <c r="C15" s="305" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D15" s="280" t="inlineStr">
+      <c r="D15" s="305" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E15" s="279" t="inlineStr">
+      <c r="E15" s="304" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F15" s="281" t="n">
+      <c r="F15" s="306" t="n">
         <v>15000</v>
       </c>
-      <c r="G15" s="279" t="inlineStr">
+      <c r="G15" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51733,31 +51751,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="243">
-      <c r="A16" s="279" t="n">
+      <c r="A16" s="304" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="279" t="n">
+      <c r="B16" s="304" t="n">
         <v>5782</v>
       </c>
-      <c r="C16" s="280" t="inlineStr">
+      <c r="C16" s="305" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D16" s="280" t="inlineStr">
+      <c r="D16" s="305" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E16" s="279" t="inlineStr">
+      <c r="E16" s="304" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="281" t="n">
+      <c r="F16" s="306" t="n">
         <v>10500</v>
       </c>
-      <c r="G16" s="279" t="inlineStr">
+      <c r="G16" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51773,31 +51791,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="243">
-      <c r="A17" s="279" t="n">
+      <c r="A17" s="304" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="279" t="n">
+      <c r="B17" s="304" t="n">
         <v>6624</v>
       </c>
-      <c r="C17" s="280" t="inlineStr">
+      <c r="C17" s="305" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D17" s="280" t="inlineStr">
+      <c r="D17" s="305" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E17" s="279" t="inlineStr">
+      <c r="E17" s="304" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F17" s="281" t="n">
+      <c r="F17" s="306" t="n">
         <v>15288</v>
       </c>
-      <c r="G17" s="279" t="inlineStr">
+      <c r="G17" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51813,31 +51831,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="243">
-      <c r="A18" s="279" t="n">
+      <c r="A18" s="304" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="279" t="n">
+      <c r="B18" s="304" t="n">
         <v>5731</v>
       </c>
-      <c r="C18" s="280" t="inlineStr">
+      <c r="C18" s="305" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="280" t="inlineStr">
+      <c r="D18" s="305" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E18" s="279" t="inlineStr">
+      <c r="E18" s="304" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F18" s="281" t="n">
+      <c r="F18" s="306" t="n">
         <v>37030</v>
       </c>
-      <c r="G18" s="279" t="inlineStr">
+      <c r="G18" s="304" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -816,7 +816,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1616,6 +1616,24 @@
     <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51271,31 +51289,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="243">
-      <c r="A4" s="301" t="n">
+      <c r="A4" s="307" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="301" t="n">
+      <c r="B4" s="307" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="302" t="inlineStr">
+      <c r="C4" s="308" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="302" t="inlineStr">
+      <c r="D4" s="308" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="301" t="inlineStr">
+      <c r="E4" s="307" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="303" t="n">
+      <c r="F4" s="309" t="n">
         <v>18860</v>
       </c>
-      <c r="G4" s="301" t="inlineStr">
+      <c r="G4" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51311,31 +51329,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="243">
-      <c r="A5" s="301" t="n">
+      <c r="A5" s="307" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="301" t="n">
+      <c r="B5" s="307" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="302" t="inlineStr">
+      <c r="C5" s="308" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="302" t="inlineStr">
+      <c r="D5" s="308" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="301" t="inlineStr">
+      <c r="E5" s="307" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="303" t="n">
+      <c r="F5" s="309" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="301" t="inlineStr">
+      <c r="G5" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51351,31 +51369,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="243">
-      <c r="A6" s="301" t="n">
+      <c r="A6" s="307" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="301" t="n">
+      <c r="B6" s="307" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="302" t="inlineStr">
+      <c r="C6" s="308" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="302" t="inlineStr">
+      <c r="D6" s="308" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="301" t="inlineStr">
+      <c r="E6" s="307" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="303" t="n">
+      <c r="F6" s="309" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="301" t="inlineStr">
+      <c r="G6" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51391,31 +51409,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="243">
-      <c r="A7" s="301" t="n">
+      <c r="A7" s="307" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="301" t="n">
+      <c r="B7" s="307" t="n">
         <v>5389</v>
       </c>
-      <c r="C7" s="302" t="inlineStr">
+      <c r="C7" s="308" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="302" t="inlineStr">
+      <c r="D7" s="308" t="inlineStr">
         <is>
           <t>S-45</t>
         </is>
       </c>
-      <c r="E7" s="301" t="inlineStr">
+      <c r="E7" s="307" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="303" t="n">
+      <c r="F7" s="309" t="n">
         <v>11088</v>
       </c>
-      <c r="G7" s="301" t="inlineStr">
+      <c r="G7" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51431,31 +51449,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="243">
-      <c r="A8" s="301" t="n">
+      <c r="A8" s="307" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="301" t="n">
+      <c r="B8" s="307" t="n">
         <v>4050</v>
       </c>
-      <c r="C8" s="302" t="inlineStr">
+      <c r="C8" s="308" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D8" s="302" t="inlineStr">
+      <c r="D8" s="308" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E8" s="301" t="inlineStr">
+      <c r="E8" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="303" t="n">
+      <c r="F8" s="309" t="n">
         <v>9450</v>
       </c>
-      <c r="G8" s="301" t="inlineStr">
+      <c r="G8" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51471,31 +51489,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="243">
-      <c r="A9" s="301" t="n">
+      <c r="A9" s="307" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="301" t="n">
+      <c r="B9" s="307" t="n">
         <v>6337</v>
       </c>
-      <c r="C9" s="302" t="inlineStr">
+      <c r="C9" s="308" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="302" t="inlineStr">
+      <c r="D9" s="308" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="301" t="inlineStr">
+      <c r="E9" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="303" t="n">
+      <c r="F9" s="309" t="n">
         <v>15680</v>
       </c>
-      <c r="G9" s="301" t="inlineStr">
+      <c r="G9" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51511,31 +51529,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="243">
-      <c r="A10" s="301" t="n">
+      <c r="A10" s="307" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="301" t="n">
+      <c r="B10" s="307" t="n">
         <v>6416</v>
       </c>
-      <c r="C10" s="302" t="inlineStr">
+      <c r="C10" s="308" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D10" s="302" t="inlineStr">
+      <c r="D10" s="308" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E10" s="301" t="inlineStr">
+      <c r="E10" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="303" t="n">
+      <c r="F10" s="309" t="n">
         <v>15435</v>
       </c>
-      <c r="G10" s="301" t="inlineStr">
+      <c r="G10" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51551,31 +51569,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="243">
-      <c r="A11" s="301" t="n">
+      <c r="A11" s="307" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="301" t="n">
+      <c r="B11" s="307" t="n">
         <v>5782</v>
       </c>
-      <c r="C11" s="302" t="inlineStr">
+      <c r="C11" s="308" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D11" s="302" t="inlineStr">
+      <c r="D11" s="308" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E11" s="301" t="inlineStr">
+      <c r="E11" s="307" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F11" s="303" t="n">
+      <c r="F11" s="309" t="n">
         <v>63648</v>
       </c>
-      <c r="G11" s="301" t="inlineStr">
+      <c r="G11" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51591,31 +51609,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="243">
-      <c r="A12" s="301" t="n">
+      <c r="A12" s="307" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="301" t="n">
+      <c r="B12" s="307" t="n">
         <v>6531</v>
       </c>
-      <c r="C12" s="302" t="inlineStr">
+      <c r="C12" s="308" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D12" s="302" t="inlineStr">
+      <c r="D12" s="308" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E12" s="301" t="inlineStr">
+      <c r="E12" s="307" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F12" s="303" t="n">
+      <c r="F12" s="309" t="n">
         <v>4380</v>
       </c>
-      <c r="G12" s="301" t="inlineStr">
+      <c r="G12" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51631,31 +51649,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="243">
-      <c r="A13" s="301" t="n">
+      <c r="A13" s="307" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="301" t="n">
+      <c r="B13" s="307" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="302" t="inlineStr">
+      <c r="C13" s="308" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="302" t="inlineStr">
+      <c r="D13" s="308" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="301" t="inlineStr">
+      <c r="E13" s="307" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="303" t="n">
+      <c r="F13" s="309" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="301" t="inlineStr">
+      <c r="G13" s="307" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51671,31 +51689,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="243">
-      <c r="A14" s="304" t="n">
+      <c r="A14" s="310" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="304" t="n">
+      <c r="B14" s="310" t="n">
         <v>6515</v>
       </c>
-      <c r="C14" s="305" t="inlineStr">
+      <c r="C14" s="311" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="305" t="inlineStr">
+      <c r="D14" s="311" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E14" s="304" t="inlineStr">
+      <c r="E14" s="310" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F14" s="306" t="n">
+      <c r="F14" s="312" t="n">
         <v>38896</v>
       </c>
-      <c r="G14" s="304" t="inlineStr">
+      <c r="G14" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51711,31 +51729,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="243">
-      <c r="A15" s="304" t="n">
+      <c r="A15" s="310" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="304" t="n">
+      <c r="B15" s="310" t="n">
         <v>6530</v>
       </c>
-      <c r="C15" s="305" t="inlineStr">
+      <c r="C15" s="311" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D15" s="305" t="inlineStr">
+      <c r="D15" s="311" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E15" s="304" t="inlineStr">
+      <c r="E15" s="310" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F15" s="306" t="n">
+      <c r="F15" s="312" t="n">
         <v>15000</v>
       </c>
-      <c r="G15" s="304" t="inlineStr">
+      <c r="G15" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51751,31 +51769,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="243">
-      <c r="A16" s="304" t="n">
+      <c r="A16" s="310" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="304" t="n">
+      <c r="B16" s="310" t="n">
         <v>5782</v>
       </c>
-      <c r="C16" s="305" t="inlineStr">
+      <c r="C16" s="311" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D16" s="305" t="inlineStr">
+      <c r="D16" s="311" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E16" s="304" t="inlineStr">
+      <c r="E16" s="310" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="306" t="n">
+      <c r="F16" s="312" t="n">
         <v>10500</v>
       </c>
-      <c r="G16" s="304" t="inlineStr">
+      <c r="G16" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51791,31 +51809,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="243">
-      <c r="A17" s="304" t="n">
+      <c r="A17" s="310" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="304" t="n">
+      <c r="B17" s="310" t="n">
         <v>6624</v>
       </c>
-      <c r="C17" s="305" t="inlineStr">
+      <c r="C17" s="311" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D17" s="305" t="inlineStr">
+      <c r="D17" s="311" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E17" s="304" t="inlineStr">
+      <c r="E17" s="310" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F17" s="306" t="n">
+      <c r="F17" s="312" t="n">
         <v>15288</v>
       </c>
-      <c r="G17" s="304" t="inlineStr">
+      <c r="G17" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51831,31 +51849,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="243">
-      <c r="A18" s="304" t="n">
+      <c r="A18" s="310" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="304" t="n">
+      <c r="B18" s="310" t="n">
         <v>5731</v>
       </c>
-      <c r="C18" s="305" t="inlineStr">
+      <c r="C18" s="311" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="305" t="inlineStr">
+      <c r="D18" s="311" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E18" s="304" t="inlineStr">
+      <c r="E18" s="310" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F18" s="306" t="n">
+      <c r="F18" s="312" t="n">
         <v>37030</v>
       </c>
-      <c r="G18" s="304" t="inlineStr">
+      <c r="G18" s="310" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -816,7 +816,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="313">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1634,6 +1634,24 @@
     <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51289,31 +51307,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="243">
-      <c r="A4" s="307" t="n">
+      <c r="A4" s="313" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="307" t="n">
+      <c r="B4" s="313" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="308" t="inlineStr">
+      <c r="C4" s="314" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="308" t="inlineStr">
+      <c r="D4" s="314" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="307" t="inlineStr">
+      <c r="E4" s="313" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="309" t="n">
+      <c r="F4" s="315" t="n">
         <v>18860</v>
       </c>
-      <c r="G4" s="307" t="inlineStr">
+      <c r="G4" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51329,31 +51347,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="243">
-      <c r="A5" s="307" t="n">
+      <c r="A5" s="313" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="307" t="n">
+      <c r="B5" s="313" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="308" t="inlineStr">
+      <c r="C5" s="314" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="308" t="inlineStr">
+      <c r="D5" s="314" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="307" t="inlineStr">
+      <c r="E5" s="313" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="309" t="n">
+      <c r="F5" s="315" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="307" t="inlineStr">
+      <c r="G5" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51369,31 +51387,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="243">
-      <c r="A6" s="307" t="n">
+      <c r="A6" s="313" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="307" t="n">
+      <c r="B6" s="313" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="308" t="inlineStr">
+      <c r="C6" s="314" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="308" t="inlineStr">
+      <c r="D6" s="314" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="307" t="inlineStr">
+      <c r="E6" s="313" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="309" t="n">
+      <c r="F6" s="315" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="307" t="inlineStr">
+      <c r="G6" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51409,31 +51427,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="243">
-      <c r="A7" s="307" t="n">
+      <c r="A7" s="313" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="307" t="n">
+      <c r="B7" s="313" t="n">
         <v>5389</v>
       </c>
-      <c r="C7" s="308" t="inlineStr">
+      <c r="C7" s="314" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="308" t="inlineStr">
+      <c r="D7" s="314" t="inlineStr">
         <is>
           <t>S-45</t>
         </is>
       </c>
-      <c r="E7" s="307" t="inlineStr">
+      <c r="E7" s="313" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="309" t="n">
+      <c r="F7" s="315" t="n">
         <v>11088</v>
       </c>
-      <c r="G7" s="307" t="inlineStr">
+      <c r="G7" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51449,31 +51467,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="243">
-      <c r="A8" s="307" t="n">
+      <c r="A8" s="313" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="307" t="n">
+      <c r="B8" s="313" t="n">
         <v>4050</v>
       </c>
-      <c r="C8" s="308" t="inlineStr">
+      <c r="C8" s="314" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D8" s="308" t="inlineStr">
+      <c r="D8" s="314" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E8" s="307" t="inlineStr">
+      <c r="E8" s="313" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="309" t="n">
+      <c r="F8" s="315" t="n">
         <v>9450</v>
       </c>
-      <c r="G8" s="307" t="inlineStr">
+      <c r="G8" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51489,31 +51507,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="243">
-      <c r="A9" s="307" t="n">
+      <c r="A9" s="313" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="307" t="n">
+      <c r="B9" s="313" t="n">
         <v>6337</v>
       </c>
-      <c r="C9" s="308" t="inlineStr">
+      <c r="C9" s="314" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="308" t="inlineStr">
+      <c r="D9" s="314" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="307" t="inlineStr">
+      <c r="E9" s="313" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="309" t="n">
+      <c r="F9" s="315" t="n">
         <v>15680</v>
       </c>
-      <c r="G9" s="307" t="inlineStr">
+      <c r="G9" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51529,31 +51547,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="243">
-      <c r="A10" s="307" t="n">
+      <c r="A10" s="313" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="307" t="n">
+      <c r="B10" s="313" t="n">
         <v>6416</v>
       </c>
-      <c r="C10" s="308" t="inlineStr">
+      <c r="C10" s="314" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D10" s="308" t="inlineStr">
+      <c r="D10" s="314" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E10" s="307" t="inlineStr">
+      <c r="E10" s="313" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="309" t="n">
+      <c r="F10" s="315" t="n">
         <v>15435</v>
       </c>
-      <c r="G10" s="307" t="inlineStr">
+      <c r="G10" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51569,31 +51587,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="243">
-      <c r="A11" s="307" t="n">
+      <c r="A11" s="313" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="307" t="n">
+      <c r="B11" s="313" t="n">
         <v>5782</v>
       </c>
-      <c r="C11" s="308" t="inlineStr">
+      <c r="C11" s="314" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D11" s="308" t="inlineStr">
+      <c r="D11" s="314" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E11" s="307" t="inlineStr">
+      <c r="E11" s="313" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F11" s="309" t="n">
+      <c r="F11" s="315" t="n">
         <v>63648</v>
       </c>
-      <c r="G11" s="307" t="inlineStr">
+      <c r="G11" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51609,31 +51627,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="243">
-      <c r="A12" s="307" t="n">
+      <c r="A12" s="313" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="307" t="n">
+      <c r="B12" s="313" t="n">
         <v>6531</v>
       </c>
-      <c r="C12" s="308" t="inlineStr">
+      <c r="C12" s="314" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D12" s="308" t="inlineStr">
+      <c r="D12" s="314" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E12" s="307" t="inlineStr">
+      <c r="E12" s="313" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F12" s="309" t="n">
+      <c r="F12" s="315" t="n">
         <v>4380</v>
       </c>
-      <c r="G12" s="307" t="inlineStr">
+      <c r="G12" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51649,31 +51667,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="243">
-      <c r="A13" s="307" t="n">
+      <c r="A13" s="313" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="307" t="n">
+      <c r="B13" s="313" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="308" t="inlineStr">
+      <c r="C13" s="314" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="308" t="inlineStr">
+      <c r="D13" s="314" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="307" t="inlineStr">
+      <c r="E13" s="313" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="309" t="n">
+      <c r="F13" s="315" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="307" t="inlineStr">
+      <c r="G13" s="313" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51689,31 +51707,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="243">
-      <c r="A14" s="310" t="n">
+      <c r="A14" s="316" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="310" t="n">
+      <c r="B14" s="316" t="n">
         <v>6515</v>
       </c>
-      <c r="C14" s="311" t="inlineStr">
+      <c r="C14" s="317" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="311" t="inlineStr">
+      <c r="D14" s="317" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E14" s="310" t="inlineStr">
+      <c r="E14" s="316" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F14" s="312" t="n">
+      <c r="F14" s="318" t="n">
         <v>38896</v>
       </c>
-      <c r="G14" s="310" t="inlineStr">
+      <c r="G14" s="316" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51729,31 +51747,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="243">
-      <c r="A15" s="310" t="n">
+      <c r="A15" s="316" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="310" t="n">
+      <c r="B15" s="316" t="n">
         <v>6530</v>
       </c>
-      <c r="C15" s="311" t="inlineStr">
+      <c r="C15" s="317" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D15" s="311" t="inlineStr">
+      <c r="D15" s="317" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E15" s="310" t="inlineStr">
+      <c r="E15" s="316" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F15" s="312" t="n">
+      <c r="F15" s="318" t="n">
         <v>15000</v>
       </c>
-      <c r="G15" s="310" t="inlineStr">
+      <c r="G15" s="316" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51769,31 +51787,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="243">
-      <c r="A16" s="310" t="n">
+      <c r="A16" s="316" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="310" t="n">
+      <c r="B16" s="316" t="n">
         <v>5782</v>
       </c>
-      <c r="C16" s="311" t="inlineStr">
+      <c r="C16" s="317" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D16" s="311" t="inlineStr">
+      <c r="D16" s="317" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E16" s="310" t="inlineStr">
+      <c r="E16" s="316" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="312" t="n">
+      <c r="F16" s="318" t="n">
         <v>10500</v>
       </c>
-      <c r="G16" s="310" t="inlineStr">
+      <c r="G16" s="316" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51809,31 +51827,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="243">
-      <c r="A17" s="310" t="n">
+      <c r="A17" s="316" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="310" t="n">
+      <c r="B17" s="316" t="n">
         <v>6624</v>
       </c>
-      <c r="C17" s="311" t="inlineStr">
+      <c r="C17" s="317" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D17" s="311" t="inlineStr">
+      <c r="D17" s="317" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E17" s="310" t="inlineStr">
+      <c r="E17" s="316" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F17" s="312" t="n">
+      <c r="F17" s="318" t="n">
         <v>15288</v>
       </c>
-      <c r="G17" s="310" t="inlineStr">
+      <c r="G17" s="316" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51849,31 +51867,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="243">
-      <c r="A18" s="310" t="n">
+      <c r="A18" s="316" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="310" t="n">
+      <c r="B18" s="316" t="n">
         <v>5731</v>
       </c>
-      <c r="C18" s="311" t="inlineStr">
+      <c r="C18" s="317" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="311" t="inlineStr">
+      <c r="D18" s="317" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E18" s="310" t="inlineStr">
+      <c r="E18" s="316" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F18" s="312" t="n">
+      <c r="F18" s="318" t="n">
         <v>37030</v>
       </c>
-      <c r="G18" s="310" t="inlineStr">
+      <c r="G18" s="316" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -816,7 +816,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="21"/>
     <xf numFmtId="43" fontId="24" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="325">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1652,6 +1652,24 @@
     <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="10" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51307,31 +51325,31 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="243">
-      <c r="A4" s="313" t="n">
+      <c r="A4" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="313" t="n">
+      <c r="B4" s="319" t="n">
         <v>8001</v>
       </c>
-      <c r="C4" s="314" t="inlineStr">
+      <c r="C4" s="320" t="inlineStr">
         <is>
           <t>Alpha Labs PVT LTD</t>
         </is>
       </c>
-      <c r="D4" s="314" t="inlineStr">
+      <c r="D4" s="320" t="inlineStr">
         <is>
           <t>TRANSPARENT BOTTLE 150ML</t>
         </is>
       </c>
-      <c r="E4" s="313" t="inlineStr">
+      <c r="E4" s="319" t="inlineStr">
         <is>
           <t>150ml</t>
         </is>
       </c>
-      <c r="F4" s="315" t="n">
+      <c r="F4" s="321" t="n">
         <v>18860</v>
       </c>
-      <c r="G4" s="313" t="inlineStr">
+      <c r="G4" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51347,31 +51365,31 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="243">
-      <c r="A5" s="313" t="n">
+      <c r="A5" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="313" t="n">
+      <c r="B5" s="319" t="n">
         <v>5699</v>
       </c>
-      <c r="C5" s="314" t="inlineStr">
+      <c r="C5" s="320" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D5" s="314" t="inlineStr">
+      <c r="D5" s="320" t="inlineStr">
         <is>
           <t>S-43 DIA 20.5</t>
         </is>
       </c>
-      <c r="E5" s="313" t="inlineStr">
+      <c r="E5" s="319" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F5" s="315" t="n">
+      <c r="F5" s="321" t="n">
         <v>14790</v>
       </c>
-      <c r="G5" s="313" t="inlineStr">
+      <c r="G5" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51387,31 +51405,31 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="243">
-      <c r="A6" s="313" t="n">
+      <c r="A6" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="313" t="n">
+      <c r="B6" s="319" t="n">
         <v>5731</v>
       </c>
-      <c r="C6" s="314" t="inlineStr">
+      <c r="C6" s="320" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D6" s="314" t="inlineStr">
+      <c r="D6" s="320" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E6" s="313" t="inlineStr">
+      <c r="E6" s="319" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F6" s="315" t="n">
+      <c r="F6" s="321" t="n">
         <v>13770</v>
       </c>
-      <c r="G6" s="313" t="inlineStr">
+      <c r="G6" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51427,31 +51445,31 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="243">
-      <c r="A7" s="313" t="n">
+      <c r="A7" s="319" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="313" t="n">
+      <c r="B7" s="319" t="n">
         <v>5389</v>
       </c>
-      <c r="C7" s="314" t="inlineStr">
+      <c r="C7" s="320" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="314" t="inlineStr">
+      <c r="D7" s="320" t="inlineStr">
         <is>
           <t>S-45</t>
         </is>
       </c>
-      <c r="E7" s="313" t="inlineStr">
+      <c r="E7" s="319" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="315" t="n">
+      <c r="F7" s="321" t="n">
         <v>11088</v>
       </c>
-      <c r="G7" s="313" t="inlineStr">
+      <c r="G7" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51467,31 +51485,31 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="243">
-      <c r="A8" s="313" t="n">
+      <c r="A8" s="319" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="313" t="n">
+      <c r="B8" s="319" t="n">
         <v>4050</v>
       </c>
-      <c r="C8" s="314" t="inlineStr">
+      <c r="C8" s="320" t="inlineStr">
         <is>
           <t>Professional Beauty Solution (PVT) LTD.Pakistan</t>
         </is>
       </c>
-      <c r="D8" s="314" t="inlineStr">
+      <c r="D8" s="320" t="inlineStr">
         <is>
           <t>EAZICOLOR PREMIUM HAIR COLOUR 60ML</t>
         </is>
       </c>
-      <c r="E8" s="313" t="inlineStr">
+      <c r="E8" s="319" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="315" t="n">
+      <c r="F8" s="321" t="n">
         <v>9450</v>
       </c>
-      <c r="G8" s="313" t="inlineStr">
+      <c r="G8" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51507,31 +51525,31 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="243">
-      <c r="A9" s="313" t="n">
+      <c r="A9" s="319" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="313" t="n">
+      <c r="B9" s="319" t="n">
         <v>6337</v>
       </c>
-      <c r="C9" s="314" t="inlineStr">
+      <c r="C9" s="320" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D9" s="314" t="inlineStr">
+      <c r="D9" s="320" t="inlineStr">
         <is>
           <t>ACTIVE PRO HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E9" s="313" t="inlineStr">
+      <c r="E9" s="319" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F9" s="315" t="n">
+      <c r="F9" s="321" t="n">
         <v>15680</v>
       </c>
-      <c r="G9" s="313" t="inlineStr">
+      <c r="G9" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51547,31 +51565,31 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="243">
-      <c r="A10" s="313" t="n">
+      <c r="A10" s="319" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="313" t="n">
+      <c r="B10" s="319" t="n">
         <v>6416</v>
       </c>
-      <c r="C10" s="314" t="inlineStr">
+      <c r="C10" s="320" t="inlineStr">
         <is>
           <t>Al-Rehman Group</t>
         </is>
       </c>
-      <c r="D10" s="314" t="inlineStr">
+      <c r="D10" s="320" t="inlineStr">
         <is>
           <t>SIGNATURE HAIR COLOR CREAM 60ML</t>
         </is>
       </c>
-      <c r="E10" s="313" t="inlineStr">
+      <c r="E10" s="319" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="315" t="n">
+      <c r="F10" s="321" t="n">
         <v>15435</v>
       </c>
-      <c r="G10" s="313" t="inlineStr">
+      <c r="G10" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51587,31 +51605,31 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="243">
-      <c r="A11" s="313" t="n">
+      <c r="A11" s="319" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="313" t="n">
+      <c r="B11" s="319" t="n">
         <v>5782</v>
       </c>
-      <c r="C11" s="314" t="inlineStr">
+      <c r="C11" s="320" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D11" s="314" t="inlineStr">
+      <c r="D11" s="320" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E11" s="313" t="inlineStr">
+      <c r="E11" s="319" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F11" s="315" t="n">
+      <c r="F11" s="321" t="n">
         <v>63648</v>
       </c>
-      <c r="G11" s="313" t="inlineStr">
+      <c r="G11" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51627,31 +51645,31 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="243">
-      <c r="A12" s="313" t="n">
+      <c r="A12" s="319" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="313" t="n">
+      <c r="B12" s="319" t="n">
         <v>6531</v>
       </c>
-      <c r="C12" s="314" t="inlineStr">
+      <c r="C12" s="320" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D12" s="314" t="inlineStr">
+      <c r="D12" s="320" t="inlineStr">
         <is>
           <t>V-HC BLACK</t>
         </is>
       </c>
-      <c r="E12" s="313" t="inlineStr">
+      <c r="E12" s="319" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F12" s="315" t="n">
+      <c r="F12" s="321" t="n">
         <v>4380</v>
       </c>
-      <c r="G12" s="313" t="inlineStr">
+      <c r="G12" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51667,31 +51685,31 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="243">
-      <c r="A13" s="313" t="n">
+      <c r="A13" s="319" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="313" t="n">
+      <c r="B13" s="319" t="n">
         <v>6206</v>
       </c>
-      <c r="C13" s="314" t="inlineStr">
+      <c r="C13" s="320" t="inlineStr">
         <is>
           <t>Golden Pearl Cosmetics (PVT) LTD</t>
         </is>
       </c>
-      <c r="D13" s="314" t="inlineStr">
+      <c r="D13" s="320" t="inlineStr">
         <is>
           <t>HELLO HAIR COLOR</t>
         </is>
       </c>
-      <c r="E13" s="313" t="inlineStr">
+      <c r="E13" s="319" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="315" t="n">
+      <c r="F13" s="321" t="n">
         <v>100674</v>
       </c>
-      <c r="G13" s="313" t="inlineStr">
+      <c r="G13" s="319" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -51707,31 +51725,31 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="243">
-      <c r="A14" s="316" t="n">
+      <c r="A14" s="322" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="316" t="n">
+      <c r="B14" s="322" t="n">
         <v>6515</v>
       </c>
-      <c r="C14" s="317" t="inlineStr">
+      <c r="C14" s="323" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D14" s="317" t="inlineStr">
+      <c r="D14" s="323" t="inlineStr">
         <is>
           <t>H.H 100GM</t>
         </is>
       </c>
-      <c r="E14" s="316" t="inlineStr">
+      <c r="E14" s="322" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F14" s="318" t="n">
+      <c r="F14" s="324" t="n">
         <v>38896</v>
       </c>
-      <c r="G14" s="316" t="inlineStr">
+      <c r="G14" s="322" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51747,31 +51765,31 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="243">
-      <c r="A15" s="316" t="n">
+      <c r="A15" s="322" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="316" t="n">
+      <c r="B15" s="322" t="n">
         <v>6530</v>
       </c>
-      <c r="C15" s="317" t="inlineStr">
+      <c r="C15" s="323" t="inlineStr">
         <is>
           <t>Adore</t>
         </is>
       </c>
-      <c r="D15" s="317" t="inlineStr">
+      <c r="D15" s="323" t="inlineStr">
         <is>
           <t>V- HC BROWN</t>
         </is>
       </c>
-      <c r="E15" s="316" t="inlineStr">
+      <c r="E15" s="322" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F15" s="318" t="n">
+      <c r="F15" s="324" t="n">
         <v>15000</v>
       </c>
-      <c r="G15" s="316" t="inlineStr">
+      <c r="G15" s="322" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51787,31 +51805,31 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="243">
-      <c r="A16" s="316" t="n">
+      <c r="A16" s="322" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="316" t="n">
+      <c r="B16" s="322" t="n">
         <v>5782</v>
       </c>
-      <c r="C16" s="317" t="inlineStr">
+      <c r="C16" s="323" t="inlineStr">
         <is>
           <t>Mega Grey</t>
         </is>
       </c>
-      <c r="D16" s="317" t="inlineStr">
+      <c r="D16" s="323" t="inlineStr">
         <is>
           <t>M.G</t>
         </is>
       </c>
-      <c r="E16" s="316" t="inlineStr">
+      <c r="E16" s="322" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="318" t="n">
+      <c r="F16" s="324" t="n">
         <v>10500</v>
       </c>
-      <c r="G16" s="316" t="inlineStr">
+      <c r="G16" s="322" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51827,31 +51845,31 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="243">
-      <c r="A17" s="316" t="n">
+      <c r="A17" s="322" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="316" t="n">
+      <c r="B17" s="322" t="n">
         <v>6624</v>
       </c>
-      <c r="C17" s="317" t="inlineStr">
+      <c r="C17" s="323" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D17" s="317" t="inlineStr">
+      <c r="D17" s="323" t="inlineStr">
         <is>
           <t>S-45 DIA 19MM</t>
         </is>
       </c>
-      <c r="E17" s="316" t="inlineStr">
+      <c r="E17" s="322" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F17" s="318" t="n">
+      <c r="F17" s="324" t="n">
         <v>15288</v>
       </c>
-      <c r="G17" s="316" t="inlineStr">
+      <c r="G17" s="322" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
@@ -51867,31 +51885,31 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="243">
-      <c r="A18" s="316" t="n">
+      <c r="A18" s="322" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="316" t="n">
+      <c r="B18" s="322" t="n">
         <v>5731</v>
       </c>
-      <c r="C18" s="317" t="inlineStr">
+      <c r="C18" s="323" t="inlineStr">
         <is>
           <t>Samsol International Private Limited</t>
         </is>
       </c>
-      <c r="D18" s="317" t="inlineStr">
+      <c r="D18" s="323" t="inlineStr">
         <is>
           <t>SAMSOL HAIR COLOR 45 DIA 20.5 MM</t>
         </is>
       </c>
-      <c r="E18" s="316" t="inlineStr">
+      <c r="E18" s="322" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="F18" s="318" t="n">
+      <c r="F18" s="324" t="n">
         <v>37030</v>
       </c>
-      <c r="G18" s="316" t="inlineStr">
+      <c r="G18" s="322" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5A288000BF9E7B29E5898637B6F9489DE5310DD0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_D2E9F5EE007A181A118828C73443357FECF13C7C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4605" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="925">
   <si>
     <t>June 2026 Tube Required Orders</t>
   </si>
@@ -1907,7 +1907,7 @@
     <t>Top 10 inks = 81.7% of all consumption. Remaining 15 inks share 18.3%.  Source: ERP ST_Stk_Cons_YFI.rpt · May 2025–Apr 2026 · 8,617,293 pcs produced.</t>
   </si>
   <si>
-    <t>FG STOCK IN HAND — Last Updated: 15-Jun-2026</t>
+    <t>FG STOCK IN HAND — Last Updated: 17-Jun-2026</t>
   </si>
   <si>
     <t>Shows latest date only from FG Stock In hand (Production.xlsx). Older dates are discarded. Re-run update_production.py to refresh.</t>
@@ -1953,9 +1953,6 @@
   </si>
   <si>
     <t>35</t>
-  </si>
-  <si>
-    <t>No JOF</t>
   </si>
   <si>
     <t>Not Ready</t>
@@ -4206,25 +4203,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="36" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4234,6 +4218,19 @@
     <xf numFmtId="0" fontId="42" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4255,9 +4252,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4265,6 +4259,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4740,8 +4737,8 @@
     <col min="13" max="13" width="14.7109375" style="139" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="139" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="139" customWidth="1"/>
-    <col min="16" max="59" width="8.7109375" style="139" customWidth="1"/>
-    <col min="60" max="16384" width="8.7109375" style="139"/>
+    <col min="16" max="60" width="8.7109375" style="139" customWidth="1"/>
+    <col min="61" max="16384" width="8.7109375" style="139"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4776,22 +4773,22 @@
     </row>
     <row r="2" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="136"/>
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="238" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="233"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
       <c r="P2" s="136"/>
       <c r="Q2" s="136"/>
       <c r="R2" s="136"/>
@@ -4809,25 +4806,25 @@
     </row>
     <row r="3" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="136"/>
-      <c r="B3" s="238" t="s">
+      <c r="B3" s="230" t="s">
         <v>206</v>
       </c>
-      <c r="C3" s="233"/>
-      <c r="D3" s="233"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="240">
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="233"/>
+      <c r="H3" s="235">
         <f ca="1">TODAY()-1</f>
-        <v>46188</v>
-      </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
-      <c r="M3" s="233"/>
-      <c r="N3" s="233"/>
-      <c r="O3" s="233"/>
+        <v>46189</v>
+      </c>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="M3" s="231"/>
+      <c r="N3" s="231"/>
+      <c r="O3" s="231"/>
       <c r="P3" s="136"/>
       <c r="Q3" s="136"/>
       <c r="R3" s="136"/>
@@ -4875,24 +4872,24 @@
     </row>
     <row r="5" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="136"/>
-      <c r="B5" s="236" t="s">
+      <c r="B5" s="237" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="233"/>
+      <c r="C5" s="231"/>
       <c r="D5" s="141" t="s">
         <v>208</v>
       </c>
       <c r="E5" s="141"/>
       <c r="F5" s="142"/>
-      <c r="G5" s="236" t="s">
+      <c r="G5" s="237" t="s">
         <v>209</v>
       </c>
-      <c r="H5" s="233"/>
+      <c r="H5" s="231"/>
       <c r="I5" s="143"/>
-      <c r="J5" s="236" t="s">
+      <c r="J5" s="237" t="s">
         <v>210</v>
       </c>
-      <c r="K5" s="233"/>
+      <c r="K5" s="231"/>
       <c r="L5" s="175"/>
       <c r="M5" s="144" t="s">
         <v>211</v>
@@ -4916,28 +4913,28 @@
     </row>
     <row r="6" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="136"/>
-      <c r="B6" s="239">
+      <c r="B6" s="234">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>19152</v>
-      </c>
-      <c r="C6" s="233"/>
+        <v>20832</v>
+      </c>
+      <c r="C6" s="231"/>
       <c r="D6" s="145">
         <f>SUMIF($B$11:$B$63,"TUBE",$H$11:$H$63)</f>
-        <v>151466</v>
-      </c>
-      <c r="E6" s="239"/>
-      <c r="F6" s="233"/>
+        <v>172298</v>
+      </c>
+      <c r="E6" s="234"/>
+      <c r="F6" s="231"/>
       <c r="G6" s="146">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),"-")</f>
-        <v>2.3650369033422502E-2</v>
+        <v>2.5364573316287858E-2</v>
       </c>
       <c r="H6" s="146"/>
       <c r="I6" s="143"/>
-      <c r="J6" s="239">
+      <c r="J6" s="234">
         <f>SUMIF($B$11:$B$63,"TUBE",$K$11:$K$63)</f>
         <v>283920</v>
       </c>
-      <c r="K6" s="233"/>
+      <c r="K6" s="231"/>
       <c r="L6" s="147"/>
       <c r="M6" s="180" t="s">
         <v>33</v>
@@ -4965,19 +4962,19 @@
     </row>
     <row r="7" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="136"/>
-      <c r="B7" s="241" t="s">
+      <c r="B7" s="236" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="233"/>
+      <c r="C7" s="231"/>
       <c r="D7" s="148" t="s">
         <v>215</v>
       </c>
       <c r="E7" s="148"/>
       <c r="F7" s="149"/>
-      <c r="G7" s="241" t="s">
+      <c r="G7" s="236" t="s">
         <v>216</v>
       </c>
-      <c r="H7" s="233"/>
+      <c r="H7" s="231"/>
       <c r="I7" s="150"/>
       <c r="J7" s="149" t="s">
         <v>210</v>
@@ -4990,11 +4987,11 @@
       </c>
       <c r="N7" s="158">
         <f>(IFERROR(INDEX($T$9:$T$23,MATCH(LARGE($U$9:$U$23,1),$U$9:$U$23,0)),""))/60</f>
-        <v>11.166666666666666</v>
+        <v>12.166666666666666</v>
       </c>
       <c r="O7" s="159">
         <f t="shared" ref="O7:O13" si="0">IFERROR(N7/$N$14,"")</f>
-        <v>0.48550724637681159</v>
+        <v>0.50694444444444442</v>
       </c>
       <c r="P7" s="136"/>
       <c r="Q7" s="136"/>
@@ -5013,28 +5010,28 @@
     </row>
     <row r="8" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="136"/>
-      <c r="B8" s="237">
+      <c r="B8" s="239">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$H$3:$H$8963)</f>
-        <v>5520</v>
-      </c>
-      <c r="C8" s="233"/>
+        <v>2090</v>
+      </c>
+      <c r="C8" s="231"/>
       <c r="D8" s="151">
         <f>SUMIF($B$11:$B$63,"PET",$H$11:$H$63)</f>
-        <v>55660</v>
-      </c>
-      <c r="E8" s="237"/>
-      <c r="F8" s="233"/>
+        <v>57750</v>
+      </c>
+      <c r="E8" s="239"/>
+      <c r="F8" s="231"/>
       <c r="G8" s="152">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),0)</f>
-        <v>8.9183439698903619E-2</v>
+        <v>8.6234177215189875E-2</v>
       </c>
       <c r="H8" s="152"/>
       <c r="I8" s="150"/>
-      <c r="J8" s="237">
+      <c r="J8" s="239">
         <f>SUMIF($B$11:$B$63,"PET",$K$11:$K$63)</f>
         <v>98520</v>
       </c>
-      <c r="K8" s="233"/>
+      <c r="K8" s="231"/>
       <c r="L8" s="153"/>
       <c r="M8" s="157" t="str">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,2),$U$9:$U$23,0)),"")</f>
@@ -5046,7 +5043,7 @@
       </c>
       <c r="O8" s="159">
         <f t="shared" si="0"/>
-        <v>0.21739130434782608</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="P8" s="136"/>
       <c r="Q8" s="136"/>
@@ -5065,19 +5062,19 @@
     </row>
     <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="136"/>
-      <c r="B9" s="230" t="s">
+      <c r="B9" s="240" t="s">
         <v>217</v>
       </c>
-      <c r="C9" s="231"/>
-      <c r="D9" s="231"/>
-      <c r="E9" s="231"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="231"/>
-      <c r="H9" s="231"/>
-      <c r="I9" s="231"/>
-      <c r="J9" s="231"/>
-      <c r="K9" s="231"/>
-      <c r="L9" s="231"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="M9" s="157" t="str">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,3),$U$9:$U$23,0)),"")</f>
         <v>Changeover</v>
@@ -5088,7 +5085,7 @@
       </c>
       <c r="O9" s="159">
         <f t="shared" si="0"/>
-        <v>0.21014492753623187</v>
+        <v>0.20138888888888887</v>
       </c>
       <c r="P9" s="136"/>
       <c r="Q9" s="136"/>
@@ -5158,7 +5155,7 @@
       </c>
       <c r="O10" s="159">
         <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="P10" s="136"/>
       <c r="Q10" s="136"/>
@@ -5230,7 +5227,7 @@
       </c>
       <c r="O11" s="159">
         <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="P11" s="171"/>
       <c r="Q11" s="171"/>
@@ -5268,15 +5265,15 @@
       </c>
       <c r="H12" s="219">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F12)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>4704</v>
+        <v>14112</v>
       </c>
       <c r="I12" s="218">
         <f t="shared" si="1"/>
-        <v>25296</v>
+        <v>15888</v>
       </c>
       <c r="J12" s="220">
         <f t="shared" si="2"/>
-        <v>0.15679999999999999</v>
+        <v>0.47039999999999998</v>
       </c>
       <c r="K12" s="219">
         <v>90048</v>
@@ -5433,7 +5430,7 @@
       </c>
       <c r="N14" s="155">
         <f>SUM($T$9:$T$23)/60</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O14" s="155" t="s">
         <v>233</v>
@@ -5562,11 +5559,11 @@
       </c>
       <c r="T16" s="170">
         <f>SUMPRODUCT(((LEFT(Production_Log!$B$3:$B$8963,5)="Press")+(LEFT(Production_Log!$B$3:$B$8963,5)="Print"))*Production_Log!$P$3:$P$8963)</f>
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="U16" s="169">
         <f>T16+0.00006</f>
-        <v>670.00005999999996</v>
+        <v>730.00005999999996</v>
       </c>
       <c r="V16" s="136"/>
       <c r="W16" s="136"/>
@@ -5600,15 +5597,15 @@
       </c>
       <c r="H17" s="219">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F17)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
-        <v>2618</v>
+        <v>14042</v>
       </c>
       <c r="I17" s="218">
         <f t="shared" si="1"/>
-        <v>299326</v>
+        <v>287902</v>
       </c>
       <c r="J17" s="220">
         <f t="shared" si="2"/>
-        <v>8.6704819436716745E-3</v>
+        <v>4.6505312243329891E-2</v>
       </c>
       <c r="K17" s="219"/>
       <c r="L17" s="221" t="s">
@@ -5765,11 +5762,11 @@
       </c>
       <c r="H20" s="225">
         <f>SUM(H11:H19)</f>
-        <v>151466</v>
+        <v>172298</v>
       </c>
       <c r="I20" s="225">
         <f>SUMIF(I11:I19,"&gt;"&amp;0)</f>
-        <v>392922</v>
+        <v>372090</v>
       </c>
       <c r="J20" s="225"/>
       <c r="K20" s="225">
@@ -5865,15 +5862,15 @@
       </c>
       <c r="H22" s="219">
         <f>SUMPRODUCT((Production_Log!$F$3:$F$8963=F22)*Production_Log!$H$3:$H$8963)</f>
-        <v>55660</v>
+        <v>57750</v>
       </c>
       <c r="I22" s="218">
         <f>G22-H22</f>
-        <v>194337</v>
+        <v>192247</v>
       </c>
       <c r="J22" s="220">
         <f>IF(G22=0,"-",H22/G22)</f>
-        <v>0.22264267171206054</v>
+        <v>0.23100277203326439</v>
       </c>
       <c r="K22" s="219">
         <v>63480</v>
@@ -6066,11 +6063,11 @@
       </c>
       <c r="H26" s="225">
         <f>SUM(H21:H25)</f>
-        <v>55660</v>
+        <v>57750</v>
       </c>
       <c r="I26" s="225">
         <f>SUMIF(I21:I25,"&gt;"&amp;0)</f>
-        <v>276577</v>
+        <v>274487</v>
       </c>
       <c r="J26" s="225"/>
       <c r="K26" s="225">
@@ -8137,7 +8134,7 @@
       </c>
       <c r="H1" s="163">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -8288,11 +8285,11 @@
       </c>
       <c r="G5" s="19">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$58,MATCH(MRP!D5,Tubex_Dashboard!$F$11:$F$58,0))</f>
-        <v>4704</v>
+        <v>14112</v>
       </c>
       <c r="H5" s="186">
         <f t="shared" si="0"/>
-        <v>25296</v>
+        <v>15888</v>
       </c>
       <c r="I5" s="186" t="s">
         <v>18</v>
@@ -8418,11 +8415,11 @@
       </c>
       <c r="G9" s="194">
         <f>INDEX(Tubex_Dashboard!$H$11:$H$100,MATCH(MRP!D9,Tubex_Dashboard!$F$11:$F$100,0))</f>
-        <v>2618</v>
+        <v>14042</v>
       </c>
       <c r="H9" s="195">
         <f t="shared" si="0"/>
-        <v>299326</v>
+        <v>287902</v>
       </c>
       <c r="I9" s="195" t="s">
         <v>26</v>
@@ -8484,11 +8481,11 @@
       </c>
       <c r="G11" s="156">
         <f>SUM(G3:G10)</f>
-        <v>151466</v>
+        <v>172298</v>
       </c>
       <c r="H11" s="156">
         <f>SUMIF(H3:H10, "&gt;0")</f>
-        <v>392922</v>
+        <v>372090</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="11"/>
@@ -8922,15 +8919,15 @@
       </c>
       <c r="E21" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A21)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>164.6440752</v>
+        <v>103.4102256</v>
       </c>
       <c r="F21" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A21,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A21,TableInventory[Item ID],0)),0)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G21" s="31">
         <f t="shared" si="1"/>
-        <v>-149.6440752</v>
+        <v>-103.4102256</v>
       </c>
       <c r="H21" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -8987,7 +8984,7 @@
       </c>
       <c r="K22" s="30">
         <f t="shared" si="3"/>
-        <v>149.6440752</v>
+        <v>103.4102256</v>
       </c>
     </row>
     <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9047,15 +9044,15 @@
       </c>
       <c r="E24" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A24)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>2898.0688000000005</v>
+        <v>2797.5376000000001</v>
       </c>
       <c r="F24" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A24,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A24,TableInventory[Item ID],0)),0)</f>
-        <v>695</v>
+        <v>740</v>
       </c>
       <c r="G24" s="31">
         <f t="shared" si="1"/>
-        <v>-2203.0688000000005</v>
+        <v>-2057.5376000000001</v>
       </c>
       <c r="H24" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -9123,7 +9120,7 @@
       </c>
       <c r="K25" s="30">
         <f t="shared" si="3"/>
-        <v>2203.0688000000005</v>
+        <v>2057.5376000000001</v>
       </c>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
@@ -9296,7 +9293,7 @@
       </c>
       <c r="E29" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A29)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>15.073426720000001</v>
+        <v>11.206080159999999</v>
       </c>
       <c r="F29" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A29,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A29,TableInventory[Item ID],0)),0)</f>
@@ -9304,7 +9301,7 @@
       </c>
       <c r="G29" s="31">
         <f t="shared" si="1"/>
-        <v>134.92657328000001</v>
+        <v>138.79391984</v>
       </c>
       <c r="H29" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A29)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A29)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A29)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A29)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A29)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A29)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A29)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A29)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A29)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A29)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A29)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A29)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A29)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A29)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A29)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A29)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A29)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A29)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A29)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A29)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A29)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A29)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A29)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A29)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -9452,7 +9449,7 @@
       </c>
       <c r="E32" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A32)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>104.29790800000002</v>
+        <v>100.77931600000002</v>
       </c>
       <c r="F32" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A32,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A32,TableInventory[Item ID],0)),0)</f>
@@ -9460,7 +9457,7 @@
       </c>
       <c r="G32" s="31">
         <f t="shared" si="1"/>
-        <v>120.70209199999998</v>
+        <v>124.22068399999998</v>
       </c>
       <c r="H32" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A32)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A32)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A32)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A32)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A32)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A32)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A32)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A32)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A32)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A32)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A32)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A32)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A32)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A32)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A32)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A32)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -9660,15 +9657,15 @@
       </c>
       <c r="E36" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A36)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>279.02047800000008</v>
+        <v>264.28822200000002</v>
       </c>
       <c r="F36" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A36,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A36,TableInventory[Item ID],0)),0)</f>
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="G36" s="31">
         <f t="shared" si="1"/>
-        <v>-39.020478000000082</v>
+        <v>-54.288222000000019</v>
       </c>
       <c r="H36" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A36)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A36)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A36)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A36)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A36)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A36)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A36)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A36)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A36)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A36)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A36)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A36)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A36)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A36)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A36)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A36)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A36)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A36)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A36)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A36)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A36)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A36)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A36)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A36)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -9736,7 +9733,7 @@
       </c>
       <c r="K37" s="30">
         <f t="shared" si="3"/>
-        <v>39.020478000000082</v>
+        <v>54.288222000000019</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
@@ -10026,7 +10023,7 @@
       </c>
       <c r="E44" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A44)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>96.152408000000008</v>
+        <v>92.63381600000001</v>
       </c>
       <c r="F44" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A44,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A44,TableInventory[Item ID],0)),0)</f>
@@ -10034,7 +10031,7 @@
       </c>
       <c r="G44" s="31">
         <f t="shared" si="1"/>
-        <v>-6.1524080000000083</v>
+        <v>-2.6338160000000101</v>
       </c>
       <c r="H44" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A44)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A44)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A44)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A44)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A44)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A44)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A44)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A44)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A44)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A44)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A44)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A44)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A44)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A44)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A44)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A44)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A44)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A44)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A44)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A44)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A44)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A44)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A44)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A44)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10068,15 +10065,15 @@
       </c>
       <c r="E45" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A45)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>3.1771780920000001</v>
+        <v>3.008980524</v>
       </c>
       <c r="F45" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A45,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A45,TableInventory[Item ID],0)),0)</f>
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="G45" s="31">
         <f t="shared" si="1"/>
-        <v>22.322821908000002</v>
+        <v>16.991019475999998</v>
       </c>
       <c r="H45" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A45)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A45)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A45)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A45)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A45)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A45)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A45)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A45)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A45)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A45)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A45)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A45)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A45)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A45)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A45)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A45)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A45)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A45)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A45)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A45)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A45)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A45)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A45)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A45)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10092,7 +10089,7 @@
       </c>
       <c r="K45" s="30">
         <f t="shared" si="3"/>
-        <v>6.1524080000000083</v>
+        <v>2.6338160000000101</v>
       </c>
     </row>
     <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
@@ -10779,15 +10776,15 @@
       </c>
       <c r="E61" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A61)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>331114.44</v>
+        <v>309865.8</v>
       </c>
       <c r="F61" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A61,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A61,TableInventory[Item ID],0)),0)</f>
-        <v>70000</v>
+        <v>40000</v>
       </c>
       <c r="G61" s="31">
         <f t="shared" si="5"/>
-        <v>-261114.44</v>
+        <v>-269865.8</v>
       </c>
       <c r="H61" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10845,7 +10842,7 @@
       </c>
       <c r="K62">
         <f t="shared" si="6"/>
-        <v>261114.44</v>
+        <v>269865.8</v>
       </c>
     </row>
     <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
@@ -11051,7 +11048,7 @@
       </c>
       <c r="J67">
         <f>IF(B67&lt;&gt;"CAP","",SUMPRODUCT((ISNUMBER(SEARCH("Cap Not Available",'FG Stock'!$H$4:$H$100)))*('FG Stock'!$I$4:$I$100=A67)*'FG Stock'!$F$4:$F$100))</f>
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="K67" t="str">
         <f t="shared" si="6"/>
@@ -11097,7 +11094,7 @@
       </c>
       <c r="K68">
         <f t="shared" si="6"/>
-        <v>59166</v>
+        <v>54166</v>
       </c>
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -11323,7 +11320,7 @@
       </c>
       <c r="E74" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A74)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>1466.2219193599999</v>
+        <v>1382.62490432</v>
       </c>
       <c r="F74" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A74,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A74,TableInventory[Item ID],0)),0)</f>
@@ -11331,7 +11328,7 @@
       </c>
       <c r="G74" s="31">
         <f t="shared" si="5"/>
-        <v>-1466.2219193599999</v>
+        <v>-1382.62490432</v>
       </c>
       <c r="H74" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A74)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A74)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A74)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A74)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A74)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A74)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A74)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A74)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A74)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A74)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A74)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A74)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -11389,7 +11386,7 @@
       </c>
       <c r="K75" s="30">
         <f t="shared" si="6"/>
-        <v>1466.2219193599999</v>
+        <v>1382.62490432</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -11453,11 +11450,11 @@
       </c>
       <c r="F77" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A77,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A77,TableInventory[Item ID],0)),0)</f>
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G77" s="31">
         <f t="shared" si="5"/>
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H77" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A77)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A77)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A77)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A77)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A77)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A77)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A77)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A77)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A77)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A77)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A77)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A77)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A77)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A77)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A77)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A77)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A77)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A77)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A77)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A77)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A77)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A77)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A77)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A77)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -11491,15 +11488,15 @@
       </c>
       <c r="E78" s="27">
         <f>SUMPRODUCT((TableBOM[Item ID]=A78)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>193.35690879999999</v>
+        <v>142.63300480000001</v>
       </c>
       <c r="F78" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A78,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A78,TableInventory[Item ID],0)),0)</f>
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="G78" s="31">
-        <f t="shared" ref="G78:G95" si="9">F78-E78</f>
-        <v>397.64309120000001</v>
+        <f t="shared" ref="G78:G109" si="9">F78-E78</f>
+        <v>436.36699520000002</v>
       </c>
       <c r="H78" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A78)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A78)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A78)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A78)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A78)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A78)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A78)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A78)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A78)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A78)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A78)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A78)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A78)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A78)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A78)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A78)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A78)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A78)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A78)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A78)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A78)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A78)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A78)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A78)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -11537,11 +11534,11 @@
       </c>
       <c r="F79" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A79,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A79,TableInventory[Item ID],0)),0)</f>
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G79" s="31">
         <f t="shared" si="9"/>
-        <v>223.35</v>
+        <v>198.35</v>
       </c>
       <c r="H79" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A79)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A79)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A79)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A79)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A79)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A79)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A79)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A79)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A79)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A79)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A79)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A79)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A79)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A79)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A79)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A79)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A79)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A79)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A79)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A79)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A79)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A79)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A79)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A79)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -11621,11 +11618,11 @@
       </c>
       <c r="F81" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A81,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A81,TableInventory[Item ID],0)),0)</f>
-        <v>1350</v>
+        <v>1100</v>
       </c>
       <c r="G81" s="31">
         <f t="shared" si="9"/>
-        <v>1350</v>
+        <v>1100</v>
       </c>
       <c r="H81" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A81)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A81)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A81)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A81)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A81)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A81)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A81)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A81)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A81)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A81)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A81)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A81)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A81)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A81)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A81)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A81)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A81)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A81)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A81)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A81)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A81)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A81)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A81)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A81)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -12209,11 +12206,11 @@
       </c>
       <c r="F95" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A95,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A95,TableInventory[Item ID],0)),0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G95" s="31">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H95" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A95)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A95)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A95)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A95)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A95)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A95)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A95)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A95)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A95)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A95)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A95)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A95)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A95)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A95)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A95)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A95)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A95)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A95)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A95)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A95)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A95)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A95)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A95)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A95)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -12676,7 +12673,7 @@
       </c>
       <c r="F113" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A108,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A108,TableInventory[Item ID],0)),0)</f>
-        <v>1350</v>
+        <v>1100</v>
       </c>
       <c r="G113" s="22">
         <f ca="1">F108-E108</f>
@@ -12863,7 +12860,7 @@
       </c>
       <c r="E119" s="33">
         <f>SUMPRODUCT((TableBOM[Item ID]=A114)*TableBOM[Per 1000 Units]*(1+TableBOM[Scrap %])*SUMIF($D$3:$D$10,TableBOM[Product ID],$H$3:$H$10)/1000)</f>
-        <v>193.35690879999999</v>
+        <v>142.63300480000001</v>
       </c>
       <c r="F119" s="165" t="e">
         <f t="shared" ref="F119:F150" ca="1" si="12">IF(E114=0,0,ROUND(H114/E114*30,1))</f>
@@ -12875,7 +12872,7 @@
       </c>
       <c r="H119" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A114,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A114,TableInventory[Item ID],0)),0)</f>
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="I119" s="166">
         <v>6.38</v>
@@ -12920,7 +12917,7 @@
       </c>
       <c r="H120" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A115,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A115,TableInventory[Item ID],0)),0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I120" s="166">
         <v>2.9</v>
@@ -13092,7 +13089,7 @@
       </c>
       <c r="F124" s="165">
         <f t="shared" si="12"/>
-        <v>91.7</v>
+        <v>121.8</v>
       </c>
       <c r="G124" s="22" t="str">
         <f t="shared" si="13"/>
@@ -13190,7 +13187,7 @@
       </c>
       <c r="H126" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A121,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A121,TableInventory[Item ID],0)),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I126" s="166">
         <v>1.6</v>
@@ -13640,7 +13637,7 @@
       </c>
       <c r="H136" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A131,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A131,TableInventory[Item ID],0)),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I136" s="166">
         <v>0.35</v>
@@ -13820,7 +13817,7 @@
       </c>
       <c r="H140" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A135,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A135,TableInventory[Item ID],0)),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="166">
         <v>0.12</v>
@@ -18383,7 +18380,7 @@
         <v>450</v>
       </c>
       <c r="J99" s="200">
-        <f t="shared" ref="J99:J101" si="3">IFERROR(I99/(H99+I99),"")</f>
+        <f t="shared" ref="J99:J130" si="3">IFERROR(I99/(H99+I99),"")</f>
         <v>3.0205396697543293E-2</v>
       </c>
       <c r="K99" s="198"/>
@@ -18477,172 +18474,350 @@
       <c r="S101" s="198"/>
     </row>
     <row r="102" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="176"/>
-      <c r="B102" s="177"/>
-      <c r="C102" s="177"/>
-      <c r="D102" s="177"/>
-      <c r="E102" s="177"/>
-      <c r="F102" s="177"/>
-      <c r="G102" s="178"/>
-      <c r="H102" s="178"/>
-      <c r="I102" s="178"/>
-      <c r="J102" s="179"/>
-      <c r="K102" s="177"/>
-      <c r="L102" s="177"/>
-      <c r="M102" s="177"/>
-      <c r="N102" s="177"/>
-      <c r="O102" s="177"/>
-      <c r="P102" s="177"/>
-      <c r="Q102" s="177"/>
-      <c r="R102" s="177"/>
-      <c r="S102" s="177"/>
+      <c r="A102" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B102" s="198" t="s">
+        <v>309</v>
+      </c>
+      <c r="C102" s="198" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" s="198" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" s="198">
+        <v>30</v>
+      </c>
+      <c r="F102" s="198">
+        <v>6206</v>
+      </c>
+      <c r="G102" s="199">
+        <v>17000</v>
+      </c>
+      <c r="H102" s="199">
+        <v>16780</v>
+      </c>
+      <c r="I102" s="199">
+        <v>220</v>
+      </c>
+      <c r="J102" s="200">
+        <f t="shared" si="3"/>
+        <v>1.2941176470588235E-2</v>
+      </c>
+      <c r="K102" s="198"/>
+      <c r="L102" s="198"/>
+      <c r="M102" s="198"/>
+      <c r="N102" s="198"/>
+      <c r="O102" s="198"/>
+      <c r="P102" s="198">
+        <v>30</v>
+      </c>
+      <c r="Q102" s="198"/>
+      <c r="R102" s="198"/>
+      <c r="S102" s="198"/>
     </row>
     <row r="103" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="176"/>
-      <c r="B103" s="177"/>
-      <c r="C103" s="177"/>
-      <c r="D103" s="177"/>
-      <c r="E103" s="177"/>
-      <c r="F103" s="177"/>
-      <c r="G103" s="178"/>
-      <c r="H103" s="178"/>
-      <c r="I103" s="178"/>
-      <c r="J103" s="179"/>
-      <c r="K103" s="177"/>
-      <c r="L103" s="177"/>
-      <c r="M103" s="177"/>
-      <c r="N103" s="177"/>
-      <c r="O103" s="177"/>
-      <c r="P103" s="177"/>
-      <c r="Q103" s="177"/>
-      <c r="R103" s="177"/>
-      <c r="S103" s="177"/>
+      <c r="A103" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B103" s="198" t="s">
+        <v>310</v>
+      </c>
+      <c r="C103" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="198" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="198">
+        <v>25</v>
+      </c>
+      <c r="F103" s="198">
+        <v>3447</v>
+      </c>
+      <c r="G103" s="199">
+        <v>9000</v>
+      </c>
+      <c r="H103" s="199">
+        <v>8805</v>
+      </c>
+      <c r="I103" s="199">
+        <v>195</v>
+      </c>
+      <c r="J103" s="200">
+        <f t="shared" si="3"/>
+        <v>2.1666666666666667E-2</v>
+      </c>
+      <c r="K103" s="198"/>
+      <c r="L103" s="198"/>
+      <c r="M103" s="198"/>
+      <c r="N103" s="198"/>
+      <c r="O103" s="198"/>
+      <c r="P103" s="198"/>
+      <c r="Q103" s="198"/>
+      <c r="R103" s="198"/>
+      <c r="S103" s="198"/>
     </row>
     <row r="104" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="176"/>
-      <c r="B104" s="177"/>
-      <c r="C104" s="177"/>
-      <c r="D104" s="177"/>
-      <c r="E104" s="177"/>
-      <c r="F104" s="177"/>
-      <c r="G104" s="178"/>
-      <c r="H104" s="178"/>
-      <c r="I104" s="178"/>
-      <c r="J104" s="179"/>
-      <c r="K104" s="177"/>
-      <c r="L104" s="177"/>
-      <c r="M104" s="177"/>
-      <c r="N104" s="177"/>
-      <c r="O104" s="177"/>
-      <c r="P104" s="177"/>
-      <c r="Q104" s="177"/>
-      <c r="R104" s="177"/>
-      <c r="S104" s="177"/>
+      <c r="A104" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B104" s="198" t="s">
+        <v>311</v>
+      </c>
+      <c r="C104" s="198" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104" s="198" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" s="198">
+        <v>30</v>
+      </c>
+      <c r="F104" s="198">
+        <v>6206</v>
+      </c>
+      <c r="G104" s="199">
+        <v>6426</v>
+      </c>
+      <c r="H104" s="199">
+        <v>6416</v>
+      </c>
+      <c r="I104" s="199">
+        <v>10</v>
+      </c>
+      <c r="J104" s="200">
+        <f t="shared" si="3"/>
+        <v>1.556178026766262E-3</v>
+      </c>
+      <c r="K104" s="198"/>
+      <c r="L104" s="198"/>
+      <c r="M104" s="198"/>
+      <c r="N104" s="198"/>
+      <c r="O104" s="198">
+        <v>360</v>
+      </c>
+      <c r="P104" s="198"/>
+      <c r="Q104" s="198"/>
+      <c r="R104" s="198"/>
+      <c r="S104" s="198"/>
     </row>
     <row r="105" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="176"/>
-      <c r="B105" s="177"/>
-      <c r="C105" s="177"/>
-      <c r="D105" s="177"/>
-      <c r="E105" s="177"/>
-      <c r="F105" s="177"/>
-      <c r="G105" s="178"/>
-      <c r="H105" s="178"/>
-      <c r="I105" s="178"/>
-      <c r="J105" s="179"/>
-      <c r="K105" s="177"/>
-      <c r="L105" s="177"/>
-      <c r="M105" s="177"/>
-      <c r="N105" s="177"/>
-      <c r="O105" s="177"/>
-      <c r="P105" s="177"/>
-      <c r="Q105" s="177"/>
-      <c r="R105" s="177"/>
-      <c r="S105" s="177"/>
+      <c r="A105" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B105" s="198" t="s">
+        <v>312</v>
+      </c>
+      <c r="C105" s="198" t="s">
+        <v>150</v>
+      </c>
+      <c r="D105" s="198" t="s">
+        <v>151</v>
+      </c>
+      <c r="E105" s="198" t="s">
+        <v>149</v>
+      </c>
+      <c r="F105" s="198">
+        <v>8001</v>
+      </c>
+      <c r="G105" s="199">
+        <v>2090</v>
+      </c>
+      <c r="H105" s="199">
+        <v>2090</v>
+      </c>
+      <c r="I105" s="199">
+        <v>0</v>
+      </c>
+      <c r="J105" s="200">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="198">
+        <v>390</v>
+      </c>
+      <c r="L105" s="198"/>
+      <c r="M105" s="198"/>
+      <c r="N105" s="198"/>
+      <c r="O105" s="198"/>
+      <c r="P105" s="198"/>
+      <c r="Q105" s="198"/>
+      <c r="R105" s="198"/>
+      <c r="S105" s="198"/>
     </row>
     <row r="106" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="176"/>
-      <c r="B106" s="177"/>
-      <c r="C106" s="177"/>
-      <c r="D106" s="177"/>
-      <c r="E106" s="177"/>
-      <c r="F106" s="177"/>
-      <c r="G106" s="178"/>
-      <c r="H106" s="178"/>
-      <c r="I106" s="178"/>
-      <c r="J106" s="179"/>
-      <c r="K106" s="177"/>
-      <c r="L106" s="177"/>
-      <c r="M106" s="177"/>
-      <c r="N106" s="177"/>
-      <c r="O106" s="177"/>
-      <c r="P106" s="177"/>
-      <c r="Q106" s="177"/>
-      <c r="R106" s="177"/>
-      <c r="S106" s="177"/>
+      <c r="A106" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B106" s="198" t="s">
+        <v>313</v>
+      </c>
+      <c r="C106" s="198" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" s="198" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="198">
+        <v>30</v>
+      </c>
+      <c r="F106" s="198">
+        <v>6206</v>
+      </c>
+      <c r="G106" s="199">
+        <v>18000</v>
+      </c>
+      <c r="H106" s="199">
+        <v>17880</v>
+      </c>
+      <c r="I106" s="199">
+        <v>120</v>
+      </c>
+      <c r="J106" s="200">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="K106" s="198"/>
+      <c r="L106" s="198"/>
+      <c r="M106" s="198"/>
+      <c r="N106" s="198"/>
+      <c r="O106" s="198"/>
+      <c r="P106" s="198">
+        <v>30</v>
+      </c>
+      <c r="Q106" s="198"/>
+      <c r="R106" s="198"/>
+      <c r="S106" s="198"/>
     </row>
     <row r="107" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="176"/>
-      <c r="B107" s="177"/>
-      <c r="C107" s="177"/>
-      <c r="D107" s="177"/>
-      <c r="E107" s="177"/>
-      <c r="F107" s="177"/>
-      <c r="G107" s="178"/>
-      <c r="H107" s="178"/>
-      <c r="I107" s="178"/>
-      <c r="J107" s="179"/>
-      <c r="K107" s="177"/>
-      <c r="L107" s="177"/>
-      <c r="M107" s="177"/>
-      <c r="N107" s="177"/>
-      <c r="O107" s="177"/>
-      <c r="P107" s="177"/>
-      <c r="Q107" s="177"/>
-      <c r="R107" s="177"/>
-      <c r="S107" s="177"/>
+      <c r="A107" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B107" s="198" t="s">
+        <v>314</v>
+      </c>
+      <c r="C107" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="198" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="198">
+        <v>25</v>
+      </c>
+      <c r="F107" s="198">
+        <v>3447</v>
+      </c>
+      <c r="G107" s="199">
+        <v>3300</v>
+      </c>
+      <c r="H107" s="199">
+        <v>3260</v>
+      </c>
+      <c r="I107" s="199">
+        <v>40</v>
+      </c>
+      <c r="J107" s="200">
+        <f t="shared" si="3"/>
+        <v>1.2121212121212121E-2</v>
+      </c>
+      <c r="K107" s="198"/>
+      <c r="L107" s="198"/>
+      <c r="M107" s="198"/>
+      <c r="N107" s="198"/>
+      <c r="O107" s="198"/>
+      <c r="P107" s="198"/>
+      <c r="Q107" s="198"/>
+      <c r="R107" s="198"/>
+      <c r="S107" s="198"/>
     </row>
     <row r="108" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="176"/>
-      <c r="B108" s="177"/>
-      <c r="C108" s="177"/>
-      <c r="D108" s="177"/>
-      <c r="E108" s="177"/>
-      <c r="F108" s="177"/>
-      <c r="G108" s="178"/>
-      <c r="H108" s="178"/>
-      <c r="I108" s="178"/>
-      <c r="J108" s="179"/>
-      <c r="K108" s="177"/>
-      <c r="L108" s="177"/>
-      <c r="M108" s="177"/>
-      <c r="N108" s="177"/>
-      <c r="O108" s="177"/>
-      <c r="P108" s="177"/>
-      <c r="Q108" s="177"/>
-      <c r="R108" s="177"/>
-      <c r="S108" s="177"/>
+      <c r="A108" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B108" s="198" t="s">
+        <v>315</v>
+      </c>
+      <c r="C108" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" s="198" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="198">
+        <v>25</v>
+      </c>
+      <c r="F108" s="198">
+        <v>3447</v>
+      </c>
+      <c r="G108" s="199">
+        <v>9773</v>
+      </c>
+      <c r="H108" s="199">
+        <v>9408</v>
+      </c>
+      <c r="I108" s="199">
+        <v>365</v>
+      </c>
+      <c r="J108" s="200">
+        <f t="shared" si="3"/>
+        <v>3.7347794945257341E-2</v>
+      </c>
+      <c r="K108" s="198"/>
+      <c r="L108" s="198"/>
+      <c r="M108" s="198"/>
+      <c r="N108" s="198"/>
+      <c r="O108" s="198"/>
+      <c r="P108" s="198">
+        <v>30</v>
+      </c>
+      <c r="Q108" s="198"/>
+      <c r="R108" s="198"/>
+      <c r="S108" s="198"/>
     </row>
     <row r="109" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="176"/>
-      <c r="B109" s="177"/>
-      <c r="C109" s="177"/>
-      <c r="D109" s="177"/>
-      <c r="E109" s="177"/>
-      <c r="F109" s="177"/>
-      <c r="G109" s="178"/>
-      <c r="H109" s="178"/>
-      <c r="I109" s="178"/>
-      <c r="J109" s="179"/>
-      <c r="K109" s="177"/>
-      <c r="L109" s="177"/>
-      <c r="M109" s="177"/>
-      <c r="N109" s="177"/>
-      <c r="O109" s="177"/>
-      <c r="P109" s="177"/>
-      <c r="Q109" s="177"/>
-      <c r="R109" s="177"/>
-      <c r="S109" s="177"/>
+      <c r="A109" s="197">
+        <v>46189</v>
+      </c>
+      <c r="B109" s="198" t="s">
+        <v>316</v>
+      </c>
+      <c r="C109" s="198" t="s">
+        <v>23</v>
+      </c>
+      <c r="D109" s="198" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" s="198">
+        <v>30</v>
+      </c>
+      <c r="F109" s="198">
+        <v>6206</v>
+      </c>
+      <c r="G109" s="199">
+        <v>11874</v>
+      </c>
+      <c r="H109" s="199">
+        <v>11424</v>
+      </c>
+      <c r="I109" s="199">
+        <v>450</v>
+      </c>
+      <c r="J109" s="200">
+        <f t="shared" si="3"/>
+        <v>3.7897928246589184E-2</v>
+      </c>
+      <c r="K109" s="198"/>
+      <c r="L109" s="198"/>
+      <c r="M109" s="198"/>
+      <c r="N109" s="198"/>
+      <c r="O109" s="198"/>
+      <c r="P109" s="198"/>
+      <c r="Q109" s="198"/>
+      <c r="R109" s="198"/>
+      <c r="S109" s="198"/>
     </row>
     <row r="110" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="176"/>
@@ -35135,19 +35310,19 @@
       <c r="A1" s="247" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="231"/>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
       <c r="I1" s="69" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="70">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="71" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -35336,12 +35511,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="37">
-        <v>15</v>
-      </c>
+      <c r="I7" s="37"/>
       <c r="J7" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>2532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35371,11 +35544,11 @@
         <v>685</v>
       </c>
       <c r="I8" s="37">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="J8" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>86875</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35459,7 +35632,7 @@
       <c r="I12" s="74"/>
       <c r="J12" s="70">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -35776,16 +35949,16 @@
         <v>210</v>
       </c>
       <c r="G22" s="37">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H22" s="38">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A22,TableBOM[Per 1000 Units])=0,"-",ROUND((H22+I22)/(AVERAGEIF(TableBOM[Item ID],A22,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>448892</v>
+        <v>392780</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36096,16 +36269,16 @@
         <v>0</v>
       </c>
       <c r="G31" s="37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="38">
         <f t="shared" si="1"/>
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="I31" s="37"/>
       <c r="J31" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A31,TableBOM[Per 1000 Units])=0,"-",ROUND((H31+I31)/(AVERAGEIF(TableBOM[Item ID],A31,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>3815999</v>
+        <v>2992940</v>
       </c>
       <c r="K31" s="75"/>
       <c r="L31" s="75"/>
@@ -36642,16 +36815,16 @@
         <v>100000</v>
       </c>
       <c r="G46" s="37">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="H46" s="38">
         <f t="shared" ref="H46:H77" si="2">E46+F46-G46</f>
-        <v>70000</v>
+        <v>40000</v>
       </c>
       <c r="I46" s="37"/>
       <c r="J46" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])=0,"-",ROUND((H46+I46)/(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>70000</v>
+        <v>40000</v>
       </c>
       <c r="K46" s="75"/>
       <c r="L46" s="75"/>
@@ -37246,16 +37419,16 @@
         <v>0</v>
       </c>
       <c r="G62" s="37">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H62" s="38">
         <f t="shared" si="2"/>
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I62" s="37"/>
       <c r="J62" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A62,TableBOM[Per 1000 Units])=0,"-",ROUND((H62+I62)/(AVERAGEIF(TableBOM[Item ID],A62,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>35585</v>
+        <v>28322</v>
       </c>
       <c r="K62" s="76"/>
       <c r="L62" s="76"/>
@@ -37284,16 +37457,16 @@
         <v>0</v>
       </c>
       <c r="G63" s="37">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H63" s="38">
         <f t="shared" si="2"/>
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="I63" s="37"/>
       <c r="J63" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A63,TableBOM[Per 1000 Units])=0,"-",ROUND((H63+I63)/(AVERAGEIF(TableBOM[Item ID],A63,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>1621898</v>
+        <v>1588966</v>
       </c>
       <c r="K63" s="76"/>
       <c r="L63" s="76"/>
@@ -37322,16 +37495,16 @@
         <v>0</v>
       </c>
       <c r="G64" s="37">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H64" s="38">
         <f t="shared" si="2"/>
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="I64" s="37"/>
       <c r="J64" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A64,TableBOM[Per 1000 Units])=0,"-",ROUND((H64+I64)/(AVERAGEIF(TableBOM[Item ID],A64,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>3750000</v>
+        <v>3333333</v>
       </c>
       <c r="K64" s="76"/>
       <c r="L64" s="76"/>
@@ -37704,11 +37877,11 @@
         <v>1</v>
       </c>
       <c r="G74" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="38">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="37"/>
       <c r="J74" s="37" t="str">
@@ -37859,7 +38032,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="38">
-        <f t="shared" ref="H78:H94" si="3">E78+F78-G78</f>
+        <f t="shared" ref="H78:H109" si="3">E78+F78-G78</f>
         <v>5</v>
       </c>
       <c r="I78" s="37"/>
@@ -38002,11 +38175,11 @@
         <v>7</v>
       </c>
       <c r="G82" s="37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H82" s="38">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82" s="37"/>
       <c r="J82" s="37" t="str">
@@ -38156,17 +38329,17 @@
         <v>44</v>
       </c>
       <c r="E87" s="37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87" s="37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G87" s="37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I87" s="37"/>
       <c r="J87" s="37" t="str">
@@ -38461,18 +38634,18 @@
         <v>0</v>
       </c>
       <c r="G98" s="37">
-        <v>1650</v>
+        <v>1900</v>
       </c>
       <c r="H98" s="38">
         <f t="shared" ref="H98:H113" si="4">E98+F98-G98</f>
-        <v>1350</v>
+        <v>1100</v>
       </c>
       <c r="I98" s="37">
         <v>0</v>
       </c>
       <c r="J98" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A98,TableBOM[Per 1000 Units])=0,"-",ROUND((H98+I98)/(AVERAGEIF(TableBOM[Item ID],A98,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>56645</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38961,16 +39134,16 @@
         <v>0</v>
       </c>
       <c r="G113" s="37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H113" s="38">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I113" s="37"/>
       <c r="J113" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A113,TableBOM[Per 1000 Units])=0,"-",ROUND((H113+I113)/(AVERAGEIF(TableBOM[Item ID],A113,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>1000000</v>
+        <v>600000</v>
       </c>
     </row>
   </sheetData>
@@ -45586,15 +45759,15 @@
     </sortState>
   </autoFilter>
   <mergeCells count="9">
-    <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -45686,7 +45859,7 @@
         <v>618</v>
       </c>
       <c r="F4" s="203">
-        <v>18860</v>
+        <v>20700</v>
       </c>
       <c r="G4" s="201" t="s">
         <v>619</v>
@@ -45776,7 +45949,7 @@
         <v>622</v>
       </c>
       <c r="F7" s="203">
-        <v>11088</v>
+        <v>25536</v>
       </c>
       <c r="G7" s="201" t="s">
         <v>619</v>
@@ -45794,19 +45967,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="201">
-        <v>4050</v>
+        <v>3447</v>
       </c>
       <c r="C8" s="202" t="s">
-        <v>271</v>
+        <v>14</v>
       </c>
       <c r="D8" s="202" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="E8" s="201" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F8" s="203">
-        <v>9450</v>
+        <v>16464</v>
       </c>
       <c r="G8" s="201" t="s">
         <v>619</v>
@@ -45816,7 +45989,7 @@
       </c>
       <c r="I8" s="94">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B8)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45824,19 +45997,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="201">
-        <v>6337</v>
+        <v>4050</v>
       </c>
       <c r="C9" s="202" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D9" s="202" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E9" s="201" t="s">
         <v>623</v>
       </c>
       <c r="F9" s="203">
-        <v>15680</v>
+        <v>9450</v>
       </c>
       <c r="G9" s="201" t="s">
         <v>619</v>
@@ -45854,19 +46027,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="201">
-        <v>6416</v>
+        <v>6337</v>
       </c>
       <c r="C10" s="202" t="s">
         <v>267</v>
       </c>
       <c r="D10" s="202" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E10" s="201" t="s">
         <v>623</v>
       </c>
       <c r="F10" s="203">
-        <v>15435</v>
+        <v>15680</v>
       </c>
       <c r="G10" s="201" t="s">
         <v>619</v>
@@ -45884,19 +46057,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="201">
-        <v>5782</v>
+        <v>6416</v>
       </c>
       <c r="C11" s="202" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D11" s="202" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E11" s="201" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F11" s="203">
-        <v>63648</v>
+        <v>15435</v>
       </c>
       <c r="G11" s="201" t="s">
         <v>619</v>
@@ -45906,7 +46079,7 @@
       </c>
       <c r="I11" s="94">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B11)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>1285</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45914,19 +46087,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="201">
-        <v>6531</v>
+        <v>5782</v>
       </c>
       <c r="C12" s="202" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
       <c r="D12" s="202" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E12" s="201" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F12" s="203">
-        <v>4380</v>
+        <v>63648</v>
       </c>
       <c r="G12" s="201" t="s">
         <v>619</v>
@@ -45936,7 +46109,7 @@
       </c>
       <c r="I12" s="94">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B12)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45944,89 +46117,89 @@
         <v>10</v>
       </c>
       <c r="B13" s="201">
-        <v>6206</v>
+        <v>6531</v>
       </c>
       <c r="C13" s="202" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D13" s="202" t="s">
-        <v>24</v>
+        <v>281</v>
       </c>
       <c r="E13" s="201" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F13" s="203">
-        <v>100674</v>
+        <v>4380</v>
       </c>
       <c r="G13" s="201" t="s">
         <v>619</v>
       </c>
       <c r="H13" s="204" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="I13" s="94">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B13)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>68</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="205">
+      <c r="A14" s="201">
         <v>11</v>
       </c>
-      <c r="B14" s="205">
-        <v>6515</v>
-      </c>
-      <c r="C14" s="206" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="206" t="s">
-        <v>278</v>
-      </c>
-      <c r="E14" s="205" t="s">
-        <v>624</v>
-      </c>
-      <c r="F14" s="207">
-        <v>38896</v>
-      </c>
-      <c r="G14" s="205" t="s">
-        <v>627</v>
-      </c>
-      <c r="H14" s="208" t="s">
-        <v>628</v>
+      <c r="B14" s="201">
+        <v>6530</v>
+      </c>
+      <c r="C14" s="202" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="202" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="201" t="s">
+        <v>625</v>
+      </c>
+      <c r="F14" s="203">
+        <v>4500</v>
+      </c>
+      <c r="G14" s="201" t="s">
+        <v>619</v>
+      </c>
+      <c r="H14" s="204" t="s">
+        <v>620</v>
       </c>
       <c r="I14" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B14)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>1073</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="205">
+      <c r="A15" s="201">
         <v>12</v>
       </c>
-      <c r="B15" s="205">
-        <v>6530</v>
-      </c>
-      <c r="C15" s="206" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="206" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="205" t="s">
-        <v>625</v>
-      </c>
-      <c r="F15" s="207">
-        <v>15000</v>
-      </c>
-      <c r="G15" s="205" t="s">
-        <v>627</v>
-      </c>
-      <c r="H15" s="208" t="s">
-        <v>629</v>
+      <c r="B15" s="201">
+        <v>6206</v>
+      </c>
+      <c r="C15" s="202" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="202" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="201" t="s">
+        <v>623</v>
+      </c>
+      <c r="F15" s="203">
+        <v>100674</v>
+      </c>
+      <c r="G15" s="201" t="s">
+        <v>619</v>
+      </c>
+      <c r="H15" s="204" t="s">
+        <v>620</v>
       </c>
       <c r="I15" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B15)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>578</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46034,29 +46207,29 @@
         <v>13</v>
       </c>
       <c r="B16" s="205">
-        <v>5782</v>
+        <v>6515</v>
       </c>
       <c r="C16" s="206" t="s">
-        <v>279</v>
+        <v>14</v>
       </c>
       <c r="D16" s="206" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E16" s="205" t="s">
         <v>624</v>
       </c>
       <c r="F16" s="207">
-        <v>10500</v>
+        <v>38896</v>
       </c>
       <c r="G16" s="205" t="s">
+        <v>626</v>
+      </c>
+      <c r="H16" s="208" t="s">
         <v>627</v>
-      </c>
-      <c r="H16" s="208" t="s">
-        <v>629</v>
       </c>
       <c r="I16" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B16)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>1285</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46064,29 +46237,29 @@
         <v>14</v>
       </c>
       <c r="B17" s="205">
-        <v>6624</v>
+        <v>6530</v>
       </c>
       <c r="C17" s="206" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D17" s="206" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="E17" s="205" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F17" s="207">
-        <v>15288</v>
+        <v>10000</v>
       </c>
       <c r="G17" s="205" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H17" s="208" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I17" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B17)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>80</v>
+        <v>578</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46094,57 +46267,89 @@
         <v>15</v>
       </c>
       <c r="B18" s="205">
-        <v>5731</v>
+        <v>5782</v>
       </c>
       <c r="C18" s="206" t="s">
-        <v>14</v>
+        <v>279</v>
       </c>
       <c r="D18" s="206" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="E18" s="205" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F18" s="207">
-        <v>37030</v>
+        <v>10500</v>
       </c>
       <c r="G18" s="205" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H18" s="208" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I18" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B18)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>6971</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="209"/>
-      <c r="B19" s="209"/>
-      <c r="C19" s="210"/>
-      <c r="D19" s="210"/>
-      <c r="E19" s="209"/>
-      <c r="F19" s="211"/>
-      <c r="G19" s="209"/>
-      <c r="H19" s="212"/>
+      <c r="A19" s="205">
+        <v>16</v>
+      </c>
+      <c r="B19" s="205">
+        <v>6624</v>
+      </c>
+      <c r="C19" s="206" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="206" t="s">
+        <v>246</v>
+      </c>
+      <c r="E19" s="205" t="s">
+        <v>629</v>
+      </c>
+      <c r="F19" s="207">
+        <v>15288</v>
+      </c>
+      <c r="G19" s="205" t="s">
+        <v>626</v>
+      </c>
+      <c r="H19" s="208" t="s">
+        <v>628</v>
+      </c>
       <c r="I19" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B19)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="209"/>
-      <c r="B20" s="209"/>
-      <c r="C20" s="210"/>
-      <c r="D20" s="210"/>
-      <c r="E20" s="209"/>
-      <c r="F20" s="211"/>
-      <c r="G20" s="209"/>
-      <c r="H20" s="212"/>
+      <c r="A20" s="205">
+        <v>17</v>
+      </c>
+      <c r="B20" s="205">
+        <v>5731</v>
+      </c>
+      <c r="C20" s="206" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="206" t="s">
+        <v>254</v>
+      </c>
+      <c r="E20" s="205" t="s">
+        <v>621</v>
+      </c>
+      <c r="F20" s="207">
+        <v>37030</v>
+      </c>
+      <c r="G20" s="205" t="s">
+        <v>626</v>
+      </c>
+      <c r="H20" s="208" t="s">
+        <v>628</v>
+      </c>
       <c r="I20" s="95">
         <f>IFERROR(SUMPRODUCT((TableBOM[Product ID]=B20)*(TableBOM[Material Category]="CAP")*TableBOM[Item ID]),0)</f>
-        <v>0</v>
+        <v>6971</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47276,8 +47481,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="251" t="s">
-        <v>631</v>
+      <c r="A1" s="254" t="s">
+        <v>630</v>
       </c>
       <c r="B1" s="243"/>
       <c r="C1" s="243"/>
@@ -47286,8 +47491,8 @@
       <c r="F1" s="243"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="254" t="s">
-        <v>632</v>
+      <c r="A2" s="253" t="s">
+        <v>631</v>
       </c>
       <c r="B2" s="243"/>
       <c r="C2" s="243"/>
@@ -47305,7 +47510,7 @@
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="248" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B4" s="243"/>
       <c r="C4" s="243"/>
@@ -47314,8 +47519,8 @@
       <c r="F4" s="243"/>
     </row>
     <row r="5" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="252" t="s">
-        <v>634</v>
+      <c r="A5" s="251" t="s">
+        <v>633</v>
       </c>
       <c r="B5" s="243"/>
       <c r="C5" s="243"/>
@@ -47325,19 +47530,19 @@
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="102" t="s">
+        <v>634</v>
+      </c>
+      <c r="B6" s="103" t="s">
         <v>635</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="C6" s="103" t="s">
         <v>636</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="D6" s="103" t="s">
         <v>637</v>
       </c>
-      <c r="D6" s="103" t="s">
+      <c r="E6" s="103" t="s">
         <v>638</v>
-      </c>
-      <c r="E6" s="103" t="s">
-        <v>639</v>
       </c>
       <c r="F6" s="103" t="s">
         <v>203</v>
@@ -47345,190 +47550,190 @@
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="126" t="s">
+        <v>639</v>
+      </c>
+      <c r="B7" s="100" t="s">
         <v>640</v>
       </c>
-      <c r="B7" s="100" t="s">
+      <c r="C7" s="100" t="s">
         <v>641</v>
       </c>
-      <c r="C7" s="100" t="s">
+      <c r="D7" s="100" t="s">
         <v>642</v>
       </c>
-      <c r="D7" s="100" t="s">
+      <c r="E7" s="100" t="s">
         <v>643</v>
       </c>
-      <c r="E7" s="100" t="s">
+      <c r="F7" s="100" t="s">
         <v>644</v>
-      </c>
-      <c r="F7" s="100" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="93" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="127" t="s">
+        <v>645</v>
+      </c>
+      <c r="B8" s="107" t="s">
         <v>646</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="C8" s="107" t="s">
+        <v>641</v>
+      </c>
+      <c r="D8" s="107" t="s">
         <v>647</v>
       </c>
-      <c r="C8" s="107" t="s">
-        <v>642</v>
-      </c>
-      <c r="D8" s="107" t="s">
+      <c r="E8" s="107" t="s">
         <v>648</v>
       </c>
-      <c r="E8" s="107" t="s">
+      <c r="F8" s="107" t="s">
         <v>649</v>
-      </c>
-      <c r="F8" s="107" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="93" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="126" t="s">
+        <v>650</v>
+      </c>
+      <c r="B9" s="100" t="s">
         <v>651</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="C9" s="100" t="s">
         <v>652</v>
       </c>
-      <c r="C9" s="100" t="s">
+      <c r="D9" s="100" t="s">
         <v>653</v>
       </c>
-      <c r="D9" s="100" t="s">
+      <c r="E9" s="100" t="s">
         <v>654</v>
       </c>
-      <c r="E9" s="100" t="s">
+      <c r="F9" s="100" t="s">
         <v>655</v>
-      </c>
-      <c r="F9" s="100" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="93" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="106"/>
       <c r="B10" s="107" t="s">
+        <v>656</v>
+      </c>
+      <c r="C10" s="107" t="s">
         <v>657</v>
       </c>
-      <c r="C10" s="107" t="s">
+      <c r="D10" s="107" t="s">
+        <v>648</v>
+      </c>
+      <c r="E10" s="107" t="s">
         <v>658</v>
       </c>
-      <c r="D10" s="107" t="s">
-        <v>649</v>
-      </c>
-      <c r="E10" s="107" t="s">
+      <c r="F10" s="107" t="s">
         <v>659</v>
-      </c>
-      <c r="F10" s="107" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="99"/>
       <c r="B11" s="100" t="s">
+        <v>660</v>
+      </c>
+      <c r="C11" s="100" t="s">
         <v>661</v>
       </c>
-      <c r="C11" s="100" t="s">
+      <c r="D11" s="100" t="s">
         <v>662</v>
       </c>
-      <c r="D11" s="100" t="s">
+      <c r="E11" s="100" t="s">
         <v>663</v>
       </c>
-      <c r="E11" s="100" t="s">
+      <c r="F11" s="100" t="s">
         <v>664</v>
-      </c>
-      <c r="F11" s="100" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="106"/>
       <c r="B12" s="107" t="s">
+        <v>665</v>
+      </c>
+      <c r="C12" s="107" t="s">
         <v>666</v>
       </c>
-      <c r="C12" s="107" t="s">
+      <c r="D12" s="107" t="s">
         <v>667</v>
       </c>
-      <c r="D12" s="107" t="s">
+      <c r="E12" s="107" t="s">
         <v>668</v>
       </c>
-      <c r="E12" s="107" t="s">
+      <c r="F12" s="107" t="s">
         <v>669</v>
-      </c>
-      <c r="F12" s="107" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="99"/>
       <c r="B13" s="100" t="s">
+        <v>670</v>
+      </c>
+      <c r="C13" s="100" t="s">
         <v>671</v>
       </c>
-      <c r="C13" s="100" t="s">
+      <c r="D13" s="100" t="s">
         <v>672</v>
       </c>
-      <c r="D13" s="100" t="s">
+      <c r="E13" s="100" t="s">
         <v>673</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="F13" s="100" t="s">
         <v>674</v>
-      </c>
-      <c r="F13" s="100" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="106"/>
       <c r="B14" s="107" t="s">
+        <v>675</v>
+      </c>
+      <c r="C14" s="107" t="s">
         <v>676</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="D14" s="107" t="s">
         <v>677</v>
       </c>
-      <c r="D14" s="107" t="s">
+      <c r="E14" s="107" t="s">
         <v>678</v>
       </c>
-      <c r="E14" s="107" t="s">
+      <c r="F14" s="107" t="s">
         <v>679</v>
-      </c>
-      <c r="F14" s="107" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="93" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="126" t="s">
+        <v>680</v>
+      </c>
+      <c r="B15" s="100" t="s">
         <v>681</v>
       </c>
-      <c r="B15" s="100" t="s">
+      <c r="C15" s="100" t="s">
         <v>682</v>
-      </c>
-      <c r="C15" s="100" t="s">
-        <v>683</v>
       </c>
       <c r="D15" s="100"/>
       <c r="E15" s="100" t="s">
+        <v>683</v>
+      </c>
+      <c r="F15" s="100" t="s">
         <v>684</v>
-      </c>
-      <c r="F15" s="100" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="127" t="s">
+        <v>685</v>
+      </c>
+      <c r="B16" s="107" t="s">
         <v>686</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="C16" s="107" t="s">
+        <v>641</v>
+      </c>
+      <c r="D16" s="107" t="s">
         <v>687</v>
       </c>
-      <c r="C16" s="107" t="s">
-        <v>642</v>
-      </c>
-      <c r="D16" s="107" t="s">
+      <c r="E16" s="107" t="s">
         <v>688</v>
       </c>
-      <c r="E16" s="107" t="s">
+      <c r="F16" s="107" t="s">
         <v>689</v>
-      </c>
-      <c r="F16" s="107" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="93" customFormat="1" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -47540,34 +47745,34 @@
       <c r="F17" s="125"/>
     </row>
     <row r="18" spans="1:6" s="93" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="252" t="s">
+      <c r="A18" s="251" t="s">
+        <v>690</v>
+      </c>
+      <c r="B18" s="252"/>
+      <c r="C18" s="252"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+    </row>
+    <row r="19" spans="1:6" s="93" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="251" t="s">
         <v>691</v>
       </c>
-      <c r="B18" s="253"/>
-      <c r="C18" s="253"/>
-      <c r="D18" s="253"/>
-      <c r="E18" s="253"/>
-      <c r="F18" s="253"/>
-    </row>
-    <row r="19" spans="1:6" s="93" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="252" t="s">
+      <c r="B19" s="252"/>
+      <c r="C19" s="252"/>
+      <c r="D19" s="252"/>
+      <c r="E19" s="252"/>
+      <c r="F19" s="252"/>
+    </row>
+    <row r="20" spans="1:6" s="93" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="251" t="s">
         <v>692</v>
       </c>
-      <c r="B19" s="253"/>
-      <c r="C19" s="253"/>
-      <c r="D19" s="253"/>
-      <c r="E19" s="253"/>
-      <c r="F19" s="253"/>
-    </row>
-    <row r="20" spans="1:6" s="93" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="252" t="s">
-        <v>693</v>
-      </c>
-      <c r="B20" s="253"/>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
+      <c r="B20" s="252"/>
+      <c r="C20" s="252"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="252"/>
+      <c r="F20" s="252"/>
     </row>
     <row r="21" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="130"/>
@@ -47579,7 +47784,7 @@
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="248" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B22" s="243"/>
       <c r="C22" s="243"/>
@@ -47589,109 +47794,109 @@
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="102" t="s">
+        <v>694</v>
+      </c>
+      <c r="B23" s="103" t="s">
         <v>695</v>
-      </c>
-      <c r="B23" s="103" t="s">
-        <v>696</v>
       </c>
       <c r="C23" s="103" t="s">
         <v>203</v>
       </c>
       <c r="D23" s="103" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E23" s="103"/>
       <c r="F23" s="103"/>
     </row>
     <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="99" t="s">
+        <v>697</v>
+      </c>
+      <c r="B24" s="100" t="s">
         <v>698</v>
       </c>
-      <c r="B24" s="100" t="s">
+      <c r="C24" s="100" t="s">
         <v>699</v>
       </c>
-      <c r="C24" s="100" t="s">
+      <c r="D24" s="100" t="s">
         <v>700</v>
-      </c>
-      <c r="D24" s="100" t="s">
-        <v>701</v>
       </c>
       <c r="E24" s="100"/>
       <c r="F24" s="100"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="106" t="s">
+        <v>701</v>
+      </c>
+      <c r="B25" s="107" t="s">
         <v>702</v>
       </c>
-      <c r="B25" s="107" t="s">
+      <c r="C25" s="107" t="s">
         <v>703</v>
       </c>
-      <c r="C25" s="107" t="s">
+      <c r="D25" s="107" t="s">
         <v>704</v>
-      </c>
-      <c r="D25" s="107" t="s">
-        <v>705</v>
       </c>
       <c r="E25" s="107"/>
       <c r="F25" s="107"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="99" t="s">
+        <v>705</v>
+      </c>
+      <c r="B26" s="100" t="s">
         <v>706</v>
       </c>
-      <c r="B26" s="100" t="s">
+      <c r="C26" s="100" t="s">
         <v>707</v>
       </c>
-      <c r="C26" s="100" t="s">
-        <v>708</v>
-      </c>
       <c r="D26" s="100" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E26" s="100"/>
       <c r="F26" s="100"/>
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="106" t="s">
+        <v>708</v>
+      </c>
+      <c r="B27" s="107" t="s">
         <v>709</v>
       </c>
-      <c r="B27" s="107" t="s">
+      <c r="C27" s="107" t="s">
         <v>710</v>
       </c>
-      <c r="C27" s="107" t="s">
-        <v>711</v>
-      </c>
       <c r="D27" s="107" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E27" s="107"/>
       <c r="F27" s="107"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="99" t="s">
+        <v>711</v>
+      </c>
+      <c r="B28" s="100" t="s">
         <v>712</v>
       </c>
-      <c r="B28" s="100" t="s">
+      <c r="C28" s="100" t="s">
         <v>713</v>
       </c>
-      <c r="C28" s="100" t="s">
-        <v>714</v>
-      </c>
       <c r="D28" s="100" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E28" s="100"/>
       <c r="F28" s="100"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="106" t="s">
+        <v>714</v>
+      </c>
+      <c r="B29" s="107" t="s">
         <v>715</v>
       </c>
-      <c r="B29" s="107" t="s">
+      <c r="C29" s="107" t="s">
         <v>716</v>
-      </c>
-      <c r="C29" s="107" t="s">
-        <v>717</v>
       </c>
       <c r="D29" s="107"/>
       <c r="E29" s="107"/>
@@ -47707,7 +47912,7 @@
     </row>
     <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="248" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B31" s="243"/>
       <c r="C31" s="243"/>
@@ -47717,13 +47922,13 @@
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="102" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B32" s="103" t="s">
         <v>39</v>
       </c>
       <c r="C32" s="103" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D32" s="103"/>
       <c r="E32" s="103"/>
@@ -47731,13 +47936,13 @@
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="99" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B33" s="100" t="s">
+        <v>720</v>
+      </c>
+      <c r="C33" s="100" t="s">
         <v>721</v>
-      </c>
-      <c r="C33" s="100" t="s">
-        <v>722</v>
       </c>
       <c r="D33" s="100"/>
       <c r="E33" s="100"/>
@@ -47745,13 +47950,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="106" t="s">
+        <v>722</v>
+      </c>
+      <c r="B34" s="107" t="s">
         <v>723</v>
       </c>
-      <c r="B34" s="107" t="s">
+      <c r="C34" s="107" t="s">
         <v>724</v>
-      </c>
-      <c r="C34" s="107" t="s">
-        <v>725</v>
       </c>
       <c r="D34" s="107"/>
       <c r="E34" s="107"/>
@@ -47759,13 +47964,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="99" t="s">
+        <v>725</v>
+      </c>
+      <c r="B35" s="100" t="s">
         <v>726</v>
       </c>
-      <c r="B35" s="100" t="s">
+      <c r="C35" s="100" t="s">
         <v>727</v>
-      </c>
-      <c r="C35" s="100" t="s">
-        <v>728</v>
       </c>
       <c r="D35" s="100"/>
       <c r="E35" s="100"/>
@@ -47793,10 +47998,10 @@
     </row>
     <row r="38" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="99" t="s">
+        <v>728</v>
+      </c>
+      <c r="B38" s="100" t="s">
         <v>729</v>
-      </c>
-      <c r="B38" s="100" t="s">
-        <v>730</v>
       </c>
       <c r="C38" s="100"/>
       <c r="D38" s="100"/>
@@ -47805,10 +48010,10 @@
     </row>
     <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="106" t="s">
+        <v>730</v>
+      </c>
+      <c r="B39" s="107" t="s">
         <v>731</v>
-      </c>
-      <c r="B39" s="107" t="s">
-        <v>732</v>
       </c>
       <c r="C39" s="107"/>
       <c r="D39" s="107"/>
@@ -47817,10 +48022,10 @@
     </row>
     <row r="40" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="99" t="s">
+        <v>732</v>
+      </c>
+      <c r="B40" s="100" t="s">
         <v>733</v>
-      </c>
-      <c r="B40" s="100" t="s">
-        <v>734</v>
       </c>
       <c r="C40" s="100"/>
       <c r="D40" s="100"/>
@@ -47832,7 +48037,7 @@
         <v>145</v>
       </c>
       <c r="B41" s="107" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C41" s="107"/>
       <c r="D41" s="107"/>
@@ -47841,10 +48046,10 @@
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="99" t="s">
+        <v>735</v>
+      </c>
+      <c r="B42" s="100" t="s">
         <v>736</v>
-      </c>
-      <c r="B42" s="100" t="s">
-        <v>737</v>
       </c>
       <c r="C42" s="100"/>
       <c r="D42" s="100"/>
@@ -47861,7 +48066,7 @@
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="248" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B44" s="243"/>
       <c r="C44" s="243"/>
@@ -47871,13 +48076,13 @@
     </row>
     <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="102" t="s">
+        <v>738</v>
+      </c>
+      <c r="B45" s="103" t="s">
         <v>739</v>
       </c>
-      <c r="B45" s="103" t="s">
+      <c r="C45" s="103" t="s">
         <v>740</v>
-      </c>
-      <c r="C45" s="103" t="s">
-        <v>741</v>
       </c>
       <c r="D45" s="103"/>
       <c r="E45" s="103"/>
@@ -47885,13 +48090,13 @@
     </row>
     <row r="46" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="99" t="s">
+        <v>741</v>
+      </c>
+      <c r="B46" s="100" t="s">
         <v>742</v>
       </c>
-      <c r="B46" s="100" t="s">
+      <c r="C46" s="100" t="s">
         <v>743</v>
-      </c>
-      <c r="C46" s="100" t="s">
-        <v>744</v>
       </c>
       <c r="D46" s="100"/>
       <c r="E46" s="100"/>
@@ -47899,13 +48104,13 @@
     </row>
     <row r="47" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="106" t="s">
+        <v>744</v>
+      </c>
+      <c r="B47" s="107" t="s">
         <v>745</v>
       </c>
-      <c r="B47" s="107" t="s">
+      <c r="C47" s="107" t="s">
         <v>746</v>
-      </c>
-      <c r="C47" s="107" t="s">
-        <v>747</v>
       </c>
       <c r="D47" s="107"/>
       <c r="E47" s="107"/>
@@ -47913,10 +48118,10 @@
     </row>
     <row r="48" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="99" t="s">
+        <v>747</v>
+      </c>
+      <c r="B48" s="100" t="s">
         <v>748</v>
-      </c>
-      <c r="B48" s="100" t="s">
-        <v>749</v>
       </c>
       <c r="C48" s="100"/>
       <c r="D48" s="100"/>
@@ -47925,10 +48130,10 @@
     </row>
     <row r="49" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="106" t="s">
+        <v>749</v>
+      </c>
+      <c r="B49" s="107" t="s">
         <v>750</v>
-      </c>
-      <c r="B49" s="107" t="s">
-        <v>751</v>
       </c>
       <c r="C49" s="107"/>
       <c r="D49" s="107"/>
@@ -47937,10 +48142,10 @@
     </row>
     <row r="50" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="99" t="s">
+        <v>751</v>
+      </c>
+      <c r="B50" s="100" t="s">
         <v>752</v>
-      </c>
-      <c r="B50" s="100" t="s">
-        <v>753</v>
       </c>
       <c r="C50" s="100"/>
       <c r="D50" s="100"/>
@@ -47949,13 +48154,13 @@
     </row>
     <row r="51" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="106" t="s">
+        <v>753</v>
+      </c>
+      <c r="B51" s="107" t="s">
         <v>754</v>
       </c>
-      <c r="B51" s="107" t="s">
+      <c r="C51" s="107" t="s">
         <v>755</v>
-      </c>
-      <c r="C51" s="107" t="s">
-        <v>756</v>
       </c>
       <c r="D51" s="107"/>
       <c r="E51" s="107"/>
@@ -47963,13 +48168,13 @@
     </row>
     <row r="52" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="99" t="s">
+        <v>756</v>
+      </c>
+      <c r="B52" s="100" t="s">
         <v>757</v>
       </c>
-      <c r="B52" s="100" t="s">
+      <c r="C52" s="100" t="s">
         <v>758</v>
-      </c>
-      <c r="C52" s="100" t="s">
-        <v>759</v>
       </c>
       <c r="D52" s="100"/>
       <c r="E52" s="100"/>
@@ -47977,10 +48182,10 @@
     </row>
     <row r="53" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="106" t="s">
+        <v>759</v>
+      </c>
+      <c r="B53" s="107" t="s">
         <v>760</v>
-      </c>
-      <c r="B53" s="107" t="s">
-        <v>761</v>
       </c>
       <c r="C53" s="107"/>
       <c r="D53" s="107"/>
@@ -47989,10 +48194,10 @@
     </row>
     <row r="54" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="99" t="s">
+        <v>761</v>
+      </c>
+      <c r="B54" s="100" t="s">
         <v>762</v>
-      </c>
-      <c r="B54" s="100" t="s">
-        <v>763</v>
       </c>
       <c r="C54" s="100"/>
       <c r="D54" s="100"/>
@@ -48009,7 +48214,7 @@
     </row>
     <row r="56" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="248" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B56" s="243"/>
       <c r="C56" s="243"/>
@@ -48019,125 +48224,125 @@
     </row>
     <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="102" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B57" s="103" t="s">
+        <v>764</v>
+      </c>
+      <c r="C57" s="103" t="s">
+        <v>739</v>
+      </c>
+      <c r="D57" s="103" t="s">
         <v>765</v>
-      </c>
-      <c r="C57" s="103" t="s">
-        <v>740</v>
-      </c>
-      <c r="D57" s="103" t="s">
-        <v>766</v>
       </c>
       <c r="E57" s="103"/>
       <c r="F57" s="103"/>
     </row>
     <row r="58" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="99" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B58" s="100" t="s">
+        <v>766</v>
+      </c>
+      <c r="C58" s="100" t="s">
         <v>767</v>
       </c>
-      <c r="C58" s="100" t="s">
+      <c r="D58" s="100" t="s">
         <v>768</v>
-      </c>
-      <c r="D58" s="100" t="s">
-        <v>769</v>
       </c>
       <c r="E58" s="100"/>
       <c r="F58" s="100"/>
     </row>
     <row r="59" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="106" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B59" s="107" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C59" s="107" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D59" s="107" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E59" s="107"/>
       <c r="F59" s="107"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="99" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B60" s="100" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C60" s="100" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D60" s="100" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E60" s="100"/>
       <c r="F60" s="100"/>
     </row>
     <row r="61" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="106" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B61" s="107" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C61" s="107" t="s">
+        <v>771</v>
+      </c>
+      <c r="D61" s="107" t="s">
         <v>772</v>
-      </c>
-      <c r="D61" s="107" t="s">
-        <v>773</v>
       </c>
       <c r="E61" s="107"/>
       <c r="F61" s="107"/>
     </row>
     <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="99" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B62" s="100" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C62" s="100" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D62" s="100" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E62" s="100"/>
       <c r="F62" s="100"/>
     </row>
     <row r="63" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="106" t="s">
+        <v>774</v>
+      </c>
+      <c r="B63" s="107" t="s">
+        <v>766</v>
+      </c>
+      <c r="C63" s="107" t="s">
         <v>775</v>
       </c>
-      <c r="B63" s="107" t="s">
-        <v>767</v>
-      </c>
-      <c r="C63" s="107" t="s">
-        <v>776</v>
-      </c>
       <c r="D63" s="107" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E63" s="107"/>
       <c r="F63" s="107"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="99" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B64" s="100" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C64" s="100" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D64" s="100"/>
       <c r="E64" s="100"/>
@@ -48145,13 +48350,13 @@
     </row>
     <row r="65" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="106" t="s">
+        <v>777</v>
+      </c>
+      <c r="B65" s="107" t="s">
+        <v>766</v>
+      </c>
+      <c r="C65" s="107" t="s">
         <v>778</v>
-      </c>
-      <c r="B65" s="107" t="s">
-        <v>767</v>
-      </c>
-      <c r="C65" s="107" t="s">
-        <v>779</v>
       </c>
       <c r="D65" s="107"/>
       <c r="E65" s="107"/>
@@ -48159,13 +48364,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="99" t="s">
+        <v>779</v>
+      </c>
+      <c r="B66" s="100" t="s">
+        <v>766</v>
+      </c>
+      <c r="C66" s="100" t="s">
         <v>780</v>
-      </c>
-      <c r="B66" s="100" t="s">
-        <v>767</v>
-      </c>
-      <c r="C66" s="100" t="s">
-        <v>781</v>
       </c>
       <c r="D66" s="100"/>
       <c r="E66" s="100"/>
@@ -48181,7 +48386,7 @@
     </row>
     <row r="68" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="248" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B68" s="243"/>
       <c r="C68" s="243"/>
@@ -48203,10 +48408,10 @@
     </row>
     <row r="70" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="99" t="s">
+        <v>782</v>
+      </c>
+      <c r="B70" s="100" t="s">
         <v>783</v>
-      </c>
-      <c r="B70" s="100" t="s">
-        <v>784</v>
       </c>
       <c r="C70" s="100"/>
       <c r="D70" s="100"/>
@@ -48215,10 +48420,10 @@
     </row>
     <row r="71" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="106" t="s">
+        <v>784</v>
+      </c>
+      <c r="B71" s="107" t="s">
         <v>785</v>
-      </c>
-      <c r="B71" s="107" t="s">
-        <v>786</v>
       </c>
       <c r="C71" s="107"/>
       <c r="D71" s="107"/>
@@ -48227,10 +48432,10 @@
     </row>
     <row r="72" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="99" t="s">
+        <v>786</v>
+      </c>
+      <c r="B72" s="100" t="s">
         <v>787</v>
-      </c>
-      <c r="B72" s="100" t="s">
-        <v>788</v>
       </c>
       <c r="C72" s="100"/>
       <c r="D72" s="100"/>
@@ -48239,10 +48444,10 @@
     </row>
     <row r="73" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="106" t="s">
+        <v>788</v>
+      </c>
+      <c r="B73" s="107" t="s">
         <v>789</v>
-      </c>
-      <c r="B73" s="107" t="s">
-        <v>790</v>
       </c>
       <c r="C73" s="107"/>
       <c r="D73" s="107"/>
@@ -48251,10 +48456,10 @@
     </row>
     <row r="74" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="99" t="s">
+        <v>790</v>
+      </c>
+      <c r="B74" s="100" t="s">
         <v>791</v>
-      </c>
-      <c r="B74" s="100" t="s">
-        <v>792</v>
       </c>
       <c r="C74" s="100"/>
       <c r="D74" s="100"/>
@@ -48263,10 +48468,10 @@
     </row>
     <row r="75" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="106" t="s">
+        <v>792</v>
+      </c>
+      <c r="B75" s="107" t="s">
         <v>793</v>
-      </c>
-      <c r="B75" s="107" t="s">
-        <v>794</v>
       </c>
       <c r="C75" s="107"/>
       <c r="D75" s="107"/>
@@ -48275,10 +48480,10 @@
     </row>
     <row r="76" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="99" t="s">
+        <v>794</v>
+      </c>
+      <c r="B76" s="100" t="s">
         <v>795</v>
-      </c>
-      <c r="B76" s="100" t="s">
-        <v>796</v>
       </c>
       <c r="C76" s="100"/>
       <c r="D76" s="100"/>
@@ -48287,10 +48492,10 @@
     </row>
     <row r="77" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="106" t="s">
+        <v>796</v>
+      </c>
+      <c r="B77" s="107" t="s">
         <v>797</v>
-      </c>
-      <c r="B77" s="107" t="s">
-        <v>798</v>
       </c>
       <c r="C77" s="107"/>
       <c r="D77" s="107"/>
@@ -48299,10 +48504,10 @@
     </row>
     <row r="78" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="99" t="s">
+        <v>798</v>
+      </c>
+      <c r="B78" s="100" t="s">
         <v>799</v>
-      </c>
-      <c r="B78" s="100" t="s">
-        <v>800</v>
       </c>
       <c r="C78" s="100"/>
       <c r="D78" s="100"/>
@@ -48319,7 +48524,7 @@
     </row>
     <row r="80" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="248" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B80" s="243"/>
       <c r="C80" s="243"/>
@@ -48341,10 +48546,10 @@
     </row>
     <row r="82" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="99" t="s">
+        <v>801</v>
+      </c>
+      <c r="B82" s="100" t="s">
         <v>802</v>
-      </c>
-      <c r="B82" s="100" t="s">
-        <v>803</v>
       </c>
       <c r="C82" s="100"/>
       <c r="D82" s="100"/>
@@ -48353,10 +48558,10 @@
     </row>
     <row r="83" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="106" t="s">
+        <v>803</v>
+      </c>
+      <c r="B83" s="107" t="s">
         <v>804</v>
-      </c>
-      <c r="B83" s="107" t="s">
-        <v>805</v>
       </c>
       <c r="C83" s="107"/>
       <c r="D83" s="107"/>
@@ -48365,10 +48570,10 @@
     </row>
     <row r="84" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="99" t="s">
+        <v>805</v>
+      </c>
+      <c r="B84" s="100" t="s">
         <v>806</v>
-      </c>
-      <c r="B84" s="100" t="s">
-        <v>807</v>
       </c>
       <c r="C84" s="100"/>
       <c r="D84" s="100"/>
@@ -48377,10 +48582,10 @@
     </row>
     <row r="85" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="106" t="s">
+        <v>807</v>
+      </c>
+      <c r="B85" s="107" t="s">
         <v>808</v>
-      </c>
-      <c r="B85" s="107" t="s">
-        <v>809</v>
       </c>
       <c r="C85" s="107"/>
       <c r="D85" s="107"/>
@@ -48389,10 +48594,10 @@
     </row>
     <row r="86" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="99" t="s">
+        <v>809</v>
+      </c>
+      <c r="B86" s="100" t="s">
         <v>810</v>
-      </c>
-      <c r="B86" s="100" t="s">
-        <v>811</v>
       </c>
       <c r="C86" s="100"/>
       <c r="D86" s="100"/>
@@ -48401,10 +48606,10 @@
     </row>
     <row r="87" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="106" t="s">
+        <v>811</v>
+      </c>
+      <c r="B87" s="107" t="s">
         <v>812</v>
-      </c>
-      <c r="B87" s="107" t="s">
-        <v>813</v>
       </c>
       <c r="C87" s="107"/>
       <c r="D87" s="107"/>
@@ -48413,10 +48618,10 @@
     </row>
     <row r="88" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="99" t="s">
+        <v>813</v>
+      </c>
+      <c r="B88" s="100" t="s">
         <v>814</v>
-      </c>
-      <c r="B88" s="100" t="s">
-        <v>815</v>
       </c>
       <c r="C88" s="100"/>
       <c r="D88" s="100"/>
@@ -48425,10 +48630,10 @@
     </row>
     <row r="89" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="106" t="s">
+        <v>815</v>
+      </c>
+      <c r="B89" s="107" t="s">
         <v>816</v>
-      </c>
-      <c r="B89" s="107" t="s">
-        <v>817</v>
       </c>
       <c r="C89" s="107"/>
       <c r="D89" s="107"/>
@@ -48437,10 +48642,10 @@
     </row>
     <row r="90" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="99" t="s">
+        <v>817</v>
+      </c>
+      <c r="B90" s="100" t="s">
         <v>818</v>
-      </c>
-      <c r="B90" s="100" t="s">
-        <v>819</v>
       </c>
       <c r="C90" s="100"/>
       <c r="D90" s="100"/>
@@ -48449,10 +48654,10 @@
     </row>
     <row r="91" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="106" t="s">
+        <v>819</v>
+      </c>
+      <c r="B91" s="107" t="s">
         <v>820</v>
-      </c>
-      <c r="B91" s="107" t="s">
-        <v>821</v>
       </c>
       <c r="C91" s="107"/>
       <c r="D91" s="107"/>
@@ -48461,10 +48666,10 @@
     </row>
     <row r="92" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="99" t="s">
+        <v>821</v>
+      </c>
+      <c r="B92" s="100" t="s">
         <v>822</v>
-      </c>
-      <c r="B92" s="100" t="s">
-        <v>823</v>
       </c>
       <c r="C92" s="100"/>
       <c r="D92" s="100"/>
@@ -48481,7 +48686,7 @@
     </row>
     <row r="94" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="248" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B94" s="243"/>
       <c r="C94" s="243"/>
@@ -48491,7 +48696,7 @@
     </row>
     <row r="95" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="102" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B95" s="103" t="s">
         <v>510</v>
@@ -48505,13 +48710,13 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="99" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B96" s="100" t="s">
         <v>14</v>
       </c>
       <c r="C96" s="100" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D96" s="100"/>
       <c r="E96" s="100"/>
@@ -48519,7 +48724,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="106" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B97" s="107" t="s">
         <v>27</v>
@@ -48531,7 +48736,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="99" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B98" s="100" t="s">
         <v>279</v>
@@ -48543,7 +48748,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="106" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B99" s="107" t="s">
         <v>259</v>
@@ -48555,10 +48760,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="99" t="s">
+        <v>830</v>
+      </c>
+      <c r="B100" s="100" t="s">
         <v>831</v>
-      </c>
-      <c r="B100" s="100" t="s">
-        <v>832</v>
       </c>
       <c r="C100" s="100"/>
       <c r="D100" s="100"/>
@@ -48567,13 +48772,13 @@
     </row>
     <row r="101" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="106" t="s">
+        <v>832</v>
+      </c>
+      <c r="B101" s="107" t="s">
         <v>833</v>
       </c>
-      <c r="B101" s="107" t="s">
+      <c r="C101" s="107" t="s">
         <v>834</v>
-      </c>
-      <c r="C101" s="107" t="s">
-        <v>835</v>
       </c>
       <c r="D101" s="107"/>
       <c r="E101" s="107"/>
@@ -48581,10 +48786,10 @@
     </row>
     <row r="102" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="99" t="s">
+        <v>835</v>
+      </c>
+      <c r="B102" s="100" t="s">
         <v>836</v>
-      </c>
-      <c r="B102" s="100" t="s">
-        <v>837</v>
       </c>
       <c r="C102" s="100"/>
       <c r="D102" s="100"/>
@@ -48593,7 +48798,7 @@
     </row>
     <row r="103" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="99" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B103" s="100"/>
       <c r="C103" s="100"/>
@@ -48603,7 +48808,7 @@
     </row>
     <row r="104" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="99" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B104" s="100"/>
       <c r="C104" s="100"/>
@@ -48613,10 +48818,10 @@
     </row>
     <row r="105" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="99" t="s">
+        <v>839</v>
+      </c>
+      <c r="B105" s="100" t="s">
         <v>840</v>
-      </c>
-      <c r="B105" s="100" t="s">
-        <v>841</v>
       </c>
       <c r="C105" s="100"/>
       <c r="D105" s="100"/>
@@ -48628,7 +48833,7 @@
         <v>361</v>
       </c>
       <c r="B106" s="107" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C106" s="107"/>
       <c r="D106" s="107"/>
@@ -48637,13 +48842,13 @@
     </row>
     <row r="107" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="99" t="s">
+        <v>842</v>
+      </c>
+      <c r="B107" s="100" t="s">
         <v>843</v>
       </c>
-      <c r="B107" s="100" t="s">
+      <c r="C107" s="100" t="s">
         <v>844</v>
-      </c>
-      <c r="C107" s="100" t="s">
-        <v>845</v>
       </c>
       <c r="D107" s="100"/>
       <c r="E107" s="100"/>
@@ -48651,10 +48856,10 @@
     </row>
     <row r="108" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="106" t="s">
+        <v>845</v>
+      </c>
+      <c r="B108" s="107" t="s">
         <v>846</v>
-      </c>
-      <c r="B108" s="107" t="s">
-        <v>847</v>
       </c>
       <c r="C108" s="107"/>
       <c r="D108" s="107"/>
@@ -48671,7 +48876,7 @@
     </row>
     <row r="110" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="248" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B110" s="243"/>
       <c r="C110" s="243"/>
@@ -48681,7 +48886,7 @@
     </row>
     <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="102" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B111" s="103" t="s">
         <v>510</v>
@@ -48695,10 +48900,10 @@
     </row>
     <row r="112" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="99" t="s">
+        <v>849</v>
+      </c>
+      <c r="B112" s="100" t="s">
         <v>850</v>
-      </c>
-      <c r="B112" s="100" t="s">
-        <v>851</v>
       </c>
       <c r="C112" s="100"/>
       <c r="D112" s="100"/>
@@ -48707,13 +48912,13 @@
     </row>
     <row r="113" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="106" t="s">
+        <v>851</v>
+      </c>
+      <c r="B113" s="107" t="s">
         <v>852</v>
       </c>
-      <c r="B113" s="107" t="s">
+      <c r="C113" s="107" t="s">
         <v>853</v>
-      </c>
-      <c r="C113" s="107" t="s">
-        <v>854</v>
       </c>
       <c r="D113" s="107"/>
       <c r="E113" s="107"/>
@@ -48721,10 +48926,10 @@
     </row>
     <row r="114" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="99" t="s">
+        <v>854</v>
+      </c>
+      <c r="B114" s="100" t="s">
         <v>855</v>
-      </c>
-      <c r="B114" s="100" t="s">
-        <v>856</v>
       </c>
       <c r="C114" s="100"/>
       <c r="D114" s="100"/>
@@ -48733,13 +48938,13 @@
     </row>
     <row r="115" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="106" t="s">
+        <v>856</v>
+      </c>
+      <c r="B115" s="107" t="s">
         <v>857</v>
       </c>
-      <c r="B115" s="107" t="s">
+      <c r="C115" s="107" t="s">
         <v>858</v>
-      </c>
-      <c r="C115" s="107" t="s">
-        <v>859</v>
       </c>
       <c r="D115" s="107"/>
       <c r="E115" s="107"/>
@@ -48747,10 +48952,10 @@
     </row>
     <row r="116" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="99" t="s">
+        <v>859</v>
+      </c>
+      <c r="B116" s="100" t="s">
         <v>860</v>
-      </c>
-      <c r="B116" s="100" t="s">
-        <v>861</v>
       </c>
       <c r="C116" s="100"/>
       <c r="D116" s="100"/>
@@ -48767,7 +48972,7 @@
     </row>
     <row r="118" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="248" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B118" s="243"/>
       <c r="C118" s="243"/>
@@ -48776,8 +48981,8 @@
       <c r="F118" s="243"/>
     </row>
     <row r="119" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="252" t="s">
-        <v>863</v>
+      <c r="A119" s="251" t="s">
+        <v>862</v>
       </c>
       <c r="B119" s="243"/>
       <c r="C119" s="243"/>
@@ -48814,7 +49019,7 @@
         <v>569</v>
       </c>
       <c r="B122" s="107" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C122" s="107"/>
       <c r="D122" s="107"/>
@@ -48838,7 +49043,7 @@
         <v>573</v>
       </c>
       <c r="B124" s="107" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C124" s="107"/>
       <c r="D124" s="107"/>
@@ -48862,7 +49067,7 @@
         <v>577</v>
       </c>
       <c r="B126" s="107" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C126" s="107"/>
       <c r="D126" s="107"/>
@@ -48879,7 +49084,7 @@
     </row>
     <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="248" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B128" s="243"/>
       <c r="C128" s="243"/>
@@ -48889,13 +49094,13 @@
     </row>
     <row r="129" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="102" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B129" s="103" t="s">
+        <v>867</v>
+      </c>
+      <c r="C129" s="103" t="s">
         <v>868</v>
-      </c>
-      <c r="C129" s="103" t="s">
-        <v>869</v>
       </c>
       <c r="D129" s="103" t="s">
         <v>145</v>
@@ -48905,13 +49110,13 @@
     </row>
     <row r="130" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="126" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B130" s="100" t="s">
+        <v>869</v>
+      </c>
+      <c r="C130" s="100" t="s">
         <v>870</v>
-      </c>
-      <c r="C130" s="100" t="s">
-        <v>871</v>
       </c>
       <c r="D130" s="104" t="s">
         <v>424</v>
@@ -48921,13 +49126,13 @@
     </row>
     <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="127" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B131" s="107" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C131" s="107" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D131" s="108" t="s">
         <v>442</v>
@@ -48937,13 +49142,13 @@
     </row>
     <row r="132" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="126" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B132" s="100" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C132" s="100" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D132" s="104" t="s">
         <v>424</v>
@@ -48953,13 +49158,13 @@
     </row>
     <row r="133" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="127" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B133" s="107" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C133" s="107" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D133" s="108" t="s">
         <v>424</v>
@@ -48969,13 +49174,13 @@
     </row>
     <row r="134" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="126" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B134" s="100" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C134" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D134" s="104" t="s">
         <v>424</v>
@@ -48985,13 +49190,13 @@
     </row>
     <row r="135" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="127" t="s">
+        <v>875</v>
+      </c>
+      <c r="B135" s="107" t="s">
         <v>876</v>
       </c>
-      <c r="B135" s="107" t="s">
-        <v>877</v>
-      </c>
       <c r="C135" s="107" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D135" s="113" t="s">
         <v>461</v>
@@ -49001,13 +49206,13 @@
     </row>
     <row r="136" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="126" t="s">
+        <v>877</v>
+      </c>
+      <c r="B136" s="100" t="s">
         <v>878</v>
       </c>
-      <c r="B136" s="100" t="s">
-        <v>879</v>
-      </c>
       <c r="C136" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D136" s="114" t="s">
         <v>461</v>
@@ -49017,13 +49222,13 @@
     </row>
     <row r="137" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="127" t="s">
+        <v>879</v>
+      </c>
+      <c r="B137" s="107" t="s">
         <v>880</v>
       </c>
-      <c r="B137" s="107" t="s">
-        <v>881</v>
-      </c>
       <c r="C137" s="107" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D137" s="108" t="s">
         <v>424</v>
@@ -49033,13 +49238,13 @@
     </row>
     <row r="138" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="126" t="s">
+        <v>881</v>
+      </c>
+      <c r="B138" s="100" t="s">
         <v>882</v>
       </c>
-      <c r="B138" s="100" t="s">
-        <v>883</v>
-      </c>
       <c r="C138" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D138" s="104" t="s">
         <v>424</v>
@@ -49049,13 +49254,13 @@
     </row>
     <row r="139" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="127" t="s">
+        <v>883</v>
+      </c>
+      <c r="B139" s="107" t="s">
         <v>884</v>
       </c>
-      <c r="B139" s="107" t="s">
-        <v>885</v>
-      </c>
       <c r="C139" s="107" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D139" s="107" t="s">
         <v>525</v>
@@ -49065,13 +49270,13 @@
     </row>
     <row r="140" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="126" t="s">
+        <v>885</v>
+      </c>
+      <c r="B140" s="100" t="s">
         <v>886</v>
       </c>
-      <c r="B140" s="100" t="s">
-        <v>887</v>
-      </c>
       <c r="C140" s="100" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D140" s="104" t="s">
         <v>424</v>
@@ -49081,13 +49286,13 @@
     </row>
     <row r="141" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="127" t="s">
+        <v>887</v>
+      </c>
+      <c r="B141" s="107" t="s">
         <v>888</v>
       </c>
-      <c r="B141" s="107" t="s">
-        <v>889</v>
-      </c>
       <c r="C141" s="107" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D141" s="113" t="s">
         <v>461</v>
@@ -49097,13 +49302,13 @@
     </row>
     <row r="142" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="126" t="s">
+        <v>889</v>
+      </c>
+      <c r="B142" s="100" t="s">
         <v>890</v>
       </c>
-      <c r="B142" s="100" t="s">
-        <v>891</v>
-      </c>
       <c r="C142" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D142" s="114" t="s">
         <v>461</v>
@@ -49113,13 +49318,13 @@
     </row>
     <row r="143" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="127" t="s">
+        <v>891</v>
+      </c>
+      <c r="B143" s="107" t="s">
         <v>892</v>
       </c>
-      <c r="B143" s="107" t="s">
-        <v>893</v>
-      </c>
       <c r="C143" s="107" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D143" s="113" t="s">
         <v>461</v>
@@ -49129,13 +49334,13 @@
     </row>
     <row r="144" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="126" t="s">
+        <v>893</v>
+      </c>
+      <c r="B144" s="100" t="s">
         <v>894</v>
       </c>
-      <c r="B144" s="100" t="s">
-        <v>895</v>
-      </c>
       <c r="C144" s="100" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D144" s="114" t="s">
         <v>461</v>
@@ -49145,13 +49350,13 @@
     </row>
     <row r="145" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="127" t="s">
+        <v>895</v>
+      </c>
+      <c r="B145" s="107" t="s">
         <v>896</v>
       </c>
-      <c r="B145" s="107" t="s">
-        <v>897</v>
-      </c>
       <c r="C145" s="107" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D145" s="108" t="s">
         <v>424</v>
@@ -49161,13 +49366,13 @@
     </row>
     <row r="146" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="126" t="s">
+        <v>897</v>
+      </c>
+      <c r="B146" s="100" t="s">
         <v>898</v>
       </c>
-      <c r="B146" s="100" t="s">
-        <v>899</v>
-      </c>
       <c r="C146" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D146" s="100" t="s">
         <v>525</v>
@@ -49177,13 +49382,13 @@
     </row>
     <row r="147" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="127" t="s">
+        <v>899</v>
+      </c>
+      <c r="B147" s="107" t="s">
         <v>900</v>
       </c>
-      <c r="B147" s="107" t="s">
-        <v>901</v>
-      </c>
       <c r="C147" s="107" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D147" s="107" t="s">
         <v>525</v>
@@ -49193,13 +49398,13 @@
     </row>
     <row r="148" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="126" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B148" s="100" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C148" s="100" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D148" s="114" t="s">
         <v>461</v>
@@ -49209,13 +49414,13 @@
     </row>
     <row r="149" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="127" t="s">
+        <v>902</v>
+      </c>
+      <c r="B149" s="107" t="s">
         <v>903</v>
       </c>
-      <c r="B149" s="107" t="s">
-        <v>904</v>
-      </c>
       <c r="C149" s="107" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D149" s="113" t="s">
         <v>461</v>
@@ -49225,13 +49430,13 @@
     </row>
     <row r="150" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="126" t="s">
+        <v>904</v>
+      </c>
+      <c r="B150" s="100" t="s">
         <v>905</v>
       </c>
-      <c r="B150" s="100" t="s">
-        <v>906</v>
-      </c>
       <c r="C150" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D150" s="104" t="s">
         <v>424</v>
@@ -49249,7 +49454,7 @@
     </row>
     <row r="152" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="248" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B152" s="243"/>
       <c r="C152" s="243"/>
@@ -49259,10 +49464,10 @@
     </row>
     <row r="153" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="102" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B153" s="103" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C153" s="103" t="s">
         <v>510</v>
@@ -49275,13 +49480,13 @@
     </row>
     <row r="154" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="131" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B154" s="132" t="s">
+        <v>907</v>
+      </c>
+      <c r="C154" s="132" t="s">
         <v>908</v>
-      </c>
-      <c r="C154" s="132" t="s">
-        <v>909</v>
       </c>
       <c r="D154" s="133" t="s">
         <v>424</v>
@@ -49291,13 +49496,13 @@
     </row>
     <row r="155" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="131" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B155" s="132" t="s">
+        <v>909</v>
+      </c>
+      <c r="C155" s="132" t="s">
         <v>910</v>
-      </c>
-      <c r="C155" s="132" t="s">
-        <v>911</v>
       </c>
       <c r="D155" s="133" t="s">
         <v>424</v>
@@ -49307,7 +49512,7 @@
     </row>
     <row r="156" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="248" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B156" s="243"/>
       <c r="C156" s="243"/>
@@ -49317,10 +49522,10 @@
     </row>
     <row r="157" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="102" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B157" s="103" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C157" s="103" t="s">
         <v>294</v>
@@ -49331,13 +49536,13 @@
     </row>
     <row r="158" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="134" t="s">
+        <v>913</v>
+      </c>
+      <c r="B158" s="135" t="s">
         <v>914</v>
       </c>
-      <c r="B158" s="135" t="s">
+      <c r="C158" s="135" t="s">
         <v>915</v>
-      </c>
-      <c r="C158" s="135" t="s">
-        <v>916</v>
       </c>
       <c r="D158" s="135"/>
       <c r="E158" s="135"/>
@@ -49345,13 +49550,13 @@
     </row>
     <row r="159" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="134" t="s">
+        <v>916</v>
+      </c>
+      <c r="B159" s="135" t="s">
         <v>917</v>
       </c>
-      <c r="B159" s="135" t="s">
-        <v>918</v>
-      </c>
       <c r="C159" s="135" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D159" s="135"/>
       <c r="E159" s="135"/>
@@ -49359,13 +49564,13 @@
     </row>
     <row r="160" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="134" t="s">
+        <v>918</v>
+      </c>
+      <c r="B160" s="135" t="s">
         <v>919</v>
       </c>
-      <c r="B160" s="135" t="s">
-        <v>920</v>
-      </c>
       <c r="C160" s="135" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D160" s="135"/>
       <c r="E160" s="135"/>
@@ -49373,13 +49578,13 @@
     </row>
     <row r="161" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="106" t="s">
+        <v>920</v>
+      </c>
+      <c r="B161" s="107" t="s">
         <v>921</v>
       </c>
-      <c r="B161" s="107" t="s">
-        <v>922</v>
-      </c>
       <c r="C161" s="107" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D161" s="107"/>
       <c r="E161" s="107"/>
@@ -49387,13 +49592,13 @@
     </row>
     <row r="162" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="99" t="s">
+        <v>922</v>
+      </c>
+      <c r="B162" s="100" t="s">
         <v>923</v>
       </c>
-      <c r="B162" s="100" t="s">
+      <c r="C162" s="100" t="s">
         <v>924</v>
-      </c>
-      <c r="C162" s="100" t="s">
-        <v>925</v>
       </c>
       <c r="D162" s="100"/>
       <c r="E162" s="100"/>
@@ -49401,10 +49606,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A118:F118"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
@@ -49421,6 +49622,10 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2A579610B26AACB496A3B35CE417A1A0C4F31653" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2FD118E5273BD980398C52F038A5143670CB433C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4672,8 +4672,8 @@
     <col min="13" max="13" width="14.7109375" style="138" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="138" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="138" customWidth="1"/>
-    <col min="16" max="65" width="8.7109375" style="138" customWidth="1"/>
-    <col min="66" max="16384" width="8.7109375" style="138"/>
+    <col min="16" max="66" width="8.7109375" style="138" customWidth="1"/>
+    <col min="67" max="16384" width="8.7109375" style="138"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -8787,11 +8787,11 @@
       </c>
       <c r="F21" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A21,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A21,TableInventory[Item ID],0)),0)</f>
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="G21" s="31">
         <f t="shared" si="1"/>
-        <v>-727.70098400000006</v>
+        <v>-827.70098400000006</v>
       </c>
       <c r="H21" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -8889,11 +8889,11 @@
       </c>
       <c r="F24" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A24,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A24,TableInventory[Item ID],0)),0)</f>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="G24" s="31">
         <f t="shared" si="1"/>
-        <v>-2303.2592000000004</v>
+        <v>-1812.2592000000004</v>
       </c>
       <c r="H24" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -9406,11 +9406,11 @@
       </c>
       <c r="F36" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A36,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A36,TableInventory[Item ID],0)),0)</f>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G36" s="31">
         <f t="shared" si="1"/>
-        <v>-157.47227800000002</v>
+        <v>-187.47227800000002</v>
       </c>
       <c r="H36" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A36)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A36)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A36)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A36)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A36)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A36)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A36)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A36)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A36)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A36)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A36)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A36)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A36)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A36)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A36)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A36)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A36)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A36)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A36)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A36)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A36)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A36)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A36)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A36)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10325,11 +10325,11 @@
       </c>
       <c r="F61" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A61,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A61,TableInventory[Item ID],0)),0)</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G61" s="31">
         <f t="shared" si="4"/>
-        <v>-434415.07999999996</v>
+        <v>-234415.07999999996</v>
       </c>
       <c r="H61" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10765,11 +10765,11 @@
       </c>
       <c r="F74" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A74,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A74,TableInventory[Item ID],0)),0)</f>
-        <v>1275</v>
+        <v>975</v>
       </c>
       <c r="G74" s="31">
         <f t="shared" si="4"/>
-        <v>-405.95608384000025</v>
+        <v>-705.95608384000025</v>
       </c>
       <c r="H74" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A74)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A74)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A74)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A74)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A74)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A74)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A74)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A74)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A74)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A74)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A74)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A74)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A74)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A74)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A74)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A74)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10901,11 +10901,11 @@
       </c>
       <c r="F78" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A78,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A78,TableInventory[Item ID],0)),0)</f>
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="G78" s="31">
         <f t="shared" ref="G78:G109" si="7">F78-E78</f>
-        <v>54.252281600000003</v>
+        <v>18.252281600000003</v>
       </c>
       <c r="H78" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A78)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A78)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A78)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A78)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A78)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A78)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A78)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A78)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A78)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A78)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A78)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A78)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A78)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A78)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A78)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A78)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A78)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A78)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A78)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A78)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A78)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A78)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A78)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A78)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -12009,11 +12009,11 @@
       </c>
       <c r="F114" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A114,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A114,TableInventory[Item ID],0)),0)</f>
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="G114" s="22">
         <f t="shared" si="8"/>
-        <v>556.58431740000003</v>
+        <v>520.58431740000003</v>
       </c>
       <c r="H114" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A114)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A114)&gt;0)*($H$101&gt;0),$C$101&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$102,TableBOM[Item ID],$A114)&gt;0)*($H$102&gt;0),$C$102&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$103,TableBOM[Item ID],$A114)&gt;0)*($H$103&gt;0),$C$103&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$104,TableBOM[Item ID],$A114)&gt;0)*($H$104&gt;0),$C$104&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A114)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A114)&gt;0)*($H$101&gt;0),$C$101&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$102,TableBOM[Item ID],$A114)&gt;0)*($H$102&gt;0),$C$102&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$103,TableBOM[Item ID],$A114)&gt;0)*($H$103&gt;0),$C$103&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$104,TableBOM[Item ID],$A114)&gt;0)*($H$104&gt;0),$C$104&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A114)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A114)&gt;0)*($H$101&gt;0),$C$101&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$102,TableBOM[Item ID],$A114)&gt;0)*($H$102&gt;0),$C$102&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$103,TableBOM[Item ID],$A114)&gt;0)*($H$103&gt;0),$C$103&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$104,TableBOM[Item ID],$A114)&gt;0)*($H$104&gt;0),$C$104&amp;", ",""))-2),"")</f>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="H119" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A114,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A114,TableInventory[Item ID],0)),0)</f>
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="I119" s="165">
         <v>6.38</v>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="F124" s="164">
         <f t="shared" si="10"/>
-        <v>33.200000000000003</v>
+        <v>31.1</v>
       </c>
       <c r="G124" s="22" t="str">
         <f t="shared" si="11"/>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="H126" s="33">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A121,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A121,TableInventory[Item ID],0)),0)</f>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="I126" s="165">
         <v>1.6</v>
@@ -35590,18 +35590,18 @@
         <v>623</v>
       </c>
       <c r="G7" s="37">
-        <v>1413</v>
+        <v>1513</v>
       </c>
       <c r="H7" s="38">
         <f t="shared" si="0"/>
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="I7" s="37">
         <v>60</v>
       </c>
       <c r="J7" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>81875</v>
+        <v>64994</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35621,19 +35621,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="37">
-        <v>685</v>
+        <v>1276</v>
       </c>
       <c r="G8" s="37">
-        <v>685</v>
+        <v>785</v>
       </c>
       <c r="H8" s="38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="I8" s="37"/>
       <c r="J8" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>0</v>
+        <v>61375</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36034,16 +36034,16 @@
         <v>210</v>
       </c>
       <c r="G22" s="37">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="H22" s="38">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A22,TableBOM[Per 1000 Units])=0,"-",ROUND((H22+I22)/(AVERAGEIF(TableBOM[Item ID],A22,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>336669</v>
+        <v>280557</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36897,19 +36897,19 @@
         <v>70000</v>
       </c>
       <c r="F46" s="37">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="G46" s="37">
         <v>170000</v>
       </c>
       <c r="H46" s="38">
         <f t="shared" ref="H46:H77" si="2">E46+F46-G46</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="I46" s="37"/>
       <c r="J46" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])=0,"-",ROUND((H46+I46)/(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K46" s="74"/>
       <c r="L46" s="74"/>
@@ -37390,16 +37390,16 @@
         <v>1275</v>
       </c>
       <c r="G59" s="37">
-        <v>301</v>
+        <v>601</v>
       </c>
       <c r="H59" s="38">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>975</v>
       </c>
       <c r="I59" s="37"/>
       <c r="J59" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A59,TableBOM[Per 1000 Units])=0,"-",ROUND((H59+I59)/(AVERAGEIF(TableBOM[Item ID],A59,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>388434</v>
+        <v>297038</v>
       </c>
       <c r="K59" s="74"/>
       <c r="L59" s="74"/>
@@ -37542,16 +37542,16 @@
         <v>0</v>
       </c>
       <c r="G63" s="37">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="H63" s="38">
         <f t="shared" si="2"/>
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="I63" s="37"/>
       <c r="J63" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A63,TableBOM[Per 1000 Units])=0,"-",ROUND((H63+I63)/(AVERAGEIF(TableBOM[Item ID],A63,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>1539569</v>
+        <v>1440773</v>
       </c>
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
@@ -38257,14 +38257,14 @@
         <v>0</v>
       </c>
       <c r="F82" s="37">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="G82" s="37">
         <v>5</v>
       </c>
       <c r="H82" s="38">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="I82" s="37"/>
       <c r="J82" s="37" t="str">
@@ -45845,14 +45845,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -49692,6 +49692,7 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A156:F156"/>
@@ -49700,7 +49701,6 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A22:F22"/>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2FD118E5273BD980398C52F038A5143670CB433C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEE6CE1-2821-47C2-88EA-1FDA8EEC944E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4166,12 +4166,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="36" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4181,19 +4194,6 @@
     <xf numFmtId="0" fontId="42" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4215,6 +4215,9 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4222,9 +4225,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4708,22 +4708,22 @@
     </row>
     <row r="2" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="135"/>
-      <c r="B2" s="238" t="s">
+      <c r="B2" s="232" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="D2" s="231"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="231"/>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
-      <c r="M2" s="231"/>
-      <c r="N2" s="231"/>
-      <c r="O2" s="231"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="233"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="M2" s="233"/>
+      <c r="N2" s="233"/>
+      <c r="O2" s="233"/>
       <c r="P2" s="135"/>
       <c r="Q2" s="135"/>
       <c r="R2" s="135"/>
@@ -4741,25 +4741,25 @@
     </row>
     <row r="3" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="135"/>
-      <c r="B3" s="230" t="s">
+      <c r="B3" s="238" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="233"/>
-      <c r="H3" s="235">
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="235"/>
+      <c r="H3" s="240">
         <f ca="1">TODAY()-1</f>
         <v>46196</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="M3" s="231"/>
-      <c r="N3" s="231"/>
-      <c r="O3" s="231"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
+      <c r="M3" s="233"/>
+      <c r="N3" s="233"/>
+      <c r="O3" s="233"/>
       <c r="P3" s="135"/>
       <c r="Q3" s="135"/>
       <c r="R3" s="135"/>
@@ -4807,24 +4807,24 @@
     </row>
     <row r="5" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="135"/>
-      <c r="B5" s="237" t="s">
+      <c r="B5" s="236" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="231"/>
+      <c r="C5" s="233"/>
       <c r="D5" s="140" t="s">
         <v>198</v>
       </c>
       <c r="E5" s="140"/>
       <c r="F5" s="141"/>
-      <c r="G5" s="237" t="s">
+      <c r="G5" s="236" t="s">
         <v>199</v>
       </c>
-      <c r="H5" s="231"/>
+      <c r="H5" s="233"/>
       <c r="I5" s="142"/>
-      <c r="J5" s="237" t="s">
+      <c r="J5" s="236" t="s">
         <v>200</v>
       </c>
-      <c r="K5" s="231"/>
+      <c r="K5" s="233"/>
       <c r="L5" s="172"/>
       <c r="M5" s="143" t="s">
         <v>201</v>
@@ -4848,28 +4848,28 @@
     </row>
     <row r="6" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="135"/>
-      <c r="B6" s="234">
+      <c r="B6" s="239">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$H$3:$H$8963)</f>
         <v>18480</v>
       </c>
-      <c r="C6" s="231"/>
+      <c r="C6" s="233"/>
       <c r="D6" s="144">
         <f>SUMIF($B$11:$B$63,"TUBE",$H$11:$H$63)</f>
         <v>258034</v>
       </c>
-      <c r="E6" s="234"/>
-      <c r="F6" s="231"/>
+      <c r="E6" s="239"/>
+      <c r="F6" s="233"/>
       <c r="G6" s="145">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$F$3:$F$8963&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8963,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8963)))*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),"-")</f>
         <v>2.469686432221584E-2</v>
       </c>
       <c r="H6" s="145"/>
       <c r="I6" s="142"/>
-      <c r="J6" s="234">
+      <c r="J6" s="239">
         <f>SUMIF($B$11:$B$63,"TUBE",$K$11:$K$63)</f>
         <v>384118</v>
       </c>
-      <c r="K6" s="231"/>
+      <c r="K6" s="233"/>
       <c r="L6" s="146"/>
       <c r="M6" s="177" t="s">
         <v>31</v>
@@ -4897,19 +4897,19 @@
     </row>
     <row r="7" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="135"/>
-      <c r="B7" s="236" t="s">
+      <c r="B7" s="241" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="231"/>
+      <c r="C7" s="233"/>
       <c r="D7" s="147" t="s">
         <v>205</v>
       </c>
       <c r="E7" s="147"/>
       <c r="F7" s="148"/>
-      <c r="G7" s="236" t="s">
+      <c r="G7" s="241" t="s">
         <v>206</v>
       </c>
-      <c r="H7" s="231"/>
+      <c r="H7" s="233"/>
       <c r="I7" s="149"/>
       <c r="J7" s="148" t="s">
         <v>200</v>
@@ -4945,28 +4945,28 @@
     </row>
     <row r="8" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="135"/>
-      <c r="B8" s="239">
+      <c r="B8" s="237">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8963=MAX(Production_Log!$A$3:$A$8963))*(Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$H$3:$H$8963)</f>
         <v>7705</v>
       </c>
-      <c r="C8" s="231"/>
+      <c r="C8" s="233"/>
       <c r="D8" s="150">
         <f>SUMIF($B$11:$B$63,"PET",$H$11:$H$63)</f>
         <v>108790</v>
       </c>
-      <c r="E8" s="239"/>
-      <c r="F8" s="231"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="233"/>
       <c r="G8" s="151">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*Production_Log!$I$3:$I$8963)/SUMPRODUCT((Production_Log!$B$3:$B$8963="PF Machine")*(Production_Log!$H$3:$H$8963+Production_Log!$I$3:$I$8963)),0)</f>
         <v>6.8658505264960187E-2</v>
       </c>
       <c r="H8" s="151"/>
       <c r="I8" s="149"/>
-      <c r="J8" s="239">
+      <c r="J8" s="237">
         <f>SUMIF($B$11:$B$63,"PET",$K$11:$K$63)</f>
         <v>133480</v>
       </c>
-      <c r="K8" s="231"/>
+      <c r="K8" s="233"/>
       <c r="L8" s="152"/>
       <c r="M8" s="156" t="str">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,2),$U$9:$U$23,0)),"")</f>
@@ -4997,19 +4997,19 @@
     </row>
     <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="135"/>
-      <c r="B9" s="240" t="s">
+      <c r="B9" s="230" t="s">
         <v>207</v>
       </c>
-      <c r="C9" s="241"/>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="231"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="231"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="231"/>
+      <c r="I9" s="231"/>
+      <c r="J9" s="231"/>
+      <c r="K9" s="231"/>
+      <c r="L9" s="231"/>
       <c r="M9" s="156" t="str">
         <f>IFERROR(INDEX($S$9:$S$23,MATCH(LARGE($U$9:$U$23,3),$U$9:$U$23,0)),"")</f>
         <v>Changeover</v>
@@ -8787,11 +8787,11 @@
       </c>
       <c r="F21" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A21,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A21,TableInventory[Item ID],0)),0)</f>
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="G21" s="31">
         <f t="shared" si="1"/>
-        <v>-827.70098400000006</v>
+        <v>-887.70098400000006</v>
       </c>
       <c r="H21" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A21)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A21)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A21)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A21)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A21)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A21)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A21)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A21)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -10904,7 +10904,7 @@
         <v>525</v>
       </c>
       <c r="G78" s="31">
-        <f t="shared" ref="G78:G109" si="7">F78-E78</f>
+        <f t="shared" ref="G78:G95" si="7">F78-E78</f>
         <v>18.252281600000003</v>
       </c>
       <c r="H78" s="28" t="str">
@@ -18745,7 +18745,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="203" t="str">
-        <f t="shared" ref="J131:J162" si="4">IFERROR(I131/(H131+I131),"")</f>
+        <f t="shared" ref="J131:J161" si="4">IFERROR(I131/(H131+I131),"")</f>
         <v/>
       </c>
       <c r="K131" s="201"/>
@@ -35380,7 +35380,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" style="66" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="66" customWidth="1"/>
@@ -35395,13 +35395,13 @@
       <c r="A1" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-      <c r="H1" s="241"/>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
       <c r="I1" s="68" t="s">
         <v>1</v>
       </c>
@@ -35596,12 +35596,10 @@
         <f t="shared" si="0"/>
         <v>325</v>
       </c>
-      <c r="I7" s="37">
-        <v>60</v>
-      </c>
+      <c r="I7" s="37"/>
       <c r="J7" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>64994</v>
+        <v>54865</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38117,7 +38115,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="38">
-        <f t="shared" ref="H78:H109" si="3">E78+F78-G78</f>
+        <f t="shared" ref="H78:H94" si="3">E78+F78-G78</f>
         <v>5</v>
       </c>
       <c r="I78" s="37"/>
@@ -45844,15 +45842,15 @@
     </sortState>
   </autoFilter>
   <mergeCells count="9">
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A81:K81"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A81:K81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -47566,7 +47564,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="251" t="s">
         <v>618</v>
       </c>
       <c r="B1" s="243"/>
@@ -47576,7 +47574,7 @@
       <c r="F1" s="243"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="253" t="s">
+      <c r="A2" s="254" t="s">
         <v>619</v>
       </c>
       <c r="B2" s="243"/>
@@ -47604,7 +47602,7 @@
       <c r="F4" s="243"/>
     </row>
     <row r="5" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="251" t="s">
+      <c r="A5" s="252" t="s">
         <v>621</v>
       </c>
       <c r="B5" s="243"/>
@@ -47830,34 +47828,34 @@
       <c r="F17" s="124"/>
     </row>
     <row r="18" spans="1:6" s="92" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="251" t="s">
+      <c r="A18" s="252" t="s">
         <v>678</v>
       </c>
-      <c r="B18" s="252"/>
-      <c r="C18" s="252"/>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="252"/>
+      <c r="B18" s="253"/>
+      <c r="C18" s="253"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
+      <c r="F18" s="253"/>
     </row>
     <row r="19" spans="1:6" s="92" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="251" t="s">
+      <c r="A19" s="252" t="s">
         <v>679</v>
       </c>
-      <c r="B19" s="252"/>
-      <c r="C19" s="252"/>
-      <c r="D19" s="252"/>
-      <c r="E19" s="252"/>
-      <c r="F19" s="252"/>
+      <c r="B19" s="253"/>
+      <c r="C19" s="253"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
+      <c r="F19" s="253"/>
     </row>
     <row r="20" spans="1:6" s="92" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="251" t="s">
+      <c r="A20" s="252" t="s">
         <v>680</v>
       </c>
-      <c r="B20" s="252"/>
-      <c r="C20" s="252"/>
-      <c r="D20" s="252"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="252"/>
+      <c r="B20" s="253"/>
+      <c r="C20" s="253"/>
+      <c r="D20" s="253"/>
+      <c r="E20" s="253"/>
+      <c r="F20" s="253"/>
     </row>
     <row r="21" spans="1:6" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="129"/>
@@ -49066,7 +49064,7 @@
       <c r="F118" s="243"/>
     </row>
     <row r="119" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="251" t="s">
+      <c r="A119" s="252" t="s">
         <v>850</v>
       </c>
       <c r="B119" s="243"/>
@@ -49691,6 +49689,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
@@ -49707,10 +49709,6 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A118:F118"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CC56081DEA7444EEFC24FC4E23EA7E3CC918A9E0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8C13585F4C1F3F7ABD522D3E7A893947FD78BDD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5115" yWindow="3015" windowWidth="15375" windowHeight="7785" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3510,6 +3510,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -3522,13 +3529,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -3570,20 +3570,20 @@
     </border>
   </borders>
   <cellStyleXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24"/>
-    <xf numFmtId="172" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23"/>
+    <xf numFmtId="172" fontId="24" fillId="0" borderId="23"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="24"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23"/>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="23"/>
   </cellStyleXfs>
   <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -4122,10 +4122,10 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4187,48 +4187,48 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="41" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="41" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="41" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="41" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="36" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="36" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="36" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -4240,25 +4240,25 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4706,8 +4706,8 @@
     <col min="13" max="13" width="14.7109375" style="138" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="138" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="138" customWidth="1"/>
-    <col min="16" max="71" width="8.7109375" style="138" customWidth="1"/>
-    <col min="72" max="16384" width="8.7109375" style="138"/>
+    <col min="16" max="72" width="8.7109375" style="138" customWidth="1"/>
+    <col min="73" max="16384" width="8.7109375" style="138"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4998,7 +4998,7 @@
       <c r="I8" s="149"/>
       <c r="J8" s="241">
         <f>SUMIF($B$11:$B$64,"PET",$K$11:$K$64)</f>
-        <v>133480</v>
+        <v>175848</v>
       </c>
       <c r="K8" s="233"/>
       <c r="L8" s="152"/>
@@ -5845,7 +5845,7 @@
         <v>0.93840000000000001</v>
       </c>
       <c r="K22" s="224">
-        <v>0</v>
+        <v>12928</v>
       </c>
       <c r="L22" s="226"/>
       <c r="M22" s="135"/>
@@ -5947,7 +5947,7 @@
         <v>0.43342284125226094</v>
       </c>
       <c r="K24" s="224">
-        <v>98440</v>
+        <v>127880</v>
       </c>
       <c r="L24" s="226"/>
       <c r="M24" s="135"/>
@@ -6148,7 +6148,7 @@
       <c r="J28" s="230"/>
       <c r="K28" s="230">
         <f>SUM(K21:K27)</f>
-        <v>133480</v>
+        <v>175848</v>
       </c>
       <c r="L28" s="230"/>
       <c r="M28" s="135"/>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="F24" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A24,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A24,TableInventory[Item ID],0)),0)</f>
-        <v>316</v>
+        <v>879</v>
       </c>
       <c r="G24" s="31">
         <f t="shared" si="1"/>
-        <v>-1675.1936000000001</v>
+        <v>-1112.1936000000001</v>
       </c>
       <c r="H24" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A24)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A24)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A24)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A24)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A24)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A24)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A24)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A24)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -12039,11 +12039,11 @@
       </c>
       <c r="F61" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A61,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A61,TableInventory[Item ID],0)),0)</f>
-        <v>160000</v>
+        <v>360000</v>
       </c>
       <c r="G61" s="31">
         <f t="shared" si="4"/>
-        <v>-230704</v>
+        <v>-30704</v>
       </c>
       <c r="H61" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A61)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A61)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A61)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A61)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A61)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A61)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A61)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A61)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -12141,11 +12141,11 @@
       </c>
       <c r="F64" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A64,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A64,TableInventory[Item ID],0)),0)</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G64" s="31">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H64" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A64)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A64)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A64)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A64)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A64)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A64)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A64)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A64)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A64)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A64)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A64)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A64)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A64)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A64)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A64)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A64)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A64)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A64)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A64)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A64)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A64)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A64)&gt;0)*($H$8&gt;0),$C$8&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$9,TableBOM[Item ID],$A64)&gt;0)*($H$9&gt;0),$C$9&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$10,TableBOM[Item ID],$A64)&gt;0)*($H$10&gt;0),$C$10&amp;", ",""))-2),"")</f>
@@ -38197,21 +38197,21 @@
         <v>0</v>
       </c>
       <c r="F8" s="37">
-        <v>1276</v>
+        <v>1839</v>
       </c>
       <c r="G8" s="37">
         <v>985</v>
       </c>
       <c r="H8" s="38">
         <f t="shared" si="0"/>
-        <v>291</v>
+        <v>854</v>
       </c>
       <c r="I8" s="37">
         <v>25</v>
       </c>
       <c r="J8" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>39500</v>
+        <v>109875</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39475,19 +39475,19 @@
         <v>70000</v>
       </c>
       <c r="F46" s="37">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="G46" s="37">
         <v>210000</v>
       </c>
       <c r="H46" s="38">
         <f t="shared" ref="H46:H77" si="2">E46+F46-G46</f>
-        <v>160000</v>
+        <v>360000</v>
       </c>
       <c r="I46" s="37"/>
       <c r="J46" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])=0,"-",ROUND((H46+I46)/(AVERAGEIF(TableBOM[Item ID],A46,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>160000</v>
+        <v>360000</v>
       </c>
       <c r="K46" s="74"/>
       <c r="L46" s="74"/>
@@ -39586,22 +39586,22 @@
         <v>80</v>
       </c>
       <c r="E49" s="37">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="37">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G49" s="37">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I49" s="37"/>
       <c r="J49" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A49,TableBOM[Per 1000 Units])=0,"-",ROUND((H49+I49)/(AVERAGEIF(TableBOM[Item ID],A49,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="K49" s="75"/>
       <c r="L49" s="75"/>
@@ -48437,14 +48437,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -52300,7 +52300,6 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A156:F156"/>
@@ -52309,6 +52308,7 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A22:F22"/>

--- a/Tubex_v10_30.xlsx
+++ b/Tubex_v10_30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_69C085BA9A2C5D31644DCB0CE83433013A505F1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F43D94C2FB251B11FC84CE0220F7C3C31728CFB6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="3015" windowWidth="15375" windowHeight="7785" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tubex_Dashboard" sheetId="1" r:id="rId1"/>
@@ -4734,8 +4734,8 @@
     <col min="13" max="13" width="14.7109375" style="136" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="136" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="136" customWidth="1"/>
-    <col min="16" max="81" width="8.7109375" style="136" customWidth="1"/>
-    <col min="82" max="16384" width="8.7109375" style="136"/>
+    <col min="16" max="82" width="8.7109375" style="136" customWidth="1"/>
+    <col min="83" max="16384" width="8.7109375" style="136"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4929,7 +4929,7 @@
       <c r="I6" s="140"/>
       <c r="J6" s="238">
         <f>SUMIF($B$11:$B$64,"TUBE",$K$11:$K$64)</f>
-        <v>0</v>
+        <v>76160</v>
       </c>
       <c r="K6" s="235"/>
       <c r="L6" s="144"/>
@@ -5416,7 +5416,9 @@
         <f t="shared" si="2"/>
         <v>0.29248067624527674</v>
       </c>
-      <c r="K14" s="226"/>
+      <c r="K14" s="226">
+        <v>76160</v>
+      </c>
       <c r="L14" s="228"/>
       <c r="M14" s="152" t="s">
         <v>39</v>
@@ -5588,7 +5590,7 @@
       <c r="J17" s="232"/>
       <c r="K17" s="232">
         <f>SUM(K11:K16)</f>
-        <v>0</v>
+        <v>76160</v>
       </c>
       <c r="L17" s="232"/>
       <c r="P17" s="133"/>
@@ -10446,11 +10448,11 @@
       </c>
       <c r="F19" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A19,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A19,TableInventory[Item ID],0)),0)</f>
-        <v>335</v>
+        <v>255</v>
       </c>
       <c r="G19" s="31">
         <f t="shared" si="1"/>
-        <v>-829.90109119999988</v>
+        <v>-909.90109119999988</v>
       </c>
       <c r="H19" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A19)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A19)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A19)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A19)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A19)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A19)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A19)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A19)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A19)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A19)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A19)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A19)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A19)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A19)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A19)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A19)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A19)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A19)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))-2),"")</f>
@@ -10548,11 +10550,11 @@
       </c>
       <c r="F22" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A22,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A22,TableInventory[Item ID],0)),0)</f>
-        <v>275</v>
+        <v>135</v>
       </c>
       <c r="G22" s="31">
         <f t="shared" si="1"/>
-        <v>-1073.2128</v>
+        <v>-1213.2128</v>
       </c>
       <c r="H22" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A22)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A22)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A22)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A22)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A22)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A22)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A22)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A22)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A22)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A22)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A22)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A22)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A22)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A22)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A22)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A22)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A22)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A22)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))-2),"")</f>
@@ -10757,11 +10759,11 @@
       </c>
       <c r="F27" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A27,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A27,TableInventory[Item ID],0)),0)</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G27" s="31">
         <f t="shared" si="1"/>
-        <v>30.740335680000015</v>
+        <v>5.7403356800000154</v>
       </c>
       <c r="H27" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A27)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A27)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A27)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A27)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A27)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A27)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A27)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A27)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A27)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A27)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A27)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A27)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A27)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A27)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A27)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A27)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A27)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A27)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))-2),"")</f>
@@ -10769,7 +10771,7 @@
       </c>
       <c r="I27" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>OK</v>
+        <v>LOW</v>
       </c>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -12594,11 +12596,11 @@
       </c>
       <c r="F77" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A77,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A77,TableInventory[Item ID],0)),0)</f>
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G77" s="31">
         <f t="shared" si="7"/>
-        <v>173.35</v>
+        <v>148.35</v>
       </c>
       <c r="H77" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A77)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A77)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A77)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A77)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A77)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A77)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A77)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A77)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A77)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A77)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A77)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A77)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A77)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A77)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A77)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A77)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A77)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A77)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))-2),"")</f>
@@ -13138,11 +13140,11 @@
       </c>
       <c r="F93" s="27">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A93,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A93,TableInventory[Item ID],0)),0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G93" s="31">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H93" s="28" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A93)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A93)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A93)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A93)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A93)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A93)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A93)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A93)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A93)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A93)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A93)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A93)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$3,TableBOM[Item ID],$A93)&gt;0)*($H$3&gt;0),$C$3&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$4,TableBOM[Item ID],$A93)&gt;0)*($H$4&gt;0),$C$4&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$5,TableBOM[Item ID],$A93)&gt;0)*($H$5&gt;0),$C$5&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$6,TableBOM[Item ID],$A93)&gt;0)*($H$6&gt;0),$C$6&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$7,TableBOM[Item ID],$A93)&gt;0)*($H$7&gt;0),$C$7&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$8,TableBOM[Item ID],$A93)&gt;0)*($H$8&gt;0),$C$8&amp;", ",""))-2),"")</f>
@@ -13735,11 +13737,11 @@
       </c>
       <c r="F114" s="32">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A114,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[Work In Process],MATCH(A114,TableInventory[Item ID],0)),0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G114" s="22">
         <f t="shared" si="9"/>
-        <v>1.6464097499999999</v>
+        <v>-1.3535902500000001</v>
       </c>
       <c r="H114" s="45" t="str">
         <f>IF(LEN(IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A114)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A114)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A114)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A114)&gt;0)*($H$101&gt;0),$C$101&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$102,TableBOM[Item ID],$A114)&gt;0)*($H$102&gt;0),$C$102&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$103,TableBOM[Item ID],$A114)&gt;0)*($H$103&gt;0),$C$103&amp;", ",""))&gt;1,LEFT(IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A114)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A114)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A114)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A114)&gt;0)*($H$101&gt;0),$C$101&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$102,TableBOM[Item ID],$A114)&gt;0)*($H$102&gt;0),$C$102&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$103,TableBOM[Item ID],$A114)&gt;0)*($H$103&gt;0),$C$103&amp;", ",""),LEN(IF((COUNTIFS(TableBOM[Product ID],$D$98,TableBOM[Item ID],$A114)&gt;0)*($H$98&gt;0),$C$98&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$99,TableBOM[Item ID],$A114)&gt;0)*($H$99&gt;0),$C$99&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$100,TableBOM[Item ID],$A114)&gt;0)*($H$100&gt;0),$C$100&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$101,TableBOM[Item ID],$A114)&gt;0)*($H$101&gt;0),$C$101&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$102,TableBOM[Item ID],$A114)&gt;0)*($H$102&gt;0),$C$102&amp;", ","") &amp; IF((COUNTIFS(TableBOM[Product ID],$D$103,TableBOM[Item ID],$A114)&gt;0)*($H$103&gt;0),$C$103&amp;", ",""))-2),"")</f>
@@ -13747,7 +13749,7 @@
       </c>
       <c r="I114" s="47" t="str">
         <f t="shared" si="10"/>
-        <v>OK</v>
+        <v>SHORTAGE</v>
       </c>
     </row>
     <row r="115" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35000,13 +35002,13 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" style="66" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="66" customWidth="1"/>
     <col min="7" max="7" width="11.140625" style="66" customWidth="1"/>
     <col min="8" max="8" width="8.5703125" style="67" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="66" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" style="66" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="16.140625" style="66" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
@@ -35210,18 +35212,18 @@
         <v>0</v>
       </c>
       <c r="G7" s="37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="38">
         <f t="shared" si="0"/>
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="I7" s="37">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J7" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])=0,"-",ROUND((H7+I7)/(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>56553</v>
+        <v>43048</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35244,18 +35246,18 @@
         <v>0</v>
       </c>
       <c r="G8" s="37">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H8" s="38">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="I8" s="37">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J8" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])=0,"-",ROUND((H8+I8)/(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>34375</v>
+        <v>16875</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35426,16 +35428,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H15" s="38">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I15" s="37"/>
       <c r="J15" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A15,TableBOM[Per 1000 Units])=0,"-",ROUND((H15+I15)/(AVERAGEIF(TableBOM[Item ID],A15,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>419966</v>
+        <v>314975</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="71" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37202,16 +37204,16 @@
         <v>0</v>
       </c>
       <c r="G64" s="37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H64" s="38">
         <f t="shared" si="2"/>
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I64" s="37"/>
       <c r="J64" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A64,TableBOM[Per 1000 Units])=0,"-",ROUND((H64+I64)/(AVERAGEIF(TableBOM[Item ID],A64,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>2916667</v>
+        <v>2500000</v>
       </c>
       <c r="K64" s="75"/>
       <c r="L64" s="75"/>
@@ -38841,16 +38843,16 @@
         <v>0</v>
       </c>
       <c r="G113" s="37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H113" s="38">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I113" s="37"/>
       <c r="J113" s="37">
         <f>IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A113,TableBOM[Per 1000 Units])=0,"-",ROUND((H113+I113)/(AVERAGEIF(TableBOM[Item ID],A113,TableBOM[Per 1000 Units])/1000),0)),"-")</f>
-        <v>600000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
